--- a/reports/selenium/Excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/Excel/Automation_Test_Report.xlsx
@@ -35,61 +35,61 @@
     <t>FAILED</t>
   </si>
   <si>
-    <t>20.71</t>
+    <t>20.63</t>
   </si>
   <si>
     <t xml:space="preserve">Landing page did not load — Sign In button not found
-Wait timed out after 20177ms</t>
+Wait timed out after 20053ms</t>
   </si>
   <si>
     <t>should navigate to the login form</t>
   </si>
   <si>
-    <t>20.51</t>
+    <t>20.44</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20148ms</t>
+Wait timed out after 20038ms</t>
   </si>
   <si>
     <t>should login with valid credentials and reach the dashboard</t>
   </si>
   <si>
-    <t>20.50</t>
+    <t>20.48</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20135ms</t>
+Wait timed out after 20015ms</t>
   </si>
   <si>
     <t>should reject invalid credentials with an error message</t>
   </si>
   <si>
-    <t>20.59</t>
+    <t>20.41</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20183ms</t>
+Wait timed out after 20032ms</t>
   </si>
   <si>
     <t>should open the sign-up form from landing</t>
   </si>
   <si>
-    <t>20.92</t>
+    <t>20.37</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signup-btn"])
-Wait timed out after 20163ms</t>
+Wait timed out after 20016ms</t>
   </si>
   <si>
     <t>Security — should reject login for invalid credentials</t>
   </si>
   <si>
-    <t>20.76</t>
+    <t>21.06</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20203ms</t>
+Wait timed out after 20075ms</t>
   </si>
   <si>
     <t>Security — should prevent access to protected routes/dashboard for unauthenticated users</t>
@@ -98,7 +98,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>3.98</t>
+    <t>3.67</t>
   </si>
   <si>
     <t/>
@@ -107,1398 +107,1398 @@
     <t>Security — should not execute XSS script payloads submitted in login fields</t>
   </si>
   <si>
-    <t>20.93</t>
+    <t>20.39</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20168ms</t>
+Wait timed out after 20025ms</t>
   </si>
   <si>
     <t>Security — should enforce session termination and clean storage upon logout</t>
   </si>
   <si>
-    <t>21.15</t>
+    <t>20.77</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20151ms</t>
+Wait timed out after 20024ms</t>
   </si>
   <si>
     <t>Security — should confirm Firebase authentication rejects empty credentials</t>
   </si>
   <si>
-    <t>20.52</t>
+    <t>20.81</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20145ms</t>
+Wait timed out after 20043ms</t>
   </si>
   <si>
     <t>Security — should not expose sensitive API keys or secrets in page HTML source</t>
   </si>
   <si>
+    <t>0.38</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #11)</t>
+  </si>
+  <si>
+    <t>0.31</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #12)</t>
+  </si>
+  <si>
+    <t>0.92</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #13)</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #14)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #15)</t>
+  </si>
+  <si>
+    <t>0.84</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #16)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #17)</t>
+  </si>
+  <si>
+    <t>0.83</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #18)</t>
+  </si>
+  <si>
+    <t>0.29</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #19)</t>
+  </si>
+  <si>
+    <t>0.46</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #20)</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #21)</t>
+  </si>
+  <si>
+    <t>0.45</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #22)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #23)</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #24)</t>
+  </si>
+  <si>
+    <t>0.55</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #25)</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #26)</t>
+  </si>
+  <si>
+    <t>0.52</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #27)</t>
+  </si>
+  <si>
+    <t>0.73</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #28)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #29)</t>
+  </si>
+  <si>
+    <t>0.69</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #30)</t>
+  </si>
+  <si>
+    <t>0.49</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #31)</t>
+  </si>
+  <si>
+    <t>0.79</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #32)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #33)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #34)</t>
+  </si>
+  <si>
+    <t>0.66</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #35)</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #36)</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #37)</t>
+  </si>
+  <si>
+    <t>0.48</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #38)</t>
+  </si>
+  <si>
+    <t>0.80</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #39)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #40)</t>
+  </si>
+  <si>
+    <t>0.81</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #41)</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #42)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #43)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #44)</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #45)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #46)</t>
+  </si>
+  <si>
+    <t>0.60</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #47)</t>
+  </si>
+  <si>
+    <t>0.53</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #48)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #49)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #50)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #51)</t>
+  </si>
+  <si>
+    <t>0.37</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #52)</t>
+  </si>
+  <si>
+    <t>0.86</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #53)</t>
+  </si>
+  <si>
+    <t>0.44</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #54)</t>
+  </si>
+  <si>
+    <t>0.59</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #55)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #56)</t>
+  </si>
+  <si>
+    <t>0.97</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #57)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #58)</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #59)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #60)</t>
+  </si>
+  <si>
+    <t>0.65</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #61)</t>
+  </si>
+  <si>
+    <t>0.30</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #62)</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #63)</t>
+  </si>
+  <si>
+    <t>0.63</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #64)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #65)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #66)</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #67)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #68)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #69)</t>
+  </si>
+  <si>
+    <t>0.40</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #70)</t>
+  </si>
+  <si>
     <t>0.42</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #11)</t>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #71)</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #72)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #73)</t>
+  </si>
+  <si>
+    <t>0.72</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #74)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #75)</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #76)</t>
+  </si>
+  <si>
+    <t>0.90</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #77)</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #78)</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #79)</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #80)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #81)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #82)</t>
+  </si>
+  <si>
+    <t>0.88</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #83)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #84)</t>
+  </si>
+  <si>
+    <t>0.99</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #85)</t>
+  </si>
+  <si>
+    <t>0.67</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #86)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #87)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #88)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #89)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #90)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #91)</t>
+  </si>
+  <si>
+    <t>0.82</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #92)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #93)</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #94)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #95)</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #96)</t>
+  </si>
+  <si>
+    <t>0.91</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #97)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #98)</t>
   </si>
   <si>
     <t>0.25</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #12)</t>
-  </si>
-  <si>
-    <t>0.65</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #13)</t>
-  </si>
-  <si>
-    <t>1.00</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #14)</t>
-  </si>
-  <si>
-    <t>0.67</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #15)</t>
-  </si>
-  <si>
-    <t>0.69</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #16)</t>
-  </si>
-  <si>
-    <t>0.84</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #17)</t>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #99)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #100)</t>
+  </si>
+  <si>
+    <t>0.47</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #101)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #102)</t>
+  </si>
+  <si>
+    <t>0.61</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #103)</t>
+  </si>
+  <si>
+    <t>0.87</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #104)</t>
+  </si>
+  <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #105)</t>
+  </si>
+  <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #106)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #107)</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #108)</t>
   </si>
   <si>
     <t>0.96</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #18)</t>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #109)</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #110)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #111)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #112)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #113)</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #114)</t>
+  </si>
+  <si>
+    <t>0.68</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #115)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #116)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #117)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #118)</t>
+  </si>
+  <si>
+    <t>0.54</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #119)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #120)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #121)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #122)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #123)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #124)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #125)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #126)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #127)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #128)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #129)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #130)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #131)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #132)</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #133)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #134)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #135)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #136)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #137)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #138)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #139)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #140)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #141)</t>
+  </si>
+  <si>
+    <t>0.28</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #142)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #143)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #144)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #145)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #146)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #147)</t>
+  </si>
+  <si>
+    <t>0.70</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #148)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #149)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #150)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #151)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #152)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #153)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #154)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #155)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #156)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #157)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #158)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #159)</t>
+  </si>
+  <si>
+    <t>0.89</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #160)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #161)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #162)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #163)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #164)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #165)</t>
+  </si>
+  <si>
+    <t>0.74</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #166)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #167)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #168)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #169)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #170)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #171)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #172)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #173)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #174)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #175)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #176)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #177)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #178)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #179)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #180)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #181)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #182)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #183)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #184)</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #185)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #186)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #187)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #188)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #189)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #190)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #191)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #192)</t>
+  </si>
+  <si>
+    <t>0.32</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #193)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #194)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #195)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #196)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #197)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #198)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #199)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #200)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #201)</t>
+  </si>
+  <si>
+    <t>0.78</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #202)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #203)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #204)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #205)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #206)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #207)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #208)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #209)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #210)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #211)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #212)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #213)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #214)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #215)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #216)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #217)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #218)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #219)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #220)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #221)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #222)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #223)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #224)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #225)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #226)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #227)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #228)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #229)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #230)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #231)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #232)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #233)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #234)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #235)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #236)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #237)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #238)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #239)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #240)</t>
+  </si>
+  <si>
+    <t>0.93</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #241)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #242)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #243)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #244)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #245)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #246)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #247)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #248)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #249)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #250)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #251)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #252)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #253)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #254)</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #255)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #256)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #257)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #258)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #259)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #260)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #261)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #262)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #263)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #264)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #265)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #266)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #267)</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #268)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #269)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #270)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #271)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #272)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #273)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #274)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #275)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #276)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #277)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #278)</t>
   </si>
   <si>
     <t>0.77</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #19)</t>
-  </si>
-  <si>
-    <t>0.93</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #20)</t>
-  </si>
-  <si>
-    <t>0.92</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #21)</t>
-  </si>
-  <si>
-    <t>0.43</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #22)</t>
-  </si>
-  <si>
-    <t>0.35</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #23)</t>
-  </si>
-  <si>
-    <t>0.50</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #24)</t>
-  </si>
-  <si>
-    <t>0.37</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #25)</t>
-  </si>
-  <si>
-    <t>0.82</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #26)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #27)</t>
-  </si>
-  <si>
-    <t>0.53</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #28)</t>
-  </si>
-  <si>
-    <t>0.81</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #29)</t>
-  </si>
-  <si>
-    <t>0.34</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #30)</t>
-  </si>
-  <si>
-    <t>0.99</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #31)</t>
-  </si>
-  <si>
-    <t>0.21</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #32)</t>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #279)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #280)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #281)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #282)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #283)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #284)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #285)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #286)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #287)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #288)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #289)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #290)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #291)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #292)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #293)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #294)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #295)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #296)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #297)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #298)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #299)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #300)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #301)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #302)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #303)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #304)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #305)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #306)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #307)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #308)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #309)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #310)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #311)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #312)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #313)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #314)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #315)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #316)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #317)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #318)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #319)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #320)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #321)</t>
+  </si>
+  <si>
+    <t>0.71</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #322)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #323)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #324)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #325)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #326)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #327)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #328)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #329)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #330)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #331)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #332)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #333)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #334)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #335)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #336)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #337)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #338)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #339)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #340)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #341)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #342)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #343)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #344)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #345)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #346)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #347)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #348)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #349)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #350)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #351)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #352)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #353)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #354)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #355)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #356)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #357)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #358)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #359)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #360)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #361)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #362)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #363)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #364)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #365)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #366)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #367)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #368)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #369)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #370)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #371)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #372)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #373)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #374)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #375)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #376)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #377)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #378)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #379)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #380)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #381)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #382)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #383)</t>
   </si>
   <si>
     <t>0.76</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #33)</t>
-  </si>
-  <si>
-    <t>0.94</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #34)</t>
-  </si>
-  <si>
-    <t>0.78</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #35)</t>
-  </si>
-  <si>
-    <t>0.79</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #36)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #37)</t>
-  </si>
-  <si>
-    <t>0.23</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #38)</t>
-  </si>
-  <si>
-    <t>0.64</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #39)</t>
-  </si>
-  <si>
-    <t>0.46</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #40)</t>
-  </si>
-  <si>
-    <t>0.60</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #41)</t>
-  </si>
-  <si>
-    <t>0.68</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #42)</t>
-  </si>
-  <si>
-    <t>0.24</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #43)</t>
-  </si>
-  <si>
-    <t>0.30</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #44)</t>
-  </si>
-  <si>
-    <t>0.90</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #45)</t>
-  </si>
-  <si>
-    <t>0.28</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #46)</t>
-  </si>
-  <si>
-    <t>0.41</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #47)</t>
-  </si>
-  <si>
-    <t>0.52</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #48)</t>
-  </si>
-  <si>
-    <t>0.71</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #49)</t>
-  </si>
-  <si>
-    <t>0.62</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #50)</t>
-  </si>
-  <si>
-    <t>0.70</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #51)</t>
-  </si>
-  <si>
-    <t>0.51</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #52)</t>
-  </si>
-  <si>
-    <t>0.39</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #53)</t>
-  </si>
-  <si>
-    <t>0.95</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #54)</t>
-  </si>
-  <si>
-    <t>0.32</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #55)</t>
-  </si>
-  <si>
-    <t>0.57</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #56)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #57)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #58)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #59)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #60)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #61)</t>
-  </si>
-  <si>
-    <t>0.75</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #62)</t>
-  </si>
-  <si>
-    <t>0.74</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #63)</t>
-  </si>
-  <si>
-    <t>0.31</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #64)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #65)</t>
-  </si>
-  <si>
-    <t>0.72</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #66)</t>
-  </si>
-  <si>
-    <t>0.29</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #67)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #68)</t>
-  </si>
-  <si>
-    <t>0.47</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #69)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #70)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #71)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #72)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #73)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #74)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #75)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #76)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #77)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #78)</t>
-  </si>
-  <si>
-    <t>0.58</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #79)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #80)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #81)</t>
-  </si>
-  <si>
-    <t>0.45</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #82)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #83)</t>
-  </si>
-  <si>
-    <t>0.89</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #84)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #85)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #86)</t>
-  </si>
-  <si>
-    <t>0.97</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #87)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #88)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #89)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #90)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #91)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #92)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #93)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #94)</t>
-  </si>
-  <si>
-    <t>0.88</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #95)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #96)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #97)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #98)</t>
-  </si>
-  <si>
-    <t>0.49</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #99)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #100)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #101)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #102)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #103)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #104)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #105)</t>
-  </si>
-  <si>
-    <t>0.73</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #106)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #107)</t>
-  </si>
-  <si>
-    <t>0.54</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #108)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #109)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #110)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #111)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #112)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #113)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #114)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #115)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #116)</t>
-  </si>
-  <si>
-    <t>0.85</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #117)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #118)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #119)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #120)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #121)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #122)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #123)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #124)</t>
-  </si>
-  <si>
-    <t>0.63</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #125)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #126)</t>
-  </si>
-  <si>
-    <t>0.80</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #127)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #128)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #129)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #130)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #131)</t>
-  </si>
-  <si>
-    <t>0.44</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #132)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #133)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #134)</t>
-  </si>
-  <si>
-    <t>0.48</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #135)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #136)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #137)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #138)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #139)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #140)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #141)</t>
-  </si>
-  <si>
-    <t>0.66</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #142)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #143)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #144)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #145)</t>
-  </si>
-  <si>
-    <t>0.56</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #146)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #147)</t>
-  </si>
-  <si>
-    <t>0.59</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #148)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #149)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #150)</t>
-  </si>
-  <si>
-    <t>0.83</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #151)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #152)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #153)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #154)</t>
-  </si>
-  <si>
-    <t>0.86</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #155)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #156)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #157)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #158)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #159)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #160)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #161)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #162)</t>
-  </si>
-  <si>
-    <t>0.26</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #163)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #164)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #165)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #166)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #167)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #168)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #169)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #170)</t>
-  </si>
-  <si>
-    <t>0.91</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #171)</t>
-  </si>
-  <si>
-    <t>0.20</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #172)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #173)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #174)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #175)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #176)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #177)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #178)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #179)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #180)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #181)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #182)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #183)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #184)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #185)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #186)</t>
-  </si>
-  <si>
-    <t>0.38</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #187)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #188)</t>
-  </si>
-  <si>
-    <t>0.33</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #189)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #190)</t>
-  </si>
-  <si>
-    <t>0.36</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #191)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #192)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #193)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #194)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #195)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #196)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #197)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #198)</t>
-  </si>
-  <si>
-    <t>0.61</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #199)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #200)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #201)</t>
-  </si>
-  <si>
-    <t>0.40</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #202)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #203)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #204)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #205)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #206)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #207)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #208)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #209)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #210)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #211)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #212)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #213)</t>
-  </si>
-  <si>
-    <t>0.22</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #214)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #215)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #216)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #217)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #218)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #219)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #220)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #221)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #222)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #223)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #224)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #225)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #226)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #227)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #228)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #229)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #230)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #231)</t>
-  </si>
-  <si>
-    <t>0.27</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #232)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #233)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #234)</t>
-  </si>
-  <si>
-    <t>0.55</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #235)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #236)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #237)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #238)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #239)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #240)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #241)</t>
-  </si>
-  <si>
-    <t>0.87</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #242)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #243)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #244)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #245)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #246)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #247)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #248)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #249)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #250)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #251)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #252)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #253)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #254)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #255)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #256)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #257)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #258)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #259)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #260)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #261)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #262)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #263)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #264)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #265)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #266)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #267)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #268)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #269)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #270)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #271)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #272)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #273)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #274)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #275)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #276)</t>
-  </si>
-  <si>
-    <t>0.98</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #277)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #278)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #279)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #280)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #281)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #282)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #283)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #284)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #285)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #286)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #287)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #288)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #289)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #290)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #291)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #292)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #293)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #294)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #295)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #296)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #297)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #298)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #299)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #300)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #301)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #302)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #303)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #304)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #305)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #306)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #307)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #308)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #309)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #310)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #311)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #312)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #313)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #314)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #315)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #316)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #317)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #318)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #319)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #320)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #321)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #322)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #323)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #324)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #325)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #326)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #327)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #328)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #329)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #330)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #331)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #332)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #333)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #334)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #335)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #336)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #337)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #338)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #339)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #340)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #341)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #342)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #343)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #344)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #345)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #346)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #347)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #348)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #349)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #350)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #351)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #352)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #353)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #354)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #355)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #356)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #357)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #358)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #359)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #360)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #361)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #362)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #363)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #364)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #365)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #366)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #367)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #368)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #369)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #370)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #371)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #372)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #373)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #374)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #375)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #376)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #377)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #378)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #379)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #380)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #381)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #382)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #383)</t>
-  </si>
-  <si>
     <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #384)</t>
   </si>
   <si>
@@ -1556,13 +1556,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>10</t>
+    <t>11</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 11:27:16 UTC</t>
+    <t>2026-06-23 12:10:46 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1574,7 +1574,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>edcce0c</t>
+    <t>348580a</t>
   </si>
   <si>
     <t>Total</t>
@@ -2255,7 +2255,7 @@
         <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E16" t="s">
         <v>27</v>
@@ -2266,13 +2266,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" t="s">
         <v>47</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" t="s">
-        <v>48</v>
       </c>
       <c r="E17" t="s">
         <v>27</v>
@@ -2283,13 +2283,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E18" t="s">
         <v>27</v>
@@ -2300,13 +2300,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E19" t="s">
         <v>27</v>
@@ -2317,13 +2317,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E20" t="s">
         <v>27</v>
@@ -2334,13 +2334,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E21" t="s">
         <v>27</v>
@@ -2351,13 +2351,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
         <v>27</v>
@@ -2368,13 +2368,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="s">
         <v>27</v>
@@ -2385,13 +2385,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E24" t="s">
         <v>27</v>
@@ -2402,13 +2402,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E25" t="s">
         <v>27</v>
@@ -2419,13 +2419,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E26" t="s">
         <v>27</v>
@@ -2436,13 +2436,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E27" t="s">
         <v>27</v>
@@ -2453,13 +2453,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E28" t="s">
         <v>27</v>
@@ -2470,13 +2470,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E29" t="s">
         <v>27</v>
@@ -2487,13 +2487,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E30" t="s">
         <v>27</v>
@@ -2504,13 +2504,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E31" t="s">
         <v>27</v>
@@ -2521,13 +2521,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E32" t="s">
         <v>27</v>
@@ -2538,13 +2538,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D33" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E33" t="s">
         <v>27</v>
@@ -2555,13 +2555,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D34" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E34" t="s">
         <v>27</v>
@@ -2572,13 +2572,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E35" t="s">
         <v>27</v>
@@ -2589,13 +2589,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E36" t="s">
         <v>27</v>
@@ -2606,13 +2606,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E37" t="s">
         <v>27</v>
@@ -2623,13 +2623,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E38" t="s">
         <v>27</v>
@@ -2640,13 +2640,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E39" t="s">
         <v>27</v>
@@ -2657,13 +2657,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E40" t="s">
         <v>27</v>
@@ -2674,13 +2674,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D41" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="E41" t="s">
         <v>27</v>
@@ -2691,13 +2691,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D42" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E42" t="s">
         <v>27</v>
@@ -2708,13 +2708,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E43" t="s">
         <v>27</v>
@@ -2725,13 +2725,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="E44" t="s">
         <v>27</v>
@@ -2742,13 +2742,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="E45" t="s">
         <v>27</v>
@@ -2759,13 +2759,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E46" t="s">
         <v>27</v>
@@ -2776,13 +2776,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="E47" t="s">
         <v>27</v>
@@ -2793,13 +2793,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E48" t="s">
         <v>27</v>
@@ -2810,13 +2810,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E49" t="s">
         <v>27</v>
@@ -2827,13 +2827,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="E50" t="s">
         <v>27</v>
@@ -2844,13 +2844,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D51" t="s">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="E51" t="s">
         <v>27</v>
@@ -2861,13 +2861,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="E52" t="s">
         <v>27</v>
@@ -2878,13 +2878,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E53" t="s">
         <v>27</v>
@@ -2895,13 +2895,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="E54" t="s">
         <v>27</v>
@@ -2912,13 +2912,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D55" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E55" t="s">
         <v>27</v>
@@ -2929,13 +2929,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D56" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E56" t="s">
         <v>27</v>
@@ -2946,13 +2946,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D57" t="s">
-        <v>126</v>
+        <v>52</v>
       </c>
       <c r="E57" t="s">
         <v>27</v>
@@ -2963,13 +2963,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D58" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="E58" t="s">
         <v>27</v>
@@ -2980,13 +2980,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D59" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E59" t="s">
         <v>27</v>
@@ -2997,13 +2997,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D60" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="E60" t="s">
         <v>27</v>
@@ -3014,13 +3014,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E61" t="s">
         <v>27</v>
@@ -3031,13 +3031,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D62" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E62" t="s">
         <v>27</v>
@@ -3048,13 +3048,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D63" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E63" t="s">
         <v>27</v>
@@ -3065,13 +3065,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D64" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E64" t="s">
         <v>27</v>
@@ -3082,13 +3082,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E65" t="s">
         <v>27</v>
@@ -3099,13 +3099,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D66" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E66" t="s">
         <v>27</v>
@@ -3116,13 +3116,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D67" t="s">
-        <v>140</v>
+        <v>72</v>
       </c>
       <c r="E67" t="s">
         <v>27</v>
@@ -3133,13 +3133,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D68" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="E68" t="s">
         <v>27</v>
@@ -3150,13 +3150,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D69" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="E69" t="s">
         <v>27</v>
@@ -3167,13 +3167,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D70" t="s">
-        <v>145</v>
+        <v>61</v>
       </c>
       <c r="E70" t="s">
         <v>27</v>
@@ -3184,13 +3184,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D71" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E71" t="s">
         <v>27</v>
@@ -3201,13 +3201,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D72" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="E72" t="s">
         <v>27</v>
@@ -3218,13 +3218,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D73" t="s">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="E73" t="s">
         <v>27</v>
@@ -3235,13 +3235,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D74" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="E74" t="s">
         <v>27</v>
@@ -3252,13 +3252,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D75" t="s">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="E75" t="s">
         <v>27</v>
@@ -3269,13 +3269,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D76" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="E76" t="s">
         <v>27</v>
@@ -3286,13 +3286,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D77" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="E77" t="s">
         <v>27</v>
@@ -3303,13 +3303,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>52</v>
+        <v>148</v>
       </c>
       <c r="E78" t="s">
         <v>27</v>
@@ -3320,13 +3320,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D79" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="E79" t="s">
         <v>27</v>
@@ -3337,13 +3337,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D80" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E80" t="s">
         <v>27</v>
@@ -3354,13 +3354,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D81" t="s">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="E81" t="s">
         <v>27</v>
@@ -3371,13 +3371,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D82" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="E82" t="s">
         <v>27</v>
@@ -3388,13 +3388,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D83" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E83" t="s">
         <v>27</v>
@@ -3405,13 +3405,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D84" t="s">
-        <v>50</v>
+        <v>158</v>
       </c>
       <c r="E84" t="s">
         <v>27</v>
@@ -3422,13 +3422,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D85" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="E85" t="s">
         <v>27</v>
@@ -3439,13 +3439,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D86" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="E86" t="s">
         <v>27</v>
@@ -3456,13 +3456,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D87" t="s">
-        <v>100</v>
+        <v>163</v>
       </c>
       <c r="E87" t="s">
         <v>27</v>
@@ -3473,13 +3473,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D88" t="s">
-        <v>167</v>
+        <v>58</v>
       </c>
       <c r="E88" t="s">
         <v>27</v>
@@ -3490,13 +3490,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D89" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E89" t="s">
         <v>27</v>
@@ -3507,13 +3507,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D90" t="s">
-        <v>66</v>
+        <v>143</v>
       </c>
       <c r="E90" t="s">
         <v>27</v>
@@ -3524,13 +3524,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D91" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="E91" t="s">
         <v>27</v>
@@ -3541,13 +3541,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D92" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E92" t="s">
         <v>27</v>
@@ -3558,13 +3558,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D93" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="E93" t="s">
         <v>27</v>
@@ -3575,13 +3575,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D94" t="s">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="E94" t="s">
         <v>27</v>
@@ -3592,13 +3592,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D95" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="E95" t="s">
         <v>27</v>
@@ -3609,13 +3609,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D96" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="E96" t="s">
         <v>27</v>
@@ -3626,13 +3626,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D97" t="s">
-        <v>94</v>
+        <v>176</v>
       </c>
       <c r="E97" t="s">
         <v>27</v>
@@ -3643,13 +3643,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
+        <v>177</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D98" t="s">
         <v>178</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D98" t="s">
-        <v>71</v>
       </c>
       <c r="E98" t="s">
         <v>27</v>
@@ -3666,7 +3666,7 @@
         <v>25</v>
       </c>
       <c r="D99" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="E99" t="s">
         <v>27</v>
@@ -3700,7 +3700,7 @@
         <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="E101" t="s">
         <v>27</v>
@@ -3717,7 +3717,7 @@
         <v>25</v>
       </c>
       <c r="D102" t="s">
-        <v>40</v>
+        <v>184</v>
       </c>
       <c r="E102" t="s">
         <v>27</v>
@@ -3728,13 +3728,13 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D103" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E103" t="s">
         <v>27</v>
@@ -3745,13 +3745,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D104" t="s">
-        <v>44</v>
+        <v>187</v>
       </c>
       <c r="E104" t="s">
         <v>27</v>
@@ -3762,13 +3762,13 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D105" t="s">
-        <v>98</v>
+        <v>189</v>
       </c>
       <c r="E105" t="s">
         <v>27</v>
@@ -3779,13 +3779,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D106" t="s">
-        <v>66</v>
+        <v>191</v>
       </c>
       <c r="E106" t="s">
         <v>27</v>
@@ -3796,13 +3796,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D107" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E107" t="s">
         <v>27</v>
@@ -3813,13 +3813,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D108" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E108" t="s">
         <v>27</v>
@@ -3830,13 +3830,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D109" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E109" t="s">
         <v>27</v>
@@ -3847,13 +3847,13 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D110" t="s">
-        <v>54</v>
+        <v>198</v>
       </c>
       <c r="E110" t="s">
         <v>27</v>
@@ -3864,13 +3864,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D111" t="s">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="E111" t="s">
         <v>27</v>
@@ -3881,13 +3881,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D112" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E112" t="s">
         <v>27</v>
@@ -3898,13 +3898,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D113" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="E113" t="s">
         <v>27</v>
@@ -3915,13 +3915,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D114" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="E114" t="s">
         <v>27</v>
@@ -3932,13 +3932,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D115" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="E115" t="s">
         <v>27</v>
@@ -3949,13 +3949,13 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D116" t="s">
-        <v>40</v>
+        <v>207</v>
       </c>
       <c r="E116" t="s">
         <v>27</v>
@@ -3966,13 +3966,13 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D117" t="s">
-        <v>38</v>
+        <v>187</v>
       </c>
       <c r="E117" t="s">
         <v>27</v>
@@ -3983,13 +3983,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D118" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="E118" t="s">
         <v>27</v>
@@ -4000,13 +4000,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D119" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E119" t="s">
         <v>27</v>
@@ -4017,13 +4017,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D120" t="s">
-        <v>133</v>
+        <v>212</v>
       </c>
       <c r="E120" t="s">
         <v>27</v>
@@ -4034,13 +4034,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D121" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="E121" t="s">
         <v>27</v>
@@ -4051,13 +4051,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D122" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E122" t="s">
         <v>27</v>
@@ -4068,13 +4068,13 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D123" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="E123" t="s">
         <v>27</v>
@@ -4085,13 +4085,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D124" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E124" t="s">
         <v>27</v>
@@ -4102,13 +4102,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D125" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="E125" t="s">
         <v>27</v>
@@ -4119,13 +4119,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D126" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="E126" t="s">
         <v>27</v>
@@ -4136,13 +4136,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D127" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="E127" t="s">
         <v>27</v>
@@ -4153,13 +4153,13 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D128" t="s">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="E128" t="s">
         <v>27</v>
@@ -4170,13 +4170,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D129" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="E129" t="s">
         <v>27</v>
@@ -4187,13 +4187,13 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D130" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="E130" t="s">
         <v>27</v>
@@ -4204,13 +4204,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D131" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="E131" t="s">
         <v>27</v>
@@ -4221,13 +4221,13 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D132" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="E132" t="s">
         <v>27</v>
@@ -4238,13 +4238,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D133" t="s">
-        <v>220</v>
+        <v>82</v>
       </c>
       <c r="E133" t="s">
         <v>27</v>
@@ -4255,13 +4255,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D134" t="s">
-        <v>52</v>
+        <v>227</v>
       </c>
       <c r="E134" t="s">
         <v>27</v>
@@ -4272,13 +4272,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D135" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="E135" t="s">
         <v>27</v>
@@ -4289,13 +4289,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D136" t="s">
-        <v>224</v>
+        <v>72</v>
       </c>
       <c r="E136" t="s">
         <v>27</v>
@@ -4306,13 +4306,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D137" t="s">
-        <v>83</v>
+        <v>193</v>
       </c>
       <c r="E137" t="s">
         <v>27</v>
@@ -4323,13 +4323,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D138" t="s">
-        <v>135</v>
+        <v>181</v>
       </c>
       <c r="E138" t="s">
         <v>27</v>
@@ -4340,13 +4340,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D139" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="E139" t="s">
         <v>27</v>
@@ -4357,13 +4357,13 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D140" t="s">
-        <v>42</v>
+        <v>184</v>
       </c>
       <c r="E140" t="s">
         <v>27</v>
@@ -4374,13 +4374,13 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D141" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E141" t="s">
         <v>27</v>
@@ -4391,13 +4391,13 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D142" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E142" t="s">
         <v>27</v>
@@ -4408,13 +4408,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D143" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E143" t="s">
         <v>27</v>
@@ -4425,13 +4425,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D144" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E144" t="s">
         <v>27</v>
@@ -4442,13 +4442,13 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D145" t="s">
-        <v>142</v>
+        <v>52</v>
       </c>
       <c r="E145" t="s">
         <v>27</v>
@@ -4459,13 +4459,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D146" t="s">
-        <v>202</v>
+        <v>61</v>
       </c>
       <c r="E146" t="s">
         <v>27</v>
@@ -4476,13 +4476,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D147" t="s">
-        <v>237</v>
+        <v>200</v>
       </c>
       <c r="E147" t="s">
         <v>27</v>
@@ -4493,13 +4493,13 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D148" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="E148" t="s">
         <v>27</v>
@@ -4510,13 +4510,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D149" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E149" t="s">
         <v>27</v>
@@ -4527,13 +4527,13 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D150" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E150" t="s">
         <v>27</v>
@@ -4544,13 +4544,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D151" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="E151" t="s">
         <v>27</v>
@@ -4561,13 +4561,13 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D152" t="s">
-        <v>244</v>
+        <v>158</v>
       </c>
       <c r="E152" t="s">
         <v>27</v>
@@ -4578,13 +4578,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D153" t="s">
-        <v>94</v>
+        <v>163</v>
       </c>
       <c r="E153" t="s">
         <v>27</v>
@@ -4595,13 +4595,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D154" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="E154" t="s">
         <v>27</v>
@@ -4612,13 +4612,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D155" t="s">
-        <v>156</v>
+        <v>102</v>
       </c>
       <c r="E155" t="s">
         <v>27</v>
@@ -4629,13 +4629,13 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D156" t="s">
-        <v>249</v>
+        <v>173</v>
       </c>
       <c r="E156" t="s">
         <v>27</v>
@@ -4646,13 +4646,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D157" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="E157" t="s">
         <v>27</v>
@@ -4663,13 +4663,13 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D158" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="E158" t="s">
         <v>27</v>
@@ -4680,13 +4680,13 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D159" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="E159" t="s">
         <v>27</v>
@@ -4697,13 +4697,13 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D160" t="s">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="E160" t="s">
         <v>27</v>
@@ -4714,13 +4714,13 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D161" t="s">
-        <v>42</v>
+        <v>257</v>
       </c>
       <c r="E161" t="s">
         <v>27</v>
@@ -4731,13 +4731,13 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D162" t="s">
-        <v>249</v>
+        <v>184</v>
       </c>
       <c r="E162" t="s">
         <v>27</v>
@@ -4748,13 +4748,13 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D163" t="s">
-        <v>114</v>
+        <v>227</v>
       </c>
       <c r="E163" t="s">
         <v>27</v>
@@ -4765,13 +4765,13 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D164" t="s">
-        <v>258</v>
+        <v>74</v>
       </c>
       <c r="E164" t="s">
         <v>27</v>
@@ -4782,13 +4782,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D165" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="E165" t="s">
         <v>27</v>
@@ -4799,13 +4799,13 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D166" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="E166" t="s">
         <v>27</v>
@@ -4816,13 +4816,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D167" t="s">
-        <v>50</v>
+        <v>264</v>
       </c>
       <c r="E167" t="s">
         <v>27</v>
@@ -4833,13 +4833,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D168" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="E168" t="s">
         <v>27</v>
@@ -4850,13 +4850,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D169" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E169" t="s">
         <v>27</v>
@@ -4867,13 +4867,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D170" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="E170" t="s">
         <v>27</v>
@@ -4884,13 +4884,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D171" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="E171" t="s">
         <v>27</v>
@@ -4901,13 +4901,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D172" t="s">
-        <v>267</v>
+        <v>58</v>
       </c>
       <c r="E172" t="s">
         <v>27</v>
@@ -4918,13 +4918,13 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D173" t="s">
-        <v>269</v>
+        <v>181</v>
       </c>
       <c r="E173" t="s">
         <v>27</v>
@@ -4935,13 +4935,13 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D174" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="E174" t="s">
         <v>27</v>
@@ -4952,13 +4952,13 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D175" t="s">
-        <v>38</v>
+        <v>227</v>
       </c>
       <c r="E175" t="s">
         <v>27</v>
@@ -4969,13 +4969,13 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D176" t="s">
-        <v>48</v>
+        <v>264</v>
       </c>
       <c r="E176" t="s">
         <v>27</v>
@@ -4986,13 +4986,13 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D177" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E177" t="s">
         <v>27</v>
@@ -5003,13 +5003,13 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D178" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E178" t="s">
         <v>27</v>
@@ -5020,13 +5020,13 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D179" t="s">
-        <v>118</v>
+        <v>56</v>
       </c>
       <c r="E179" t="s">
         <v>27</v>
@@ -5037,13 +5037,13 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D180" t="s">
-        <v>85</v>
+        <v>158</v>
       </c>
       <c r="E180" t="s">
         <v>27</v>
@@ -5054,13 +5054,13 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D181" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="E181" t="s">
         <v>27</v>
@@ -5071,13 +5071,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D182" t="s">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="E182" t="s">
         <v>27</v>
@@ -5088,13 +5088,13 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D183" t="s">
-        <v>50</v>
+        <v>158</v>
       </c>
       <c r="E183" t="s">
         <v>27</v>
@@ -5105,13 +5105,13 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D184" t="s">
-        <v>56</v>
+        <v>140</v>
       </c>
       <c r="E184" t="s">
         <v>27</v>
@@ -5122,13 +5122,13 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D185" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="E185" t="s">
         <v>27</v>
@@ -5139,13 +5139,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D186" t="s">
-        <v>163</v>
+        <v>284</v>
       </c>
       <c r="E186" t="s">
         <v>27</v>
@@ -5156,13 +5156,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D187" t="s">
-        <v>124</v>
+        <v>178</v>
       </c>
       <c r="E187" t="s">
         <v>27</v>
@@ -5173,13 +5173,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D188" t="s">
-        <v>285</v>
+        <v>40</v>
       </c>
       <c r="E188" t="s">
         <v>27</v>
@@ -5190,13 +5190,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D189" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="E189" t="s">
         <v>27</v>
@@ -5207,13 +5207,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D190" t="s">
-        <v>288</v>
+        <v>178</v>
       </c>
       <c r="E190" t="s">
         <v>27</v>
@@ -5230,7 +5230,7 @@
         <v>25</v>
       </c>
       <c r="D191" t="s">
-        <v>214</v>
+        <v>113</v>
       </c>
       <c r="E191" t="s">
         <v>27</v>
@@ -5247,7 +5247,7 @@
         <v>25</v>
       </c>
       <c r="D192" t="s">
-        <v>291</v>
+        <v>196</v>
       </c>
       <c r="E192" t="s">
         <v>27</v>
@@ -5258,13 +5258,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D193" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="E193" t="s">
         <v>27</v>
@@ -5275,13 +5275,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
+        <v>292</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D194" t="s">
         <v>293</v>
-      </c>
-      <c r="C194" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D194" t="s">
-        <v>118</v>
       </c>
       <c r="E194" t="s">
         <v>27</v>
@@ -5298,7 +5298,7 @@
         <v>25</v>
       </c>
       <c r="D195" t="s">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="E195" t="s">
         <v>27</v>
@@ -5315,7 +5315,7 @@
         <v>25</v>
       </c>
       <c r="D196" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="E196" t="s">
         <v>27</v>
@@ -5332,7 +5332,7 @@
         <v>25</v>
       </c>
       <c r="D197" t="s">
-        <v>202</v>
+        <v>72</v>
       </c>
       <c r="E197" t="s">
         <v>27</v>
@@ -5349,7 +5349,7 @@
         <v>25</v>
       </c>
       <c r="D198" t="s">
-        <v>110</v>
+        <v>193</v>
       </c>
       <c r="E198" t="s">
         <v>27</v>
@@ -5366,7 +5366,7 @@
         <v>25</v>
       </c>
       <c r="D199" t="s">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="E199" t="s">
         <v>27</v>
@@ -5383,7 +5383,7 @@
         <v>25</v>
       </c>
       <c r="D200" t="s">
-        <v>300</v>
+        <v>102</v>
       </c>
       <c r="E200" t="s">
         <v>27</v>
@@ -5394,13 +5394,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D201" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="E201" t="s">
         <v>27</v>
@@ -5411,13 +5411,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D202" t="s">
-        <v>145</v>
+        <v>56</v>
       </c>
       <c r="E202" t="s">
         <v>27</v>
@@ -5428,13 +5428,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
+        <v>302</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D203" t="s">
         <v>303</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D203" t="s">
-        <v>304</v>
       </c>
       <c r="E203" t="s">
         <v>27</v>
@@ -5445,13 +5445,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D204" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="E204" t="s">
         <v>27</v>
@@ -5462,13 +5462,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D205" t="s">
-        <v>87</v>
+        <v>207</v>
       </c>
       <c r="E205" t="s">
         <v>27</v>
@@ -5479,13 +5479,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D206" t="s">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="E206" t="s">
         <v>27</v>
@@ -5496,13 +5496,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D207" t="s">
-        <v>60</v>
+        <v>237</v>
       </c>
       <c r="E207" t="s">
         <v>27</v>
@@ -5513,13 +5513,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D208" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="E208" t="s">
         <v>27</v>
@@ -5530,13 +5530,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D209" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E209" t="s">
         <v>27</v>
@@ -5547,13 +5547,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D210" t="s">
-        <v>249</v>
+        <v>303</v>
       </c>
       <c r="E210" t="s">
         <v>27</v>
@@ -5564,13 +5564,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D211" t="s">
-        <v>192</v>
+        <v>67</v>
       </c>
       <c r="E211" t="s">
         <v>27</v>
@@ -5581,13 +5581,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D212" t="s">
-        <v>189</v>
+        <v>69</v>
       </c>
       <c r="E212" t="s">
         <v>27</v>
@@ -5598,13 +5598,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D213" t="s">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="E213" t="s">
         <v>27</v>
@@ -5615,13 +5615,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D214" t="s">
-        <v>288</v>
+        <v>244</v>
       </c>
       <c r="E214" t="s">
         <v>27</v>
@@ -5632,13 +5632,13 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D215" t="s">
-        <v>317</v>
+        <v>138</v>
       </c>
       <c r="E215" t="s">
         <v>27</v>
@@ -5649,13 +5649,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D216" t="s">
-        <v>145</v>
+        <v>44</v>
       </c>
       <c r="E216" t="s">
         <v>27</v>
@@ -5666,13 +5666,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D217" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E217" t="s">
         <v>27</v>
@@ -5683,13 +5683,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D218" t="s">
-        <v>156</v>
+        <v>205</v>
       </c>
       <c r="E218" t="s">
         <v>27</v>
@@ -5700,13 +5700,13 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D219" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="E219" t="s">
         <v>27</v>
@@ -5717,13 +5717,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D220" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="E220" t="s">
         <v>27</v>
@@ -5734,13 +5734,13 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D221" t="s">
-        <v>104</v>
+        <v>244</v>
       </c>
       <c r="E221" t="s">
         <v>27</v>
@@ -5751,13 +5751,13 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D222" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="E222" t="s">
         <v>27</v>
@@ -5768,13 +5768,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D223" t="s">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="E223" t="s">
         <v>27</v>
@@ -5785,13 +5785,13 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D224" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="E224" t="s">
         <v>27</v>
@@ -5802,13 +5802,13 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D225" t="s">
-        <v>106</v>
+        <v>227</v>
       </c>
       <c r="E225" t="s">
         <v>27</v>
@@ -5819,13 +5819,13 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D226" t="s">
-        <v>317</v>
+        <v>122</v>
       </c>
       <c r="E226" t="s">
         <v>27</v>
@@ -5836,13 +5836,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D227" t="s">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="E227" t="s">
         <v>27</v>
@@ -5853,13 +5853,13 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D228" t="s">
-        <v>46</v>
+        <v>196</v>
       </c>
       <c r="E228" t="s">
         <v>27</v>
@@ -5870,13 +5870,13 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D229" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="E229" t="s">
         <v>27</v>
@@ -5887,13 +5887,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D230" t="s">
-        <v>304</v>
+        <v>56</v>
       </c>
       <c r="E230" t="s">
         <v>27</v>
@@ -5904,13 +5904,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D231" t="s">
-        <v>124</v>
+        <v>65</v>
       </c>
       <c r="E231" t="s">
         <v>27</v>
@@ -5921,13 +5921,13 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D232" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="E232" t="s">
         <v>27</v>
@@ -5938,13 +5938,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D233" t="s">
-        <v>336</v>
+        <v>100</v>
       </c>
       <c r="E233" t="s">
         <v>27</v>
@@ -5955,13 +5955,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D234" t="s">
-        <v>58</v>
+        <v>237</v>
       </c>
       <c r="E234" t="s">
         <v>27</v>
@@ -5972,13 +5972,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D235" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="E235" t="s">
         <v>27</v>
@@ -5989,13 +5989,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D236" t="s">
-        <v>340</v>
+        <v>61</v>
       </c>
       <c r="E236" t="s">
         <v>27</v>
@@ -6006,13 +6006,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D237" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="E237" t="s">
         <v>27</v>
@@ -6023,13 +6023,13 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D238" t="s">
-        <v>142</v>
+        <v>244</v>
       </c>
       <c r="E238" t="s">
         <v>27</v>
@@ -6040,13 +6040,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D239" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="E239" t="s">
         <v>27</v>
@@ -6057,13 +6057,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D240" t="s">
-        <v>240</v>
+        <v>61</v>
       </c>
       <c r="E240" t="s">
         <v>27</v>
@@ -6074,13 +6074,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D241" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="E241" t="s">
         <v>27</v>
@@ -6091,13 +6091,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D242" t="s">
-        <v>75</v>
+        <v>343</v>
       </c>
       <c r="E242" t="s">
         <v>27</v>
@@ -6108,13 +6108,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D243" t="s">
-        <v>348</v>
+        <v>193</v>
       </c>
       <c r="E243" t="s">
         <v>27</v>
@@ -6125,13 +6125,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D244" t="s">
-        <v>110</v>
+        <v>264</v>
       </c>
       <c r="E244" t="s">
         <v>27</v>
@@ -6142,13 +6142,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D245" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="E245" t="s">
         <v>27</v>
@@ -6159,13 +6159,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D246" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="E246" t="s">
         <v>27</v>
@@ -6176,13 +6176,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D247" t="s">
-        <v>46</v>
+        <v>237</v>
       </c>
       <c r="E247" t="s">
         <v>27</v>
@@ -6193,13 +6193,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D248" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="E248" t="s">
         <v>27</v>
@@ -6210,13 +6210,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D249" t="s">
-        <v>336</v>
+        <v>50</v>
       </c>
       <c r="E249" t="s">
         <v>27</v>
@@ -6227,13 +6227,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D250" t="s">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="E250" t="s">
         <v>27</v>
@@ -6244,13 +6244,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D251" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="E251" t="s">
         <v>27</v>
@@ -6261,13 +6261,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D252" t="s">
-        <v>336</v>
+        <v>154</v>
       </c>
       <c r="E252" t="s">
         <v>27</v>
@@ -6278,13 +6278,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D253" t="s">
-        <v>167</v>
+        <v>61</v>
       </c>
       <c r="E253" t="s">
         <v>27</v>
@@ -6295,13 +6295,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D254" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="E254" t="s">
         <v>27</v>
@@ -6312,13 +6312,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D255" t="s">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="E255" t="s">
         <v>27</v>
@@ -6329,13 +6329,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D256" t="s">
-        <v>267</v>
+        <v>358</v>
       </c>
       <c r="E256" t="s">
         <v>27</v>
@@ -6346,13 +6346,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D257" t="s">
-        <v>288</v>
+        <v>181</v>
       </c>
       <c r="E257" t="s">
         <v>27</v>
@@ -6363,13 +6363,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D258" t="s">
-        <v>112</v>
+        <v>237</v>
       </c>
       <c r="E258" t="s">
         <v>27</v>
@@ -6380,13 +6380,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D259" t="s">
-        <v>288</v>
+        <v>67</v>
       </c>
       <c r="E259" t="s">
         <v>27</v>
@@ -6397,13 +6397,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D260" t="s">
-        <v>176</v>
+        <v>207</v>
       </c>
       <c r="E260" t="s">
         <v>27</v>
@@ -6414,13 +6414,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D261" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="E261" t="s">
         <v>27</v>
@@ -6431,13 +6431,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D262" t="s">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="E262" t="s">
         <v>27</v>
@@ -6448,13 +6448,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D263" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="E263" t="s">
         <v>27</v>
@@ -6465,13 +6465,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D264" t="s">
-        <v>142</v>
+        <v>207</v>
       </c>
       <c r="E264" t="s">
         <v>27</v>
@@ -6482,13 +6482,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D265" t="s">
-        <v>106</v>
+        <v>193</v>
       </c>
       <c r="E265" t="s">
         <v>27</v>
@@ -6499,13 +6499,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D266" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="E266" t="s">
         <v>27</v>
@@ -6516,13 +6516,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D267" t="s">
-        <v>83</v>
+        <v>227</v>
       </c>
       <c r="E267" t="s">
         <v>27</v>
@@ -6533,13 +6533,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D268" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="E268" t="s">
         <v>27</v>
@@ -6550,13 +6550,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D269" t="s">
-        <v>232</v>
+        <v>372</v>
       </c>
       <c r="E269" t="s">
         <v>27</v>
@@ -6567,13 +6567,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D270" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="E270" t="s">
         <v>27</v>
@@ -6584,13 +6584,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D271" t="s">
-        <v>52</v>
+        <v>158</v>
       </c>
       <c r="E271" t="s">
         <v>27</v>
@@ -6601,13 +6601,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D272" t="s">
-        <v>118</v>
+        <v>372</v>
       </c>
       <c r="E272" t="s">
         <v>27</v>
@@ -6618,13 +6618,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D273" t="s">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="E273" t="s">
         <v>27</v>
@@ -6635,13 +6635,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D274" t="s">
-        <v>300</v>
+        <v>184</v>
       </c>
       <c r="E274" t="s">
         <v>27</v>
@@ -6652,13 +6652,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D275" t="s">
-        <v>124</v>
+        <v>67</v>
       </c>
       <c r="E275" t="s">
         <v>27</v>
@@ -6669,13 +6669,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D276" t="s">
-        <v>116</v>
+        <v>196</v>
       </c>
       <c r="E276" t="s">
         <v>27</v>
@@ -6686,13 +6686,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D277" t="s">
-        <v>202</v>
+        <v>122</v>
       </c>
       <c r="E277" t="s">
         <v>27</v>
@@ -6703,13 +6703,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D278" t="s">
-        <v>384</v>
+        <v>82</v>
       </c>
       <c r="E278" t="s">
         <v>27</v>
@@ -6720,13 +6720,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D279" t="s">
-        <v>181</v>
+        <v>113</v>
       </c>
       <c r="E279" t="s">
         <v>27</v>
@@ -6737,13 +6737,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D280" t="s">
-        <v>244</v>
+        <v>384</v>
       </c>
       <c r="E280" t="s">
         <v>27</v>
@@ -6754,13 +6754,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D281" t="s">
-        <v>224</v>
+        <v>111</v>
       </c>
       <c r="E281" t="s">
         <v>27</v>
@@ -6771,13 +6771,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D282" t="s">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="E282" t="s">
         <v>27</v>
@@ -6788,13 +6788,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D283" t="s">
-        <v>116</v>
+        <v>207</v>
       </c>
       <c r="E283" t="s">
         <v>27</v>
@@ -6805,13 +6805,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D284" t="s">
-        <v>267</v>
+        <v>150</v>
       </c>
       <c r="E284" t="s">
         <v>27</v>
@@ -6822,13 +6822,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D285" t="s">
-        <v>118</v>
+        <v>154</v>
       </c>
       <c r="E285" t="s">
         <v>27</v>
@@ -6839,13 +6839,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D286" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="E286" t="s">
         <v>27</v>
@@ -6856,13 +6856,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D287" t="s">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="E287" t="s">
         <v>27</v>
@@ -6873,13 +6873,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D288" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="E288" t="s">
         <v>27</v>
@@ -6890,13 +6890,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D289" t="s">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="E289" t="s">
         <v>27</v>
@@ -6907,13 +6907,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D290" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="E290" t="s">
         <v>27</v>
@@ -6924,13 +6924,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D291" t="s">
-        <v>100</v>
+        <v>384</v>
       </c>
       <c r="E291" t="s">
         <v>27</v>
@@ -6941,13 +6941,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D292" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E292" t="s">
         <v>27</v>
@@ -6958,13 +6958,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D293" t="s">
-        <v>85</v>
+        <v>181</v>
       </c>
       <c r="E293" t="s">
         <v>27</v>
@@ -6975,13 +6975,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D294" t="s">
-        <v>269</v>
+        <v>343</v>
       </c>
       <c r="E294" t="s">
         <v>27</v>
@@ -6992,13 +6992,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D295" t="s">
-        <v>202</v>
+        <v>42</v>
       </c>
       <c r="E295" t="s">
         <v>27</v>
@@ -7009,13 +7009,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D296" t="s">
-        <v>118</v>
+        <v>61</v>
       </c>
       <c r="E296" t="s">
         <v>27</v>
@@ -7026,13 +7026,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D297" t="s">
-        <v>181</v>
+        <v>47</v>
       </c>
       <c r="E297" t="s">
         <v>27</v>
@@ -7043,13 +7043,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D298" t="s">
-        <v>244</v>
+        <v>173</v>
       </c>
       <c r="E298" t="s">
         <v>27</v>
@@ -7060,13 +7060,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D299" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="E299" t="s">
         <v>27</v>
@@ -7077,13 +7077,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D300" t="s">
-        <v>87</v>
+        <v>264</v>
       </c>
       <c r="E300" t="s">
         <v>27</v>
@@ -7094,13 +7094,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D301" t="s">
-        <v>56</v>
+        <v>187</v>
       </c>
       <c r="E301" t="s">
         <v>27</v>
@@ -7111,13 +7111,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D302" t="s">
-        <v>118</v>
+        <v>154</v>
       </c>
       <c r="E302" t="s">
         <v>27</v>
@@ -7128,13 +7128,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D303" t="s">
-        <v>202</v>
+        <v>154</v>
       </c>
       <c r="E303" t="s">
         <v>27</v>
@@ -7145,13 +7145,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D304" t="s">
-        <v>202</v>
+        <v>113</v>
       </c>
       <c r="E304" t="s">
         <v>27</v>
@@ -7162,13 +7162,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D305" t="s">
-        <v>211</v>
+        <v>132</v>
       </c>
       <c r="E305" t="s">
         <v>27</v>
@@ -7179,13 +7179,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D306" t="s">
-        <v>54</v>
+        <v>191</v>
       </c>
       <c r="E306" t="s">
         <v>27</v>
@@ -7196,13 +7196,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D307" t="s">
-        <v>38</v>
+        <v>119</v>
       </c>
       <c r="E307" t="s">
         <v>27</v>
@@ -7213,13 +7213,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D308" t="s">
-        <v>142</v>
+        <v>200</v>
       </c>
       <c r="E308" t="s">
         <v>27</v>
@@ -7230,13 +7230,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D309" t="s">
-        <v>52</v>
+        <v>227</v>
       </c>
       <c r="E309" t="s">
         <v>27</v>
@@ -7247,13 +7247,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D310" t="s">
-        <v>237</v>
+        <v>143</v>
       </c>
       <c r="E310" t="s">
         <v>27</v>
@@ -7264,13 +7264,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D311" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="E311" t="s">
         <v>27</v>
@@ -7281,13 +7281,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D312" t="s">
-        <v>140</v>
+        <v>67</v>
       </c>
       <c r="E312" t="s">
         <v>27</v>
@@ -7298,13 +7298,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D313" t="s">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="E313" t="s">
         <v>27</v>
@@ -7315,13 +7315,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D314" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E314" t="s">
         <v>27</v>
@@ -7332,13 +7332,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D315" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="E315" t="s">
         <v>27</v>
@@ -7349,13 +7349,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D316" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="E316" t="s">
         <v>27</v>
@@ -7366,13 +7366,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D317" t="s">
-        <v>232</v>
+        <v>163</v>
       </c>
       <c r="E317" t="s">
         <v>27</v>
@@ -7383,13 +7383,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D318" t="s">
-        <v>181</v>
+        <v>52</v>
       </c>
       <c r="E318" t="s">
         <v>27</v>
@@ -7400,13 +7400,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D319" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E319" t="s">
         <v>27</v>
@@ -7417,13 +7417,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D320" t="s">
-        <v>317</v>
+        <v>148</v>
       </c>
       <c r="E320" t="s">
         <v>27</v>
@@ -7434,13 +7434,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D321" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="E321" t="s">
         <v>27</v>
@@ -7451,13 +7451,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D322" t="s">
-        <v>44</v>
+        <v>205</v>
       </c>
       <c r="E322" t="s">
         <v>27</v>
@@ -7468,13 +7468,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D323" t="s">
-        <v>44</v>
+        <v>428</v>
       </c>
       <c r="E323" t="s">
         <v>27</v>
@@ -7485,13 +7485,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D324" t="s">
-        <v>118</v>
+        <v>212</v>
       </c>
       <c r="E324" t="s">
         <v>27</v>
@@ -7502,13 +7502,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D325" t="s">
-        <v>145</v>
+        <v>372</v>
       </c>
       <c r="E325" t="s">
         <v>27</v>
@@ -7519,13 +7519,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D326" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E326" t="s">
         <v>27</v>
@@ -7536,13 +7536,13 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D327" t="s">
-        <v>224</v>
+        <v>152</v>
       </c>
       <c r="E327" t="s">
         <v>27</v>
@@ -7553,13 +7553,13 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D328" t="s">
-        <v>40</v>
+        <v>176</v>
       </c>
       <c r="E328" t="s">
         <v>27</v>
@@ -7570,13 +7570,13 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D329" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E329" t="s">
         <v>27</v>
@@ -7587,13 +7587,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D330" t="s">
-        <v>192</v>
+        <v>91</v>
       </c>
       <c r="E330" t="s">
         <v>27</v>
@@ -7604,13 +7604,13 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D331" t="s">
-        <v>224</v>
+        <v>119</v>
       </c>
       <c r="E331" t="s">
         <v>27</v>
@@ -7621,13 +7621,13 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D332" t="s">
-        <v>106</v>
+        <v>343</v>
       </c>
       <c r="E332" t="s">
         <v>27</v>
@@ -7638,13 +7638,13 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D333" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="E333" t="s">
         <v>27</v>
@@ -7655,13 +7655,13 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D334" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="E334" t="s">
         <v>27</v>
@@ -7672,13 +7672,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D335" t="s">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="E335" t="s">
         <v>27</v>
@@ -7689,13 +7689,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D336" t="s">
-        <v>189</v>
+        <v>38</v>
       </c>
       <c r="E336" t="s">
         <v>27</v>
@@ -7706,13 +7706,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D337" t="s">
-        <v>66</v>
+        <v>184</v>
       </c>
       <c r="E337" t="s">
         <v>27</v>
@@ -7723,13 +7723,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D338" t="s">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="E338" t="s">
         <v>27</v>
@@ -7740,13 +7740,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D339" t="s">
-        <v>100</v>
+        <v>244</v>
       </c>
       <c r="E339" t="s">
         <v>27</v>
@@ -7757,13 +7757,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D340" t="s">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="E340" t="s">
         <v>27</v>
@@ -7774,13 +7774,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D341" t="s">
-        <v>340</v>
+        <v>170</v>
       </c>
       <c r="E341" t="s">
         <v>27</v>
@@ -7791,13 +7791,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D342" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="E342" t="s">
         <v>27</v>
@@ -7808,7 +7808,7 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>25</v>
@@ -7825,13 +7825,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D344" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="E344" t="s">
         <v>27</v>
@@ -7842,13 +7842,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D345" t="s">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="E345" t="s">
         <v>27</v>
@@ -7859,13 +7859,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D346" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="E346" t="s">
         <v>27</v>
@@ -7876,13 +7876,13 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D347" t="s">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="E347" t="s">
         <v>27</v>
@@ -7893,13 +7893,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D348" t="s">
-        <v>232</v>
+        <v>69</v>
       </c>
       <c r="E348" t="s">
         <v>27</v>
@@ -7910,13 +7910,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D349" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E349" t="s">
         <v>27</v>
@@ -7927,13 +7927,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D350" t="s">
-        <v>340</v>
+        <v>293</v>
       </c>
       <c r="E350" t="s">
         <v>27</v>
@@ -7944,13 +7944,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D351" t="s">
-        <v>232</v>
+        <v>187</v>
       </c>
       <c r="E351" t="s">
         <v>27</v>
@@ -7961,13 +7961,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D352" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="E352" t="s">
         <v>27</v>
@@ -7978,13 +7978,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D353" t="s">
-        <v>267</v>
+        <v>372</v>
       </c>
       <c r="E353" t="s">
         <v>27</v>
@@ -7995,13 +7995,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D354" t="s">
-        <v>220</v>
+        <v>126</v>
       </c>
       <c r="E354" t="s">
         <v>27</v>
@@ -8012,13 +8012,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D355" t="s">
-        <v>317</v>
+        <v>107</v>
       </c>
       <c r="E355" t="s">
         <v>27</v>
@@ -8029,13 +8029,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D356" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="E356" t="s">
         <v>27</v>
@@ -8046,13 +8046,13 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D357" t="s">
-        <v>110</v>
+        <v>264</v>
       </c>
       <c r="E357" t="s">
         <v>27</v>
@@ -8063,13 +8063,13 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D358" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="E358" t="s">
         <v>27</v>
@@ -8080,13 +8080,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D359" t="s">
-        <v>317</v>
+        <v>42</v>
       </c>
       <c r="E359" t="s">
         <v>27</v>
@@ -8097,13 +8097,13 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D360" t="s">
-        <v>258</v>
+        <v>158</v>
       </c>
       <c r="E360" t="s">
         <v>27</v>
@@ -8114,13 +8114,13 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D361" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="E361" t="s">
         <v>27</v>
@@ -8131,13 +8131,13 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D362" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="E362" t="s">
         <v>27</v>
@@ -8148,13 +8148,13 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D363" t="s">
-        <v>202</v>
+        <v>148</v>
       </c>
       <c r="E363" t="s">
         <v>27</v>
@@ -8165,13 +8165,13 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D364" t="s">
-        <v>126</v>
+        <v>181</v>
       </c>
       <c r="E364" t="s">
         <v>27</v>
@@ -8182,13 +8182,13 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D365" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="E365" t="s">
         <v>27</v>
@@ -8199,13 +8199,13 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D366" t="s">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="E366" t="s">
         <v>27</v>
@@ -8216,13 +8216,13 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D367" t="s">
-        <v>300</v>
+        <v>187</v>
       </c>
       <c r="E367" t="s">
         <v>27</v>
@@ -8233,13 +8233,13 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D368" t="s">
-        <v>79</v>
+        <v>343</v>
       </c>
       <c r="E368" t="s">
         <v>27</v>
@@ -8250,13 +8250,13 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D369" t="s">
-        <v>102</v>
+        <v>189</v>
       </c>
       <c r="E369" t="s">
         <v>27</v>
@@ -8267,13 +8267,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D370" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="E370" t="s">
         <v>27</v>
@@ -8284,13 +8284,13 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D371" t="s">
-        <v>133</v>
+        <v>181</v>
       </c>
       <c r="E371" t="s">
         <v>27</v>
@@ -8301,7 +8301,7 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>25</v>
@@ -8318,13 +8318,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D373" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
       <c r="E373" t="s">
         <v>27</v>
@@ -8335,13 +8335,13 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D374" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="E374" t="s">
         <v>27</v>
@@ -8352,13 +8352,13 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D375" t="s">
-        <v>118</v>
+        <v>207</v>
       </c>
       <c r="E375" t="s">
         <v>27</v>
@@ -8369,13 +8369,13 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D376" t="s">
-        <v>116</v>
+        <v>237</v>
       </c>
       <c r="E376" t="s">
         <v>27</v>
@@ -8386,13 +8386,13 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D377" t="s">
-        <v>249</v>
+        <v>88</v>
       </c>
       <c r="E377" t="s">
         <v>27</v>
@@ -8403,13 +8403,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D378" t="s">
-        <v>90</v>
+        <v>212</v>
       </c>
       <c r="E378" t="s">
         <v>27</v>
@@ -8420,13 +8420,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C379" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D379" t="s">
-        <v>237</v>
+        <v>74</v>
       </c>
       <c r="E379" t="s">
         <v>27</v>
@@ -8437,13 +8437,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D380" t="s">
-        <v>96</v>
+        <v>143</v>
       </c>
       <c r="E380" t="s">
         <v>27</v>
@@ -8454,13 +8454,13 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C381" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D381" t="s">
-        <v>291</v>
+        <v>150</v>
       </c>
       <c r="E381" t="s">
         <v>27</v>
@@ -8471,13 +8471,13 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D382" t="s">
-        <v>90</v>
+        <v>198</v>
       </c>
       <c r="E382" t="s">
         <v>27</v>
@@ -8488,13 +8488,13 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D383" t="s">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="E383" t="s">
         <v>27</v>
@@ -8505,13 +8505,13 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D384" t="s">
-        <v>46</v>
+        <v>428</v>
       </c>
       <c r="E384" t="s">
         <v>27</v>
@@ -8522,13 +8522,13 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
+        <v>490</v>
+      </c>
+      <c r="C385" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D385" t="s">
         <v>491</v>
-      </c>
-      <c r="C385" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D385" t="s">
-        <v>189</v>
       </c>
       <c r="E385" t="s">
         <v>27</v>
@@ -8545,7 +8545,7 @@
         <v>25</v>
       </c>
       <c r="D386" t="s">
-        <v>224</v>
+        <v>126</v>
       </c>
       <c r="E386" t="s">
         <v>27</v>
@@ -8562,7 +8562,7 @@
         <v>25</v>
       </c>
       <c r="D387" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E387" t="s">
         <v>27</v>
@@ -8579,7 +8579,7 @@
         <v>25</v>
       </c>
       <c r="D388" t="s">
-        <v>133</v>
+        <v>176</v>
       </c>
       <c r="E388" t="s">
         <v>27</v>
@@ -8596,7 +8596,7 @@
         <v>25</v>
       </c>
       <c r="D389" t="s">
-        <v>269</v>
+        <v>52</v>
       </c>
       <c r="E389" t="s">
         <v>27</v>
@@ -8613,7 +8613,7 @@
         <v>25</v>
       </c>
       <c r="D390" t="s">
-        <v>40</v>
+        <v>212</v>
       </c>
       <c r="E390" t="s">
         <v>27</v>
@@ -8630,7 +8630,7 @@
         <v>25</v>
       </c>
       <c r="D391" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E391" t="s">
         <v>27</v>
@@ -8647,7 +8647,7 @@
         <v>25</v>
       </c>
       <c r="D392" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="E392" t="s">
         <v>27</v>
@@ -8664,7 +8664,7 @@
         <v>25</v>
       </c>
       <c r="D393" t="s">
-        <v>340</v>
+        <v>116</v>
       </c>
       <c r="E393" t="s">
         <v>27</v>
@@ -8681,7 +8681,7 @@
         <v>25</v>
       </c>
       <c r="D394" t="s">
-        <v>124</v>
+        <v>56</v>
       </c>
       <c r="E394" t="s">
         <v>27</v>
@@ -8698,7 +8698,7 @@
         <v>25</v>
       </c>
       <c r="D395" t="s">
-        <v>48</v>
+        <v>163</v>
       </c>
       <c r="E395" t="s">
         <v>27</v>
@@ -8715,7 +8715,7 @@
         <v>25</v>
       </c>
       <c r="D396" t="s">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="E396" t="s">
         <v>27</v>
@@ -8732,7 +8732,7 @@
         <v>25</v>
       </c>
       <c r="D397" t="s">
-        <v>133</v>
+        <v>227</v>
       </c>
       <c r="E397" t="s">
         <v>27</v>
@@ -8749,7 +8749,7 @@
         <v>25</v>
       </c>
       <c r="D398" t="s">
-        <v>133</v>
+        <v>196</v>
       </c>
       <c r="E398" t="s">
         <v>27</v>
@@ -8766,7 +8766,7 @@
         <v>25</v>
       </c>
       <c r="D399" t="s">
-        <v>285</v>
+        <v>82</v>
       </c>
       <c r="E399" t="s">
         <v>27</v>
@@ -8783,7 +8783,7 @@
         <v>25</v>
       </c>
       <c r="D400" t="s">
-        <v>142</v>
+        <v>491</v>
       </c>
       <c r="E400" t="s">
         <v>27</v>
@@ -8800,7 +8800,7 @@
         <v>25</v>
       </c>
       <c r="D401" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="E401" t="s">
         <v>27</v>

--- a/reports/selenium/Excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/Excel/Automation_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="522">
   <si>
     <t>#</t>
   </si>
@@ -35,61 +35,61 @@
     <t>FAILED</t>
   </si>
   <si>
-    <t>20.63</t>
+    <t>20.74</t>
   </si>
   <si>
     <t xml:space="preserve">Landing page did not load — Sign In button not found
-Wait timed out after 20053ms</t>
+Wait timed out after 20193ms</t>
   </si>
   <si>
     <t>should navigate to the login form</t>
   </si>
   <si>
-    <t>20.44</t>
+    <t>20.54</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20038ms</t>
+Wait timed out after 20180ms</t>
   </si>
   <si>
     <t>should login with valid credentials and reach the dashboard</t>
   </si>
   <si>
-    <t>20.48</t>
+    <t>20.53</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20015ms</t>
+Wait timed out after 20157ms</t>
   </si>
   <si>
     <t>should reject invalid credentials with an error message</t>
   </si>
   <si>
-    <t>20.41</t>
+    <t>20.66</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20032ms</t>
+Wait timed out after 20194ms</t>
   </si>
   <si>
     <t>should open the sign-up form from landing</t>
   </si>
   <si>
-    <t>20.37</t>
+    <t>20.70</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signup-btn"])
-Wait timed out after 20016ms</t>
+Wait timed out after 20005ms</t>
   </si>
   <si>
     <t>Security — should reject login for invalid credentials</t>
   </si>
   <si>
-    <t>21.06</t>
+    <t>20.56</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20075ms</t>
+Wait timed out after 20000ms</t>
   </si>
   <si>
     <t>Security — should prevent access to protected routes/dashboard for unauthenticated users</t>
@@ -98,7 +98,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>3.67</t>
+    <t>3.78</t>
   </si>
   <si>
     <t/>
@@ -107,1134 +107,1134 @@
     <t>Security — should not execute XSS script payloads submitted in login fields</t>
   </si>
   <si>
-    <t>20.39</t>
-  </si>
-  <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20025ms</t>
+Wait timed out after 20186ms</t>
   </si>
   <si>
     <t>Security — should enforce session termination and clean storage upon logout</t>
   </si>
   <si>
-    <t>20.77</t>
+    <t>20.90</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20024ms</t>
+Wait timed out after 20201ms</t>
   </si>
   <si>
     <t>Security — should confirm Firebase authentication rejects empty credentials</t>
   </si>
   <si>
-    <t>20.81</t>
-  </si>
-  <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20043ms</t>
+Wait timed out after 20171ms</t>
   </si>
   <si>
     <t>Security — should not expose sensitive API keys or secrets in page HTML source</t>
   </si>
   <si>
+    <t>0.84</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #11)</t>
+  </si>
+  <si>
+    <t>0.72</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #12)</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #13)</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #14)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #15)</t>
+  </si>
+  <si>
+    <t>0.46</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #16)</t>
+  </si>
+  <si>
+    <t>0.32</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #17)</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #18)</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #19)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #20)</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #21)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #22)</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #23)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #24)</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #25)</t>
+  </si>
+  <si>
+    <t>0.71</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #26)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #27)</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #28)</t>
+  </si>
+  <si>
+    <t>0.68</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #29)</t>
+  </si>
+  <si>
+    <t>0.52</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #30)</t>
+  </si>
+  <si>
+    <t>0.70</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #31)</t>
+  </si>
+  <si>
+    <t>0.30</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #32)</t>
+  </si>
+  <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #33)</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #34)</t>
+  </si>
+  <si>
+    <t>0.63</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #35)</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #36)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #37)</t>
+  </si>
+  <si>
+    <t>0.90</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #38)</t>
+  </si>
+  <si>
+    <t>0.44</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #39)</t>
+  </si>
+  <si>
+    <t>0.77</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #40)</t>
+  </si>
+  <si>
+    <t>0.88</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #41)</t>
+  </si>
+  <si>
+    <t>0.80</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #42)</t>
+  </si>
+  <si>
+    <t>0.67</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #43)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #44)</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #45)</t>
+  </si>
+  <si>
+    <t>0.86</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #46)</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #47)</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #48)</t>
+  </si>
+  <si>
+    <t>0.79</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #49)</t>
+  </si>
+  <si>
+    <t>0.47</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #50)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #51)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #52)</t>
+  </si>
+  <si>
+    <t>0.61</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #53)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #54)</t>
+  </si>
+  <si>
+    <t>0.65</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #55)</t>
+  </si>
+  <si>
     <t>0.38</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #11)</t>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #56)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #57)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #58)</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #59)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #60)</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #61)</t>
+  </si>
+  <si>
+    <t>0.89</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #62)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #63)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #64)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #65)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #66)</t>
+  </si>
+  <si>
+    <t>0.29</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #67)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #68)</t>
+  </si>
+  <si>
+    <t>0.97</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #69)</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #70)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #71)</t>
+  </si>
+  <si>
+    <t>0.93</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #72)</t>
   </si>
   <si>
     <t>0.31</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #12)</t>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #73)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #74)</t>
+  </si>
+  <si>
+    <t>0.81</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #75)</t>
+  </si>
+  <si>
+    <t>0.83</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #76)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #77)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #78)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #79)</t>
+  </si>
+  <si>
+    <t>0.76</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #80)</t>
+  </si>
+  <si>
+    <t>0.73</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #81)</t>
+  </si>
+  <si>
+    <t>0.96</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #82)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #83)</t>
+  </si>
+  <si>
+    <t>0.48</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #84)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #85)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #86)</t>
+  </si>
+  <si>
+    <t>0.37</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #87)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #88)</t>
+  </si>
+  <si>
+    <t>0.91</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #89)</t>
   </si>
   <si>
     <t>0.92</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #13)</t>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #90)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #91)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #92)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #93)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #94)</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #95)</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #96)</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #97)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #98)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #99)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #100)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #101)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #102)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #103)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #104)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #105)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #106)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #107)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #108)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #109)</t>
+  </si>
+  <si>
+    <t>0.28</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #110)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #111)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #112)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #113)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #114)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #115)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #116)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #117)</t>
+  </si>
+  <si>
+    <t>0.59</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #118)</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #119)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #120)</t>
+  </si>
+  <si>
+    <t>0.53</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #121)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #122)</t>
+  </si>
+  <si>
+    <t>0.99</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #123)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #124)</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #125)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #126)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #127)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #128)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #129)</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #130)</t>
+  </si>
+  <si>
+    <t>0.82</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #131)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #132)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #133)</t>
+  </si>
+  <si>
+    <t>0.69</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #134)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #135)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #136)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #137)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #138)</t>
+  </si>
+  <si>
+    <t>0.66</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #139)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #140)</t>
+  </si>
+  <si>
+    <t>0.87</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #141)</t>
+  </si>
+  <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #142)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #143)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #144)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #145)</t>
+  </si>
+  <si>
+    <t>0.74</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #146)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #147)</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #148)</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #149)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #150)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #151)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #152)</t>
+  </si>
+  <si>
+    <t>0.60</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #153)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #154)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #155)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #156)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #157)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #158)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #159)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #160)</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #161)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #162)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #163)</t>
+  </si>
+  <si>
+    <t>0.55</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #164)</t>
+  </si>
+  <si>
+    <t>0.54</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #165)</t>
+  </si>
+  <si>
+    <t>0.49</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #166)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #167)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #168)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #169)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #170)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #171)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #172)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #173)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #174)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #175)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #176)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #177)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #178)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #179)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #180)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #181)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #182)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #183)</t>
   </si>
   <si>
     <t>0.21</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #14)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #15)</t>
-  </si>
-  <si>
-    <t>0.84</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #16)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #17)</t>
-  </si>
-  <si>
-    <t>0.83</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #18)</t>
-  </si>
-  <si>
-    <t>0.29</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #19)</t>
-  </si>
-  <si>
-    <t>0.46</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #20)</t>
-  </si>
-  <si>
-    <t>0.24</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #21)</t>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #184)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #185)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #186)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #187)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #188)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #189)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #190)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #191)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #192)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #193)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #194)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #195)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #196)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #197)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #198)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #199)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #200)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #201)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #202)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #203)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #204)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #205)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #206)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #207)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #208)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #209)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #210)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #211)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #212)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #213)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #214)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #215)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #216)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #217)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #218)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #219)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #220)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #221)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #222)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #223)</t>
   </si>
   <si>
     <t>0.45</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #22)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #23)</t>
-  </si>
-  <si>
-    <t>0.26</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #24)</t>
-  </si>
-  <si>
-    <t>0.55</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #25)</t>
-  </si>
-  <si>
-    <t>0.64</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #26)</t>
-  </si>
-  <si>
-    <t>0.52</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #27)</t>
-  </si>
-  <si>
-    <t>0.73</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #28)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #29)</t>
-  </si>
-  <si>
-    <t>0.69</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #30)</t>
-  </si>
-  <si>
-    <t>0.49</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #31)</t>
-  </si>
-  <si>
-    <t>0.79</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #32)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #33)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #34)</t>
-  </si>
-  <si>
-    <t>0.66</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #35)</t>
-  </si>
-  <si>
-    <t>0.23</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #36)</t>
-  </si>
-  <si>
-    <t>0.56</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #37)</t>
-  </si>
-  <si>
-    <t>0.48</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #38)</t>
-  </si>
-  <si>
-    <t>0.80</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #39)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #40)</t>
-  </si>
-  <si>
-    <t>0.81</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #41)</t>
-  </si>
-  <si>
-    <t>0.35</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #42)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #43)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #44)</t>
-  </si>
-  <si>
-    <t>0.22</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #45)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #46)</t>
-  </si>
-  <si>
-    <t>0.60</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #47)</t>
-  </si>
-  <si>
-    <t>0.53</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #48)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #49)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #50)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #51)</t>
-  </si>
-  <si>
-    <t>0.37</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #52)</t>
-  </si>
-  <si>
-    <t>0.86</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #53)</t>
-  </si>
-  <si>
-    <t>0.44</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #54)</t>
-  </si>
-  <si>
-    <t>0.59</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #55)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #56)</t>
-  </si>
-  <si>
-    <t>0.97</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #57)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #58)</t>
-  </si>
-  <si>
-    <t>0.98</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #59)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #60)</t>
-  </si>
-  <si>
-    <t>0.65</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #61)</t>
-  </si>
-  <si>
-    <t>0.30</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #62)</t>
-  </si>
-  <si>
-    <t>0.33</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #63)</t>
-  </si>
-  <si>
-    <t>0.63</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #64)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #65)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #66)</t>
-  </si>
-  <si>
-    <t>0.62</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #67)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #68)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #69)</t>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #224)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #225)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #226)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #227)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #228)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #229)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #230)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #231)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #232)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #233)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #234)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #235)</t>
+  </si>
+  <si>
+    <t>0.78</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #236)</t>
   </si>
   <si>
     <t>0.40</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #70)</t>
-  </si>
-  <si>
-    <t>0.42</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #71)</t>
-  </si>
-  <si>
-    <t>0.51</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #72)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #73)</t>
-  </si>
-  <si>
-    <t>0.72</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #74)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #75)</t>
-  </si>
-  <si>
-    <t>0.58</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #76)</t>
-  </si>
-  <si>
-    <t>0.90</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #77)</t>
-  </si>
-  <si>
-    <t>0.34</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #78)</t>
-  </si>
-  <si>
-    <t>0.20</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #79)</t>
-  </si>
-  <si>
-    <t>0.41</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #80)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #81)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #82)</t>
-  </si>
-  <si>
-    <t>0.88</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #83)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #84)</t>
-  </si>
-  <si>
-    <t>0.99</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #85)</t>
-  </si>
-  <si>
-    <t>0.67</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #86)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #87)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #88)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #89)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #90)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #91)</t>
-  </si>
-  <si>
-    <t>0.82</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #92)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #93)</t>
-  </si>
-  <si>
-    <t>0.85</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #94)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #95)</t>
-  </si>
-  <si>
-    <t>1.00</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #96)</t>
-  </si>
-  <si>
-    <t>0.91</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #97)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #98)</t>
-  </si>
-  <si>
-    <t>0.25</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #99)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #100)</t>
-  </si>
-  <si>
-    <t>0.47</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #101)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #102)</t>
-  </si>
-  <si>
-    <t>0.61</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #103)</t>
-  </si>
-  <si>
-    <t>0.87</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #104)</t>
-  </si>
-  <si>
-    <t>0.36</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #105)</t>
-  </si>
-  <si>
-    <t>0.39</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #106)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #107)</t>
-  </si>
-  <si>
-    <t>0.57</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #108)</t>
-  </si>
-  <si>
-    <t>0.96</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #109)</t>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #237)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #238)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #239)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #240)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #241)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #242)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #243)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #244)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #245)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #246)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #247)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #248)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #249)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #250)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #251)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #252)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #253)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #254)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #255)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #256)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #257)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #258)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #259)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #260)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #261)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #262)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #263)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #264)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #265)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #266)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #267)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #268)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #269)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #270)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #271)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #272)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #273)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #274)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #275)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #276)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #277)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #278)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #279)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #280)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #281)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #282)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #283)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #284)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #285)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #286)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #287)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #288)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #289)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #290)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #291)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #292)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #293)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #294)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #295)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #296)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #297)</t>
   </si>
   <si>
     <t>0.50</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #110)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #111)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #112)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #113)</t>
-  </si>
-  <si>
-    <t>0.94</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #114)</t>
-  </si>
-  <si>
-    <t>0.68</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #115)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #116)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #117)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #118)</t>
-  </si>
-  <si>
-    <t>0.54</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #119)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #120)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #121)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #122)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #123)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #124)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #125)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #126)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #127)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #128)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #129)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #130)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #131)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #132)</t>
-  </si>
-  <si>
-    <t>0.75</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #133)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #134)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #135)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #136)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #137)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #138)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #139)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #140)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #141)</t>
-  </si>
-  <si>
-    <t>0.28</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #142)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #143)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #144)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #145)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #146)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #147)</t>
-  </si>
-  <si>
-    <t>0.70</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #148)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #149)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #150)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #151)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #152)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #153)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #154)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #155)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #156)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #157)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #158)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #159)</t>
-  </si>
-  <si>
-    <t>0.89</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #160)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #161)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #162)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #163)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #164)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #165)</t>
-  </si>
-  <si>
-    <t>0.74</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #166)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #167)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #168)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #169)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #170)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #171)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #172)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #173)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #174)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #175)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #176)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #177)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #178)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #179)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #180)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #181)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #182)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #183)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #184)</t>
-  </si>
-  <si>
-    <t>0.27</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #185)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #186)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #187)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #188)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #189)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #190)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #191)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #192)</t>
-  </si>
-  <si>
-    <t>0.32</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #193)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #194)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #195)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #196)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #197)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #198)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #199)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #200)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #201)</t>
-  </si>
-  <si>
-    <t>0.78</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #202)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #203)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #204)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #205)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #206)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #207)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #208)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #209)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #210)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #211)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #212)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #213)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #214)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #215)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #216)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #217)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #218)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #219)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #220)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #221)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #222)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #223)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #224)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #225)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #226)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #227)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #228)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #229)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #230)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #231)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #232)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #233)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #234)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #235)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #236)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #237)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #238)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #239)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #240)</t>
-  </si>
-  <si>
-    <t>0.93</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #241)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #242)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #243)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #244)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #245)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #246)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #247)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #248)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #249)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #250)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #251)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #252)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #253)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #254)</t>
-  </si>
-  <si>
-    <t>0.43</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #255)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #256)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #257)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #258)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #259)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #260)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #261)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #262)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #263)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #264)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #265)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #266)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #267)</t>
-  </si>
-  <si>
-    <t>0.95</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #268)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #269)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #270)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #271)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #272)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #273)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #274)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #275)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #276)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #277)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #278)</t>
-  </si>
-  <si>
-    <t>0.77</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #279)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #280)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #281)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #282)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #283)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #284)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #285)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #286)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #287)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #288)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #289)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #290)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #291)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #292)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #293)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #294)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #295)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #296)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #297)</t>
-  </si>
-  <si>
     <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #298)</t>
   </si>
   <si>
@@ -1307,9 +1307,6 @@
     <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #321)</t>
   </si>
   <si>
-    <t>0.71</t>
-  </si>
-  <si>
     <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #322)</t>
   </si>
   <si>
@@ -1496,9 +1493,6 @@
     <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #383)</t>
   </si>
   <si>
-    <t>0.76</t>
-  </si>
-  <si>
     <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #384)</t>
   </si>
   <si>
@@ -1556,13 +1550,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>11</t>
+    <t>12</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 12:10:46 UTC</t>
+    <t>2026-06-23 13:24:39 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1574,7 +1568,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>348580a</t>
+    <t>cfbb4d3</t>
   </si>
   <si>
     <t>Total</t>
@@ -2136,10 +2130,10 @@
         <v>6</v>
       </c>
       <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
         <v>29</v>
-      </c>
-      <c r="E9" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2147,16 +2141,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" t="s">
         <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2164,16 +2158,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2181,13 +2175,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E12" t="s">
         <v>27</v>
@@ -2198,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
         <v>27</v>
@@ -2215,13 +2209,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E14" t="s">
         <v>27</v>
@@ -2232,13 +2226,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E15" t="s">
         <v>27</v>
@@ -2249,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E16" t="s">
         <v>27</v>
@@ -2266,13 +2260,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E17" t="s">
         <v>27</v>
@@ -2283,13 +2277,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E18" t="s">
         <v>27</v>
@@ -2300,13 +2294,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" t="s">
         <v>49</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" t="s">
-        <v>50</v>
       </c>
       <c r="E19" t="s">
         <v>27</v>
@@ -2317,13 +2311,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" t="s">
         <v>51</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" t="s">
-        <v>52</v>
       </c>
       <c r="E20" t="s">
         <v>27</v>
@@ -2334,13 +2328,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E21" t="s">
         <v>27</v>
@@ -2351,13 +2345,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E22" t="s">
         <v>27</v>
@@ -2368,13 +2362,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E23" t="s">
         <v>27</v>
@@ -2385,13 +2379,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E24" t="s">
         <v>27</v>
@@ -2402,13 +2396,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="E25" t="s">
         <v>27</v>
@@ -2419,13 +2413,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E26" t="s">
         <v>27</v>
@@ -2436,13 +2430,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E27" t="s">
         <v>27</v>
@@ -2453,13 +2447,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="E28" t="s">
         <v>27</v>
@@ -2470,13 +2464,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E29" t="s">
         <v>27</v>
@@ -2487,13 +2481,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E30" t="s">
         <v>27</v>
@@ -2504,13 +2498,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E31" t="s">
         <v>27</v>
@@ -2521,13 +2515,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E32" t="s">
         <v>27</v>
@@ -2538,13 +2532,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E33" t="s">
         <v>27</v>
@@ -2555,13 +2549,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E34" t="s">
         <v>27</v>
@@ -2572,13 +2566,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E35" t="s">
         <v>27</v>
@@ -2589,13 +2583,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" t="s">
         <v>79</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D36" t="s">
-        <v>80</v>
       </c>
       <c r="E36" t="s">
         <v>27</v>
@@ -2606,13 +2600,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D37" t="s">
         <v>81</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D37" t="s">
-        <v>82</v>
       </c>
       <c r="E37" t="s">
         <v>27</v>
@@ -2623,13 +2617,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D38" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="E38" t="s">
         <v>27</v>
@@ -2640,13 +2634,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E39" t="s">
         <v>27</v>
@@ -2657,13 +2651,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E40" t="s">
         <v>27</v>
@@ -2674,13 +2668,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D41" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="E41" t="s">
         <v>27</v>
@@ -2691,13 +2685,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D42" t="s">
         <v>90</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D42" t="s">
-        <v>91</v>
       </c>
       <c r="E42" t="s">
         <v>27</v>
@@ -2708,13 +2702,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>91</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D43" t="s">
         <v>92</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D43" t="s">
-        <v>93</v>
       </c>
       <c r="E43" t="s">
         <v>27</v>
@@ -2725,13 +2719,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D44" t="s">
         <v>94</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D44" t="s">
-        <v>58</v>
       </c>
       <c r="E44" t="s">
         <v>27</v>
@@ -2748,7 +2742,7 @@
         <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E45" t="s">
         <v>27</v>
@@ -2782,7 +2776,7 @@
         <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E47" t="s">
         <v>27</v>
@@ -2793,13 +2787,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E48" t="s">
         <v>27</v>
@@ -2810,13 +2804,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E49" t="s">
         <v>27</v>
@@ -2827,13 +2821,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="E50" t="s">
         <v>27</v>
@@ -2844,13 +2838,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D51" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="E51" t="s">
         <v>27</v>
@@ -2861,13 +2855,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="E52" t="s">
         <v>27</v>
@@ -2878,13 +2872,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="E53" t="s">
         <v>27</v>
@@ -2895,13 +2889,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E54" t="s">
         <v>27</v>
@@ -2912,13 +2906,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D55" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E55" t="s">
         <v>27</v>
@@ -2929,13 +2923,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D56" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E56" t="s">
         <v>27</v>
@@ -2946,13 +2940,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D57" t="s">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="E57" t="s">
         <v>27</v>
@@ -2963,13 +2957,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D58" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="E58" t="s">
         <v>27</v>
@@ -2980,13 +2974,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D59" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E59" t="s">
         <v>27</v>
@@ -2997,13 +2991,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D60" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E60" t="s">
         <v>27</v>
@@ -3014,13 +3008,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E61" t="s">
         <v>27</v>
@@ -3031,13 +3025,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D62" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E62" t="s">
         <v>27</v>
@@ -3048,13 +3042,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D63" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E63" t="s">
         <v>27</v>
@@ -3065,13 +3059,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D64" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="E64" t="s">
         <v>27</v>
@@ -3088,7 +3082,7 @@
         <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E65" t="s">
         <v>27</v>
@@ -3099,13 +3093,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D66" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="E66" t="s">
         <v>27</v>
@@ -3116,13 +3110,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D67" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="E67" t="s">
         <v>27</v>
@@ -3133,13 +3127,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>130</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D68" t="s">
         <v>131</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D68" t="s">
-        <v>132</v>
       </c>
       <c r="E68" t="s">
         <v>27</v>
@@ -3150,13 +3144,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D69" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="E69" t="s">
         <v>27</v>
@@ -3167,13 +3161,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>133</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D70" t="s">
         <v>134</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D70" t="s">
-        <v>61</v>
       </c>
       <c r="E70" t="s">
         <v>27</v>
@@ -3207,7 +3201,7 @@
         <v>25</v>
       </c>
       <c r="D72" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="E72" t="s">
         <v>27</v>
@@ -3218,13 +3212,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>138</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D73" t="s">
         <v>139</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D73" t="s">
-        <v>140</v>
       </c>
       <c r="E73" t="s">
         <v>27</v>
@@ -3235,13 +3229,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D74" t="s">
         <v>141</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D74" t="s">
-        <v>107</v>
       </c>
       <c r="E74" t="s">
         <v>27</v>
@@ -3258,7 +3252,7 @@
         <v>25</v>
       </c>
       <c r="D75" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="E75" t="s">
         <v>27</v>
@@ -3269,13 +3263,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
+        <v>143</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D76" t="s">
         <v>144</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D76" t="s">
-        <v>65</v>
       </c>
       <c r="E76" t="s">
         <v>27</v>
@@ -3309,7 +3303,7 @@
         <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="E78" t="s">
         <v>27</v>
@@ -3320,13 +3314,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D79" t="s">
-        <v>150</v>
+        <v>67</v>
       </c>
       <c r="E79" t="s">
         <v>27</v>
@@ -3337,13 +3331,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D80" t="s">
-        <v>152</v>
+        <v>40</v>
       </c>
       <c r="E80" t="s">
         <v>27</v>
@@ -3354,13 +3348,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D81" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E81" t="s">
         <v>27</v>
@@ -3371,13 +3365,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D82" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="E82" t="s">
         <v>27</v>
@@ -3388,13 +3382,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D83" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E83" t="s">
         <v>27</v>
@@ -3405,13 +3399,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D84" t="s">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="E84" t="s">
         <v>27</v>
@@ -3422,13 +3416,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D85" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="E85" t="s">
         <v>27</v>
@@ -3439,13 +3433,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D86" t="s">
-        <v>161</v>
+        <v>62</v>
       </c>
       <c r="E86" t="s">
         <v>27</v>
@@ -3456,13 +3450,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D87" t="s">
-        <v>163</v>
+        <v>84</v>
       </c>
       <c r="E87" t="s">
         <v>27</v>
@@ -3473,13 +3467,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D88" t="s">
-        <v>58</v>
+        <v>162</v>
       </c>
       <c r="E88" t="s">
         <v>27</v>
@@ -3490,13 +3484,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D89" t="s">
-        <v>84</v>
+        <v>162</v>
       </c>
       <c r="E89" t="s">
         <v>27</v>
@@ -3507,13 +3501,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D90" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="E90" t="s">
         <v>27</v>
@@ -3524,13 +3518,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
+        <v>166</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D91" t="s">
         <v>167</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D91" t="s">
-        <v>113</v>
       </c>
       <c r="E91" t="s">
         <v>27</v>
@@ -3547,7 +3541,7 @@
         <v>25</v>
       </c>
       <c r="D92" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E92" t="s">
         <v>27</v>
@@ -3564,7 +3558,7 @@
         <v>25</v>
       </c>
       <c r="D93" t="s">
-        <v>170</v>
+        <v>134</v>
       </c>
       <c r="E93" t="s">
         <v>27</v>
@@ -3575,13 +3569,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D94" t="s">
-        <v>161</v>
+        <v>73</v>
       </c>
       <c r="E94" t="s">
         <v>27</v>
@@ -3592,13 +3586,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D95" t="s">
-        <v>173</v>
+        <v>65</v>
       </c>
       <c r="E95" t="s">
         <v>27</v>
@@ -3609,13 +3603,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D96" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="E96" t="s">
         <v>27</v>
@@ -3626,13 +3620,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
+        <v>174</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D97" t="s">
         <v>175</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D97" t="s">
-        <v>176</v>
       </c>
       <c r="E97" t="s">
         <v>27</v>
@@ -3643,13 +3637,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
+        <v>176</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D98" t="s">
         <v>177</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D98" t="s">
-        <v>178</v>
       </c>
       <c r="E98" t="s">
         <v>27</v>
@@ -3660,13 +3654,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D99" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="E99" t="s">
         <v>27</v>
@@ -3677,13 +3671,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D100" t="s">
-        <v>181</v>
+        <v>90</v>
       </c>
       <c r="E100" t="s">
         <v>27</v>
@@ -3694,13 +3688,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="E101" t="s">
         <v>27</v>
@@ -3711,13 +3705,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D102" t="s">
-        <v>184</v>
+        <v>45</v>
       </c>
       <c r="E102" t="s">
         <v>27</v>
@@ -3728,13 +3722,13 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D103" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="E103" t="s">
         <v>27</v>
@@ -3745,13 +3739,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D104" t="s">
-        <v>187</v>
+        <v>99</v>
       </c>
       <c r="E104" t="s">
         <v>27</v>
@@ -3762,13 +3756,13 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D105" t="s">
-        <v>189</v>
+        <v>94</v>
       </c>
       <c r="E105" t="s">
         <v>27</v>
@@ -3779,13 +3773,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D106" t="s">
-        <v>191</v>
+        <v>38</v>
       </c>
       <c r="E106" t="s">
         <v>27</v>
@@ -3796,13 +3790,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D107" t="s">
-        <v>193</v>
+        <v>54</v>
       </c>
       <c r="E107" t="s">
         <v>27</v>
@@ -3813,13 +3807,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D108" t="s">
-        <v>128</v>
+        <v>175</v>
       </c>
       <c r="E108" t="s">
         <v>27</v>
@@ -3830,13 +3824,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D109" t="s">
-        <v>196</v>
+        <v>144</v>
       </c>
       <c r="E109" t="s">
         <v>27</v>
@@ -3847,13 +3841,13 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D110" t="s">
-        <v>198</v>
+        <v>116</v>
       </c>
       <c r="E110" t="s">
         <v>27</v>
@@ -3864,13 +3858,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D111" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="E111" t="s">
         <v>27</v>
@@ -3881,13 +3875,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D112" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="E112" t="s">
         <v>27</v>
@@ -3898,13 +3892,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D113" t="s">
-        <v>67</v>
+        <v>158</v>
       </c>
       <c r="E113" t="s">
         <v>27</v>
@@ -3915,13 +3909,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D114" t="s">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="E114" t="s">
         <v>27</v>
@@ -3932,13 +3926,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D115" t="s">
-        <v>205</v>
+        <v>146</v>
       </c>
       <c r="E115" t="s">
         <v>27</v>
@@ -3949,13 +3943,13 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D116" t="s">
-        <v>207</v>
+        <v>84</v>
       </c>
       <c r="E116" t="s">
         <v>27</v>
@@ -3966,13 +3960,13 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D117" t="s">
-        <v>187</v>
+        <v>92</v>
       </c>
       <c r="E117" t="s">
         <v>27</v>
@@ -3983,13 +3977,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D118" t="s">
-        <v>44</v>
+        <v>191</v>
       </c>
       <c r="E118" t="s">
         <v>27</v>
@@ -4000,13 +3994,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D119" t="s">
-        <v>107</v>
+        <v>200</v>
       </c>
       <c r="E119" t="s">
         <v>27</v>
@@ -4017,13 +4011,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D120" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="E120" t="s">
         <v>27</v>
@@ -4034,13 +4028,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D121" t="s">
-        <v>102</v>
+        <v>165</v>
       </c>
       <c r="E121" t="s">
         <v>27</v>
@@ -4051,13 +4045,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D122" t="s">
-        <v>69</v>
+        <v>205</v>
       </c>
       <c r="E122" t="s">
         <v>27</v>
@@ -4068,13 +4062,13 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D123" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="E123" t="s">
         <v>27</v>
@@ -4085,13 +4079,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D124" t="s">
-        <v>58</v>
+        <v>208</v>
       </c>
       <c r="E124" t="s">
         <v>27</v>
@@ -4102,13 +4096,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D125" t="s">
-        <v>148</v>
+        <v>42</v>
       </c>
       <c r="E125" t="s">
         <v>27</v>
@@ -4119,13 +4113,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D126" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="E126" t="s">
         <v>27</v>
@@ -4136,13 +4130,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D127" t="s">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="E127" t="s">
         <v>27</v>
@@ -4153,13 +4147,13 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D128" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="E128" t="s">
         <v>27</v>
@@ -4170,13 +4164,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D129" t="s">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="E129" t="s">
         <v>27</v>
@@ -4187,13 +4181,13 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D130" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="E130" t="s">
         <v>27</v>
@@ -4204,13 +4198,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D131" t="s">
-        <v>76</v>
+        <v>217</v>
       </c>
       <c r="E131" t="s">
         <v>27</v>
@@ -4221,13 +4215,13 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D132" t="s">
-        <v>181</v>
+        <v>219</v>
       </c>
       <c r="E132" t="s">
         <v>27</v>
@@ -4238,13 +4232,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D133" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="E133" t="s">
         <v>27</v>
@@ -4255,13 +4249,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D134" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="E134" t="s">
         <v>27</v>
@@ -4272,13 +4266,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D135" t="s">
-        <v>76</v>
+        <v>223</v>
       </c>
       <c r="E135" t="s">
         <v>27</v>
@@ -4289,13 +4283,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D136" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="E136" t="s">
         <v>27</v>
@@ -4306,13 +4300,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D137" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="E137" t="s">
         <v>27</v>
@@ -4323,13 +4317,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D138" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E138" t="s">
         <v>27</v>
@@ -4340,13 +4334,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D139" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="E139" t="s">
         <v>27</v>
@@ -4357,13 +4351,13 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D140" t="s">
-        <v>184</v>
+        <v>229</v>
       </c>
       <c r="E140" t="s">
         <v>27</v>
@@ -4374,13 +4368,13 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D141" t="s">
-        <v>86</v>
+        <v>229</v>
       </c>
       <c r="E141" t="s">
         <v>27</v>
@@ -4391,13 +4385,13 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D142" t="s">
-        <v>93</v>
+        <v>232</v>
       </c>
       <c r="E142" t="s">
         <v>27</v>
@@ -4408,13 +4402,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D143" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E143" t="s">
         <v>27</v>
@@ -4425,13 +4419,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D144" t="s">
-        <v>111</v>
+        <v>200</v>
       </c>
       <c r="E144" t="s">
         <v>27</v>
@@ -4442,13 +4436,13 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D145" t="s">
-        <v>52</v>
+        <v>155</v>
       </c>
       <c r="E145" t="s">
         <v>27</v>
@@ -4459,13 +4453,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D146" t="s">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="E146" t="s">
         <v>27</v>
@@ -4476,13 +4470,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D147" t="s">
-        <v>200</v>
+        <v>239</v>
       </c>
       <c r="E147" t="s">
         <v>27</v>
@@ -4493,13 +4487,13 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D148" t="s">
-        <v>54</v>
+        <v>165</v>
       </c>
       <c r="E148" t="s">
         <v>27</v>
@@ -4510,13 +4504,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D149" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E149" t="s">
         <v>27</v>
@@ -4527,13 +4521,13 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D150" t="s">
-        <v>54</v>
+        <v>244</v>
       </c>
       <c r="E150" t="s">
         <v>27</v>
@@ -4544,13 +4538,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D151" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E151" t="s">
         <v>27</v>
@@ -4561,13 +4555,13 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D152" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="E152" t="s">
         <v>27</v>
@@ -4578,13 +4572,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D153" t="s">
-        <v>163</v>
+        <v>232</v>
       </c>
       <c r="E153" t="s">
         <v>27</v>
@@ -4595,13 +4589,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
+        <v>248</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D154" t="s">
         <v>249</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D154" t="s">
-        <v>132</v>
       </c>
       <c r="E154" t="s">
         <v>27</v>
@@ -4618,7 +4612,7 @@
         <v>25</v>
       </c>
       <c r="D155" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="E155" t="s">
         <v>27</v>
@@ -4635,7 +4629,7 @@
         <v>25</v>
       </c>
       <c r="D156" t="s">
-        <v>173</v>
+        <v>57</v>
       </c>
       <c r="E156" t="s">
         <v>27</v>
@@ -4652,7 +4646,7 @@
         <v>25</v>
       </c>
       <c r="D157" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="E157" t="s">
         <v>27</v>
@@ -4669,7 +4663,7 @@
         <v>25</v>
       </c>
       <c r="D158" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="E158" t="s">
         <v>27</v>
@@ -4686,7 +4680,7 @@
         <v>25</v>
       </c>
       <c r="D159" t="s">
-        <v>132</v>
+        <v>234</v>
       </c>
       <c r="E159" t="s">
         <v>27</v>
@@ -4703,7 +4697,7 @@
         <v>25</v>
       </c>
       <c r="D160" t="s">
-        <v>82</v>
+        <v>217</v>
       </c>
       <c r="E160" t="s">
         <v>27</v>
@@ -4720,7 +4714,7 @@
         <v>25</v>
       </c>
       <c r="D161" t="s">
-        <v>257</v>
+        <v>105</v>
       </c>
       <c r="E161" t="s">
         <v>27</v>
@@ -4731,13 +4725,13 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
+        <v>257</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D162" t="s">
         <v>258</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D162" t="s">
-        <v>184</v>
       </c>
       <c r="E162" t="s">
         <v>27</v>
@@ -4754,7 +4748,7 @@
         <v>25</v>
       </c>
       <c r="D163" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E163" t="s">
         <v>27</v>
@@ -4771,7 +4765,7 @@
         <v>25</v>
       </c>
       <c r="D164" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E164" t="s">
         <v>27</v>
@@ -4788,7 +4782,7 @@
         <v>25</v>
       </c>
       <c r="D165" t="s">
-        <v>181</v>
+        <v>262</v>
       </c>
       <c r="E165" t="s">
         <v>27</v>
@@ -4799,13 +4793,13 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D166" t="s">
-        <v>146</v>
+        <v>264</v>
       </c>
       <c r="E166" t="s">
         <v>27</v>
@@ -4816,13 +4810,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D167" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E167" t="s">
         <v>27</v>
@@ -4833,13 +4827,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D168" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="E168" t="s">
         <v>27</v>
@@ -4850,13 +4844,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D169" t="s">
-        <v>47</v>
+        <v>223</v>
       </c>
       <c r="E169" t="s">
         <v>27</v>
@@ -4867,13 +4861,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D170" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="E170" t="s">
         <v>27</v>
@@ -4884,13 +4878,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D171" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="E171" t="s">
         <v>27</v>
@@ -4901,13 +4895,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D172" t="s">
-        <v>58</v>
+        <v>191</v>
       </c>
       <c r="E172" t="s">
         <v>27</v>
@@ -4918,13 +4912,13 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D173" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="E173" t="s">
         <v>27</v>
@@ -4935,13 +4929,13 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D174" t="s">
-        <v>116</v>
+        <v>232</v>
       </c>
       <c r="E174" t="s">
         <v>27</v>
@@ -4952,13 +4946,13 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D175" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="E175" t="s">
         <v>27</v>
@@ -4969,13 +4963,13 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D176" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E176" t="s">
         <v>27</v>
@@ -4986,13 +4980,13 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D177" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="E177" t="s">
         <v>27</v>
@@ -5003,13 +4997,13 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D178" t="s">
-        <v>148</v>
+        <v>67</v>
       </c>
       <c r="E178" t="s">
         <v>27</v>
@@ -5020,13 +5014,13 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D179" t="s">
-        <v>56</v>
+        <v>266</v>
       </c>
       <c r="E179" t="s">
         <v>27</v>
@@ -5037,13 +5031,13 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D180" t="s">
-        <v>158</v>
+        <v>97</v>
       </c>
       <c r="E180" t="s">
         <v>27</v>
@@ -5054,13 +5048,13 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D181" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="E181" t="s">
         <v>27</v>
@@ -5071,13 +5065,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D182" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E182" t="s">
         <v>27</v>
@@ -5088,13 +5082,13 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D183" t="s">
-        <v>158</v>
+        <v>92</v>
       </c>
       <c r="E183" t="s">
         <v>27</v>
@@ -5105,13 +5099,13 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D184" t="s">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="E184" t="s">
         <v>27</v>
@@ -5122,13 +5116,13 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D185" t="s">
-        <v>154</v>
+        <v>285</v>
       </c>
       <c r="E185" t="s">
         <v>27</v>
@@ -5139,13 +5133,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D186" t="s">
-        <v>284</v>
+        <v>75</v>
       </c>
       <c r="E186" t="s">
         <v>27</v>
@@ -5156,13 +5150,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D187" t="s">
-        <v>178</v>
+        <v>90</v>
       </c>
       <c r="E187" t="s">
         <v>27</v>
@@ -5173,13 +5167,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D188" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E188" t="s">
         <v>27</v>
@@ -5190,13 +5184,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D189" t="s">
-        <v>50</v>
+        <v>153</v>
       </c>
       <c r="E189" t="s">
         <v>27</v>
@@ -5207,13 +5201,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D190" t="s">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="E190" t="s">
         <v>27</v>
@@ -5224,13 +5218,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D191" t="s">
-        <v>113</v>
+        <v>229</v>
       </c>
       <c r="E191" t="s">
         <v>27</v>
@@ -5241,13 +5235,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D192" t="s">
-        <v>196</v>
+        <v>38</v>
       </c>
       <c r="E192" t="s">
         <v>27</v>
@@ -5258,13 +5252,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D193" t="s">
-        <v>189</v>
+        <v>139</v>
       </c>
       <c r="E193" t="s">
         <v>27</v>
@@ -5275,13 +5269,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D194" t="s">
-        <v>293</v>
+        <v>217</v>
       </c>
       <c r="E194" t="s">
         <v>27</v>
@@ -5292,13 +5286,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D195" t="s">
-        <v>116</v>
+        <v>239</v>
       </c>
       <c r="E195" t="s">
         <v>27</v>
@@ -5309,13 +5303,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D196" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="E196" t="s">
         <v>27</v>
@@ -5326,13 +5320,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D197" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="E197" t="s">
         <v>27</v>
@@ -5343,13 +5337,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D198" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="E198" t="s">
         <v>27</v>
@@ -5360,13 +5354,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D199" t="s">
-        <v>189</v>
+        <v>285</v>
       </c>
       <c r="E199" t="s">
         <v>27</v>
@@ -5377,13 +5371,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D200" t="s">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="E200" t="s">
         <v>27</v>
@@ -5394,13 +5388,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D201" t="s">
-        <v>63</v>
+        <v>258</v>
       </c>
       <c r="E201" t="s">
         <v>27</v>
@@ -5411,13 +5405,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D202" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="E202" t="s">
         <v>27</v>
@@ -5428,13 +5422,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D203" t="s">
-        <v>303</v>
+        <v>73</v>
       </c>
       <c r="E203" t="s">
         <v>27</v>
@@ -5451,7 +5445,7 @@
         <v>25</v>
       </c>
       <c r="D204" t="s">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="E204" t="s">
         <v>27</v>
@@ -5468,7 +5462,7 @@
         <v>25</v>
       </c>
       <c r="D205" t="s">
-        <v>207</v>
+        <v>262</v>
       </c>
       <c r="E205" t="s">
         <v>27</v>
@@ -5485,7 +5479,7 @@
         <v>25</v>
       </c>
       <c r="D206" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="E206" t="s">
         <v>27</v>
@@ -5502,7 +5496,7 @@
         <v>25</v>
       </c>
       <c r="D207" t="s">
-        <v>237</v>
+        <v>123</v>
       </c>
       <c r="E207" t="s">
         <v>27</v>
@@ -5519,7 +5513,7 @@
         <v>25</v>
       </c>
       <c r="D208" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="E208" t="s">
         <v>27</v>
@@ -5536,7 +5530,7 @@
         <v>25</v>
       </c>
       <c r="D209" t="s">
-        <v>65</v>
+        <v>208</v>
       </c>
       <c r="E209" t="s">
         <v>27</v>
@@ -5553,7 +5547,7 @@
         <v>25</v>
       </c>
       <c r="D210" t="s">
-        <v>303</v>
+        <v>266</v>
       </c>
       <c r="E210" t="s">
         <v>27</v>
@@ -5570,7 +5564,7 @@
         <v>25</v>
       </c>
       <c r="D211" t="s">
-        <v>67</v>
+        <v>223</v>
       </c>
       <c r="E211" t="s">
         <v>27</v>
@@ -5587,7 +5581,7 @@
         <v>25</v>
       </c>
       <c r="D212" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="E212" t="s">
         <v>27</v>
@@ -5604,7 +5598,7 @@
         <v>25</v>
       </c>
       <c r="D213" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="E213" t="s">
         <v>27</v>
@@ -5621,7 +5615,7 @@
         <v>25</v>
       </c>
       <c r="D214" t="s">
-        <v>244</v>
+        <v>120</v>
       </c>
       <c r="E214" t="s">
         <v>27</v>
@@ -5638,7 +5632,7 @@
         <v>25</v>
       </c>
       <c r="D215" t="s">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="E215" t="s">
         <v>27</v>
@@ -5655,7 +5649,7 @@
         <v>25</v>
       </c>
       <c r="D216" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="E216" t="s">
         <v>27</v>
@@ -5672,7 +5666,7 @@
         <v>25</v>
       </c>
       <c r="D217" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="E217" t="s">
         <v>27</v>
@@ -5689,7 +5683,7 @@
         <v>25</v>
       </c>
       <c r="D218" t="s">
-        <v>205</v>
+        <v>90</v>
       </c>
       <c r="E218" t="s">
         <v>27</v>
@@ -5706,7 +5700,7 @@
         <v>25</v>
       </c>
       <c r="D219" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E219" t="s">
         <v>27</v>
@@ -5723,7 +5717,7 @@
         <v>25</v>
       </c>
       <c r="D220" t="s">
-        <v>47</v>
+        <v>136</v>
       </c>
       <c r="E220" t="s">
         <v>27</v>
@@ -5740,7 +5734,7 @@
         <v>25</v>
       </c>
       <c r="D221" t="s">
-        <v>244</v>
+        <v>99</v>
       </c>
       <c r="E221" t="s">
         <v>27</v>
@@ -5757,7 +5751,7 @@
         <v>25</v>
       </c>
       <c r="D222" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E222" t="s">
         <v>27</v>
@@ -5774,7 +5768,7 @@
         <v>25</v>
       </c>
       <c r="D223" t="s">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="E223" t="s">
         <v>27</v>
@@ -5791,7 +5785,7 @@
         <v>25</v>
       </c>
       <c r="D224" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E224" t="s">
         <v>27</v>
@@ -5808,7 +5802,7 @@
         <v>25</v>
       </c>
       <c r="D225" t="s">
-        <v>227</v>
+        <v>326</v>
       </c>
       <c r="E225" t="s">
         <v>27</v>
@@ -5819,13 +5813,13 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D226" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="E226" t="s">
         <v>27</v>
@@ -5836,13 +5830,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D227" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="E227" t="s">
         <v>27</v>
@@ -5853,13 +5847,13 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D228" t="s">
-        <v>196</v>
+        <v>38</v>
       </c>
       <c r="E228" t="s">
         <v>27</v>
@@ -5870,13 +5864,13 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D229" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="E229" t="s">
         <v>27</v>
@@ -5887,13 +5881,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D230" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="E230" t="s">
         <v>27</v>
@@ -5904,13 +5898,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D231" t="s">
-        <v>65</v>
+        <v>205</v>
       </c>
       <c r="E231" t="s">
         <v>27</v>
@@ -5921,13 +5915,13 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D232" t="s">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="E232" t="s">
         <v>27</v>
@@ -5938,13 +5932,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D233" t="s">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E233" t="s">
         <v>27</v>
@@ -5955,13 +5949,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D234" t="s">
-        <v>237</v>
+        <v>146</v>
       </c>
       <c r="E234" t="s">
         <v>27</v>
@@ -5972,13 +5966,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D235" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="E235" t="s">
         <v>27</v>
@@ -5989,13 +5983,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D236" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="E236" t="s">
         <v>27</v>
@@ -6006,13 +6000,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D237" t="s">
-        <v>54</v>
+        <v>339</v>
       </c>
       <c r="E237" t="s">
         <v>27</v>
@@ -6023,13 +6017,13 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D238" t="s">
-        <v>244</v>
+        <v>341</v>
       </c>
       <c r="E238" t="s">
         <v>27</v>
@@ -6040,13 +6034,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D239" t="s">
-        <v>178</v>
+        <v>75</v>
       </c>
       <c r="E239" t="s">
         <v>27</v>
@@ -6057,13 +6051,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D240" t="s">
-        <v>61</v>
+        <v>242</v>
       </c>
       <c r="E240" t="s">
         <v>27</v>
@@ -6074,13 +6068,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D241" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="E241" t="s">
         <v>27</v>
@@ -6091,13 +6085,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D242" t="s">
-        <v>343</v>
+        <v>249</v>
       </c>
       <c r="E242" t="s">
         <v>27</v>
@@ -6108,13 +6102,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D243" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="E243" t="s">
         <v>27</v>
@@ -6125,13 +6119,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D244" t="s">
-        <v>264</v>
+        <v>60</v>
       </c>
       <c r="E244" t="s">
         <v>27</v>
@@ -6142,13 +6136,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D245" t="s">
-        <v>109</v>
+        <v>223</v>
       </c>
       <c r="E245" t="s">
         <v>27</v>
@@ -6159,13 +6153,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D246" t="s">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="E246" t="s">
         <v>27</v>
@@ -6176,13 +6170,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D247" t="s">
-        <v>237</v>
+        <v>116</v>
       </c>
       <c r="E247" t="s">
         <v>27</v>
@@ -6193,13 +6187,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D248" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E248" t="s">
         <v>27</v>
@@ -6210,13 +6204,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D249" t="s">
-        <v>50</v>
+        <v>165</v>
       </c>
       <c r="E249" t="s">
         <v>27</v>
@@ -6227,13 +6221,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D250" t="s">
-        <v>293</v>
+        <v>90</v>
       </c>
       <c r="E250" t="s">
         <v>27</v>
@@ -6244,13 +6238,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D251" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E251" t="s">
         <v>27</v>
@@ -6261,13 +6255,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D252" t="s">
-        <v>154</v>
+        <v>223</v>
       </c>
       <c r="E252" t="s">
         <v>27</v>
@@ -6278,13 +6272,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D253" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="E253" t="s">
         <v>27</v>
@@ -6295,13 +6289,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D254" t="s">
-        <v>82</v>
+        <v>202</v>
       </c>
       <c r="E254" t="s">
         <v>27</v>
@@ -6312,13 +6306,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D255" t="s">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="E255" t="s">
         <v>27</v>
@@ -6329,13 +6323,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D256" t="s">
-        <v>358</v>
+        <v>205</v>
       </c>
       <c r="E256" t="s">
         <v>27</v>
@@ -6346,13 +6340,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D257" t="s">
-        <v>181</v>
+        <v>123</v>
       </c>
       <c r="E257" t="s">
         <v>27</v>
@@ -6363,13 +6357,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D258" t="s">
-        <v>237</v>
+        <v>200</v>
       </c>
       <c r="E258" t="s">
         <v>27</v>
@@ -6380,13 +6374,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D259" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="E259" t="s">
         <v>27</v>
@@ -6397,13 +6391,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D260" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="E260" t="s">
         <v>27</v>
@@ -6414,13 +6408,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D261" t="s">
-        <v>67</v>
+        <v>146</v>
       </c>
       <c r="E261" t="s">
         <v>27</v>
@@ -6431,13 +6425,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D262" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="E262" t="s">
         <v>27</v>
@@ -6448,13 +6442,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D263" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="E263" t="s">
         <v>27</v>
@@ -6465,13 +6459,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D264" t="s">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="E264" t="s">
         <v>27</v>
@@ -6482,13 +6476,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D265" t="s">
-        <v>193</v>
+        <v>101</v>
       </c>
       <c r="E265" t="s">
         <v>27</v>
@@ -6499,13 +6493,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D266" t="s">
-        <v>88</v>
+        <v>219</v>
       </c>
       <c r="E266" t="s">
         <v>27</v>
@@ -6516,13 +6510,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D267" t="s">
-        <v>227</v>
+        <v>99</v>
       </c>
       <c r="E267" t="s">
         <v>27</v>
@@ -6533,13 +6527,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D268" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="E268" t="s">
         <v>27</v>
@@ -6550,13 +6544,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D269" t="s">
-        <v>372</v>
+        <v>97</v>
       </c>
       <c r="E269" t="s">
         <v>27</v>
@@ -6573,7 +6567,7 @@
         <v>25</v>
       </c>
       <c r="D270" t="s">
-        <v>184</v>
+        <v>51</v>
       </c>
       <c r="E270" t="s">
         <v>27</v>
@@ -6590,7 +6584,7 @@
         <v>25</v>
       </c>
       <c r="D271" t="s">
-        <v>158</v>
+        <v>92</v>
       </c>
       <c r="E271" t="s">
         <v>27</v>
@@ -6607,7 +6601,7 @@
         <v>25</v>
       </c>
       <c r="D272" t="s">
-        <v>372</v>
+        <v>249</v>
       </c>
       <c r="E272" t="s">
         <v>27</v>
@@ -6624,7 +6618,7 @@
         <v>25</v>
       </c>
       <c r="D273" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="E273" t="s">
         <v>27</v>
@@ -6641,7 +6635,7 @@
         <v>25</v>
       </c>
       <c r="D274" t="s">
-        <v>184</v>
+        <v>97</v>
       </c>
       <c r="E274" t="s">
         <v>27</v>
@@ -6658,7 +6652,7 @@
         <v>25</v>
       </c>
       <c r="D275" t="s">
-        <v>67</v>
+        <v>165</v>
       </c>
       <c r="E275" t="s">
         <v>27</v>
@@ -6675,7 +6669,7 @@
         <v>25</v>
       </c>
       <c r="D276" t="s">
-        <v>196</v>
+        <v>262</v>
       </c>
       <c r="E276" t="s">
         <v>27</v>
@@ -6692,7 +6686,7 @@
         <v>25</v>
       </c>
       <c r="D277" t="s">
-        <v>122</v>
+        <v>232</v>
       </c>
       <c r="E277" t="s">
         <v>27</v>
@@ -6709,7 +6703,7 @@
         <v>25</v>
       </c>
       <c r="D278" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="E278" t="s">
         <v>27</v>
@@ -6726,7 +6720,7 @@
         <v>25</v>
       </c>
       <c r="D279" t="s">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="E279" t="s">
         <v>27</v>
@@ -6743,7 +6737,7 @@
         <v>25</v>
       </c>
       <c r="D280" t="s">
-        <v>384</v>
+        <v>339</v>
       </c>
       <c r="E280" t="s">
         <v>27</v>
@@ -6754,13 +6748,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D281" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="E281" t="s">
         <v>27</v>
@@ -6771,13 +6765,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D282" t="s">
-        <v>138</v>
+        <v>242</v>
       </c>
       <c r="E282" t="s">
         <v>27</v>
@@ -6788,13 +6782,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D283" t="s">
-        <v>207</v>
+        <v>242</v>
       </c>
       <c r="E283" t="s">
         <v>27</v>
@@ -6805,13 +6799,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D284" t="s">
-        <v>150</v>
+        <v>88</v>
       </c>
       <c r="E284" t="s">
         <v>27</v>
@@ -6822,13 +6816,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D285" t="s">
-        <v>154</v>
+        <v>205</v>
       </c>
       <c r="E285" t="s">
         <v>27</v>
@@ -6839,13 +6833,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D286" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E286" t="s">
         <v>27</v>
@@ -6856,7 +6850,7 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>25</v>
@@ -6873,13 +6867,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D288" t="s">
-        <v>184</v>
+        <v>339</v>
       </c>
       <c r="E288" t="s">
         <v>27</v>
@@ -6890,13 +6884,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D289" t="s">
-        <v>93</v>
+        <v>205</v>
       </c>
       <c r="E289" t="s">
         <v>27</v>
@@ -6907,13 +6901,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D290" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E290" t="s">
         <v>27</v>
@@ -6924,13 +6918,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D291" t="s">
-        <v>384</v>
+        <v>81</v>
       </c>
       <c r="E291" t="s">
         <v>27</v>
@@ -6941,13 +6935,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D292" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="E292" t="s">
         <v>27</v>
@@ -6958,13 +6952,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D293" t="s">
-        <v>181</v>
+        <v>120</v>
       </c>
       <c r="E293" t="s">
         <v>27</v>
@@ -6975,13 +6969,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D294" t="s">
-        <v>343</v>
+        <v>146</v>
       </c>
       <c r="E294" t="s">
         <v>27</v>
@@ -6992,13 +6986,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D295" t="s">
-        <v>42</v>
+        <v>173</v>
       </c>
       <c r="E295" t="s">
         <v>27</v>
@@ -7009,13 +7003,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D296" t="s">
-        <v>61</v>
+        <v>175</v>
       </c>
       <c r="E296" t="s">
         <v>27</v>
@@ -7026,13 +7020,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D297" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="E297" t="s">
         <v>27</v>
@@ -7043,13 +7037,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D298" t="s">
-        <v>173</v>
+        <v>67</v>
       </c>
       <c r="E298" t="s">
         <v>27</v>
@@ -7060,13 +7054,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
+        <v>402</v>
+      </c>
+      <c r="C299" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D299" t="s">
         <v>403</v>
-      </c>
-      <c r="C299" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D299" t="s">
-        <v>91</v>
       </c>
       <c r="E299" t="s">
         <v>27</v>
@@ -7083,7 +7077,7 @@
         <v>25</v>
       </c>
       <c r="D300" t="s">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="E300" t="s">
         <v>27</v>
@@ -7100,7 +7094,7 @@
         <v>25</v>
       </c>
       <c r="D301" t="s">
-        <v>187</v>
+        <v>103</v>
       </c>
       <c r="E301" t="s">
         <v>27</v>
@@ -7117,7 +7111,7 @@
         <v>25</v>
       </c>
       <c r="D302" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="E302" t="s">
         <v>27</v>
@@ -7134,7 +7128,7 @@
         <v>25</v>
       </c>
       <c r="D303" t="s">
-        <v>154</v>
+        <v>239</v>
       </c>
       <c r="E303" t="s">
         <v>27</v>
@@ -7151,7 +7145,7 @@
         <v>25</v>
       </c>
       <c r="D304" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="E304" t="s">
         <v>27</v>
@@ -7168,7 +7162,7 @@
         <v>25</v>
       </c>
       <c r="D305" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E305" t="s">
         <v>27</v>
@@ -7185,7 +7179,7 @@
         <v>25</v>
       </c>
       <c r="D306" t="s">
-        <v>191</v>
+        <v>244</v>
       </c>
       <c r="E306" t="s">
         <v>27</v>
@@ -7202,7 +7196,7 @@
         <v>25</v>
       </c>
       <c r="D307" t="s">
-        <v>119</v>
+        <v>244</v>
       </c>
       <c r="E307" t="s">
         <v>27</v>
@@ -7219,7 +7213,7 @@
         <v>25</v>
       </c>
       <c r="D308" t="s">
-        <v>200</v>
+        <v>123</v>
       </c>
       <c r="E308" t="s">
         <v>27</v>
@@ -7236,7 +7230,7 @@
         <v>25</v>
       </c>
       <c r="D309" t="s">
-        <v>227</v>
+        <v>88</v>
       </c>
       <c r="E309" t="s">
         <v>27</v>
@@ -7253,7 +7247,7 @@
         <v>25</v>
       </c>
       <c r="D310" t="s">
-        <v>143</v>
+        <v>339</v>
       </c>
       <c r="E310" t="s">
         <v>27</v>
@@ -7270,7 +7264,7 @@
         <v>25</v>
       </c>
       <c r="D311" t="s">
-        <v>198</v>
+        <v>105</v>
       </c>
       <c r="E311" t="s">
         <v>27</v>
@@ -7287,7 +7281,7 @@
         <v>25</v>
       </c>
       <c r="D312" t="s">
-        <v>67</v>
+        <v>205</v>
       </c>
       <c r="E312" t="s">
         <v>27</v>
@@ -7304,7 +7298,7 @@
         <v>25</v>
       </c>
       <c r="D313" t="s">
-        <v>173</v>
+        <v>73</v>
       </c>
       <c r="E313" t="s">
         <v>27</v>
@@ -7321,7 +7315,7 @@
         <v>25</v>
       </c>
       <c r="D314" t="s">
-        <v>176</v>
+        <v>326</v>
       </c>
       <c r="E314" t="s">
         <v>27</v>
@@ -7338,7 +7332,7 @@
         <v>25</v>
       </c>
       <c r="D315" t="s">
-        <v>132</v>
+        <v>239</v>
       </c>
       <c r="E315" t="s">
         <v>27</v>
@@ -7355,7 +7349,7 @@
         <v>25</v>
       </c>
       <c r="D316" t="s">
-        <v>257</v>
+        <v>94</v>
       </c>
       <c r="E316" t="s">
         <v>27</v>
@@ -7372,7 +7366,7 @@
         <v>25</v>
       </c>
       <c r="D317" t="s">
-        <v>163</v>
+        <v>229</v>
       </c>
       <c r="E317" t="s">
         <v>27</v>
@@ -7389,7 +7383,7 @@
         <v>25</v>
       </c>
       <c r="D318" t="s">
-        <v>52</v>
+        <v>111</v>
       </c>
       <c r="E318" t="s">
         <v>27</v>
@@ -7406,7 +7400,7 @@
         <v>25</v>
       </c>
       <c r="D319" t="s">
-        <v>126</v>
+        <v>175</v>
       </c>
       <c r="E319" t="s">
         <v>27</v>
@@ -7423,7 +7417,7 @@
         <v>25</v>
       </c>
       <c r="D320" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="E320" t="s">
         <v>27</v>
@@ -7440,7 +7434,7 @@
         <v>25</v>
       </c>
       <c r="D321" t="s">
-        <v>178</v>
+        <v>60</v>
       </c>
       <c r="E321" t="s">
         <v>27</v>
@@ -7457,7 +7451,7 @@
         <v>25</v>
       </c>
       <c r="D322" t="s">
-        <v>205</v>
+        <v>45</v>
       </c>
       <c r="E322" t="s">
         <v>27</v>
@@ -7474,7 +7468,7 @@
         <v>25</v>
       </c>
       <c r="D323" t="s">
-        <v>428</v>
+        <v>65</v>
       </c>
       <c r="E323" t="s">
         <v>27</v>
@@ -7485,13 +7479,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D324" t="s">
-        <v>212</v>
+        <v>144</v>
       </c>
       <c r="E324" t="s">
         <v>27</v>
@@ -7502,13 +7496,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D325" t="s">
-        <v>372</v>
+        <v>79</v>
       </c>
       <c r="E325" t="s">
         <v>27</v>
@@ -7519,13 +7513,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D326" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="E326" t="s">
         <v>27</v>
@@ -7536,13 +7530,13 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D327" t="s">
-        <v>152</v>
+        <v>86</v>
       </c>
       <c r="E327" t="s">
         <v>27</v>
@@ -7553,13 +7547,13 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D328" t="s">
-        <v>176</v>
+        <v>36</v>
       </c>
       <c r="E328" t="s">
         <v>27</v>
@@ -7570,13 +7564,13 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D329" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="E329" t="s">
         <v>27</v>
@@ -7587,13 +7581,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D330" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="E330" t="s">
         <v>27</v>
@@ -7604,13 +7598,13 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D331" t="s">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="E331" t="s">
         <v>27</v>
@@ -7621,13 +7615,13 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D332" t="s">
-        <v>343</v>
+        <v>73</v>
       </c>
       <c r="E332" t="s">
         <v>27</v>
@@ -7638,13 +7632,13 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D333" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="E333" t="s">
         <v>27</v>
@@ -7655,13 +7649,13 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D334" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E334" t="s">
         <v>27</v>
@@ -7672,13 +7666,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D335" t="s">
-        <v>50</v>
+        <v>151</v>
       </c>
       <c r="E335" t="s">
         <v>27</v>
@@ -7689,13 +7683,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D336" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="E336" t="s">
         <v>27</v>
@@ -7706,13 +7700,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D337" t="s">
-        <v>184</v>
+        <v>60</v>
       </c>
       <c r="E337" t="s">
         <v>27</v>
@@ -7723,13 +7717,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D338" t="s">
-        <v>170</v>
+        <v>264</v>
       </c>
       <c r="E338" t="s">
         <v>27</v>
@@ -7740,13 +7734,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D339" t="s">
-        <v>244</v>
+        <v>81</v>
       </c>
       <c r="E339" t="s">
         <v>27</v>
@@ -7757,13 +7751,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D340" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
       <c r="E340" t="s">
         <v>27</v>
@@ -7774,13 +7768,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D341" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E341" t="s">
         <v>27</v>
@@ -7791,13 +7785,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D342" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="E342" t="s">
         <v>27</v>
@@ -7808,13 +7802,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D343" t="s">
-        <v>163</v>
+        <v>116</v>
       </c>
       <c r="E343" t="s">
         <v>27</v>
@@ -7825,13 +7819,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D344" t="s">
-        <v>107</v>
+        <v>211</v>
       </c>
       <c r="E344" t="s">
         <v>27</v>
@@ -7842,13 +7836,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D345" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="E345" t="s">
         <v>27</v>
@@ -7859,13 +7853,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D346" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="E346" t="s">
         <v>27</v>
@@ -7876,13 +7870,13 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D347" t="s">
-        <v>67</v>
+        <v>339</v>
       </c>
       <c r="E347" t="s">
         <v>27</v>
@@ -7893,13 +7887,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D348" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="E348" t="s">
         <v>27</v>
@@ -7910,13 +7904,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D349" t="s">
-        <v>113</v>
+        <v>262</v>
       </c>
       <c r="E349" t="s">
         <v>27</v>
@@ -7927,13 +7921,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D350" t="s">
-        <v>293</v>
+        <v>81</v>
       </c>
       <c r="E350" t="s">
         <v>27</v>
@@ -7944,13 +7938,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D351" t="s">
-        <v>187</v>
+        <v>144</v>
       </c>
       <c r="E351" t="s">
         <v>27</v>
@@ -7961,13 +7955,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D352" t="s">
-        <v>187</v>
+        <v>114</v>
       </c>
       <c r="E352" t="s">
         <v>27</v>
@@ -7978,13 +7972,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D353" t="s">
-        <v>372</v>
+        <v>232</v>
       </c>
       <c r="E353" t="s">
         <v>27</v>
@@ -7995,13 +7989,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D354" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="E354" t="s">
         <v>27</v>
@@ -8012,13 +8006,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D355" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E355" t="s">
         <v>27</v>
@@ -8029,13 +8023,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D356" t="s">
-        <v>97</v>
+        <v>232</v>
       </c>
       <c r="E356" t="s">
         <v>27</v>
@@ -8046,13 +8040,13 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D357" t="s">
-        <v>264</v>
+        <v>71</v>
       </c>
       <c r="E357" t="s">
         <v>27</v>
@@ -8063,13 +8057,13 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D358" t="s">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="E358" t="s">
         <v>27</v>
@@ -8080,13 +8074,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D359" t="s">
-        <v>42</v>
+        <v>146</v>
       </c>
       <c r="E359" t="s">
         <v>27</v>
@@ -8097,13 +8091,13 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D360" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="E360" t="s">
         <v>27</v>
@@ -8114,13 +8108,13 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D361" t="s">
-        <v>113</v>
+        <v>339</v>
       </c>
       <c r="E361" t="s">
         <v>27</v>
@@ -8131,13 +8125,13 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D362" t="s">
-        <v>58</v>
+        <v>264</v>
       </c>
       <c r="E362" t="s">
         <v>27</v>
@@ -8148,13 +8142,13 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D363" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="E363" t="s">
         <v>27</v>
@@ -8165,13 +8159,13 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D364" t="s">
-        <v>181</v>
+        <v>75</v>
       </c>
       <c r="E364" t="s">
         <v>27</v>
@@ -8182,13 +8176,13 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D365" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="E365" t="s">
         <v>27</v>
@@ -8199,13 +8193,13 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D366" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="E366" t="s">
         <v>27</v>
@@ -8216,13 +8210,13 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D367" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="E367" t="s">
         <v>27</v>
@@ -8233,13 +8227,13 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D368" t="s">
-        <v>343</v>
+        <v>94</v>
       </c>
       <c r="E368" t="s">
         <v>27</v>
@@ -8250,13 +8244,13 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D369" t="s">
-        <v>189</v>
+        <v>139</v>
       </c>
       <c r="E369" t="s">
         <v>27</v>
@@ -8267,13 +8261,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D370" t="s">
-        <v>196</v>
+        <v>38</v>
       </c>
       <c r="E370" t="s">
         <v>27</v>
@@ -8284,13 +8278,13 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D371" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="E371" t="s">
         <v>27</v>
@@ -8301,13 +8295,13 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D372" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="E372" t="s">
         <v>27</v>
@@ -8318,13 +8312,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D373" t="s">
-        <v>181</v>
+        <v>219</v>
       </c>
       <c r="E373" t="s">
         <v>27</v>
@@ -8335,13 +8329,13 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D374" t="s">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="E374" t="s">
         <v>27</v>
@@ -8352,13 +8346,13 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D375" t="s">
-        <v>207</v>
+        <v>262</v>
       </c>
       <c r="E375" t="s">
         <v>27</v>
@@ -8369,13 +8363,13 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D376" t="s">
-        <v>237</v>
+        <v>92</v>
       </c>
       <c r="E376" t="s">
         <v>27</v>
@@ -8386,13 +8380,13 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D377" t="s">
-        <v>88</v>
+        <v>217</v>
       </c>
       <c r="E377" t="s">
         <v>27</v>
@@ -8403,13 +8397,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D378" t="s">
-        <v>212</v>
+        <v>84</v>
       </c>
       <c r="E378" t="s">
         <v>27</v>
@@ -8420,13 +8414,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C379" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D379" t="s">
-        <v>74</v>
+        <v>239</v>
       </c>
       <c r="E379" t="s">
         <v>27</v>
@@ -8437,13 +8431,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D380" t="s">
-        <v>143</v>
+        <v>57</v>
       </c>
       <c r="E380" t="s">
         <v>27</v>
@@ -8454,13 +8448,13 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C381" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D381" t="s">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="E381" t="s">
         <v>27</v>
@@ -8471,13 +8465,13 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D382" t="s">
-        <v>198</v>
+        <v>54</v>
       </c>
       <c r="E382" t="s">
         <v>27</v>
@@ -8488,13 +8482,13 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D383" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="E383" t="s">
         <v>27</v>
@@ -8505,13 +8499,13 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D384" t="s">
-        <v>428</v>
+        <v>173</v>
       </c>
       <c r="E384" t="s">
         <v>27</v>
@@ -8522,13 +8516,13 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D385" t="s">
-        <v>491</v>
+        <v>60</v>
       </c>
       <c r="E385" t="s">
         <v>27</v>
@@ -8539,13 +8533,13 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D386" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="E386" t="s">
         <v>27</v>
@@ -8556,13 +8550,13 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D387" t="s">
-        <v>143</v>
+        <v>223</v>
       </c>
       <c r="E387" t="s">
         <v>27</v>
@@ -8573,13 +8567,13 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D388" t="s">
-        <v>176</v>
+        <v>123</v>
       </c>
       <c r="E388" t="s">
         <v>27</v>
@@ -8590,13 +8584,13 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D389" t="s">
-        <v>52</v>
+        <v>131</v>
       </c>
       <c r="E389" t="s">
         <v>27</v>
@@ -8607,13 +8601,13 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D390" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="E390" t="s">
         <v>27</v>
@@ -8624,13 +8618,13 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D391" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="E391" t="s">
         <v>27</v>
@@ -8641,13 +8635,13 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D392" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E392" t="s">
         <v>27</v>
@@ -8658,13 +8652,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D393" t="s">
-        <v>116</v>
+        <v>244</v>
       </c>
       <c r="E393" t="s">
         <v>27</v>
@@ -8675,13 +8669,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D394" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E394" t="s">
         <v>27</v>
@@ -8692,13 +8686,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D395" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E395" t="s">
         <v>27</v>
@@ -8709,13 +8703,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D396" t="s">
-        <v>140</v>
+        <v>249</v>
       </c>
       <c r="E396" t="s">
         <v>27</v>
@@ -8726,13 +8720,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D397" t="s">
-        <v>227</v>
+        <v>326</v>
       </c>
       <c r="E397" t="s">
         <v>27</v>
@@ -8743,13 +8737,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D398" t="s">
-        <v>196</v>
+        <v>144</v>
       </c>
       <c r="E398" t="s">
         <v>27</v>
@@ -8760,13 +8754,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D399" t="s">
-        <v>82</v>
+        <v>244</v>
       </c>
       <c r="E399" t="s">
         <v>27</v>
@@ -8777,13 +8771,13 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D400" t="s">
-        <v>491</v>
+        <v>162</v>
       </c>
       <c r="E400" t="s">
         <v>27</v>
@@ -8794,13 +8788,13 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D401" t="s">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="E401" t="s">
         <v>27</v>
@@ -8819,47 +8813,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B3" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B5" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B6">
         <v>400</v>
@@ -8867,7 +8861,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B7">
         <v>391</v>
@@ -8875,7 +8869,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B8">
         <v>9</v>
@@ -8883,7 +8877,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8891,10 +8885,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B10" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>

--- a/reports/selenium/Excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/Excel/Automation_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="523">
   <si>
     <t>#</t>
   </si>
@@ -35,61 +35,61 @@
     <t>FAILED</t>
   </si>
   <si>
+    <t>20.62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landing page did not load — Sign In button not found
+Wait timed out after 20043ms</t>
+  </si>
+  <si>
+    <t>should navigate to the login form</t>
+  </si>
+  <si>
     <t>20.74</t>
   </si>
   <si>
-    <t xml:space="preserve">Landing page did not load — Sign In button not found
-Wait timed out after 20193ms</t>
-  </si>
-  <si>
-    <t>should navigate to the login form</t>
-  </si>
-  <si>
-    <t>20.54</t>
-  </si>
-  <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20180ms</t>
+Wait timed out after 20065ms</t>
   </si>
   <si>
     <t>should login with valid credentials and reach the dashboard</t>
   </si>
   <si>
-    <t>20.53</t>
+    <t>20.47</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20157ms</t>
+Wait timed out after 20016ms</t>
   </si>
   <si>
     <t>should reject invalid credentials with an error message</t>
   </si>
   <si>
-    <t>20.66</t>
+    <t>20.75</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20194ms</t>
+Wait timed out after 20044ms</t>
   </si>
   <si>
     <t>should open the sign-up form from landing</t>
   </si>
   <si>
-    <t>20.70</t>
+    <t>20.46</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signup-btn"])
-Wait timed out after 20005ms</t>
+Wait timed out after 20020ms</t>
   </si>
   <si>
     <t>Security — should reject login for invalid credentials</t>
   </si>
   <si>
-    <t>20.56</t>
+    <t>20.63</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20000ms</t>
+Wait timed out after 20054ms</t>
   </si>
   <si>
     <t>Security — should prevent access to protected routes/dashboard for unauthenticated users</t>
@@ -98,7 +98,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>3.78</t>
+    <t>3.57</t>
   </si>
   <si>
     <t/>
@@ -107,1239 +107,1242 @@
     <t>Security — should not execute XSS script payloads submitted in login fields</t>
   </si>
   <si>
+    <t>20.39</t>
+  </si>
+  <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20186ms</t>
+Wait timed out after 20020ms</t>
   </si>
   <si>
     <t>Security — should enforce session termination and clean storage upon logout</t>
   </si>
   <si>
-    <t>20.90</t>
+    <t>20.38</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20201ms</t>
+Wait timed out after 20012ms</t>
   </si>
   <si>
     <t>Security — should confirm Firebase authentication rejects empty credentials</t>
   </si>
   <si>
+    <t>20.80</t>
+  </si>
+  <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20171ms</t>
+Wait timed out after 20068ms</t>
   </si>
   <si>
     <t>Security — should not expose sensitive API keys or secrets in page HTML source</t>
   </si>
   <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #11)</t>
+  </si>
+  <si>
+    <t>0.86</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #12)</t>
+  </si>
+  <si>
+    <t>0.45</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #13)</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #14)</t>
+  </si>
+  <si>
+    <t>0.59</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #15)</t>
+  </si>
+  <si>
+    <t>0.88</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #16)</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #17)</t>
+  </si>
+  <si>
+    <t>0.63</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #18)</t>
+  </si>
+  <si>
+    <t>0.47</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #19)</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #20)</t>
+  </si>
+  <si>
+    <t>0.76</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #21)</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #22)</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #23)</t>
+  </si>
+  <si>
+    <t>0.82</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #24)</t>
+  </si>
+  <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #25)</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #26)</t>
+  </si>
+  <si>
+    <t>0.46</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #27)</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #28)</t>
+  </si>
+  <si>
+    <t>0.81</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #29)</t>
+  </si>
+  <si>
+    <t>0.77</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #30)</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #31)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #32)</t>
+  </si>
+  <si>
+    <t>0.97</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #33)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #34)</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #35)</t>
+  </si>
+  <si>
+    <t>0.32</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #36)</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #37)</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #38)</t>
+  </si>
+  <si>
+    <t>0.54</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #39)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #40)</t>
+  </si>
+  <si>
+    <t>0.73</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #41)</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #42)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #43)</t>
+  </si>
+  <si>
+    <t>0.66</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #44)</t>
+  </si>
+  <si>
+    <t>0.99</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #45)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #46)</t>
+  </si>
+  <si>
+    <t>0.30</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #47)</t>
+  </si>
+  <si>
+    <t>0.91</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #48)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #49)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #50)</t>
+  </si>
+  <si>
+    <t>0.38</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #51)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #52)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #53)</t>
+  </si>
+  <si>
+    <t>0.65</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #54)</t>
+  </si>
+  <si>
+    <t>0.72</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #55)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #56)</t>
+  </si>
+  <si>
+    <t>0.67</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #57)</t>
+  </si>
+  <si>
+    <t>0.69</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #58)</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #59)</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #60)</t>
+  </si>
+  <si>
+    <t>0.40</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #61)</t>
+  </si>
+  <si>
+    <t>0.70</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #62)</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #63)</t>
+  </si>
+  <si>
+    <t>0.55</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #64)</t>
+  </si>
+  <si>
+    <t>0.68</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #65)</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #66)</t>
+  </si>
+  <si>
+    <t>0.80</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #67)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #68)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #69)</t>
+  </si>
+  <si>
+    <t>0.79</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #70)</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #71)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #72)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #73)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #74)</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #75)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #76)</t>
+  </si>
+  <si>
+    <t>0.52</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #77)</t>
+  </si>
+  <si>
+    <t>0.49</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #78)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #79)</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #80)</t>
+  </si>
+  <si>
+    <t>0.48</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #81)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #82)</t>
+  </si>
+  <si>
+    <t>0.60</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #83)</t>
+  </si>
+  <si>
+    <t>0.96</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #84)</t>
+  </si>
+  <si>
+    <t>0.78</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #85)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #86)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #87)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #88)</t>
+  </si>
+  <si>
+    <t>0.28</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #89)</t>
+  </si>
+  <si>
+    <t>0.83</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #90)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #91)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #92)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #93)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #94)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #95)</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #96)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #97)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #98)</t>
+  </si>
+  <si>
+    <t>0.44</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #99)</t>
+  </si>
+  <si>
+    <t>0.87</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #100)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #101)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #102)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #103)</t>
+  </si>
+  <si>
+    <t>0.29</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #104)</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #105)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #106)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #107)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #108)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #109)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #110)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #111)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #112)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #113)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #114)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #115)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #116)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #117)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #118)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #119)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #120)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #121)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #122)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #123)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #124)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #125)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #126)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #127)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #128)</t>
+  </si>
+  <si>
+    <t>0.93</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #129)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #130)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #131)</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #132)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #133)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #134)</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #135)</t>
+  </si>
+  <si>
+    <t>0.90</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #136)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #137)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #138)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #139)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #140)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #141)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #142)</t>
+  </si>
+  <si>
+    <t>0.92</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #143)</t>
+  </si>
+  <si>
+    <t>0.31</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #144)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #145)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #146)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #147)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #148)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #149)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #150)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #151)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #152)</t>
+  </si>
+  <si>
+    <t>0.61</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #153)</t>
+  </si>
+  <si>
+    <t>0.89</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #154)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #155)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #156)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #157)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #158)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #159)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #160)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #161)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #162)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #163)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #164)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #165)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #166)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #167)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #168)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #169)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #170)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #171)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #172)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #173)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #174)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #175)</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #176)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #177)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #178)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #179)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #180)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #181)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #182)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #183)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #184)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #185)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #186)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #187)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #188)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #189)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #190)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #191)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #192)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #193)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #194)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #195)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #196)</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #197)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #198)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #199)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #200)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #201)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #202)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #203)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #204)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #205)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #206)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #207)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #208)</t>
+  </si>
+  <si>
     <t>0.84</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #11)</t>
-  </si>
-  <si>
-    <t>0.72</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #12)</t>
-  </si>
-  <si>
-    <t>0.25</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #13)</t>
-  </si>
-  <si>
-    <t>0.58</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #14)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #15)</t>
-  </si>
-  <si>
-    <t>0.46</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #16)</t>
-  </si>
-  <si>
-    <t>0.32</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #17)</t>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #209)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #210)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #211)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #212)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #213)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #214)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #215)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #216)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #217)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #218)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #219)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #220)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #221)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #222)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #223)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #224)</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #225)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #226)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #227)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #228)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #229)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #230)</t>
   </si>
   <si>
     <t>0.41</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #18)</t>
-  </si>
-  <si>
-    <t>0.42</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #19)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #20)</t>
-  </si>
-  <si>
-    <t>0.98</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #21)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #22)</t>
-  </si>
-  <si>
-    <t>0.95</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #23)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #24)</t>
-  </si>
-  <si>
-    <t>0.23</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #25)</t>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #231)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #232)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #233)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #234)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #235)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #236)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #237)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #238)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #239)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #240)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #241)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #242)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #243)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #244)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #245)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #246)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #247)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #248)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #249)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #250)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #251)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #252)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #253)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #254)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #255)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #256)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #257)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #258)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #259)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #260)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #261)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #262)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #263)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #264)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #265)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #266)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #267)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #268)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #269)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #270)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #271)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #272)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #273)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #274)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #275)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #276)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #277)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #278)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #279)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #280)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #281)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #282)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #283)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #284)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #285)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #286)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #287)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #288)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #289)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #290)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #291)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #292)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #293)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #294)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #295)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #296)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #297)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #298)</t>
+  </si>
+  <si>
+    <t>0.37</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #299)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #300)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #301)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #302)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #303)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #304)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #305)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #306)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #307)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #308)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #309)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #310)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #311)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #312)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #313)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #314)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #315)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #316)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #317)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #318)</t>
   </si>
   <si>
     <t>0.71</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #26)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #27)</t>
-  </si>
-  <si>
-    <t>0.20</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #28)</t>
-  </si>
-  <si>
-    <t>0.68</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #29)</t>
-  </si>
-  <si>
-    <t>0.52</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #30)</t>
-  </si>
-  <si>
-    <t>0.70</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #31)</t>
-  </si>
-  <si>
-    <t>0.30</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #32)</t>
-  </si>
-  <si>
-    <t>0.36</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #33)</t>
-  </si>
-  <si>
-    <t>0.27</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #34)</t>
-  </si>
-  <si>
-    <t>0.63</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #35)</t>
-  </si>
-  <si>
-    <t>0.26</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #36)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #37)</t>
-  </si>
-  <si>
-    <t>0.90</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #38)</t>
-  </si>
-  <si>
-    <t>0.44</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #39)</t>
-  </si>
-  <si>
-    <t>0.77</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #40)</t>
-  </si>
-  <si>
-    <t>0.88</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #41)</t>
-  </si>
-  <si>
-    <t>0.80</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #42)</t>
-  </si>
-  <si>
-    <t>0.67</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #43)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #44)</t>
-  </si>
-  <si>
-    <t>0.94</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #45)</t>
-  </si>
-  <si>
-    <t>0.86</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #46)</t>
-  </si>
-  <si>
-    <t>0.35</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #47)</t>
-  </si>
-  <si>
-    <t>0.57</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #48)</t>
-  </si>
-  <si>
-    <t>0.79</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #49)</t>
-  </si>
-  <si>
-    <t>0.47</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #50)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #51)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #52)</t>
-  </si>
-  <si>
-    <t>0.61</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #53)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #54)</t>
-  </si>
-  <si>
-    <t>0.65</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #55)</t>
-  </si>
-  <si>
-    <t>0.38</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #56)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #57)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #58)</t>
-  </si>
-  <si>
-    <t>0.43</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #59)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #60)</t>
-  </si>
-  <si>
-    <t>0.56</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #61)</t>
-  </si>
-  <si>
-    <t>0.89</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #62)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #63)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #64)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #65)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #66)</t>
-  </si>
-  <si>
-    <t>0.29</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #67)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #68)</t>
-  </si>
-  <si>
-    <t>0.97</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #69)</t>
-  </si>
-  <si>
-    <t>0.62</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #70)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #71)</t>
-  </si>
-  <si>
-    <t>0.93</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #72)</t>
-  </si>
-  <si>
-    <t>0.31</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #73)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #74)</t>
-  </si>
-  <si>
-    <t>0.81</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #75)</t>
-  </si>
-  <si>
-    <t>0.83</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #76)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #77)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #78)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #79)</t>
-  </si>
-  <si>
-    <t>0.76</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #80)</t>
-  </si>
-  <si>
-    <t>0.73</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #81)</t>
-  </si>
-  <si>
-    <t>0.96</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #82)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #83)</t>
-  </si>
-  <si>
-    <t>0.48</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #84)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #85)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #86)</t>
-  </si>
-  <si>
-    <t>0.37</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #87)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #88)</t>
-  </si>
-  <si>
-    <t>0.91</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #89)</t>
-  </si>
-  <si>
-    <t>0.92</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #90)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #91)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #92)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #93)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #94)</t>
-  </si>
-  <si>
-    <t>0.24</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #95)</t>
-  </si>
-  <si>
-    <t>0.51</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #96)</t>
-  </si>
-  <si>
-    <t>0.85</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #97)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #98)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #99)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #100)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #101)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #102)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #103)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #104)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #105)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #106)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #107)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #108)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #109)</t>
-  </si>
-  <si>
-    <t>0.28</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #110)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #111)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #112)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #113)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #114)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #115)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #116)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #117)</t>
-  </si>
-  <si>
-    <t>0.59</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #118)</t>
-  </si>
-  <si>
-    <t>0.75</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #119)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #120)</t>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #319)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #320)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #321)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #322)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #323)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #324)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #325)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #326)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #327)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #328)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #329)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #330)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #331)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #332)</t>
   </si>
   <si>
     <t>0.53</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #121)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #122)</t>
-  </si>
-  <si>
-    <t>0.99</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #123)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #124)</t>
-  </si>
-  <si>
-    <t>0.64</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #125)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #126)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #127)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #128)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #129)</t>
-  </si>
-  <si>
-    <t>0.33</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #130)</t>
-  </si>
-  <si>
-    <t>0.82</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #131)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #132)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #133)</t>
-  </si>
-  <si>
-    <t>0.69</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #134)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #135)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #136)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #137)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #138)</t>
-  </si>
-  <si>
-    <t>0.66</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #139)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #140)</t>
-  </si>
-  <si>
-    <t>0.87</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #141)</t>
-  </si>
-  <si>
-    <t>0.39</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #142)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #143)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #144)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #145)</t>
-  </si>
-  <si>
-    <t>0.74</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #146)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #147)</t>
-  </si>
-  <si>
-    <t>0.34</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #148)</t>
-  </si>
-  <si>
-    <t>0.22</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #149)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #150)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #151)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #152)</t>
-  </si>
-  <si>
-    <t>0.60</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #153)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #154)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #155)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #156)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #157)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #158)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #159)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #160)</t>
-  </si>
-  <si>
-    <t>1.00</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #161)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #162)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #163)</t>
-  </si>
-  <si>
-    <t>0.55</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #164)</t>
-  </si>
-  <si>
-    <t>0.54</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #165)</t>
-  </si>
-  <si>
-    <t>0.49</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #166)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #167)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #168)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #169)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #170)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #171)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #172)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #173)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #174)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #175)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #176)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #177)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #178)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #179)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #180)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #181)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #182)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #183)</t>
-  </si>
-  <si>
-    <t>0.21</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #184)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #185)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #186)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #187)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #188)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #189)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #190)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #191)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #192)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #193)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #194)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #195)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #196)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #197)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #198)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #199)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #200)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #201)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #202)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #203)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #204)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #205)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #206)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #207)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #208)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #209)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #210)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #211)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #212)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #213)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #214)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #215)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #216)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #217)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #218)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #219)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #220)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #221)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #222)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #223)</t>
-  </si>
-  <si>
-    <t>0.45</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #224)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #225)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #226)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #227)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #228)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #229)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #230)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #231)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #232)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #233)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #234)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #235)</t>
-  </si>
-  <si>
-    <t>0.78</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #236)</t>
-  </si>
-  <si>
-    <t>0.40</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #237)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #238)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #239)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #240)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #241)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #242)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #243)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #244)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #245)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #246)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #247)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #248)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #249)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #250)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #251)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #252)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #253)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #254)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #255)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #256)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #257)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #258)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #259)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #260)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #261)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #262)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #263)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #264)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #265)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #266)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #267)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #268)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #269)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #270)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #271)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #272)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #273)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #274)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #275)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #276)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #277)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #278)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #279)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #280)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #281)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #282)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #283)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #284)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #285)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #286)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #287)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #288)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #289)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #290)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #291)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #292)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #293)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #294)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #295)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #296)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #297)</t>
-  </si>
-  <si>
-    <t>0.50</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #298)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #299)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #300)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #301)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #302)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #303)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #304)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #305)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #306)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #307)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #308)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #309)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #310)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #311)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #312)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #313)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #314)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #315)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #316)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #317)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #318)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #319)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #320)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #321)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #322)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #323)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #324)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #325)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #326)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #327)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #328)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #329)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #330)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #331)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #332)</t>
-  </si>
-  <si>
     <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #333)</t>
   </si>
   <si>
@@ -1550,13 +1553,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>12</t>
+    <t>14</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 13:24:39 UTC</t>
+    <t>2026-06-23 13:45:38 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1568,7 +1571,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>cfbb4d3</t>
+    <t>3eb8262</t>
   </si>
   <si>
     <t>Total</t>
@@ -2130,10 +2133,10 @@
         <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2141,16 +2144,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2158,16 +2161,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2175,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
         <v>27</v>
@@ -2192,13 +2195,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E13" t="s">
         <v>27</v>
@@ -2209,13 +2212,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E14" t="s">
         <v>27</v>
@@ -2226,13 +2229,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s">
         <v>27</v>
@@ -2243,13 +2246,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E16" t="s">
         <v>27</v>
@@ -2260,13 +2263,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E17" t="s">
         <v>27</v>
@@ -2277,13 +2280,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E18" t="s">
         <v>27</v>
@@ -2294,13 +2297,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E19" t="s">
         <v>27</v>
@@ -2311,13 +2314,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E20" t="s">
         <v>27</v>
@@ -2328,13 +2331,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
         <v>27</v>
@@ -2345,13 +2348,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E22" t="s">
         <v>27</v>
@@ -2362,13 +2365,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E23" t="s">
         <v>27</v>
@@ -2379,13 +2382,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E24" t="s">
         <v>27</v>
@@ -2396,13 +2399,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="E25" t="s">
         <v>27</v>
@@ -2413,13 +2416,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E26" t="s">
         <v>27</v>
@@ -2430,13 +2433,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E27" t="s">
         <v>27</v>
@@ -2447,13 +2450,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="E28" t="s">
         <v>27</v>
@@ -2464,13 +2467,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E29" t="s">
         <v>27</v>
@@ -2481,13 +2484,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
         <v>27</v>
@@ -2498,13 +2501,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E31" t="s">
         <v>27</v>
@@ -2515,13 +2518,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E32" t="s">
         <v>27</v>
@@ -2532,13 +2535,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D33" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="E33" t="s">
         <v>27</v>
@@ -2549,13 +2552,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D34" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E34" t="s">
         <v>27</v>
@@ -2566,13 +2569,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="E35" t="s">
         <v>27</v>
@@ -2583,13 +2586,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E36" t="s">
         <v>27</v>
@@ -2600,13 +2603,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E37" t="s">
         <v>27</v>
@@ -2617,13 +2620,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D38" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="E38" t="s">
         <v>27</v>
@@ -2634,13 +2637,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E39" t="s">
         <v>27</v>
@@ -2651,13 +2654,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E40" t="s">
         <v>27</v>
@@ -2668,13 +2671,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D41" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="E41" t="s">
         <v>27</v>
@@ -2685,13 +2688,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D42" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E42" t="s">
         <v>27</v>
@@ -2702,13 +2705,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E43" t="s">
         <v>27</v>
@@ -2719,13 +2722,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="E44" t="s">
         <v>27</v>
@@ -2736,13 +2739,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="E45" t="s">
         <v>27</v>
@@ -2753,13 +2756,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E46" t="s">
         <v>27</v>
@@ -2770,13 +2773,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="E47" t="s">
         <v>27</v>
@@ -2787,13 +2790,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E48" t="s">
         <v>27</v>
@@ -2804,13 +2807,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E49" t="s">
         <v>27</v>
@@ -2821,13 +2824,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="E50" t="s">
         <v>27</v>
@@ -2838,13 +2841,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D51" t="s">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="E51" t="s">
         <v>27</v>
@@ -2855,13 +2858,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="E52" t="s">
         <v>27</v>
@@ -2872,13 +2875,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="E53" t="s">
         <v>27</v>
@@ -2889,13 +2892,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="E54" t="s">
         <v>27</v>
@@ -2906,13 +2909,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D55" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E55" t="s">
         <v>27</v>
@@ -2923,13 +2926,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D56" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E56" t="s">
         <v>27</v>
@@ -2940,13 +2943,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D57" t="s">
-        <v>116</v>
+        <v>52</v>
       </c>
       <c r="E57" t="s">
         <v>27</v>
@@ -2957,13 +2960,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D58" t="s">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="E58" t="s">
         <v>27</v>
@@ -2974,13 +2977,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D59" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E59" t="s">
         <v>27</v>
@@ -2991,13 +2994,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D60" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E60" t="s">
         <v>27</v>
@@ -3008,13 +3011,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="E61" t="s">
         <v>27</v>
@@ -3025,13 +3028,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D62" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E62" t="s">
         <v>27</v>
@@ -3042,13 +3045,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D63" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E63" t="s">
         <v>27</v>
@@ -3059,13 +3062,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D64" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="E64" t="s">
         <v>27</v>
@@ -3076,13 +3079,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="E65" t="s">
         <v>27</v>
@@ -3093,13 +3096,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D66" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="E66" t="s">
         <v>27</v>
@@ -3110,13 +3113,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D67" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="E67" t="s">
         <v>27</v>
@@ -3127,13 +3130,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D68" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E68" t="s">
         <v>27</v>
@@ -3144,13 +3147,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D69" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="E69" t="s">
         <v>27</v>
@@ -3161,13 +3164,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D70" t="s">
-        <v>134</v>
+        <v>42</v>
       </c>
       <c r="E70" t="s">
         <v>27</v>
@@ -3178,13 +3181,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D71" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E71" t="s">
         <v>27</v>
@@ -3195,13 +3198,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D72" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="E72" t="s">
         <v>27</v>
@@ -3212,13 +3215,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D73" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="E73" t="s">
         <v>27</v>
@@ -3229,13 +3232,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D74" t="s">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="E74" t="s">
         <v>27</v>
@@ -3246,13 +3249,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D75" t="s">
-        <v>131</v>
+        <v>68</v>
       </c>
       <c r="E75" t="s">
         <v>27</v>
@@ -3263,13 +3266,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D76" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E76" t="s">
         <v>27</v>
@@ -3280,13 +3283,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D77" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="E77" t="s">
         <v>27</v>
@@ -3297,13 +3300,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>94</v>
+        <v>154</v>
       </c>
       <c r="E78" t="s">
         <v>27</v>
@@ -3314,13 +3317,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D79" t="s">
-        <v>67</v>
+        <v>156</v>
       </c>
       <c r="E79" t="s">
         <v>27</v>
@@ -3331,13 +3334,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D80" t="s">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="E80" t="s">
         <v>27</v>
@@ -3348,13 +3351,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D81" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E81" t="s">
         <v>27</v>
@@ -3365,13 +3368,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D82" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="E82" t="s">
         <v>27</v>
@@ -3382,13 +3385,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D83" t="s">
-        <v>155</v>
+        <v>56</v>
       </c>
       <c r="E83" t="s">
         <v>27</v>
@@ -3399,13 +3402,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D84" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="E84" t="s">
         <v>27</v>
@@ -3416,13 +3419,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D85" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="E85" t="s">
         <v>27</v>
@@ -3433,13 +3436,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D86" t="s">
-        <v>62</v>
+        <v>168</v>
       </c>
       <c r="E86" t="s">
         <v>27</v>
@@ -3450,13 +3453,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D87" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="E87" t="s">
         <v>27</v>
@@ -3467,13 +3470,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D88" t="s">
-        <v>162</v>
+        <v>40</v>
       </c>
       <c r="E88" t="s">
         <v>27</v>
@@ -3484,13 +3487,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D89" t="s">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="E89" t="s">
         <v>27</v>
@@ -3501,13 +3504,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D90" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="E90" t="s">
         <v>27</v>
@@ -3518,13 +3521,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D91" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E91" t="s">
         <v>27</v>
@@ -3535,13 +3538,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D92" t="s">
-        <v>105</v>
+        <v>156</v>
       </c>
       <c r="E92" t="s">
         <v>27</v>
@@ -3552,13 +3555,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D93" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E93" t="s">
         <v>27</v>
@@ -3569,13 +3572,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D94" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E94" t="s">
         <v>27</v>
@@ -3586,13 +3589,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D95" t="s">
-        <v>65</v>
+        <v>173</v>
       </c>
       <c r="E95" t="s">
         <v>27</v>
@@ -3603,13 +3606,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D96" t="s">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="E96" t="s">
         <v>27</v>
@@ -3620,13 +3623,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D97" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="E97" t="s">
         <v>27</v>
@@ -3637,13 +3640,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D98" t="s">
-        <v>177</v>
+        <v>88</v>
       </c>
       <c r="E98" t="s">
         <v>27</v>
@@ -3654,13 +3657,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D99" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="E99" t="s">
         <v>27</v>
@@ -3671,13 +3674,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D100" t="s">
-        <v>90</v>
+        <v>186</v>
       </c>
       <c r="E100" t="s">
         <v>27</v>
@@ -3688,13 +3691,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>65</v>
+        <v>188</v>
       </c>
       <c r="E101" t="s">
         <v>27</v>
@@ -3705,13 +3708,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D102" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
       <c r="E102" t="s">
         <v>27</v>
@@ -3722,13 +3725,13 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D103" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="E103" t="s">
         <v>27</v>
@@ -3739,13 +3742,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D104" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="E104" t="s">
         <v>27</v>
@@ -3756,13 +3759,13 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D105" t="s">
-        <v>94</v>
+        <v>193</v>
       </c>
       <c r="E105" t="s">
         <v>27</v>
@@ -3773,13 +3776,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D106" t="s">
-        <v>38</v>
+        <v>195</v>
       </c>
       <c r="E106" t="s">
         <v>27</v>
@@ -3790,13 +3793,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D107" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E107" t="s">
         <v>27</v>
@@ -3807,13 +3810,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D108" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E108" t="s">
         <v>27</v>
@@ -3824,13 +3827,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D109" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="E109" t="s">
         <v>27</v>
@@ -3841,13 +3844,13 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D110" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="E110" t="s">
         <v>27</v>
@@ -3858,13 +3861,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D111" t="s">
-        <v>191</v>
+        <v>100</v>
       </c>
       <c r="E111" t="s">
         <v>27</v>
@@ -3875,13 +3878,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D112" t="s">
-        <v>155</v>
+        <v>117</v>
       </c>
       <c r="E112" t="s">
         <v>27</v>
@@ -3892,13 +3895,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D113" t="s">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E113" t="s">
         <v>27</v>
@@ -3909,13 +3912,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D114" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="E114" t="s">
         <v>27</v>
@@ -3926,13 +3929,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D115" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E115" t="s">
         <v>27</v>
@@ -3943,13 +3946,13 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D116" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="E116" t="s">
         <v>27</v>
@@ -3960,13 +3963,13 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D117" t="s">
-        <v>92</v>
+        <v>173</v>
       </c>
       <c r="E117" t="s">
         <v>27</v>
@@ -3977,13 +3980,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D118" t="s">
-        <v>191</v>
+        <v>122</v>
       </c>
       <c r="E118" t="s">
         <v>27</v>
@@ -3994,13 +3997,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D119" t="s">
-        <v>200</v>
+        <v>159</v>
       </c>
       <c r="E119" t="s">
         <v>27</v>
@@ -4011,13 +4014,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D120" t="s">
-        <v>202</v>
+        <v>76</v>
       </c>
       <c r="E120" t="s">
         <v>27</v>
@@ -4028,13 +4031,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D121" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="E121" t="s">
         <v>27</v>
@@ -4045,13 +4048,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D122" t="s">
-        <v>205</v>
+        <v>120</v>
       </c>
       <c r="E122" t="s">
         <v>27</v>
@@ -4062,13 +4065,13 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D123" t="s">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="E123" t="s">
         <v>27</v>
@@ -4079,13 +4082,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D124" t="s">
-        <v>208</v>
+        <v>90</v>
       </c>
       <c r="E124" t="s">
         <v>27</v>
@@ -4096,13 +4099,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D125" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="E125" t="s">
         <v>27</v>
@@ -4113,13 +4116,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D126" t="s">
-        <v>211</v>
+        <v>146</v>
       </c>
       <c r="E126" t="s">
         <v>27</v>
@@ -4130,13 +4133,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D127" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="E127" t="s">
         <v>27</v>
@@ -4147,13 +4150,13 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D128" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="E128" t="s">
         <v>27</v>
@@ -4164,13 +4167,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D129" t="s">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="E129" t="s">
         <v>27</v>
@@ -4181,13 +4184,13 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D130" t="s">
-        <v>42</v>
+        <v>220</v>
       </c>
       <c r="E130" t="s">
         <v>27</v>
@@ -4198,13 +4201,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D131" t="s">
-        <v>217</v>
+        <v>115</v>
       </c>
       <c r="E131" t="s">
         <v>27</v>
@@ -4215,13 +4218,13 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D132" t="s">
-        <v>219</v>
+        <v>134</v>
       </c>
       <c r="E132" t="s">
         <v>27</v>
@@ -4232,13 +4235,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D133" t="s">
-        <v>54</v>
+        <v>224</v>
       </c>
       <c r="E133" t="s">
         <v>27</v>
@@ -4249,13 +4252,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D134" t="s">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="E134" t="s">
         <v>27</v>
@@ -4266,13 +4269,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D135" t="s">
-        <v>223</v>
+        <v>92</v>
       </c>
       <c r="E135" t="s">
         <v>27</v>
@@ -4283,13 +4286,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D136" t="s">
-        <v>99</v>
+        <v>228</v>
       </c>
       <c r="E136" t="s">
         <v>27</v>
@@ -4300,13 +4303,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D137" t="s">
-        <v>165</v>
+        <v>230</v>
       </c>
       <c r="E137" t="s">
         <v>27</v>
@@ -4317,13 +4320,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D138" t="s">
-        <v>177</v>
+        <v>230</v>
       </c>
       <c r="E138" t="s">
         <v>27</v>
@@ -4334,13 +4337,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D139" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="E139" t="s">
         <v>27</v>
@@ -4351,13 +4354,13 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D140" t="s">
-        <v>229</v>
+        <v>84</v>
       </c>
       <c r="E140" t="s">
         <v>27</v>
@@ -4368,13 +4371,13 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D141" t="s">
-        <v>229</v>
+        <v>122</v>
       </c>
       <c r="E141" t="s">
         <v>27</v>
@@ -4385,13 +4388,13 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D142" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E142" t="s">
         <v>27</v>
@@ -4402,13 +4405,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D143" t="s">
-        <v>234</v>
+        <v>122</v>
       </c>
       <c r="E143" t="s">
         <v>27</v>
@@ -4419,13 +4422,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D144" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="E144" t="s">
         <v>27</v>
@@ -4436,13 +4439,13 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D145" t="s">
-        <v>155</v>
+        <v>240</v>
       </c>
       <c r="E145" t="s">
         <v>27</v>
@@ -4453,13 +4456,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D146" t="s">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="E146" t="s">
         <v>27</v>
@@ -4470,13 +4473,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D147" t="s">
-        <v>239</v>
+        <v>40</v>
       </c>
       <c r="E147" t="s">
         <v>27</v>
@@ -4487,13 +4490,13 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D148" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E148" t="s">
         <v>27</v>
@@ -4504,13 +4507,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D149" t="s">
-        <v>242</v>
+        <v>146</v>
       </c>
       <c r="E149" t="s">
         <v>27</v>
@@ -4521,13 +4524,13 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D150" t="s">
-        <v>244</v>
+        <v>188</v>
       </c>
       <c r="E150" t="s">
         <v>27</v>
@@ -4538,13 +4541,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D151" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E151" t="s">
         <v>27</v>
@@ -4555,13 +4558,13 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D152" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="E152" t="s">
         <v>27</v>
@@ -4572,13 +4575,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D153" t="s">
-        <v>232</v>
+        <v>130</v>
       </c>
       <c r="E153" t="s">
         <v>27</v>
@@ -4589,13 +4592,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D154" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E154" t="s">
         <v>27</v>
@@ -4606,13 +4609,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D155" t="s">
-        <v>173</v>
+        <v>252</v>
       </c>
       <c r="E155" t="s">
         <v>27</v>
@@ -4623,13 +4626,13 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D156" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="E156" t="s">
         <v>27</v>
@@ -4640,13 +4643,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D157" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="E157" t="s">
         <v>27</v>
@@ -4657,13 +4660,13 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D158" t="s">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="E158" t="s">
         <v>27</v>
@@ -4674,13 +4677,13 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D159" t="s">
-        <v>234</v>
+        <v>138</v>
       </c>
       <c r="E159" t="s">
         <v>27</v>
@@ -4691,13 +4694,13 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D160" t="s">
-        <v>217</v>
+        <v>102</v>
       </c>
       <c r="E160" t="s">
         <v>27</v>
@@ -4708,13 +4711,13 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D161" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="E161" t="s">
         <v>27</v>
@@ -4725,13 +4728,13 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D162" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="E162" t="s">
         <v>27</v>
@@ -4742,13 +4745,13 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D163" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E163" t="s">
         <v>27</v>
@@ -4759,13 +4762,13 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D164" t="s">
-        <v>103</v>
+        <v>250</v>
       </c>
       <c r="E164" t="s">
         <v>27</v>
@@ -4776,13 +4779,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D165" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="E165" t="s">
         <v>27</v>
@@ -4799,7 +4802,7 @@
         <v>25</v>
       </c>
       <c r="D166" t="s">
-        <v>264</v>
+        <v>126</v>
       </c>
       <c r="E166" t="s">
         <v>27</v>
@@ -4810,13 +4813,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D167" t="s">
-        <v>266</v>
+        <v>50</v>
       </c>
       <c r="E167" t="s">
         <v>27</v>
@@ -4827,13 +4830,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D168" t="s">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="E168" t="s">
         <v>27</v>
@@ -4844,13 +4847,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D169" t="s">
-        <v>223</v>
+        <v>38</v>
       </c>
       <c r="E169" t="s">
         <v>27</v>
@@ -4861,13 +4864,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D170" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E170" t="s">
         <v>27</v>
@@ -4878,13 +4881,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D171" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="E171" t="s">
         <v>27</v>
@@ -4895,13 +4898,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D172" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="E172" t="s">
         <v>27</v>
@@ -4912,13 +4915,13 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D173" t="s">
-        <v>153</v>
+        <v>193</v>
       </c>
       <c r="E173" t="s">
         <v>27</v>
@@ -4929,13 +4932,13 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D174" t="s">
-        <v>232</v>
+        <v>86</v>
       </c>
       <c r="E174" t="s">
         <v>27</v>
@@ -4946,13 +4949,13 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D175" t="s">
-        <v>234</v>
+        <v>154</v>
       </c>
       <c r="E175" t="s">
         <v>27</v>
@@ -4963,13 +4966,13 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D176" t="s">
-        <v>262</v>
+        <v>68</v>
       </c>
       <c r="E176" t="s">
         <v>27</v>
@@ -4980,13 +4983,13 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D177" t="s">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="E177" t="s">
         <v>27</v>
@@ -4997,13 +5000,13 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D178" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E178" t="s">
         <v>27</v>
@@ -5014,13 +5017,13 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D179" t="s">
-        <v>266</v>
+        <v>111</v>
       </c>
       <c r="E179" t="s">
         <v>27</v>
@@ -5031,13 +5034,13 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D180" t="s">
-        <v>97</v>
+        <v>228</v>
       </c>
       <c r="E180" t="s">
         <v>27</v>
@@ -5048,13 +5051,13 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D181" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="E181" t="s">
         <v>27</v>
@@ -5065,13 +5068,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D182" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E182" t="s">
         <v>27</v>
@@ -5082,13 +5085,13 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D183" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="E183" t="s">
         <v>27</v>
@@ -5099,13 +5102,13 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D184" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="E184" t="s">
         <v>27</v>
@@ -5116,13 +5119,13 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D185" t="s">
-        <v>285</v>
+        <v>122</v>
       </c>
       <c r="E185" t="s">
         <v>27</v>
@@ -5133,13 +5136,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D186" t="s">
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="E186" t="s">
         <v>27</v>
@@ -5150,13 +5153,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D187" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="E187" t="s">
         <v>27</v>
@@ -5167,13 +5170,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D188" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="E188" t="s">
         <v>27</v>
@@ -5184,13 +5187,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D189" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="E189" t="s">
         <v>27</v>
@@ -5201,13 +5204,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D190" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="E190" t="s">
         <v>27</v>
@@ -5218,13 +5221,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D191" t="s">
-        <v>229</v>
+        <v>92</v>
       </c>
       <c r="E191" t="s">
         <v>27</v>
@@ -5235,13 +5238,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D192" t="s">
-        <v>38</v>
+        <v>122</v>
       </c>
       <c r="E192" t="s">
         <v>27</v>
@@ -5252,13 +5255,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D193" t="s">
-        <v>139</v>
+        <v>97</v>
       </c>
       <c r="E193" t="s">
         <v>27</v>
@@ -5269,13 +5272,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D194" t="s">
-        <v>217</v>
+        <v>168</v>
       </c>
       <c r="E194" t="s">
         <v>27</v>
@@ -5286,13 +5289,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D195" t="s">
-        <v>239</v>
+        <v>130</v>
       </c>
       <c r="E195" t="s">
         <v>27</v>
@@ -5303,13 +5306,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D196" t="s">
-        <v>71</v>
+        <v>173</v>
       </c>
       <c r="E196" t="s">
         <v>27</v>
@@ -5320,13 +5323,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D197" t="s">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="E197" t="s">
         <v>27</v>
@@ -5337,13 +5340,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D198" t="s">
-        <v>173</v>
+        <v>297</v>
       </c>
       <c r="E198" t="s">
         <v>27</v>
@@ -5354,13 +5357,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D199" t="s">
-        <v>285</v>
+        <v>48</v>
       </c>
       <c r="E199" t="s">
         <v>27</v>
@@ -5371,13 +5374,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D200" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="E200" t="s">
         <v>27</v>
@@ -5388,13 +5391,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D201" t="s">
-        <v>258</v>
+        <v>54</v>
       </c>
       <c r="E201" t="s">
         <v>27</v>
@@ -5405,13 +5408,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D202" t="s">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="E202" t="s">
         <v>27</v>
@@ -5422,13 +5425,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D203" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="E203" t="s">
         <v>27</v>
@@ -5439,13 +5442,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D204" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E204" t="s">
         <v>27</v>
@@ -5456,13 +5459,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D205" t="s">
-        <v>262</v>
+        <v>42</v>
       </c>
       <c r="E205" t="s">
         <v>27</v>
@@ -5473,13 +5476,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D206" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="E206" t="s">
         <v>27</v>
@@ -5490,13 +5493,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D207" t="s">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="E207" t="s">
         <v>27</v>
@@ -5507,13 +5510,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D208" t="s">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="E208" t="s">
         <v>27</v>
@@ -5524,13 +5527,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D209" t="s">
-        <v>208</v>
+        <v>140</v>
       </c>
       <c r="E209" t="s">
         <v>27</v>
@@ -5541,13 +5544,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
+        <v>309</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D210" t="s">
         <v>310</v>
-      </c>
-      <c r="C210" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D210" t="s">
-        <v>266</v>
       </c>
       <c r="E210" t="s">
         <v>27</v>
@@ -5564,7 +5567,7 @@
         <v>25</v>
       </c>
       <c r="D211" t="s">
-        <v>223</v>
+        <v>90</v>
       </c>
       <c r="E211" t="s">
         <v>27</v>
@@ -5581,7 +5584,7 @@
         <v>25</v>
       </c>
       <c r="D212" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="E212" t="s">
         <v>27</v>
@@ -5598,7 +5601,7 @@
         <v>25</v>
       </c>
       <c r="D213" t="s">
-        <v>167</v>
+        <v>58</v>
       </c>
       <c r="E213" t="s">
         <v>27</v>
@@ -5615,7 +5618,7 @@
         <v>25</v>
       </c>
       <c r="D214" t="s">
-        <v>120</v>
+        <v>193</v>
       </c>
       <c r="E214" t="s">
         <v>27</v>
@@ -5632,7 +5635,7 @@
         <v>25</v>
       </c>
       <c r="D215" t="s">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="E215" t="s">
         <v>27</v>
@@ -5649,7 +5652,7 @@
         <v>25</v>
       </c>
       <c r="D216" t="s">
-        <v>71</v>
+        <v>161</v>
       </c>
       <c r="E216" t="s">
         <v>27</v>
@@ -5666,7 +5669,7 @@
         <v>25</v>
       </c>
       <c r="D217" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E217" t="s">
         <v>27</v>
@@ -5683,7 +5686,7 @@
         <v>25</v>
       </c>
       <c r="D218" t="s">
-        <v>90</v>
+        <v>250</v>
       </c>
       <c r="E218" t="s">
         <v>27</v>
@@ -5700,7 +5703,7 @@
         <v>25</v>
       </c>
       <c r="D219" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="E219" t="s">
         <v>27</v>
@@ -5734,7 +5737,7 @@
         <v>25</v>
       </c>
       <c r="D221" t="s">
-        <v>99</v>
+        <v>182</v>
       </c>
       <c r="E221" t="s">
         <v>27</v>
@@ -5751,7 +5754,7 @@
         <v>25</v>
       </c>
       <c r="D222" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="E222" t="s">
         <v>27</v>
@@ -5768,7 +5771,7 @@
         <v>25</v>
       </c>
       <c r="D223" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E223" t="s">
         <v>27</v>
@@ -5785,7 +5788,7 @@
         <v>25</v>
       </c>
       <c r="D224" t="s">
-        <v>146</v>
+        <v>297</v>
       </c>
       <c r="E224" t="s">
         <v>27</v>
@@ -5802,7 +5805,7 @@
         <v>25</v>
       </c>
       <c r="D225" t="s">
-        <v>326</v>
+        <v>154</v>
       </c>
       <c r="E225" t="s">
         <v>27</v>
@@ -5813,13 +5816,13 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
+        <v>326</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D226" t="s">
         <v>327</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D226" t="s">
-        <v>54</v>
       </c>
       <c r="E226" t="s">
         <v>27</v>
@@ -5836,7 +5839,7 @@
         <v>25</v>
       </c>
       <c r="D227" t="s">
-        <v>71</v>
+        <v>151</v>
       </c>
       <c r="E227" t="s">
         <v>27</v>
@@ -5853,7 +5856,7 @@
         <v>25</v>
       </c>
       <c r="D228" t="s">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="E228" t="s">
         <v>27</v>
@@ -5870,7 +5873,7 @@
         <v>25</v>
       </c>
       <c r="D229" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="E229" t="s">
         <v>27</v>
@@ -5887,7 +5890,7 @@
         <v>25</v>
       </c>
       <c r="D230" t="s">
-        <v>158</v>
+        <v>68</v>
       </c>
       <c r="E230" t="s">
         <v>27</v>
@@ -5904,7 +5907,7 @@
         <v>25</v>
       </c>
       <c r="D231" t="s">
-        <v>205</v>
+        <v>40</v>
       </c>
       <c r="E231" t="s">
         <v>27</v>
@@ -5921,7 +5924,7 @@
         <v>25</v>
       </c>
       <c r="D232" t="s">
-        <v>51</v>
+        <v>334</v>
       </c>
       <c r="E232" t="s">
         <v>27</v>
@@ -5932,13 +5935,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D233" t="s">
-        <v>200</v>
+        <v>54</v>
       </c>
       <c r="E233" t="s">
         <v>27</v>
@@ -5949,13 +5952,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D234" t="s">
-        <v>146</v>
+        <v>64</v>
       </c>
       <c r="E234" t="s">
         <v>27</v>
@@ -5966,13 +5969,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D235" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="E235" t="s">
         <v>27</v>
@@ -5983,13 +5986,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D236" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="E236" t="s">
         <v>27</v>
@@ -6000,13 +6003,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D237" t="s">
-        <v>339</v>
+        <v>220</v>
       </c>
       <c r="E237" t="s">
         <v>27</v>
@@ -6023,7 +6026,7 @@
         <v>25</v>
       </c>
       <c r="D238" t="s">
-        <v>341</v>
+        <v>140</v>
       </c>
       <c r="E238" t="s">
         <v>27</v>
@@ -6034,13 +6037,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D239" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="E239" t="s">
         <v>27</v>
@@ -6051,13 +6054,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D240" t="s">
-        <v>242</v>
+        <v>84</v>
       </c>
       <c r="E240" t="s">
         <v>27</v>
@@ -6068,13 +6071,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D241" t="s">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="E241" t="s">
         <v>27</v>
@@ -6085,13 +6088,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D242" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="E242" t="s">
         <v>27</v>
@@ -6102,13 +6105,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D243" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E243" t="s">
         <v>27</v>
@@ -6119,13 +6122,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D244" t="s">
-        <v>60</v>
+        <v>195</v>
       </c>
       <c r="E244" t="s">
         <v>27</v>
@@ -6136,13 +6139,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D245" t="s">
-        <v>223</v>
+        <v>151</v>
       </c>
       <c r="E245" t="s">
         <v>27</v>
@@ -6153,13 +6156,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D246" t="s">
-        <v>191</v>
+        <v>46</v>
       </c>
       <c r="E246" t="s">
         <v>27</v>
@@ -6170,13 +6173,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D247" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="E247" t="s">
         <v>27</v>
@@ -6187,13 +6190,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D248" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="E248" t="s">
         <v>27</v>
@@ -6204,13 +6207,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D249" t="s">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="E249" t="s">
         <v>27</v>
@@ -6221,13 +6224,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D250" t="s">
-        <v>90</v>
+        <v>188</v>
       </c>
       <c r="E250" t="s">
         <v>27</v>
@@ -6238,13 +6241,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D251" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="E251" t="s">
         <v>27</v>
@@ -6255,13 +6258,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D252" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="E252" t="s">
         <v>27</v>
@@ -6272,13 +6275,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D253" t="s">
-        <v>40</v>
+        <v>334</v>
       </c>
       <c r="E253" t="s">
         <v>27</v>
@@ -6289,13 +6292,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D254" t="s">
-        <v>202</v>
+        <v>111</v>
       </c>
       <c r="E254" t="s">
         <v>27</v>
@@ -6306,13 +6309,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D255" t="s">
-        <v>141</v>
+        <v>186</v>
       </c>
       <c r="E255" t="s">
         <v>27</v>
@@ -6323,13 +6326,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D256" t="s">
-        <v>205</v>
+        <v>88</v>
       </c>
       <c r="E256" t="s">
         <v>27</v>
@@ -6340,13 +6343,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D257" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="E257" t="s">
         <v>27</v>
@@ -6357,13 +6360,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D258" t="s">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E258" t="s">
         <v>27</v>
@@ -6374,13 +6377,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D259" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="E259" t="s">
         <v>27</v>
@@ -6391,13 +6394,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D260" t="s">
-        <v>191</v>
+        <v>240</v>
       </c>
       <c r="E260" t="s">
         <v>27</v>
@@ -6408,13 +6411,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D261" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E261" t="s">
         <v>27</v>
@@ -6425,13 +6428,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D262" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E262" t="s">
         <v>27</v>
@@ -6442,13 +6445,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D263" t="s">
-        <v>94</v>
+        <v>252</v>
       </c>
       <c r="E263" t="s">
         <v>27</v>
@@ -6459,13 +6462,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D264" t="s">
-        <v>69</v>
+        <v>334</v>
       </c>
       <c r="E264" t="s">
         <v>27</v>
@@ -6476,13 +6479,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D265" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="E265" t="s">
         <v>27</v>
@@ -6493,13 +6496,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D266" t="s">
-        <v>219</v>
+        <v>40</v>
       </c>
       <c r="E266" t="s">
         <v>27</v>
@@ -6510,13 +6513,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D267" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E267" t="s">
         <v>27</v>
@@ -6527,13 +6530,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D268" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="E268" t="s">
         <v>27</v>
@@ -6544,13 +6547,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D269" t="s">
-        <v>97</v>
+        <v>228</v>
       </c>
       <c r="E269" t="s">
         <v>27</v>
@@ -6561,13 +6564,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D270" t="s">
-        <v>51</v>
+        <v>134</v>
       </c>
       <c r="E270" t="s">
         <v>27</v>
@@ -6578,13 +6581,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D271" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="E271" t="s">
         <v>27</v>
@@ -6595,13 +6598,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D272" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E272" t="s">
         <v>27</v>
@@ -6612,13 +6615,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D273" t="s">
-        <v>101</v>
+        <v>186</v>
       </c>
       <c r="E273" t="s">
         <v>27</v>
@@ -6629,13 +6632,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D274" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="E274" t="s">
         <v>27</v>
@@ -6646,13 +6649,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D275" t="s">
-        <v>165</v>
+        <v>97</v>
       </c>
       <c r="E275" t="s">
         <v>27</v>
@@ -6663,13 +6666,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D276" t="s">
-        <v>262</v>
+        <v>122</v>
       </c>
       <c r="E276" t="s">
         <v>27</v>
@@ -6680,13 +6683,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D277" t="s">
-        <v>232</v>
+        <v>166</v>
       </c>
       <c r="E277" t="s">
         <v>27</v>
@@ -6697,13 +6700,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D278" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E278" t="s">
         <v>27</v>
@@ -6714,13 +6717,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D279" t="s">
-        <v>153</v>
+        <v>42</v>
       </c>
       <c r="E279" t="s">
         <v>27</v>
@@ -6731,13 +6734,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D280" t="s">
-        <v>339</v>
+        <v>70</v>
       </c>
       <c r="E280" t="s">
         <v>27</v>
@@ -6748,13 +6751,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D281" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="E281" t="s">
         <v>27</v>
@@ -6765,13 +6768,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D282" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="E282" t="s">
         <v>27</v>
@@ -6782,13 +6785,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D283" t="s">
-        <v>242</v>
+        <v>186</v>
       </c>
       <c r="E283" t="s">
         <v>27</v>
@@ -6799,13 +6802,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D284" t="s">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="E284" t="s">
         <v>27</v>
@@ -6816,13 +6819,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D285" t="s">
-        <v>205</v>
+        <v>250</v>
       </c>
       <c r="E285" t="s">
         <v>27</v>
@@ -6833,13 +6836,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D286" t="s">
-        <v>60</v>
+        <v>238</v>
       </c>
       <c r="E286" t="s">
         <v>27</v>
@@ -6850,13 +6853,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D287" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="E287" t="s">
         <v>27</v>
@@ -6867,13 +6870,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D288" t="s">
-        <v>339</v>
+        <v>195</v>
       </c>
       <c r="E288" t="s">
         <v>27</v>
@@ -6884,13 +6887,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D289" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="E289" t="s">
         <v>27</v>
@@ -6901,13 +6904,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D290" t="s">
-        <v>67</v>
+        <v>297</v>
       </c>
       <c r="E290" t="s">
         <v>27</v>
@@ -6918,13 +6921,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D291" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E291" t="s">
         <v>27</v>
@@ -6935,13 +6938,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D292" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="E292" t="s">
         <v>27</v>
@@ -6952,13 +6955,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D293" t="s">
-        <v>120</v>
+        <v>224</v>
       </c>
       <c r="E293" t="s">
         <v>27</v>
@@ -6969,13 +6972,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D294" t="s">
-        <v>146</v>
+        <v>42</v>
       </c>
       <c r="E294" t="s">
         <v>27</v>
@@ -6986,13 +6989,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D295" t="s">
-        <v>173</v>
+        <v>252</v>
       </c>
       <c r="E295" t="s">
         <v>27</v>
@@ -7003,13 +7006,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D296" t="s">
-        <v>175</v>
+        <v>117</v>
       </c>
       <c r="E296" t="s">
         <v>27</v>
@@ -7020,13 +7023,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D297" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="E297" t="s">
         <v>27</v>
@@ -7037,13 +7040,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D298" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E298" t="s">
         <v>27</v>
@@ -7054,13 +7057,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D299" t="s">
-        <v>403</v>
+        <v>327</v>
       </c>
       <c r="E299" t="s">
         <v>27</v>
@@ -7071,13 +7074,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D300" t="s">
-        <v>79</v>
+        <v>403</v>
       </c>
       <c r="E300" t="s">
         <v>27</v>
@@ -7088,13 +7091,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D301" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E301" t="s">
         <v>27</v>
@@ -7105,13 +7108,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D302" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E302" t="s">
         <v>27</v>
@@ -7122,13 +7125,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D303" t="s">
-        <v>239</v>
+        <v>186</v>
       </c>
       <c r="E303" t="s">
         <v>27</v>
@@ -7139,13 +7142,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D304" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="E304" t="s">
         <v>27</v>
@@ -7156,13 +7159,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D305" t="s">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="E305" t="s">
         <v>27</v>
@@ -7173,13 +7176,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D306" t="s">
-        <v>244</v>
+        <v>138</v>
       </c>
       <c r="E306" t="s">
         <v>27</v>
@@ -7190,13 +7193,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D307" t="s">
-        <v>244</v>
+        <v>275</v>
       </c>
       <c r="E307" t="s">
         <v>27</v>
@@ -7207,13 +7210,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D308" t="s">
-        <v>123</v>
+        <v>64</v>
       </c>
       <c r="E308" t="s">
         <v>27</v>
@@ -7224,13 +7227,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D309" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="E309" t="s">
         <v>27</v>
@@ -7241,13 +7244,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D310" t="s">
-        <v>339</v>
+        <v>240</v>
       </c>
       <c r="E310" t="s">
         <v>27</v>
@@ -7258,13 +7261,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D311" t="s">
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="E311" t="s">
         <v>27</v>
@@ -7275,13 +7278,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D312" t="s">
-        <v>205</v>
+        <v>115</v>
       </c>
       <c r="E312" t="s">
         <v>27</v>
@@ -7292,13 +7295,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D313" t="s">
-        <v>73</v>
+        <v>403</v>
       </c>
       <c r="E313" t="s">
         <v>27</v>
@@ -7309,13 +7312,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D314" t="s">
-        <v>326</v>
+        <v>117</v>
       </c>
       <c r="E314" t="s">
         <v>27</v>
@@ -7326,13 +7329,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D315" t="s">
-        <v>239</v>
+        <v>97</v>
       </c>
       <c r="E315" t="s">
         <v>27</v>
@@ -7343,13 +7346,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D316" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="E316" t="s">
         <v>27</v>
@@ -7360,13 +7363,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D317" t="s">
-        <v>229</v>
+        <v>138</v>
       </c>
       <c r="E317" t="s">
         <v>27</v>
@@ -7377,13 +7380,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D318" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="E318" t="s">
         <v>27</v>
@@ -7394,13 +7397,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D319" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E319" t="s">
         <v>27</v>
@@ -7411,13 +7414,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
+        <v>423</v>
+      </c>
+      <c r="C320" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D320" t="s">
         <v>424</v>
-      </c>
-      <c r="C320" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D320" t="s">
-        <v>165</v>
       </c>
       <c r="E320" t="s">
         <v>27</v>
@@ -7434,7 +7437,7 @@
         <v>25</v>
       </c>
       <c r="D321" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E321" t="s">
         <v>27</v>
@@ -7451,7 +7454,7 @@
         <v>25</v>
       </c>
       <c r="D322" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="E322" t="s">
         <v>27</v>
@@ -7468,7 +7471,7 @@
         <v>25</v>
       </c>
       <c r="D323" t="s">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="E323" t="s">
         <v>27</v>
@@ -7485,7 +7488,7 @@
         <v>25</v>
       </c>
       <c r="D324" t="s">
-        <v>144</v>
+        <v>76</v>
       </c>
       <c r="E324" t="s">
         <v>27</v>
@@ -7502,7 +7505,7 @@
         <v>25</v>
       </c>
       <c r="D325" t="s">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="E325" t="s">
         <v>27</v>
@@ -7519,7 +7522,7 @@
         <v>25</v>
       </c>
       <c r="D326" t="s">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="E326" t="s">
         <v>27</v>
@@ -7536,7 +7539,7 @@
         <v>25</v>
       </c>
       <c r="D327" t="s">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="E327" t="s">
         <v>27</v>
@@ -7553,7 +7556,7 @@
         <v>25</v>
       </c>
       <c r="D328" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="E328" t="s">
         <v>27</v>
@@ -7570,7 +7573,7 @@
         <v>25</v>
       </c>
       <c r="D329" t="s">
-        <v>139</v>
+        <v>238</v>
       </c>
       <c r="E329" t="s">
         <v>27</v>
@@ -7587,7 +7590,7 @@
         <v>25</v>
       </c>
       <c r="D330" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="E330" t="s">
         <v>27</v>
@@ -7604,7 +7607,7 @@
         <v>25</v>
       </c>
       <c r="D331" t="s">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="E331" t="s">
         <v>27</v>
@@ -7621,7 +7624,7 @@
         <v>25</v>
       </c>
       <c r="D332" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E332" t="s">
         <v>27</v>
@@ -7638,7 +7641,7 @@
         <v>25</v>
       </c>
       <c r="D333" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="E333" t="s">
         <v>27</v>
@@ -7655,7 +7658,7 @@
         <v>25</v>
       </c>
       <c r="D334" t="s">
-        <v>67</v>
+        <v>439</v>
       </c>
       <c r="E334" t="s">
         <v>27</v>
@@ -7666,13 +7669,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D335" t="s">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="E335" t="s">
         <v>27</v>
@@ -7683,13 +7686,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D336" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="E336" t="s">
         <v>27</v>
@@ -7700,13 +7703,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D337" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E337" t="s">
         <v>27</v>
@@ -7717,13 +7720,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D338" t="s">
-        <v>264</v>
+        <v>168</v>
       </c>
       <c r="E338" t="s">
         <v>27</v>
@@ -7734,13 +7737,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D339" t="s">
-        <v>81</v>
+        <v>168</v>
       </c>
       <c r="E339" t="s">
         <v>27</v>
@@ -7751,13 +7754,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D340" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="E340" t="s">
         <v>27</v>
@@ -7768,13 +7771,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D341" t="s">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="E341" t="s">
         <v>27</v>
@@ -7785,13 +7788,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D342" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="E342" t="s">
         <v>27</v>
@@ -7802,13 +7805,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D343" t="s">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="E343" t="s">
         <v>27</v>
@@ -7819,13 +7822,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D344" t="s">
-        <v>211</v>
+        <v>250</v>
       </c>
       <c r="E344" t="s">
         <v>27</v>
@@ -7836,13 +7839,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D345" t="s">
-        <v>153</v>
+        <v>90</v>
       </c>
       <c r="E345" t="s">
         <v>27</v>
@@ -7853,13 +7856,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D346" t="s">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="E346" t="s">
         <v>27</v>
@@ -7870,13 +7873,13 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D347" t="s">
-        <v>339</v>
+        <v>90</v>
       </c>
       <c r="E347" t="s">
         <v>27</v>
@@ -7887,13 +7890,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D348" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="E348" t="s">
         <v>27</v>
@@ -7904,13 +7907,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D349" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E349" t="s">
         <v>27</v>
@@ -7921,13 +7924,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D350" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="E350" t="s">
         <v>27</v>
@@ -7938,13 +7941,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D351" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="E351" t="s">
         <v>27</v>
@@ -7955,13 +7958,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D352" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="E352" t="s">
         <v>27</v>
@@ -7972,13 +7975,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D353" t="s">
-        <v>232</v>
+        <v>439</v>
       </c>
       <c r="E353" t="s">
         <v>27</v>
@@ -7989,13 +7992,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D354" t="s">
-        <v>97</v>
+        <v>230</v>
       </c>
       <c r="E354" t="s">
         <v>27</v>
@@ -8006,13 +8009,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D355" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="E355" t="s">
         <v>27</v>
@@ -8023,13 +8026,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D356" t="s">
-        <v>232</v>
+        <v>126</v>
       </c>
       <c r="E356" t="s">
         <v>27</v>
@@ -8040,13 +8043,13 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D357" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="E357" t="s">
         <v>27</v>
@@ -8057,7 +8060,7 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>25</v>
@@ -8074,13 +8077,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D359" t="s">
-        <v>146</v>
+        <v>188</v>
       </c>
       <c r="E359" t="s">
         <v>27</v>
@@ -8091,13 +8094,13 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D360" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E360" t="s">
         <v>27</v>
@@ -8108,13 +8111,13 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D361" t="s">
-        <v>339</v>
+        <v>166</v>
       </c>
       <c r="E361" t="s">
         <v>27</v>
@@ -8125,13 +8128,13 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D362" t="s">
-        <v>264</v>
+        <v>138</v>
       </c>
       <c r="E362" t="s">
         <v>27</v>
@@ -8142,13 +8145,13 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D363" t="s">
-        <v>47</v>
+        <v>154</v>
       </c>
       <c r="E363" t="s">
         <v>27</v>
@@ -8159,13 +8162,13 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D364" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E364" t="s">
         <v>27</v>
@@ -8176,13 +8179,13 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D365" t="s">
-        <v>49</v>
+        <v>146</v>
       </c>
       <c r="E365" t="s">
         <v>27</v>
@@ -8193,13 +8196,13 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D366" t="s">
-        <v>42</v>
+        <v>193</v>
       </c>
       <c r="E366" t="s">
         <v>27</v>
@@ -8210,13 +8213,13 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D367" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="E367" t="s">
         <v>27</v>
@@ -8227,13 +8230,13 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D368" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="E368" t="s">
         <v>27</v>
@@ -8244,13 +8247,13 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D369" t="s">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E369" t="s">
         <v>27</v>
@@ -8261,13 +8264,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D370" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E370" t="s">
         <v>27</v>
@@ -8278,13 +8281,13 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D371" t="s">
-        <v>205</v>
+        <v>76</v>
       </c>
       <c r="E371" t="s">
         <v>27</v>
@@ -8295,13 +8298,13 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D372" t="s">
-        <v>67</v>
+        <v>175</v>
       </c>
       <c r="E372" t="s">
         <v>27</v>
@@ -8312,13 +8315,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D373" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E373" t="s">
         <v>27</v>
@@ -8329,13 +8332,13 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D374" t="s">
-        <v>208</v>
+        <v>297</v>
       </c>
       <c r="E374" t="s">
         <v>27</v>
@@ -8346,13 +8349,13 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D375" t="s">
-        <v>262</v>
+        <v>134</v>
       </c>
       <c r="E375" t="s">
         <v>27</v>
@@ -8363,13 +8366,13 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D376" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E376" t="s">
         <v>27</v>
@@ -8380,13 +8383,13 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D377" t="s">
-        <v>217</v>
+        <v>92</v>
       </c>
       <c r="E377" t="s">
         <v>27</v>
@@ -8397,13 +8400,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D378" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="E378" t="s">
         <v>27</v>
@@ -8414,13 +8417,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C379" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D379" t="s">
-        <v>239</v>
+        <v>120</v>
       </c>
       <c r="E379" t="s">
         <v>27</v>
@@ -8431,13 +8434,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D380" t="s">
-        <v>57</v>
+        <v>230</v>
       </c>
       <c r="E380" t="s">
         <v>27</v>
@@ -8448,13 +8451,13 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C381" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D381" t="s">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="E381" t="s">
         <v>27</v>
@@ -8465,13 +8468,13 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D382" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="E382" t="s">
         <v>27</v>
@@ -8482,13 +8485,13 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D383" t="s">
-        <v>217</v>
+        <v>115</v>
       </c>
       <c r="E383" t="s">
         <v>27</v>
@@ -8499,13 +8502,13 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D384" t="s">
-        <v>173</v>
+        <v>76</v>
       </c>
       <c r="E384" t="s">
         <v>27</v>
@@ -8516,13 +8519,13 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D385" t="s">
-        <v>60</v>
+        <v>182</v>
       </c>
       <c r="E385" t="s">
         <v>27</v>
@@ -8533,13 +8536,13 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D386" t="s">
-        <v>165</v>
+        <v>275</v>
       </c>
       <c r="E386" t="s">
         <v>27</v>
@@ -8550,13 +8553,13 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D387" t="s">
-        <v>223</v>
+        <v>124</v>
       </c>
       <c r="E387" t="s">
         <v>27</v>
@@ -8567,13 +8570,13 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D388" t="s">
-        <v>123</v>
+        <v>40</v>
       </c>
       <c r="E388" t="s">
         <v>27</v>
@@ -8584,13 +8587,13 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D389" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="E389" t="s">
         <v>27</v>
@@ -8601,13 +8604,13 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D390" t="s">
-        <v>191</v>
+        <v>250</v>
       </c>
       <c r="E390" t="s">
         <v>27</v>
@@ -8618,13 +8621,13 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D391" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="E391" t="s">
         <v>27</v>
@@ -8635,13 +8638,13 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D392" t="s">
-        <v>139</v>
+        <v>66</v>
       </c>
       <c r="E392" t="s">
         <v>27</v>
@@ -8652,13 +8655,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D393" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="E393" t="s">
         <v>27</v>
@@ -8669,13 +8672,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D394" t="s">
-        <v>60</v>
+        <v>159</v>
       </c>
       <c r="E394" t="s">
         <v>27</v>
@@ -8686,13 +8689,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D395" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="E395" t="s">
         <v>27</v>
@@ -8703,13 +8706,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D396" t="s">
-        <v>249</v>
+        <v>334</v>
       </c>
       <c r="E396" t="s">
         <v>27</v>
@@ -8720,13 +8723,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D397" t="s">
-        <v>326</v>
+        <v>70</v>
       </c>
       <c r="E397" t="s">
         <v>27</v>
@@ -8737,13 +8740,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D398" t="s">
-        <v>144</v>
+        <v>195</v>
       </c>
       <c r="E398" t="s">
         <v>27</v>
@@ -8754,13 +8757,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D399" t="s">
-        <v>244</v>
+        <v>97</v>
       </c>
       <c r="E399" t="s">
         <v>27</v>
@@ -8771,13 +8774,13 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D400" t="s">
-        <v>162</v>
+        <v>88</v>
       </c>
       <c r="E400" t="s">
         <v>27</v>
@@ -8788,13 +8791,13 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D401" t="s">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="E401" t="s">
         <v>27</v>
@@ -8813,47 +8816,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B5" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B6">
         <v>400</v>
@@ -8861,7 +8864,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B7">
         <v>391</v>
@@ -8869,7 +8872,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B8">
         <v>9</v>
@@ -8877,7 +8880,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8885,10 +8888,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B10" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>

--- a/reports/selenium/Excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/Excel/Automation_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="522">
   <si>
     <t>#</t>
   </si>
@@ -35,61 +35,61 @@
     <t>FAILED</t>
   </si>
   <si>
-    <t>20.62</t>
+    <t>20.97</t>
   </si>
   <si>
     <t xml:space="preserve">Landing page did not load — Sign In button not found
-Wait timed out after 20043ms</t>
+Wait timed out after 20066ms</t>
   </si>
   <si>
     <t>should navigate to the login form</t>
   </si>
   <si>
-    <t>20.74</t>
+    <t>20.52</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20065ms</t>
+Wait timed out after 20036ms</t>
   </si>
   <si>
     <t>should login with valid credentials and reach the dashboard</t>
   </si>
   <si>
-    <t>20.47</t>
+    <t>20.87</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20016ms</t>
+Wait timed out after 20194ms</t>
   </si>
   <si>
     <t>should reject invalid credentials with an error message</t>
   </si>
   <si>
-    <t>20.75</t>
+    <t>20.44</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20044ms</t>
+Wait timed out after 20004ms</t>
   </si>
   <si>
     <t>should open the sign-up form from landing</t>
   </si>
   <si>
-    <t>20.46</t>
+    <t>20.93</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signup-btn"])
-Wait timed out after 20020ms</t>
+Wait timed out after 20197ms</t>
   </si>
   <si>
     <t>Security — should reject login for invalid credentials</t>
   </si>
   <si>
-    <t>20.63</t>
+    <t>20.99</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20054ms</t>
+Wait timed out after 20053ms</t>
   </si>
   <si>
     <t>Security — should prevent access to protected routes/dashboard for unauthenticated users</t>
@@ -98,7 +98,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>3.57</t>
+    <t>3.31</t>
   </si>
   <si>
     <t/>
@@ -107,1257 +107,1254 @@
     <t>Security — should not execute XSS script payloads submitted in login fields</t>
   </si>
   <si>
-    <t>20.39</t>
+    <t>20.55</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20020ms</t>
+Wait timed out after 20196ms</t>
   </si>
   <si>
     <t>Security — should enforce session termination and clean storage upon logout</t>
   </si>
   <si>
-    <t>20.38</t>
+    <t>20.77</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20012ms</t>
+Wait timed out after 20015ms</t>
   </si>
   <si>
     <t>Security — should confirm Firebase authentication rejects empty credentials</t>
   </si>
   <si>
-    <t>20.80</t>
+    <t>20.61</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20068ms</t>
+Wait timed out after 20177ms</t>
   </si>
   <si>
     <t>Security — should not expose sensitive API keys or secrets in page HTML source</t>
   </si>
   <si>
+    <t>0.77</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #11)</t>
+  </si>
+  <si>
+    <t>0.45</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #12)</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #13)</t>
+  </si>
+  <si>
+    <t>0.79</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #14)</t>
+  </si>
+  <si>
+    <t>0.81</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #15)</t>
+  </si>
+  <si>
+    <t>0.38</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #16)</t>
+  </si>
+  <si>
+    <t>0.89</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #17)</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #18)</t>
+  </si>
+  <si>
+    <t>0.92</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #19)</t>
+  </si>
+  <si>
+    <t>0.72</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #20)</t>
+  </si>
+  <si>
+    <t>0.46</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #21)</t>
+  </si>
+  <si>
+    <t>0.70</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #22)</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #23)</t>
+  </si>
+  <si>
+    <t>0.40</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #24)</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #25)</t>
+  </si>
+  <si>
+    <t>0.97</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #26)</t>
+  </si>
+  <si>
+    <t>0.86</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #27)</t>
+  </si>
+  <si>
+    <t>0.83</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #28)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #29)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #30)</t>
+  </si>
+  <si>
+    <t>0.29</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #31)</t>
+  </si>
+  <si>
+    <t>0.61</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #32)</t>
+  </si>
+  <si>
+    <t>0.28</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #33)</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #34)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #35)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #36)</t>
+  </si>
+  <si>
+    <t>0.49</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #37)</t>
+  </si>
+  <si>
+    <t>0.93</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #38)</t>
+  </si>
+  <si>
+    <t>0.53</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #39)</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #40)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #41)</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #42)</t>
+  </si>
+  <si>
+    <t>0.96</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #43)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #44)</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #45)</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #46)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #47)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #48)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #49)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #50)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #51)</t>
+  </si>
+  <si>
+    <t>0.71</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #52)</t>
+  </si>
+  <si>
+    <t>0.52</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #53)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #54)</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #55)</t>
+  </si>
+  <si>
+    <t>0.90</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #56)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #57)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #58)</t>
+  </si>
+  <si>
+    <t>0.32</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #59)</t>
+  </si>
+  <si>
+    <t>0.65</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #60)</t>
+  </si>
+  <si>
+    <t>0.54</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #61)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #62)</t>
+  </si>
+  <si>
+    <t>0.66</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #63)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #64)</t>
+  </si>
+  <si>
+    <t>0.91</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #65)</t>
+  </si>
+  <si>
+    <t>0.63</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #66)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #67)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #68)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #69)</t>
+  </si>
+  <si>
+    <t>0.76</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #70)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #71)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #72)</t>
+  </si>
+  <si>
+    <t>0.74</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #73)</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #74)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #75)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #76)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #77)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #78)</t>
+  </si>
+  <si>
+    <t>0.78</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #79)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #80)</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #81)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #82)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #83)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #84)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #85)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #86)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #87)</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #88)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #89)</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #90)</t>
+  </si>
+  <si>
+    <t>0.73</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #91)</t>
+  </si>
+  <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #92)</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #93)</t>
+  </si>
+  <si>
+    <t>0.67</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #94)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #95)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #96)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #97)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #98)</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #99)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #100)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #101)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #102)</t>
+  </si>
+  <si>
+    <t>0.30</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #103)</t>
+  </si>
+  <si>
+    <t>0.80</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #104)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #105)</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #106)</t>
+  </si>
+  <si>
+    <t>0.31</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #107)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #108)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #109)</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #110)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #111)</t>
+  </si>
+  <si>
+    <t>0.99</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #112)</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #113)</t>
+  </si>
+  <si>
+    <t>0.88</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #114)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #115)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #116)</t>
+  </si>
+  <si>
+    <t>0.47</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #117)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #118)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #119)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #120)</t>
+  </si>
+  <si>
+    <t>0.48</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #121)</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #122)</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #123)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #124)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #125)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #126)</t>
+  </si>
+  <si>
+    <t>0.44</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #127)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #128)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #129)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #130)</t>
+  </si>
+  <si>
+    <t>0.69</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #131)</t>
+  </si>
+  <si>
+    <t>0.60</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #132)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #133)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #134)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #135)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #136)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #137)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #138)</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #139)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #140)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #141)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #142)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #143)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #144)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #145)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #146)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #147)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #148)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #149)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #150)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #151)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #152)</t>
+  </si>
+  <si>
+    <t>0.87</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #153)</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #154)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #155)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #156)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #157)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #158)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #159)</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #160)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #161)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #162)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #163)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #164)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #165)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #166)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #167)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #168)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #169)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #170)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #171)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #172)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #173)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #174)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #175)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #176)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #177)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #178)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #179)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #180)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #181)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #182)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #183)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #184)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #185)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #186)</t>
+  </si>
+  <si>
+    <t>0.82</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #187)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #188)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #189)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #190)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #191)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #192)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #193)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #194)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #195)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #196)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #197)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #198)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #199)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #200)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #201)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #202)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #203)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #204)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #205)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #206)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #207)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #208)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #209)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #210)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #211)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #212)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #213)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #214)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #215)</t>
+  </si>
+  <si>
+    <t>0.68</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #216)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #217)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #218)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #219)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #220)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #221)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #222)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #223)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #224)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #225)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #226)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #227)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #228)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #229)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #230)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #231)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #232)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #233)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #234)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #235)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #236)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #237)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #238)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #239)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #240)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #241)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #242)</t>
+  </si>
+  <si>
     <t>0.39</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #11)</t>
-  </si>
-  <si>
-    <t>0.86</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #12)</t>
-  </si>
-  <si>
-    <t>0.45</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #13)</t>
-  </si>
-  <si>
-    <t>0.21</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #14)</t>
-  </si>
-  <si>
-    <t>0.59</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #15)</t>
-  </si>
-  <si>
-    <t>0.88</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #16)</t>
-  </si>
-  <si>
-    <t>0.94</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #17)</t>
-  </si>
-  <si>
-    <t>0.63</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #18)</t>
-  </si>
-  <si>
-    <t>0.47</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #19)</t>
-  </si>
-  <si>
-    <t>0.22</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #20)</t>
-  </si>
-  <si>
-    <t>0.76</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #21)</t>
-  </si>
-  <si>
-    <t>0.42</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #22)</t>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #243)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #244)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #245)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #246)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #247)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #248)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #249)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #250)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #251)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #252)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #253)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #254)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #255)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #256)</t>
+  </si>
+  <si>
+    <t>0.55</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #257)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #258)</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #259)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #260)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #261)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #262)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #263)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #264)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #265)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #266)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #267)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #268)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #269)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #270)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #271)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #272)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #273)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #274)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #275)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #276)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #277)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #278)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #279)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #280)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #281)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #282)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #283)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #284)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #285)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #286)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #287)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #288)</t>
   </si>
   <si>
     <t>1.00</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #23)</t>
-  </si>
-  <si>
-    <t>0.82</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #24)</t>
-  </si>
-  <si>
-    <t>0.36</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #25)</t>
-  </si>
-  <si>
-    <t>0.85</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #26)</t>
-  </si>
-  <si>
-    <t>0.46</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #27)</t>
-  </si>
-  <si>
-    <t>0.75</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #28)</t>
-  </si>
-  <si>
-    <t>0.81</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #29)</t>
-  </si>
-  <si>
-    <t>0.77</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #30)</t>
-  </si>
-  <si>
-    <t>0.58</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #31)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #32)</t>
-  </si>
-  <si>
-    <t>0.97</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #33)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #34)</t>
-  </si>
-  <si>
-    <t>0.98</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #35)</t>
-  </si>
-  <si>
-    <t>0.32</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #36)</t>
-  </si>
-  <si>
-    <t>0.27</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #37)</t>
-  </si>
-  <si>
-    <t>0.51</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #38)</t>
-  </si>
-  <si>
-    <t>0.54</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #39)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #40)</t>
-  </si>
-  <si>
-    <t>0.73</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #41)</t>
-  </si>
-  <si>
-    <t>0.24</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #42)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #43)</t>
-  </si>
-  <si>
-    <t>0.66</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #44)</t>
-  </si>
-  <si>
-    <t>0.99</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #45)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #46)</t>
-  </si>
-  <si>
-    <t>0.30</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #47)</t>
-  </si>
-  <si>
-    <t>0.91</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #48)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #49)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #50)</t>
-  </si>
-  <si>
-    <t>0.38</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #51)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #52)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #53)</t>
-  </si>
-  <si>
-    <t>0.65</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #54)</t>
-  </si>
-  <si>
-    <t>0.72</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #55)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #56)</t>
-  </si>
-  <si>
-    <t>0.67</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #57)</t>
-  </si>
-  <si>
-    <t>0.69</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #58)</t>
-  </si>
-  <si>
-    <t>0.26</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #59)</t>
-  </si>
-  <si>
-    <t>0.43</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #60)</t>
-  </si>
-  <si>
-    <t>0.40</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #61)</t>
-  </si>
-  <si>
-    <t>0.70</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #62)</t>
-  </si>
-  <si>
-    <t>0.57</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #63)</t>
-  </si>
-  <si>
-    <t>0.55</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #64)</t>
-  </si>
-  <si>
-    <t>0.68</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #65)</t>
-  </si>
-  <si>
-    <t>0.34</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #66)</t>
-  </si>
-  <si>
-    <t>0.80</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #67)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #68)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #69)</t>
-  </si>
-  <si>
-    <t>0.79</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #70)</t>
-  </si>
-  <si>
-    <t>0.25</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #71)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #72)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #73)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #74)</t>
-  </si>
-  <si>
-    <t>0.35</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #75)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #76)</t>
-  </si>
-  <si>
-    <t>0.52</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #77)</t>
-  </si>
-  <si>
-    <t>0.49</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #78)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #79)</t>
-  </si>
-  <si>
-    <t>0.95</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #80)</t>
-  </si>
-  <si>
-    <t>0.48</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #81)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #82)</t>
-  </si>
-  <si>
-    <t>0.60</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #83)</t>
-  </si>
-  <si>
-    <t>0.96</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #84)</t>
-  </si>
-  <si>
-    <t>0.78</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #85)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #86)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #87)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #88)</t>
-  </si>
-  <si>
-    <t>0.28</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #89)</t>
-  </si>
-  <si>
-    <t>0.83</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #90)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #91)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #92)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #93)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #94)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #95)</t>
-  </si>
-  <si>
-    <t>0.62</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #96)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #97)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #98)</t>
-  </si>
-  <si>
-    <t>0.44</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #99)</t>
-  </si>
-  <si>
-    <t>0.87</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #100)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #101)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #102)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #103)</t>
-  </si>
-  <si>
-    <t>0.29</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #104)</t>
-  </si>
-  <si>
-    <t>0.56</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #105)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #106)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #107)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #108)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #109)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #110)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #111)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #112)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #113)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #114)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #115)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #116)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #117)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #118)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #119)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #120)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #121)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #122)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #123)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #124)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #125)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #126)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #127)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #128)</t>
-  </si>
-  <si>
-    <t>0.93</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #129)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #130)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #131)</t>
-  </si>
-  <si>
-    <t>0.64</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #132)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #133)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #134)</t>
-  </si>
-  <si>
-    <t>0.23</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #135)</t>
-  </si>
-  <si>
-    <t>0.90</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #136)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #137)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #138)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #139)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #140)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #141)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #142)</t>
-  </si>
-  <si>
-    <t>0.92</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #143)</t>
-  </si>
-  <si>
-    <t>0.31</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #144)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #145)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #146)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #147)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #148)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #149)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #150)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #151)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #152)</t>
-  </si>
-  <si>
-    <t>0.61</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #153)</t>
-  </si>
-  <si>
-    <t>0.89</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #154)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #155)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #156)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #157)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #158)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #159)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #160)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #161)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #162)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #163)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #164)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #165)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #166)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #167)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #168)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #169)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #170)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #171)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #172)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #173)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #174)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #175)</t>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #289)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #290)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #291)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #292)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #293)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #294)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #295)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #296)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #297)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #298)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #299)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #300)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #301)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #302)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #303)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #304)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #305)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #306)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #307)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #308)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #309)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #310)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #311)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #312)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #313)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #314)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #315)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #316)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #317)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #318)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #319)</t>
   </si>
   <si>
     <t>0.50</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #176)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #177)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #178)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #179)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #180)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #181)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #182)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #183)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #184)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #185)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #186)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #187)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #188)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #189)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #190)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #191)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #192)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #193)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #194)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #195)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #196)</t>
-  </si>
-  <si>
-    <t>0.20</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #197)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #198)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #199)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #200)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #201)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #202)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #203)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #204)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #205)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #206)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #207)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #208)</t>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #320)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #321)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #322)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #323)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #324)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #325)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #326)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #327)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #328)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #329)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #330)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #331)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #332)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #333)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #334)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #335)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #336)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #337)</t>
   </si>
   <si>
     <t>0.84</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #209)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #210)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #211)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #212)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #213)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #214)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #215)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #216)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #217)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #218)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #219)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #220)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #221)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #222)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #223)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #224)</t>
-  </si>
-  <si>
-    <t>0.33</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #225)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #226)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #227)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #228)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #229)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #230)</t>
-  </si>
-  <si>
-    <t>0.41</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #231)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #232)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #233)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #234)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #235)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #236)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #237)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #238)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #239)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #240)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #241)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #242)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #243)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #244)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #245)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #246)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #247)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #248)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #249)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #250)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #251)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #252)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #253)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #254)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #255)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #256)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #257)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #258)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #259)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #260)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #261)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #262)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #263)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #264)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #265)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #266)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #267)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #268)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #269)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #270)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #271)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #272)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #273)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #274)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #275)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #276)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #277)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #278)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #279)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #280)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #281)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #282)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #283)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #284)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #285)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #286)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #287)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #288)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #289)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #290)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #291)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #292)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #293)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #294)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #295)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #296)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #297)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #298)</t>
-  </si>
-  <si>
-    <t>0.37</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #299)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #300)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #301)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #302)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #303)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #304)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #305)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #306)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #307)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #308)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #309)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #310)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #311)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #312)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #313)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #314)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #315)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #316)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #317)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #318)</t>
-  </si>
-  <si>
-    <t>0.71</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #319)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #320)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #321)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #322)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #323)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #324)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #325)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #326)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #327)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #328)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #329)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #330)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #331)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #332)</t>
-  </si>
-  <si>
-    <t>0.53</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #333)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #334)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #335)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #336)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #337)</t>
-  </si>
-  <si>
     <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #338)</t>
   </si>
   <si>
@@ -1553,13 +1550,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>14</t>
+    <t>15</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 13:45:38 UTC</t>
+    <t>2026-06-23 13:53:48 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1571,7 +1568,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>3eb8262</t>
+    <t>0bdfd4b</t>
   </si>
   <si>
     <t>Total</t>
@@ -2490,7 +2487,7 @@
         <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="E30" t="s">
         <v>27</v>
@@ -2501,13 +2498,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E31" t="s">
         <v>27</v>
@@ -2518,13 +2515,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E32" t="s">
         <v>27</v>
@@ -2535,13 +2532,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D33" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="E33" t="s">
         <v>27</v>
@@ -2552,13 +2549,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34" t="s">
         <v>80</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D34" t="s">
-        <v>81</v>
       </c>
       <c r="E34" t="s">
         <v>27</v>
@@ -2569,13 +2566,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" t="s">
         <v>82</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D35" t="s">
-        <v>46</v>
       </c>
       <c r="E35" t="s">
         <v>27</v>
@@ -2592,7 +2589,7 @@
         <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="E36" t="s">
         <v>27</v>
@@ -2603,13 +2600,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="E37" t="s">
         <v>27</v>
@@ -2620,13 +2617,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D38" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E38" t="s">
         <v>27</v>
@@ -2637,13 +2634,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E39" t="s">
         <v>27</v>
@@ -2654,13 +2651,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E40" t="s">
         <v>27</v>
@@ -2671,13 +2668,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="E41" t="s">
         <v>27</v>
@@ -2688,13 +2685,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D42" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="E42" t="s">
         <v>27</v>
@@ -2705,13 +2702,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E43" t="s">
         <v>27</v>
@@ -2722,13 +2719,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="E44" t="s">
         <v>27</v>
@@ -2739,13 +2736,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="E45" t="s">
         <v>27</v>
@@ -2756,13 +2753,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E46" t="s">
         <v>27</v>
@@ -2773,13 +2770,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="E47" t="s">
         <v>27</v>
@@ -2790,13 +2787,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="E48" t="s">
         <v>27</v>
@@ -2807,13 +2804,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="E49" t="s">
         <v>27</v>
@@ -2824,13 +2821,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="E50" t="s">
         <v>27</v>
@@ -2841,13 +2838,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D51" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="E51" t="s">
         <v>27</v>
@@ -2858,13 +2855,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="E52" t="s">
         <v>27</v>
@@ -2875,13 +2872,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="E53" t="s">
         <v>27</v>
@@ -2892,13 +2889,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="E54" t="s">
         <v>27</v>
@@ -2909,13 +2906,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D55" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E55" t="s">
         <v>27</v>
@@ -2926,13 +2923,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D56" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E56" t="s">
         <v>27</v>
@@ -2943,13 +2940,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D57" t="s">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="E57" t="s">
         <v>27</v>
@@ -2960,13 +2957,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D58" t="s">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="E58" t="s">
         <v>27</v>
@@ -2977,13 +2974,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D59" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="E59" t="s">
         <v>27</v>
@@ -2994,13 +2991,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D60" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E60" t="s">
         <v>27</v>
@@ -3011,13 +3008,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E61" t="s">
         <v>27</v>
@@ -3028,13 +3025,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D62" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E62" t="s">
         <v>27</v>
@@ -3045,13 +3042,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D63" t="s">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="E63" t="s">
         <v>27</v>
@@ -3062,13 +3059,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D64" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E64" t="s">
         <v>27</v>
@@ -3079,13 +3076,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="E65" t="s">
         <v>27</v>
@@ -3096,13 +3093,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D66" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E66" t="s">
         <v>27</v>
@@ -3113,13 +3110,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D67" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E67" t="s">
         <v>27</v>
@@ -3130,13 +3127,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D68" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="E68" t="s">
         <v>27</v>
@@ -3147,13 +3144,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D69" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="E69" t="s">
         <v>27</v>
@@ -3164,13 +3161,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D70" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E70" t="s">
         <v>27</v>
@@ -3181,13 +3178,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D71" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E71" t="s">
         <v>27</v>
@@ -3198,13 +3195,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D72" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="E72" t="s">
         <v>27</v>
@@ -3215,13 +3212,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D73" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="E73" t="s">
         <v>27</v>
@@ -3232,13 +3229,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D74" t="s">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="E74" t="s">
         <v>27</v>
@@ -3249,13 +3246,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D75" t="s">
-        <v>68</v>
+        <v>143</v>
       </c>
       <c r="E75" t="s">
         <v>27</v>
@@ -3266,13 +3263,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D76" t="s">
-        <v>151</v>
+        <v>46</v>
       </c>
       <c r="E76" t="s">
         <v>27</v>
@@ -3283,13 +3280,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D77" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E77" t="s">
         <v>27</v>
@@ -3300,13 +3297,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>154</v>
+        <v>100</v>
       </c>
       <c r="E78" t="s">
         <v>27</v>
@@ -3317,13 +3314,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D79" t="s">
-        <v>156</v>
+        <v>68</v>
       </c>
       <c r="E79" t="s">
         <v>27</v>
@@ -3334,13 +3331,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D80" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="E80" t="s">
         <v>27</v>
@@ -3351,13 +3348,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D81" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="E81" t="s">
         <v>27</v>
@@ -3368,13 +3365,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D82" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="E82" t="s">
         <v>27</v>
@@ -3385,13 +3382,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D83" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="E83" t="s">
         <v>27</v>
@@ -3402,13 +3399,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D84" t="s">
-        <v>164</v>
+        <v>66</v>
       </c>
       <c r="E84" t="s">
         <v>27</v>
@@ -3419,13 +3416,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D85" t="s">
-        <v>166</v>
+        <v>100</v>
       </c>
       <c r="E85" t="s">
         <v>27</v>
@@ -3436,13 +3433,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D86" t="s">
-        <v>168</v>
+        <v>90</v>
       </c>
       <c r="E86" t="s">
         <v>27</v>
@@ -3453,13 +3450,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D87" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="E87" t="s">
         <v>27</v>
@@ -3470,13 +3467,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D88" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="E88" t="s">
         <v>27</v>
@@ -3487,13 +3484,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D89" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="E89" t="s">
         <v>27</v>
@@ -3504,13 +3501,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D90" t="s">
-        <v>173</v>
+        <v>78</v>
       </c>
       <c r="E90" t="s">
         <v>27</v>
@@ -3521,13 +3518,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D91" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="E91" t="s">
         <v>27</v>
@@ -3538,13 +3535,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D92" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="E92" t="s">
         <v>27</v>
@@ -3555,13 +3552,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D93" t="s">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="E93" t="s">
         <v>27</v>
@@ -3572,13 +3569,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D94" t="s">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="E94" t="s">
         <v>27</v>
@@ -3589,13 +3586,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D95" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E95" t="s">
         <v>27</v>
@@ -3606,13 +3603,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D96" t="s">
-        <v>136</v>
+        <v>42</v>
       </c>
       <c r="E96" t="s">
         <v>27</v>
@@ -3623,13 +3620,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D97" t="s">
-        <v>182</v>
+        <v>122</v>
       </c>
       <c r="E97" t="s">
         <v>27</v>
@@ -3640,13 +3637,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D98" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="E98" t="s">
         <v>27</v>
@@ -3657,13 +3654,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D99" t="s">
-        <v>159</v>
+        <v>120</v>
       </c>
       <c r="E99" t="s">
         <v>27</v>
@@ -3674,13 +3671,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D100" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="E100" t="s">
         <v>27</v>
@@ -3691,13 +3688,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>188</v>
+        <v>42</v>
       </c>
       <c r="E101" t="s">
         <v>27</v>
@@ -3708,13 +3705,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D102" t="s">
-        <v>156</v>
+        <v>50</v>
       </c>
       <c r="E102" t="s">
         <v>27</v>
@@ -3725,13 +3722,13 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D103" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="E103" t="s">
         <v>27</v>
@@ -3742,13 +3739,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D104" t="s">
-        <v>86</v>
+        <v>182</v>
       </c>
       <c r="E104" t="s">
         <v>27</v>
@@ -3759,13 +3756,13 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D105" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="E105" t="s">
         <v>27</v>
@@ -3776,13 +3773,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D106" t="s">
-        <v>195</v>
+        <v>54</v>
       </c>
       <c r="E106" t="s">
         <v>27</v>
@@ -3793,13 +3790,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D107" t="s">
-        <v>50</v>
+        <v>187</v>
       </c>
       <c r="E107" t="s">
         <v>27</v>
@@ -3810,13 +3807,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D108" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="E108" t="s">
         <v>27</v>
@@ -3827,13 +3824,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D109" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="E109" t="s">
         <v>27</v>
@@ -3844,13 +3841,13 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D110" t="s">
-        <v>156</v>
+        <v>52</v>
       </c>
       <c r="E110" t="s">
         <v>27</v>
@@ -3861,13 +3858,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D111" t="s">
-        <v>100</v>
+        <v>193</v>
       </c>
       <c r="E111" t="s">
         <v>27</v>
@@ -3878,13 +3875,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D112" t="s">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="E112" t="s">
         <v>27</v>
@@ -3895,13 +3892,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D113" t="s">
-        <v>105</v>
+        <v>196</v>
       </c>
       <c r="E113" t="s">
         <v>27</v>
@@ -3912,13 +3909,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D114" t="s">
-        <v>151</v>
+        <v>198</v>
       </c>
       <c r="E114" t="s">
         <v>27</v>
@@ -3929,13 +3926,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D115" t="s">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E115" t="s">
         <v>27</v>
@@ -3946,13 +3943,13 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D116" t="s">
-        <v>107</v>
+        <v>165</v>
       </c>
       <c r="E116" t="s">
         <v>27</v>
@@ -3963,13 +3960,13 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D117" t="s">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="E117" t="s">
         <v>27</v>
@@ -3980,13 +3977,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D118" t="s">
-        <v>122</v>
+        <v>204</v>
       </c>
       <c r="E118" t="s">
         <v>27</v>
@@ -3997,13 +3994,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D119" t="s">
-        <v>159</v>
+        <v>88</v>
       </c>
       <c r="E119" t="s">
         <v>27</v>
@@ -4014,13 +4011,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D120" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="E120" t="s">
         <v>27</v>
@@ -4031,13 +4028,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D121" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="E121" t="s">
         <v>27</v>
@@ -4048,13 +4045,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D122" t="s">
-        <v>120</v>
+        <v>209</v>
       </c>
       <c r="E122" t="s">
         <v>27</v>
@@ -4065,13 +4062,13 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D123" t="s">
-        <v>126</v>
+        <v>211</v>
       </c>
       <c r="E123" t="s">
         <v>27</v>
@@ -4082,13 +4079,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
+        <v>212</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D124" t="s">
         <v>213</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D124" t="s">
-        <v>90</v>
       </c>
       <c r="E124" t="s">
         <v>27</v>
@@ -4105,7 +4102,7 @@
         <v>25</v>
       </c>
       <c r="D125" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E125" t="s">
         <v>27</v>
@@ -4122,7 +4119,7 @@
         <v>25</v>
       </c>
       <c r="D126" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="E126" t="s">
         <v>27</v>
@@ -4139,7 +4136,7 @@
         <v>25</v>
       </c>
       <c r="D127" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="E127" t="s">
         <v>27</v>
@@ -4156,7 +4153,7 @@
         <v>25</v>
       </c>
       <c r="D128" t="s">
-        <v>122</v>
+        <v>218</v>
       </c>
       <c r="E128" t="s">
         <v>27</v>
@@ -4167,13 +4164,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D129" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="E129" t="s">
         <v>27</v>
@@ -4184,13 +4181,13 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D130" t="s">
-        <v>220</v>
+        <v>163</v>
       </c>
       <c r="E130" t="s">
         <v>27</v>
@@ -4207,7 +4204,7 @@
         <v>25</v>
       </c>
       <c r="D131" t="s">
-        <v>115</v>
+        <v>218</v>
       </c>
       <c r="E131" t="s">
         <v>27</v>
@@ -4224,7 +4221,7 @@
         <v>25</v>
       </c>
       <c r="D132" t="s">
-        <v>134</v>
+        <v>223</v>
       </c>
       <c r="E132" t="s">
         <v>27</v>
@@ -4235,13 +4232,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D133" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E133" t="s">
         <v>27</v>
@@ -4252,13 +4249,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D134" t="s">
-        <v>81</v>
+        <v>209</v>
       </c>
       <c r="E134" t="s">
         <v>27</v>
@@ -4269,13 +4266,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D135" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E135" t="s">
         <v>27</v>
@@ -4286,13 +4283,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D136" t="s">
-        <v>228</v>
+        <v>171</v>
       </c>
       <c r="E136" t="s">
         <v>27</v>
@@ -4309,7 +4306,7 @@
         <v>25</v>
       </c>
       <c r="D137" t="s">
-        <v>230</v>
+        <v>72</v>
       </c>
       <c r="E137" t="s">
         <v>27</v>
@@ -4320,13 +4317,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D138" t="s">
-        <v>230</v>
+        <v>95</v>
       </c>
       <c r="E138" t="s">
         <v>27</v>
@@ -4337,13 +4334,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D139" t="s">
-        <v>54</v>
+        <v>182</v>
       </c>
       <c r="E139" t="s">
         <v>27</v>
@@ -4354,13 +4351,13 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
+        <v>232</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D140" t="s">
         <v>233</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D140" t="s">
-        <v>84</v>
       </c>
       <c r="E140" t="s">
         <v>27</v>
@@ -4377,7 +4374,7 @@
         <v>25</v>
       </c>
       <c r="D141" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E141" t="s">
         <v>27</v>
@@ -4394,7 +4391,7 @@
         <v>25</v>
       </c>
       <c r="D142" t="s">
-        <v>230</v>
+        <v>95</v>
       </c>
       <c r="E142" t="s">
         <v>27</v>
@@ -4411,7 +4408,7 @@
         <v>25</v>
       </c>
       <c r="D143" t="s">
-        <v>122</v>
+        <v>196</v>
       </c>
       <c r="E143" t="s">
         <v>27</v>
@@ -4428,7 +4425,7 @@
         <v>25</v>
       </c>
       <c r="D144" t="s">
-        <v>238</v>
+        <v>48</v>
       </c>
       <c r="E144" t="s">
         <v>27</v>
@@ -4439,13 +4436,13 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D145" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
       <c r="E145" t="s">
         <v>27</v>
@@ -4456,13 +4453,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D146" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E146" t="s">
         <v>27</v>
@@ -4473,13 +4470,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D147" t="s">
-        <v>40</v>
+        <v>132</v>
       </c>
       <c r="E147" t="s">
         <v>27</v>
@@ -4490,13 +4487,13 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D148" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="E148" t="s">
         <v>27</v>
@@ -4507,13 +4504,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D149" t="s">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="E149" t="s">
         <v>27</v>
@@ -4524,13 +4521,13 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D150" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="E150" t="s">
         <v>27</v>
@@ -4541,13 +4538,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D151" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="E151" t="s">
         <v>27</v>
@@ -4558,13 +4555,13 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D152" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="E152" t="s">
         <v>27</v>
@@ -4575,13 +4572,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D153" t="s">
-        <v>130</v>
+        <v>204</v>
       </c>
       <c r="E153" t="s">
         <v>27</v>
@@ -4592,13 +4589,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D154" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E154" t="s">
         <v>27</v>
@@ -4609,13 +4606,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D155" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E155" t="s">
         <v>27</v>
@@ -4626,13 +4623,13 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D156" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="E156" t="s">
         <v>27</v>
@@ -4643,13 +4640,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D157" t="s">
-        <v>126</v>
+        <v>200</v>
       </c>
       <c r="E157" t="s">
         <v>27</v>
@@ -4660,13 +4657,13 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D158" t="s">
-        <v>154</v>
+        <v>204</v>
       </c>
       <c r="E158" t="s">
         <v>27</v>
@@ -4677,13 +4674,13 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D159" t="s">
-        <v>138</v>
+        <v>204</v>
       </c>
       <c r="E159" t="s">
         <v>27</v>
@@ -4694,13 +4691,13 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D160" t="s">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="E160" t="s">
         <v>27</v>
@@ -4711,13 +4708,13 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D161" t="s">
-        <v>86</v>
+        <v>257</v>
       </c>
       <c r="E161" t="s">
         <v>27</v>
@@ -4728,13 +4725,13 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D162" t="s">
-        <v>240</v>
+        <v>86</v>
       </c>
       <c r="E162" t="s">
         <v>27</v>
@@ -4745,13 +4742,13 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D163" t="s">
-        <v>224</v>
+        <v>97</v>
       </c>
       <c r="E163" t="s">
         <v>27</v>
@@ -4762,13 +4759,13 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D164" t="s">
-        <v>250</v>
+        <v>56</v>
       </c>
       <c r="E164" t="s">
         <v>27</v>
@@ -4779,13 +4776,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D165" t="s">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="E165" t="s">
         <v>27</v>
@@ -4796,13 +4793,13 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D166" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E166" t="s">
         <v>27</v>
@@ -4813,13 +4810,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D167" t="s">
-        <v>50</v>
+        <v>177</v>
       </c>
       <c r="E167" t="s">
         <v>27</v>
@@ -4830,13 +4827,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D168" t="s">
-        <v>161</v>
+        <v>52</v>
       </c>
       <c r="E168" t="s">
         <v>27</v>
@@ -4847,13 +4844,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D169" t="s">
-        <v>38</v>
+        <v>177</v>
       </c>
       <c r="E169" t="s">
         <v>27</v>
@@ -4864,13 +4861,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D170" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="E170" t="s">
         <v>27</v>
@@ -4881,13 +4878,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D171" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E171" t="s">
         <v>27</v>
@@ -4898,13 +4895,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D172" t="s">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="E172" t="s">
         <v>27</v>
@@ -4915,13 +4912,13 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D173" t="s">
-        <v>193</v>
+        <v>40</v>
       </c>
       <c r="E173" t="s">
         <v>27</v>
@@ -4932,13 +4929,13 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D174" t="s">
-        <v>86</v>
+        <v>196</v>
       </c>
       <c r="E174" t="s">
         <v>27</v>
@@ -4949,13 +4946,13 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D175" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="E175" t="s">
         <v>27</v>
@@ -4966,13 +4963,13 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D176" t="s">
-        <v>68</v>
+        <v>160</v>
       </c>
       <c r="E176" t="s">
         <v>27</v>
@@ -4983,13 +4980,13 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D177" t="s">
-        <v>275</v>
+        <v>152</v>
       </c>
       <c r="E177" t="s">
         <v>27</v>
@@ -5000,13 +4997,13 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D178" t="s">
-        <v>56</v>
+        <v>225</v>
       </c>
       <c r="E178" t="s">
         <v>27</v>
@@ -5017,13 +5014,13 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D179" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="E179" t="s">
         <v>27</v>
@@ -5034,13 +5031,13 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D180" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E180" t="s">
         <v>27</v>
@@ -5051,13 +5048,13 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D181" t="s">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="E181" t="s">
         <v>27</v>
@@ -5068,13 +5065,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D182" t="s">
-        <v>95</v>
+        <v>177</v>
       </c>
       <c r="E182" t="s">
         <v>27</v>
@@ -5085,13 +5082,13 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D183" t="s">
-        <v>66</v>
+        <v>177</v>
       </c>
       <c r="E183" t="s">
         <v>27</v>
@@ -5102,13 +5099,13 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D184" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="E184" t="s">
         <v>27</v>
@@ -5119,13 +5116,13 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D185" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="E185" t="s">
         <v>27</v>
@@ -5136,13 +5133,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D186" t="s">
-        <v>175</v>
+        <v>46</v>
       </c>
       <c r="E186" t="s">
         <v>27</v>
@@ -5153,13 +5150,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D187" t="s">
-        <v>54</v>
+        <v>137</v>
       </c>
       <c r="E187" t="s">
         <v>27</v>
@@ -5170,13 +5167,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D188" t="s">
-        <v>161</v>
+        <v>285</v>
       </c>
       <c r="E188" t="s">
         <v>27</v>
@@ -5187,13 +5184,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D189" t="s">
-        <v>161</v>
+        <v>44</v>
       </c>
       <c r="E189" t="s">
         <v>27</v>
@@ -5204,13 +5201,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D190" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="E190" t="s">
         <v>27</v>
@@ -5221,13 +5218,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D191" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="E191" t="s">
         <v>27</v>
@@ -5238,13 +5235,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D192" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="E192" t="s">
         <v>27</v>
@@ -5255,13 +5252,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D193" t="s">
-        <v>97</v>
+        <v>250</v>
       </c>
       <c r="E193" t="s">
         <v>27</v>
@@ -5272,13 +5269,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D194" t="s">
-        <v>168</v>
+        <v>68</v>
       </c>
       <c r="E194" t="s">
         <v>27</v>
@@ -5289,13 +5286,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D195" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="E195" t="s">
         <v>27</v>
@@ -5306,13 +5303,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D196" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="E196" t="s">
         <v>27</v>
@@ -5323,13 +5320,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D197" t="s">
-        <v>102</v>
+        <v>209</v>
       </c>
       <c r="E197" t="s">
         <v>27</v>
@@ -5340,13 +5337,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D198" t="s">
-        <v>297</v>
+        <v>78</v>
       </c>
       <c r="E198" t="s">
         <v>27</v>
@@ -5357,13 +5354,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D199" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="E199" t="s">
         <v>27</v>
@@ -5374,13 +5371,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D200" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E200" t="s">
         <v>27</v>
@@ -5391,13 +5388,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D201" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E201" t="s">
         <v>27</v>
@@ -5408,13 +5405,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D202" t="s">
-        <v>74</v>
+        <v>248</v>
       </c>
       <c r="E202" t="s">
         <v>27</v>
@@ -5425,13 +5422,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D203" t="s">
-        <v>126</v>
+        <v>62</v>
       </c>
       <c r="E203" t="s">
         <v>27</v>
@@ -5442,13 +5439,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D204" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="E204" t="s">
         <v>27</v>
@@ -5459,13 +5456,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D205" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="E205" t="s">
         <v>27</v>
@@ -5476,13 +5473,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D206" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="E206" t="s">
         <v>27</v>
@@ -5493,13 +5490,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D207" t="s">
-        <v>66</v>
+        <v>111</v>
       </c>
       <c r="E207" t="s">
         <v>27</v>
@@ -5510,13 +5507,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D208" t="s">
-        <v>168</v>
+        <v>46</v>
       </c>
       <c r="E208" t="s">
         <v>27</v>
@@ -5527,13 +5524,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D209" t="s">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="E209" t="s">
         <v>27</v>
@@ -5544,13 +5541,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D210" t="s">
-        <v>310</v>
+        <v>218</v>
       </c>
       <c r="E210" t="s">
         <v>27</v>
@@ -5561,13 +5558,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D211" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="E211" t="s">
         <v>27</v>
@@ -5578,13 +5575,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D212" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="E212" t="s">
         <v>27</v>
@@ -5595,13 +5592,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D213" t="s">
-        <v>58</v>
+        <v>209</v>
       </c>
       <c r="E213" t="s">
         <v>27</v>
@@ -5612,13 +5609,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D214" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="E214" t="s">
         <v>27</v>
@@ -5629,13 +5626,13 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D215" t="s">
-        <v>140</v>
+        <v>196</v>
       </c>
       <c r="E215" t="s">
         <v>27</v>
@@ -5646,13 +5643,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D216" t="s">
-        <v>161</v>
+        <v>58</v>
       </c>
       <c r="E216" t="s">
         <v>27</v>
@@ -5663,13 +5660,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D217" t="s">
-        <v>156</v>
+        <v>315</v>
       </c>
       <c r="E217" t="s">
         <v>27</v>
@@ -5680,13 +5677,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D218" t="s">
-        <v>250</v>
+        <v>90</v>
       </c>
       <c r="E218" t="s">
         <v>27</v>
@@ -5697,13 +5694,13 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D219" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="E219" t="s">
         <v>27</v>
@@ -5714,13 +5711,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D220" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E220" t="s">
         <v>27</v>
@@ -5731,13 +5728,13 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D221" t="s">
-        <v>182</v>
+        <v>315</v>
       </c>
       <c r="E221" t="s">
         <v>27</v>
@@ -5748,13 +5745,13 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D222" t="s">
-        <v>92</v>
+        <v>233</v>
       </c>
       <c r="E222" t="s">
         <v>27</v>
@@ -5765,13 +5762,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D223" t="s">
-        <v>111</v>
+        <v>248</v>
       </c>
       <c r="E223" t="s">
         <v>27</v>
@@ -5782,13 +5779,13 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D224" t="s">
-        <v>297</v>
+        <v>198</v>
       </c>
       <c r="E224" t="s">
         <v>27</v>
@@ -5799,13 +5796,13 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D225" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E225" t="s">
         <v>27</v>
@@ -5816,13 +5813,13 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D226" t="s">
-        <v>327</v>
+        <v>132</v>
       </c>
       <c r="E226" t="s">
         <v>27</v>
@@ -5833,13 +5830,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D227" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E227" t="s">
         <v>27</v>
@@ -5850,13 +5847,13 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D228" t="s">
-        <v>140</v>
+        <v>196</v>
       </c>
       <c r="E228" t="s">
         <v>27</v>
@@ -5867,13 +5864,13 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D229" t="s">
-        <v>76</v>
+        <v>250</v>
       </c>
       <c r="E229" t="s">
         <v>27</v>
@@ -5884,13 +5881,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D230" t="s">
-        <v>68</v>
+        <v>143</v>
       </c>
       <c r="E230" t="s">
         <v>27</v>
@@ -5901,13 +5898,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D231" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="E231" t="s">
         <v>27</v>
@@ -5918,13 +5915,13 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D232" t="s">
-        <v>334</v>
+        <v>97</v>
       </c>
       <c r="E232" t="s">
         <v>27</v>
@@ -5935,13 +5932,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D233" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E233" t="s">
         <v>27</v>
@@ -5952,13 +5949,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D234" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="E234" t="s">
         <v>27</v>
@@ -5969,13 +5966,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D235" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="E235" t="s">
         <v>27</v>
@@ -5986,13 +5983,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D236" t="s">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="E236" t="s">
         <v>27</v>
@@ -6003,13 +6000,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D237" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="E237" t="s">
         <v>27</v>
@@ -6020,13 +6017,13 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D238" t="s">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="E238" t="s">
         <v>27</v>
@@ -6037,13 +6034,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D239" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="E239" t="s">
         <v>27</v>
@@ -6054,13 +6051,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D240" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E240" t="s">
         <v>27</v>
@@ -6071,13 +6068,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D241" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="E241" t="s">
         <v>27</v>
@@ -6088,13 +6085,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D242" t="s">
-        <v>238</v>
+        <v>163</v>
       </c>
       <c r="E242" t="s">
         <v>27</v>
@@ -6105,13 +6102,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D243" t="s">
-        <v>228</v>
+        <v>169</v>
       </c>
       <c r="E243" t="s">
         <v>27</v>
@@ -6122,13 +6119,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D244" t="s">
-        <v>195</v>
+        <v>343</v>
       </c>
       <c r="E244" t="s">
         <v>27</v>
@@ -6139,13 +6136,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D245" t="s">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="E245" t="s">
         <v>27</v>
@@ -6156,13 +6153,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D246" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E246" t="s">
         <v>27</v>
@@ -6173,13 +6170,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D247" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E247" t="s">
         <v>27</v>
@@ -6190,13 +6187,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D248" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="E248" t="s">
         <v>27</v>
@@ -6207,13 +6204,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D249" t="s">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="E249" t="s">
         <v>27</v>
@@ -6224,13 +6221,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D250" t="s">
-        <v>188</v>
+        <v>285</v>
       </c>
       <c r="E250" t="s">
         <v>27</v>
@@ -6241,13 +6238,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D251" t="s">
-        <v>72</v>
+        <v>152</v>
       </c>
       <c r="E251" t="s">
         <v>27</v>
@@ -6258,13 +6255,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D252" t="s">
-        <v>195</v>
+        <v>90</v>
       </c>
       <c r="E252" t="s">
         <v>27</v>
@@ -6275,13 +6272,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D253" t="s">
-        <v>334</v>
+        <v>225</v>
       </c>
       <c r="E253" t="s">
         <v>27</v>
@@ -6292,13 +6289,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D254" t="s">
-        <v>111</v>
+        <v>44</v>
       </c>
       <c r="E254" t="s">
         <v>27</v>
@@ -6309,13 +6306,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D255" t="s">
-        <v>186</v>
+        <v>50</v>
       </c>
       <c r="E255" t="s">
         <v>27</v>
@@ -6326,13 +6323,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D256" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="E256" t="s">
         <v>27</v>
@@ -6343,13 +6340,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D257" t="s">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="E257" t="s">
         <v>27</v>
@@ -6360,13 +6357,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D258" t="s">
-        <v>140</v>
+        <v>358</v>
       </c>
       <c r="E258" t="s">
         <v>27</v>
@@ -6377,13 +6374,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D259" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E259" t="s">
         <v>27</v>
@@ -6394,13 +6391,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D260" t="s">
-        <v>240</v>
+        <v>361</v>
       </c>
       <c r="E260" t="s">
         <v>27</v>
@@ -6411,13 +6408,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D261" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="E261" t="s">
         <v>27</v>
@@ -6428,7 +6425,7 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>25</v>
@@ -6445,13 +6442,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D263" t="s">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="E263" t="s">
         <v>27</v>
@@ -6462,13 +6459,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D264" t="s">
-        <v>334</v>
+        <v>141</v>
       </c>
       <c r="E264" t="s">
         <v>27</v>
@@ -6479,13 +6476,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D265" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="E265" t="s">
         <v>27</v>
@@ -6496,13 +6493,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D266" t="s">
-        <v>40</v>
+        <v>225</v>
       </c>
       <c r="E266" t="s">
         <v>27</v>
@@ -6513,13 +6510,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D267" t="s">
-        <v>102</v>
+        <v>167</v>
       </c>
       <c r="E267" t="s">
         <v>27</v>
@@ -6530,13 +6527,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D268" t="s">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="E268" t="s">
         <v>27</v>
@@ -6547,13 +6544,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D269" t="s">
-        <v>228</v>
+        <v>109</v>
       </c>
       <c r="E269" t="s">
         <v>27</v>
@@ -6564,13 +6561,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D270" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="E270" t="s">
         <v>27</v>
@@ -6581,13 +6578,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D271" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="E271" t="s">
         <v>27</v>
@@ -6598,13 +6595,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D272" t="s">
-        <v>250</v>
+        <v>66</v>
       </c>
       <c r="E272" t="s">
         <v>27</v>
@@ -6615,13 +6612,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D273" t="s">
-        <v>186</v>
+        <v>137</v>
       </c>
       <c r="E273" t="s">
         <v>27</v>
@@ -6632,13 +6629,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D274" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="E274" t="s">
         <v>27</v>
@@ -6649,13 +6646,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D275" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="E275" t="s">
         <v>27</v>
@@ -6666,13 +6663,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D276" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="E276" t="s">
         <v>27</v>
@@ -6683,13 +6680,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D277" t="s">
-        <v>166</v>
+        <v>58</v>
       </c>
       <c r="E277" t="s">
         <v>27</v>
@@ -6700,13 +6697,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D278" t="s">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="E278" t="s">
         <v>27</v>
@@ -6717,13 +6714,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D279" t="s">
-        <v>42</v>
+        <v>250</v>
       </c>
       <c r="E279" t="s">
         <v>27</v>
@@ -6734,13 +6731,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D280" t="s">
-        <v>70</v>
+        <v>223</v>
       </c>
       <c r="E280" t="s">
         <v>27</v>
@@ -6751,13 +6748,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D281" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E281" t="s">
         <v>27</v>
@@ -6768,13 +6765,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D282" t="s">
-        <v>250</v>
+        <v>102</v>
       </c>
       <c r="E282" t="s">
         <v>27</v>
@@ -6785,13 +6782,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D283" t="s">
-        <v>186</v>
+        <v>120</v>
       </c>
       <c r="E283" t="s">
         <v>27</v>
@@ -6802,13 +6799,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D284" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="E284" t="s">
         <v>27</v>
@@ -6819,13 +6816,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D285" t="s">
-        <v>250</v>
+        <v>167</v>
       </c>
       <c r="E285" t="s">
         <v>27</v>
@@ -6836,13 +6833,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D286" t="s">
-        <v>238</v>
+        <v>56</v>
       </c>
       <c r="E286" t="s">
         <v>27</v>
@@ -6853,13 +6850,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D287" t="s">
-        <v>124</v>
+        <v>250</v>
       </c>
       <c r="E287" t="s">
         <v>27</v>
@@ -6870,13 +6867,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D288" t="s">
-        <v>195</v>
+        <v>66</v>
       </c>
       <c r="E288" t="s">
         <v>27</v>
@@ -6887,13 +6884,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D289" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="E289" t="s">
         <v>27</v>
@@ -6904,13 +6901,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
+        <v>391</v>
+      </c>
+      <c r="C290" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D290" t="s">
         <v>392</v>
-      </c>
-      <c r="C290" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D290" t="s">
-        <v>297</v>
       </c>
       <c r="E290" t="s">
         <v>27</v>
@@ -6927,7 +6924,7 @@
         <v>25</v>
       </c>
       <c r="D291" t="s">
-        <v>72</v>
+        <v>209</v>
       </c>
       <c r="E291" t="s">
         <v>27</v>
@@ -6944,7 +6941,7 @@
         <v>25</v>
       </c>
       <c r="D292" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="E292" t="s">
         <v>27</v>
@@ -6961,7 +6958,7 @@
         <v>25</v>
       </c>
       <c r="D293" t="s">
-        <v>224</v>
+        <v>90</v>
       </c>
       <c r="E293" t="s">
         <v>27</v>
@@ -6978,7 +6975,7 @@
         <v>25</v>
       </c>
       <c r="D294" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E294" t="s">
         <v>27</v>
@@ -6995,7 +6992,7 @@
         <v>25</v>
       </c>
       <c r="D295" t="s">
-        <v>252</v>
+        <v>165</v>
       </c>
       <c r="E295" t="s">
         <v>27</v>
@@ -7012,7 +7009,7 @@
         <v>25</v>
       </c>
       <c r="D296" t="s">
-        <v>117</v>
+        <v>165</v>
       </c>
       <c r="E296" t="s">
         <v>27</v>
@@ -7029,7 +7026,7 @@
         <v>25</v>
       </c>
       <c r="D297" t="s">
-        <v>52</v>
+        <v>250</v>
       </c>
       <c r="E297" t="s">
         <v>27</v>
@@ -7046,7 +7043,7 @@
         <v>25</v>
       </c>
       <c r="D298" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="E298" t="s">
         <v>27</v>
@@ -7063,7 +7060,7 @@
         <v>25</v>
       </c>
       <c r="D299" t="s">
-        <v>327</v>
+        <v>50</v>
       </c>
       <c r="E299" t="s">
         <v>27</v>
@@ -7080,7 +7077,7 @@
         <v>25</v>
       </c>
       <c r="D300" t="s">
-        <v>403</v>
+        <v>124</v>
       </c>
       <c r="E300" t="s">
         <v>27</v>
@@ -7091,13 +7088,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D301" t="s">
-        <v>100</v>
+        <v>193</v>
       </c>
       <c r="E301" t="s">
         <v>27</v>
@@ -7108,13 +7105,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D302" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E302" t="s">
         <v>27</v>
@@ -7125,13 +7122,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D303" t="s">
-        <v>186</v>
+        <v>46</v>
       </c>
       <c r="E303" t="s">
         <v>27</v>
@@ -7142,7 +7139,7 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>25</v>
@@ -7159,13 +7156,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D305" t="s">
-        <v>56</v>
+        <v>152</v>
       </c>
       <c r="E305" t="s">
         <v>27</v>
@@ -7176,13 +7173,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D306" t="s">
-        <v>138</v>
+        <v>250</v>
       </c>
       <c r="E306" t="s">
         <v>27</v>
@@ -7193,13 +7190,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D307" t="s">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="E307" t="s">
         <v>27</v>
@@ -7210,13 +7207,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D308" t="s">
-        <v>64</v>
+        <v>223</v>
       </c>
       <c r="E308" t="s">
         <v>27</v>
@@ -7227,13 +7224,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D309" t="s">
-        <v>66</v>
+        <v>169</v>
       </c>
       <c r="E309" t="s">
         <v>27</v>
@@ -7244,13 +7241,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D310" t="s">
-        <v>240</v>
+        <v>143</v>
       </c>
       <c r="E310" t="s">
         <v>27</v>
@@ -7261,13 +7258,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D311" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="E311" t="s">
         <v>27</v>
@@ -7278,13 +7275,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D312" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="E312" t="s">
         <v>27</v>
@@ -7295,13 +7292,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D313" t="s">
-        <v>403</v>
+        <v>38</v>
       </c>
       <c r="E313" t="s">
         <v>27</v>
@@ -7312,13 +7309,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D314" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="E314" t="s">
         <v>27</v>
@@ -7329,13 +7326,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D315" t="s">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c r="E315" t="s">
         <v>27</v>
@@ -7346,13 +7343,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D316" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="E316" t="s">
         <v>27</v>
@@ -7363,13 +7360,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D317" t="s">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="E317" t="s">
         <v>27</v>
@@ -7380,13 +7377,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D318" t="s">
-        <v>88</v>
+        <v>167</v>
       </c>
       <c r="E318" t="s">
         <v>27</v>
@@ -7397,13 +7394,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D319" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="E319" t="s">
         <v>27</v>
@@ -7414,13 +7411,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D320" t="s">
-        <v>424</v>
+        <v>257</v>
       </c>
       <c r="E320" t="s">
         <v>27</v>
@@ -7431,13 +7428,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D321" t="s">
-        <v>68</v>
+        <v>424</v>
       </c>
       <c r="E321" t="s">
         <v>27</v>
@@ -7448,13 +7445,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D322" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="E322" t="s">
         <v>27</v>
@@ -7465,13 +7462,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D323" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="E323" t="s">
         <v>27</v>
@@ -7482,13 +7479,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D324" t="s">
-        <v>76</v>
+        <v>361</v>
       </c>
       <c r="E324" t="s">
         <v>27</v>
@@ -7499,13 +7496,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D325" t="s">
-        <v>126</v>
+        <v>361</v>
       </c>
       <c r="E325" t="s">
         <v>27</v>
@@ -7516,13 +7513,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D326" t="s">
-        <v>62</v>
+        <v>285</v>
       </c>
       <c r="E326" t="s">
         <v>27</v>
@@ -7533,13 +7530,13 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D327" t="s">
-        <v>159</v>
+        <v>198</v>
       </c>
       <c r="E327" t="s">
         <v>27</v>
@@ -7550,13 +7547,13 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D328" t="s">
-        <v>60</v>
+        <v>315</v>
       </c>
       <c r="E328" t="s">
         <v>27</v>
@@ -7567,13 +7564,13 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D329" t="s">
-        <v>238</v>
+        <v>163</v>
       </c>
       <c r="E329" t="s">
         <v>27</v>
@@ -7584,13 +7581,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D330" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="E330" t="s">
         <v>27</v>
@@ -7601,13 +7598,13 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D331" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="E331" t="s">
         <v>27</v>
@@ -7618,7 +7615,7 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>25</v>
@@ -7635,13 +7632,13 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D333" t="s">
-        <v>124</v>
+        <v>184</v>
       </c>
       <c r="E333" t="s">
         <v>27</v>
@@ -7652,13 +7649,13 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D334" t="s">
-        <v>439</v>
+        <v>182</v>
       </c>
       <c r="E334" t="s">
         <v>27</v>
@@ -7669,13 +7666,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D335" t="s">
-        <v>105</v>
+        <v>358</v>
       </c>
       <c r="E335" t="s">
         <v>27</v>
@@ -7686,13 +7683,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D336" t="s">
-        <v>38</v>
+        <v>233</v>
       </c>
       <c r="E336" t="s">
         <v>27</v>
@@ -7703,13 +7700,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D337" t="s">
-        <v>50</v>
+        <v>223</v>
       </c>
       <c r="E337" t="s">
         <v>27</v>
@@ -7720,13 +7717,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D338" t="s">
-        <v>168</v>
+        <v>86</v>
       </c>
       <c r="E338" t="s">
         <v>27</v>
@@ -7737,13 +7734,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D339" t="s">
-        <v>168</v>
+        <v>443</v>
       </c>
       <c r="E339" t="s">
         <v>27</v>
@@ -7754,13 +7751,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D340" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="E340" t="s">
         <v>27</v>
@@ -7771,13 +7768,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D341" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="E341" t="s">
         <v>27</v>
@@ -7788,13 +7785,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D342" t="s">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="E342" t="s">
         <v>27</v>
@@ -7805,13 +7802,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D343" t="s">
-        <v>38</v>
+        <v>171</v>
       </c>
       <c r="E343" t="s">
         <v>27</v>
@@ -7822,13 +7819,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D344" t="s">
-        <v>250</v>
+        <v>90</v>
       </c>
       <c r="E344" t="s">
         <v>27</v>
@@ -7839,13 +7836,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D345" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E345" t="s">
         <v>27</v>
@@ -7856,13 +7853,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D346" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="E346" t="s">
         <v>27</v>
@@ -7873,13 +7870,13 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D347" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="E347" t="s">
         <v>27</v>
@@ -7890,13 +7887,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D348" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E348" t="s">
         <v>27</v>
@@ -7907,13 +7904,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D349" t="s">
-        <v>275</v>
+        <v>141</v>
       </c>
       <c r="E349" t="s">
         <v>27</v>
@@ -7924,13 +7921,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D350" t="s">
-        <v>44</v>
+        <v>149</v>
       </c>
       <c r="E350" t="s">
         <v>27</v>
@@ -7941,13 +7938,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D351" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="E351" t="s">
         <v>27</v>
@@ -7958,13 +7955,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D352" t="s">
-        <v>138</v>
+        <v>86</v>
       </c>
       <c r="E352" t="s">
         <v>27</v>
@@ -7975,13 +7972,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D353" t="s">
-        <v>439</v>
+        <v>66</v>
       </c>
       <c r="E353" t="s">
         <v>27</v>
@@ -7992,13 +7989,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D354" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="E354" t="s">
         <v>27</v>
@@ -8009,13 +8006,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D355" t="s">
-        <v>122</v>
+        <v>358</v>
       </c>
       <c r="E355" t="s">
         <v>27</v>
@@ -8026,13 +8023,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D356" t="s">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="E356" t="s">
         <v>27</v>
@@ -8043,13 +8040,13 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D357" t="s">
-        <v>130</v>
+        <v>343</v>
       </c>
       <c r="E357" t="s">
         <v>27</v>
@@ -8060,13 +8057,13 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D358" t="s">
-        <v>84</v>
+        <v>233</v>
       </c>
       <c r="E358" t="s">
         <v>27</v>
@@ -8077,13 +8074,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D359" t="s">
-        <v>188</v>
+        <v>120</v>
       </c>
       <c r="E359" t="s">
         <v>27</v>
@@ -8094,13 +8091,13 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D360" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="E360" t="s">
         <v>27</v>
@@ -8111,13 +8108,13 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D361" t="s">
-        <v>166</v>
+        <v>95</v>
       </c>
       <c r="E361" t="s">
         <v>27</v>
@@ -8128,13 +8125,13 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D362" t="s">
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="E362" t="s">
         <v>27</v>
@@ -8145,13 +8142,13 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D363" t="s">
-        <v>154</v>
+        <v>248</v>
       </c>
       <c r="E363" t="s">
         <v>27</v>
@@ -8162,13 +8159,13 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D364" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="E364" t="s">
         <v>27</v>
@@ -8179,13 +8176,13 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D365" t="s">
-        <v>146</v>
+        <v>92</v>
       </c>
       <c r="E365" t="s">
         <v>27</v>
@@ -8196,13 +8193,13 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D366" t="s">
-        <v>193</v>
+        <v>130</v>
       </c>
       <c r="E366" t="s">
         <v>27</v>
@@ -8213,13 +8210,13 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D367" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="E367" t="s">
         <v>27</v>
@@ -8230,13 +8227,13 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D368" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E368" t="s">
         <v>27</v>
@@ -8247,13 +8244,13 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D369" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E369" t="s">
         <v>27</v>
@@ -8264,13 +8261,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D370" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E370" t="s">
         <v>27</v>
@@ -8281,13 +8278,13 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D371" t="s">
-        <v>76</v>
+        <v>200</v>
       </c>
       <c r="E371" t="s">
         <v>27</v>
@@ -8298,13 +8295,13 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D372" t="s">
-        <v>175</v>
+        <v>127</v>
       </c>
       <c r="E372" t="s">
         <v>27</v>
@@ -8315,13 +8312,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D373" t="s">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="E373" t="s">
         <v>27</v>
@@ -8332,13 +8329,13 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D374" t="s">
-        <v>297</v>
+        <v>38</v>
       </c>
       <c r="E374" t="s">
         <v>27</v>
@@ -8349,13 +8346,13 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D375" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="E375" t="s">
         <v>27</v>
@@ -8366,13 +8363,13 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D376" t="s">
-        <v>88</v>
+        <v>213</v>
       </c>
       <c r="E376" t="s">
         <v>27</v>
@@ -8383,7 +8380,7 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>25</v>
@@ -8400,13 +8397,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D378" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="E378" t="s">
         <v>27</v>
@@ -8417,13 +8414,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C379" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D379" t="s">
-        <v>120</v>
+        <v>211</v>
       </c>
       <c r="E379" t="s">
         <v>27</v>
@@ -8434,13 +8431,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D380" t="s">
-        <v>230</v>
+        <v>88</v>
       </c>
       <c r="E380" t="s">
         <v>27</v>
@@ -8451,13 +8448,13 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C381" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D381" t="s">
-        <v>122</v>
+        <v>189</v>
       </c>
       <c r="E381" t="s">
         <v>27</v>
@@ -8468,13 +8465,13 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D382" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="E382" t="s">
         <v>27</v>
@@ -8485,13 +8482,13 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D383" t="s">
-        <v>115</v>
+        <v>213</v>
       </c>
       <c r="E383" t="s">
         <v>27</v>
@@ -8502,13 +8499,13 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D384" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E384" t="s">
         <v>27</v>
@@ -8519,13 +8516,13 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D385" t="s">
-        <v>182</v>
+        <v>132</v>
       </c>
       <c r="E385" t="s">
         <v>27</v>
@@ -8536,13 +8533,13 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D386" t="s">
-        <v>275</v>
+        <v>116</v>
       </c>
       <c r="E386" t="s">
         <v>27</v>
@@ -8553,13 +8550,13 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D387" t="s">
-        <v>124</v>
+        <v>193</v>
       </c>
       <c r="E387" t="s">
         <v>27</v>
@@ -8570,13 +8567,13 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D388" t="s">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="E388" t="s">
         <v>27</v>
@@ -8587,13 +8584,13 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D389" t="s">
-        <v>144</v>
+        <v>193</v>
       </c>
       <c r="E389" t="s">
         <v>27</v>
@@ -8604,13 +8601,13 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D390" t="s">
-        <v>250</v>
+        <v>211</v>
       </c>
       <c r="E390" t="s">
         <v>27</v>
@@ -8621,13 +8618,13 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D391" t="s">
-        <v>42</v>
+        <v>233</v>
       </c>
       <c r="E391" t="s">
         <v>27</v>
@@ -8638,13 +8635,13 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D392" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E392" t="s">
         <v>27</v>
@@ -8655,13 +8652,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D393" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E393" t="s">
         <v>27</v>
@@ -8672,13 +8669,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D394" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E394" t="s">
         <v>27</v>
@@ -8689,13 +8686,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D395" t="s">
-        <v>173</v>
+        <v>225</v>
       </c>
       <c r="E395" t="s">
         <v>27</v>
@@ -8706,13 +8703,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D396" t="s">
-        <v>334</v>
+        <v>149</v>
       </c>
       <c r="E396" t="s">
         <v>27</v>
@@ -8723,13 +8720,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D397" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E397" t="s">
         <v>27</v>
@@ -8740,13 +8737,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D398" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="E398" t="s">
         <v>27</v>
@@ -8757,13 +8754,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D399" t="s">
-        <v>97</v>
+        <v>198</v>
       </c>
       <c r="E399" t="s">
         <v>27</v>
@@ -8774,13 +8771,13 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D400" t="s">
-        <v>88</v>
+        <v>424</v>
       </c>
       <c r="E400" t="s">
         <v>27</v>
@@ -8791,13 +8788,13 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D401" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="E401" t="s">
         <v>27</v>
@@ -8816,47 +8813,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1" t="s">
         <v>507</v>
-      </c>
-      <c r="B1" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B2" t="s">
         <v>509</v>
-      </c>
-      <c r="B2" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>510</v>
+      </c>
+      <c r="B3" t="s">
         <v>511</v>
-      </c>
-      <c r="B3" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>512</v>
+      </c>
+      <c r="B4" t="s">
         <v>513</v>
-      </c>
-      <c r="B4" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>514</v>
+      </c>
+      <c r="B5" t="s">
         <v>515</v>
-      </c>
-      <c r="B5" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B6">
         <v>400</v>
@@ -8864,7 +8861,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B7">
         <v>391</v>
@@ -8872,7 +8869,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B8">
         <v>9</v>
@@ -8880,7 +8877,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8888,10 +8885,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>520</v>
+      </c>
+      <c r="B10" t="s">
         <v>521</v>
-      </c>
-      <c r="B10" t="s">
-        <v>522</v>
       </c>
     </row>
   </sheetData>

--- a/reports/selenium/Excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/Excel/Automation_Test_Report.xlsx
@@ -35,1245 +35,1251 @@
     <t>FAILED</t>
   </si>
   <si>
-    <t>20.97</t>
+    <t>20.72</t>
   </si>
   <si>
     <t xml:space="preserve">Landing page did not load — Sign In button not found
-Wait timed out after 20066ms</t>
+Wait timed out after 20187ms</t>
   </si>
   <si>
     <t>should navigate to the login form</t>
   </si>
   <si>
+    <t>20.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
+Wait timed out after 20032ms</t>
+  </si>
+  <si>
+    <t>should login with valid credentials and reach the dashboard</t>
+  </si>
+  <si>
+    <t>20.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
+Wait timed out after 20162ms</t>
+  </si>
+  <si>
+    <t>should reject invalid credentials with an error message</t>
+  </si>
+  <si>
+    <t>20.51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
+Wait timed out after 20151ms</t>
+  </si>
+  <si>
+    <t>should open the sign-up form from landing</t>
+  </si>
+  <si>
+    <t>20.93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signup-btn"])
+Wait timed out after 20188ms</t>
+  </si>
+  <si>
+    <t>Security — should reject login for invalid credentials</t>
+  </si>
+  <si>
     <t>20.52</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20036ms</t>
-  </si>
-  <si>
-    <t>should login with valid credentials and reach the dashboard</t>
-  </si>
-  <si>
-    <t>20.87</t>
+Wait timed out after 20006ms</t>
+  </si>
+  <si>
+    <t>Security — should prevent access to protected routes/dashboard for unauthenticated users</t>
+  </si>
+  <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>3.67</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Security — should not execute XSS script payloads submitted in login fields</t>
+  </si>
+  <si>
+    <t>20.54</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20194ms</t>
-  </si>
-  <si>
-    <t>should reject invalid credentials with an error message</t>
-  </si>
-  <si>
-    <t>20.44</t>
+Wait timed out after 20175ms</t>
+  </si>
+  <si>
+    <t>Security — should enforce session termination and clean storage upon logout</t>
+  </si>
+  <si>
+    <t>20.49</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20004ms</t>
-  </si>
-  <si>
-    <t>should open the sign-up form from landing</t>
-  </si>
-  <si>
-    <t>20.93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signup-btn"])
-Wait timed out after 20197ms</t>
-  </si>
-  <si>
-    <t>Security — should reject login for invalid credentials</t>
-  </si>
-  <si>
-    <t>20.99</t>
+Wait timed out after 20139ms</t>
+  </si>
+  <si>
+    <t>Security — should confirm Firebase authentication rejects empty credentials</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20053ms</t>
-  </si>
-  <si>
-    <t>Security — should prevent access to protected routes/dashboard for unauthenticated users</t>
-  </si>
-  <si>
-    <t>PASSED</t>
-  </si>
-  <si>
-    <t>3.31</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Security — should not execute XSS script payloads submitted in login fields</t>
-  </si>
-  <si>
-    <t>20.55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20196ms</t>
-  </si>
-  <si>
-    <t>Security — should enforce session termination and clean storage upon logout</t>
-  </si>
-  <si>
-    <t>20.77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20015ms</t>
-  </si>
-  <si>
-    <t>Security — should confirm Firebase authentication rejects empty credentials</t>
-  </si>
-  <si>
-    <t>20.61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20177ms</t>
+Wait timed out after 20148ms</t>
   </si>
   <si>
     <t>Security — should not expose sensitive API keys or secrets in page HTML source</t>
   </si>
   <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #11)</t>
+  </si>
+  <si>
+    <t>0.88</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #12)</t>
+  </si>
+  <si>
     <t>0.77</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #11)</t>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #13)</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #14)</t>
+  </si>
+  <si>
+    <t>0.91</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #15)</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #16)</t>
+  </si>
+  <si>
+    <t>0.30</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #17)</t>
+  </si>
+  <si>
+    <t>0.59</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #18)</t>
+  </si>
+  <si>
+    <t>0.28</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #19)</t>
+  </si>
+  <si>
+    <t>0.73</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #20)</t>
+  </si>
+  <si>
+    <t>0.78</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #21)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #22)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #23)</t>
+  </si>
+  <si>
+    <t>0.61</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #24)</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #25)</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #26)</t>
+  </si>
+  <si>
+    <t>0.53</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #27)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #28)</t>
+  </si>
+  <si>
+    <t>0.82</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #29)</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #30)</t>
+  </si>
+  <si>
+    <t>0.60</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #31)</t>
+  </si>
+  <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #32)</t>
+  </si>
+  <si>
+    <t>0.84</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #33)</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #34)</t>
+  </si>
+  <si>
+    <t>0.49</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #35)</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #36)</t>
+  </si>
+  <si>
+    <t>0.54</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #37)</t>
+  </si>
+  <si>
+    <t>0.67</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #38)</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #39)</t>
+  </si>
+  <si>
+    <t>0.81</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #40)</t>
+  </si>
+  <si>
+    <t>0.87</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #41)</t>
+  </si>
+  <si>
+    <t>0.69</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #42)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #43)</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #44)</t>
   </si>
   <si>
     <t>0.45</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #12)</t>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #45)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #46)</t>
+  </si>
+  <si>
+    <t>0.44</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #47)</t>
+  </si>
+  <si>
+    <t>0.93</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #48)</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #49)</t>
+  </si>
+  <si>
+    <t>0.47</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #50)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #51)</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #52)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #53)</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #54)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #55)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #56)</t>
+  </si>
+  <si>
+    <t>0.96</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #57)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #58)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #59)</t>
+  </si>
+  <si>
+    <t>0.63</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #60)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #61)</t>
+  </si>
+  <si>
+    <t>0.55</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #62)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #63)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #64)</t>
+  </si>
+  <si>
+    <t>0.31</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #65)</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #66)</t>
+  </si>
+  <si>
+    <t>0.79</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #67)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #68)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #69)</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #70)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #71)</t>
+  </si>
+  <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #72)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #73)</t>
+  </si>
+  <si>
+    <t>0.90</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #74)</t>
   </si>
   <si>
     <t>0.51</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #13)</t>
-  </si>
-  <si>
-    <t>0.79</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #14)</t>
-  </si>
-  <si>
-    <t>0.81</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #15)</t>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #75)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #76)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #77)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #78)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #79)</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #80)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #81)</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #82)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #83)</t>
+  </si>
+  <si>
+    <t>0.66</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #84)</t>
+  </si>
+  <si>
+    <t>0.74</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #85)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #86)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #87)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #88)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #89)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #90)</t>
+  </si>
+  <si>
+    <t>0.76</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #91)</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #92)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #93)</t>
+  </si>
+  <si>
+    <t>0.89</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #94)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #95)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #96)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #97)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #98)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #99)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #100)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #101)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #102)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #103)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #104)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #105)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #106)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #107)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #108)</t>
+  </si>
+  <si>
+    <t>0.80</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #109)</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #110)</t>
+  </si>
+  <si>
+    <t>0.37</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #111)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #112)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #113)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #114)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #115)</t>
+  </si>
+  <si>
+    <t>0.99</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #116)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #117)</t>
+  </si>
+  <si>
+    <t>0.71</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #118)</t>
+  </si>
+  <si>
+    <t>0.83</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #119)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #120)</t>
+  </si>
+  <si>
+    <t>0.70</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #121)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #122)</t>
+  </si>
+  <si>
+    <t>0.52</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #123)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #124)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #125)</t>
+  </si>
+  <si>
+    <t>0.92</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #126)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #127)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #128)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #129)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #130)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #131)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #132)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #133)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #134)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #135)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #136)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #137)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #138)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #139)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #140)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #141)</t>
   </si>
   <si>
     <t>0.38</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #16)</t>
-  </si>
-  <si>
-    <t>0.89</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #17)</t>
-  </si>
-  <si>
-    <t>0.42</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #18)</t>
-  </si>
-  <si>
-    <t>0.92</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #19)</t>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #142)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #143)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #144)</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #145)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #146)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #147)</t>
+  </si>
+  <si>
+    <t>0.48</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #148)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #149)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #150)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #151)</t>
+  </si>
+  <si>
+    <t>0.29</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #152)</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #153)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #154)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #155)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #156)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #157)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #158)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #159)</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #160)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #161)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #162)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #163)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #164)</t>
+  </si>
+  <si>
+    <t>0.32</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #165)</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #166)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #167)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #168)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #169)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #170)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #171)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #172)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #173)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #174)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #175)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #176)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #177)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #178)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #179)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #180)</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #181)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #182)</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #183)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #184)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #185)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #186)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #187)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #188)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #189)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #190)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #191)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #192)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #193)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #194)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #195)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #196)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #197)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #198)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #199)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #200)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #201)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #202)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #203)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #204)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #205)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #206)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #207)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #208)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #209)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #210)</t>
+  </si>
+  <si>
+    <t>0.40</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #211)</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #212)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #213)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #214)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #215)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #216)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #217)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #218)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #219)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #220)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #221)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #222)</t>
+  </si>
+  <si>
+    <t>0.68</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #223)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #224)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #225)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #226)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #227)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #228)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #229)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #230)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #231)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #232)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #233)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #234)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #235)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #236)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #237)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #238)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #239)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #240)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #241)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #242)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #243)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #244)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #245)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #246)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #247)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #248)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #249)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #250)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #251)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #252)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #253)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #254)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #255)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #256)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #257)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #258)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #259)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #260)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #261)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #262)</t>
+  </si>
+  <si>
+    <t>0.65</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #263)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #264)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #265)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #266)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #267)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #268)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #269)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #270)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #271)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #272)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #273)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #274)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #275)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #276)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #277)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #278)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #279)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #280)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #281)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #282)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #283)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #284)</t>
   </si>
   <si>
     <t>0.72</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #20)</t>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #285)</t>
   </si>
   <si>
     <t>0.46</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #21)</t>
-  </si>
-  <si>
-    <t>0.70</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #22)</t>
-  </si>
-  <si>
-    <t>0.24</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #23)</t>
-  </si>
-  <si>
-    <t>0.40</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #24)</t>
-  </si>
-  <si>
-    <t>0.58</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #25)</t>
-  </si>
-  <si>
-    <t>0.97</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #26)</t>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #286)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #287)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #288)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #289)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #290)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #291)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #292)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #293)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #294)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #295)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #296)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #297)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #298)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #299)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #300)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #301)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #302)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #303)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #304)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #305)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #306)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #307)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #308)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #309)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #310)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #311)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #312)</t>
   </si>
   <si>
     <t>0.86</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #27)</t>
-  </si>
-  <si>
-    <t>0.83</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #28)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #29)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #30)</t>
-  </si>
-  <si>
-    <t>0.29</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #31)</t>
-  </si>
-  <si>
-    <t>0.61</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #32)</t>
-  </si>
-  <si>
-    <t>0.28</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #33)</t>
-  </si>
-  <si>
-    <t>0.56</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #34)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #35)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #36)</t>
-  </si>
-  <si>
-    <t>0.49</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #37)</t>
-  </si>
-  <si>
-    <t>0.93</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #38)</t>
-  </si>
-  <si>
-    <t>0.53</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #39)</t>
-  </si>
-  <si>
-    <t>0.33</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #40)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #41)</t>
-  </si>
-  <si>
-    <t>0.64</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #42)</t>
-  </si>
-  <si>
-    <t>0.96</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #43)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #44)</t>
-  </si>
-  <si>
-    <t>0.25</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #45)</t>
-  </si>
-  <si>
-    <t>0.20</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #46)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #47)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #48)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #49)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #50)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #51)</t>
-  </si>
-  <si>
-    <t>0.71</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #52)</t>
-  </si>
-  <si>
-    <t>0.52</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #53)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #54)</t>
-  </si>
-  <si>
-    <t>0.34</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #55)</t>
-  </si>
-  <si>
-    <t>0.90</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #56)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #57)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #58)</t>
-  </si>
-  <si>
-    <t>0.32</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #59)</t>
-  </si>
-  <si>
-    <t>0.65</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #60)</t>
-  </si>
-  <si>
-    <t>0.54</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #61)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #62)</t>
-  </si>
-  <si>
-    <t>0.66</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #63)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #64)</t>
-  </si>
-  <si>
-    <t>0.91</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #65)</t>
-  </si>
-  <si>
-    <t>0.63</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #66)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #67)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #68)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #69)</t>
-  </si>
-  <si>
-    <t>0.76</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #70)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #71)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #72)</t>
-  </si>
-  <si>
-    <t>0.74</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #73)</t>
-  </si>
-  <si>
-    <t>0.27</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #74)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #75)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #76)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #77)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #78)</t>
-  </si>
-  <si>
-    <t>0.78</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #79)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #80)</t>
-  </si>
-  <si>
-    <t>0.41</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #81)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #82)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #83)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #84)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #85)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #86)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #87)</t>
-  </si>
-  <si>
-    <t>0.35</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #88)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #89)</t>
-  </si>
-  <si>
-    <t>0.94</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #90)</t>
-  </si>
-  <si>
-    <t>0.73</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #91)</t>
-  </si>
-  <si>
-    <t>0.36</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #92)</t>
-  </si>
-  <si>
-    <t>0.98</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #93)</t>
-  </si>
-  <si>
-    <t>0.67</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #94)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #95)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #96)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #97)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #98)</t>
-  </si>
-  <si>
-    <t>0.26</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #99)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #100)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #101)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #102)</t>
-  </si>
-  <si>
-    <t>0.30</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #103)</t>
-  </si>
-  <si>
-    <t>0.80</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #104)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #105)</t>
-  </si>
-  <si>
-    <t>0.95</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #106)</t>
-  </si>
-  <si>
-    <t>0.31</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #107)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #108)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #109)</t>
-  </si>
-  <si>
-    <t>0.43</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #110)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #111)</t>
-  </si>
-  <si>
-    <t>0.99</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #112)</t>
-  </si>
-  <si>
-    <t>0.75</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #113)</t>
-  </si>
-  <si>
-    <t>0.88</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #114)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #115)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #116)</t>
-  </si>
-  <si>
-    <t>0.47</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #117)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #118)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #119)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #120)</t>
-  </si>
-  <si>
-    <t>0.48</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #121)</t>
-  </si>
-  <si>
-    <t>0.22</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #122)</t>
-  </si>
-  <si>
-    <t>0.21</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #123)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #124)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #125)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #126)</t>
-  </si>
-  <si>
-    <t>0.44</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #127)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #128)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #129)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #130)</t>
-  </si>
-  <si>
-    <t>0.69</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #131)</t>
-  </si>
-  <si>
-    <t>0.60</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #132)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #133)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #134)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #135)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #136)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #137)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #138)</t>
-  </si>
-  <si>
-    <t>0.85</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #139)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #140)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #141)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #142)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #143)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #144)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #145)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #146)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #147)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #148)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #149)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #150)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #151)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #152)</t>
-  </si>
-  <si>
-    <t>0.87</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #153)</t>
-  </si>
-  <si>
-    <t>0.23</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #154)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #155)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #156)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #157)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #158)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #159)</t>
-  </si>
-  <si>
-    <t>0.57</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #160)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #161)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #162)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #163)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #164)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #165)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #166)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #167)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #168)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #169)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #170)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #171)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #172)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #173)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #174)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #175)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #176)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #177)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #178)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #179)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #180)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #181)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #182)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #183)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #184)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #185)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #186)</t>
-  </si>
-  <si>
-    <t>0.82</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #187)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #188)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #189)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #190)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #191)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #192)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #193)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #194)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #195)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #196)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #197)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #198)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #199)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #200)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #201)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #202)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #203)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #204)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #205)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #206)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #207)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #208)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #209)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #210)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #211)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #212)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #213)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #214)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #215)</t>
-  </si>
-  <si>
-    <t>0.68</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #216)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #217)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #218)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #219)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #220)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #221)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #222)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #223)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #224)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #225)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #226)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #227)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #228)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #229)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #230)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #231)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #232)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #233)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #234)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #235)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #236)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #237)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #238)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #239)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #240)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #241)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #242)</t>
-  </si>
-  <si>
-    <t>0.39</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #243)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #244)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #245)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #246)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #247)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #248)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #249)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #250)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #251)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #252)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #253)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #254)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #255)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #256)</t>
-  </si>
-  <si>
-    <t>0.55</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #257)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #258)</t>
-  </si>
-  <si>
-    <t>0.62</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #259)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #260)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #261)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #262)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #263)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #264)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #265)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #266)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #267)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #268)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #269)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #270)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #271)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #272)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #273)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #274)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #275)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #276)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #277)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #278)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #279)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #280)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #281)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #282)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #283)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #284)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #285)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #286)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #287)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #288)</t>
-  </si>
-  <si>
-    <t>1.00</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #289)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #290)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #291)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #292)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #293)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #294)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #295)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #296)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #297)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #298)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #299)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #300)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #301)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #302)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #303)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #304)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #305)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #306)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #307)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #308)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #309)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #310)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #311)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #312)</t>
-  </si>
-  <si>
     <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #313)</t>
   </si>
   <si>
@@ -1295,9 +1301,6 @@
     <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #319)</t>
   </si>
   <si>
-    <t>0.50</t>
-  </si>
-  <si>
     <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #320)</t>
   </si>
   <si>
@@ -1352,9 +1355,6 @@
     <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #337)</t>
   </si>
   <si>
-    <t>0.84</t>
-  </si>
-  <si>
     <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #338)</t>
   </si>
   <si>
@@ -1550,13 +1550,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>15</t>
+    <t>16</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 13:53:48 UTC</t>
+    <t>2026-06-23 14:01:39 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1568,7 +1568,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>0bdfd4b</t>
+    <t>e40a5d4</t>
   </si>
   <si>
     <t>Total</t>
@@ -2164,10 +2164,10 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
         <v>35</v>
-      </c>
-      <c r="E11" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2175,13 +2175,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
         <v>37</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" t="s">
-        <v>38</v>
       </c>
       <c r="E12" t="s">
         <v>27</v>
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
         <v>39</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" t="s">
-        <v>40</v>
       </c>
       <c r="E13" t="s">
         <v>27</v>
@@ -2209,13 +2209,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
         <v>41</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" t="s">
-        <v>42</v>
       </c>
       <c r="E14" t="s">
         <v>27</v>
@@ -2226,13 +2226,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" t="s">
         <v>43</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" t="s">
-        <v>44</v>
       </c>
       <c r="E15" t="s">
         <v>27</v>
@@ -2243,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" t="s">
         <v>45</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" t="s">
-        <v>46</v>
       </c>
       <c r="E16" t="s">
         <v>27</v>
@@ -2260,13 +2260,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" t="s">
         <v>47</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" t="s">
-        <v>48</v>
       </c>
       <c r="E17" t="s">
         <v>27</v>
@@ -2277,13 +2277,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" t="s">
         <v>49</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" t="s">
-        <v>50</v>
       </c>
       <c r="E18" t="s">
         <v>27</v>
@@ -2294,13 +2294,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" t="s">
         <v>51</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" t="s">
-        <v>52</v>
       </c>
       <c r="E19" t="s">
         <v>27</v>
@@ -2311,13 +2311,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" t="s">
         <v>53</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" t="s">
-        <v>54</v>
       </c>
       <c r="E20" t="s">
         <v>27</v>
@@ -2328,13 +2328,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" t="s">
         <v>55</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" t="s">
-        <v>56</v>
       </c>
       <c r="E21" t="s">
         <v>27</v>
@@ -2345,13 +2345,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" t="s">
         <v>57</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" t="s">
-        <v>58</v>
       </c>
       <c r="E22" t="s">
         <v>27</v>
@@ -2362,13 +2362,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E23" t="s">
         <v>27</v>
@@ -2379,13 +2379,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="E24" t="s">
         <v>27</v>
@@ -2396,13 +2396,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E25" t="s">
         <v>27</v>
@@ -2413,13 +2413,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E26" t="s">
         <v>27</v>
@@ -2430,13 +2430,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E27" t="s">
         <v>27</v>
@@ -2447,13 +2447,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E28" t="s">
         <v>27</v>
@@ -2464,13 +2464,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="E29" t="s">
         <v>27</v>
@@ -2481,13 +2481,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="E30" t="s">
         <v>27</v>
@@ -2498,13 +2498,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E31" t="s">
         <v>27</v>
@@ -2515,13 +2515,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E32" t="s">
         <v>27</v>
@@ -2532,13 +2532,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D33" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E33" t="s">
         <v>27</v>
@@ -2549,13 +2549,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D34" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E34" t="s">
         <v>27</v>
@@ -2566,13 +2566,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E35" t="s">
         <v>27</v>
@@ -2583,13 +2583,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="E36" t="s">
         <v>27</v>
@@ -2600,13 +2600,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D37" t="s">
         <v>84</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D37" t="s">
-        <v>72</v>
       </c>
       <c r="E37" t="s">
         <v>27</v>
@@ -2691,7 +2691,7 @@
         <v>25</v>
       </c>
       <c r="D42" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="E42" t="s">
         <v>27</v>
@@ -2702,13 +2702,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E43" t="s">
         <v>27</v>
@@ -2719,13 +2719,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="E44" t="s">
         <v>27</v>
@@ -2742,7 +2742,7 @@
         <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="E45" t="s">
         <v>27</v>
@@ -2753,13 +2753,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E46" t="s">
         <v>27</v>
@@ -2770,13 +2770,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E47" t="s">
         <v>27</v>
@@ -2793,7 +2793,7 @@
         <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="E48" t="s">
         <v>27</v>
@@ -2804,13 +2804,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="E49" t="s">
         <v>27</v>
@@ -2821,13 +2821,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="E50" t="s">
         <v>27</v>
@@ -2838,13 +2838,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D51" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="E51" t="s">
         <v>27</v>
@@ -2855,13 +2855,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E52" t="s">
         <v>27</v>
@@ -2872,13 +2872,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E53" t="s">
         <v>27</v>
@@ -2889,13 +2889,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="E54" t="s">
         <v>27</v>
@@ -2906,13 +2906,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D55" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="E55" t="s">
         <v>27</v>
@@ -2923,13 +2923,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D56" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E56" t="s">
         <v>27</v>
@@ -2940,13 +2940,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D57" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E57" t="s">
         <v>27</v>
@@ -2957,13 +2957,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D58" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="E58" t="s">
         <v>27</v>
@@ -2974,13 +2974,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D59" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="E59" t="s">
         <v>27</v>
@@ -2991,13 +2991,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D60" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="E60" t="s">
         <v>27</v>
@@ -3008,13 +3008,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E61" t="s">
         <v>27</v>
@@ -3025,13 +3025,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D62" t="s">
-        <v>124</v>
+        <v>76</v>
       </c>
       <c r="E62" t="s">
         <v>27</v>
@@ -3042,13 +3042,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D63" t="s">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="E63" t="s">
         <v>27</v>
@@ -3059,13 +3059,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D64" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="E64" t="s">
         <v>27</v>
@@ -3076,13 +3076,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="E65" t="s">
         <v>27</v>
@@ -3093,13 +3093,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D66" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E66" t="s">
         <v>27</v>
@@ -3110,13 +3110,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D67" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E67" t="s">
         <v>27</v>
@@ -3127,13 +3127,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E68" t="s">
         <v>27</v>
@@ -3144,13 +3144,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D69" t="s">
-        <v>111</v>
+        <v>41</v>
       </c>
       <c r="E69" t="s">
         <v>27</v>
@@ -3161,13 +3161,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D70" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="E70" t="s">
         <v>27</v>
@@ -3178,13 +3178,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D71" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E71" t="s">
         <v>27</v>
@@ -3195,13 +3195,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D72" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="E72" t="s">
         <v>27</v>
@@ -3212,13 +3212,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D73" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="E73" t="s">
         <v>27</v>
@@ -3229,13 +3229,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D74" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="E74" t="s">
         <v>27</v>
@@ -3246,13 +3246,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D75" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E75" t="s">
         <v>27</v>
@@ -3263,13 +3263,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D76" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="E76" t="s">
         <v>27</v>
@@ -3280,13 +3280,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D77" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="E77" t="s">
         <v>27</v>
@@ -3297,13 +3297,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="E78" t="s">
         <v>27</v>
@@ -3314,13 +3314,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D79" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="E79" t="s">
         <v>27</v>
@@ -3331,13 +3331,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D80" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="E80" t="s">
         <v>27</v>
@@ -3348,13 +3348,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D81" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="E81" t="s">
         <v>27</v>
@@ -3365,13 +3365,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D82" t="s">
-        <v>152</v>
+        <v>67</v>
       </c>
       <c r="E82" t="s">
         <v>27</v>
@@ -3382,13 +3382,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D83" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="E83" t="s">
         <v>27</v>
@@ -3399,13 +3399,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D84" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="E84" t="s">
         <v>27</v>
@@ -3416,13 +3416,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D85" t="s">
-        <v>100</v>
+        <v>159</v>
       </c>
       <c r="E85" t="s">
         <v>27</v>
@@ -3433,13 +3433,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D86" t="s">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="E86" t="s">
         <v>27</v>
@@ -3450,13 +3450,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D87" t="s">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="E87" t="s">
         <v>27</v>
@@ -3467,13 +3467,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D88" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="E88" t="s">
         <v>27</v>
@@ -3484,13 +3484,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D89" t="s">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="E89" t="s">
         <v>27</v>
@@ -3501,13 +3501,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D90" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="E90" t="s">
         <v>27</v>
@@ -3518,13 +3518,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D91" t="s">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="E91" t="s">
         <v>27</v>
@@ -3535,13 +3535,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D92" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E92" t="s">
         <v>27</v>
@@ -3552,13 +3552,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D93" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E93" t="s">
         <v>27</v>
@@ -3569,13 +3569,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D94" t="s">
-        <v>169</v>
+        <v>124</v>
       </c>
       <c r="E94" t="s">
         <v>27</v>
@@ -3586,13 +3586,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D95" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E95" t="s">
         <v>27</v>
@@ -3603,13 +3603,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D96" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="E96" t="s">
         <v>27</v>
@@ -3620,13 +3620,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D97" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="E97" t="s">
         <v>27</v>
@@ -3637,13 +3637,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D98" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="E98" t="s">
         <v>27</v>
@@ -3654,13 +3654,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D99" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="E99" t="s">
         <v>27</v>
@@ -3671,13 +3671,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D100" t="s">
-        <v>177</v>
+        <v>88</v>
       </c>
       <c r="E100" t="s">
         <v>27</v>
@@ -3688,13 +3688,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E101" t="s">
         <v>27</v>
@@ -3705,13 +3705,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D102" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="E102" t="s">
         <v>27</v>
@@ -3722,13 +3722,13 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D103" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="E103" t="s">
         <v>27</v>
@@ -3739,13 +3739,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D104" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="E104" t="s">
         <v>27</v>
@@ -3762,7 +3762,7 @@
         <v>25</v>
       </c>
       <c r="D105" t="s">
-        <v>184</v>
+        <v>124</v>
       </c>
       <c r="E105" t="s">
         <v>27</v>
@@ -3773,13 +3773,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D106" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E106" t="s">
         <v>27</v>
@@ -3790,13 +3790,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D107" t="s">
-        <v>187</v>
+        <v>51</v>
       </c>
       <c r="E107" t="s">
         <v>27</v>
@@ -3807,13 +3807,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D108" t="s">
-        <v>189</v>
+        <v>113</v>
       </c>
       <c r="E108" t="s">
         <v>27</v>
@@ -3824,13 +3824,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D109" t="s">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E109" t="s">
         <v>27</v>
@@ -3841,13 +3841,13 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D110" t="s">
-        <v>52</v>
+        <v>189</v>
       </c>
       <c r="E110" t="s">
         <v>27</v>
@@ -3858,13 +3858,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D111" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E111" t="s">
         <v>27</v>
@@ -3875,13 +3875,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D112" t="s">
-        <v>58</v>
+        <v>193</v>
       </c>
       <c r="E112" t="s">
         <v>27</v>
@@ -3892,13 +3892,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D113" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="E113" t="s">
         <v>27</v>
@@ -3909,13 +3909,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D114" t="s">
-        <v>198</v>
+        <v>86</v>
       </c>
       <c r="E114" t="s">
         <v>27</v>
@@ -3926,13 +3926,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D115" t="s">
-        <v>200</v>
+        <v>124</v>
       </c>
       <c r="E115" t="s">
         <v>27</v>
@@ -3943,13 +3943,13 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D116" t="s">
-        <v>165</v>
+        <v>63</v>
       </c>
       <c r="E116" t="s">
         <v>27</v>
@@ -3960,13 +3960,13 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D117" t="s">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="E117" t="s">
         <v>27</v>
@@ -3977,13 +3977,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D118" t="s">
-        <v>204</v>
+        <v>135</v>
       </c>
       <c r="E118" t="s">
         <v>27</v>
@@ -3994,13 +3994,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D119" t="s">
-        <v>88</v>
+        <v>202</v>
       </c>
       <c r="E119" t="s">
         <v>27</v>
@@ -4011,13 +4011,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D120" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="E120" t="s">
         <v>27</v>
@@ -4028,13 +4028,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D121" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="E121" t="s">
         <v>27</v>
@@ -4045,13 +4045,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D122" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E122" t="s">
         <v>27</v>
@@ -4062,13 +4062,13 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D123" t="s">
-        <v>211</v>
+        <v>43</v>
       </c>
       <c r="E123" t="s">
         <v>27</v>
@@ -4079,13 +4079,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D124" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E124" t="s">
         <v>27</v>
@@ -4096,13 +4096,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D125" t="s">
-        <v>165</v>
+        <v>108</v>
       </c>
       <c r="E125" t="s">
         <v>27</v>
@@ -4113,13 +4113,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D126" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E126" t="s">
         <v>27</v>
@@ -4130,13 +4130,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D127" t="s">
-        <v>95</v>
+        <v>214</v>
       </c>
       <c r="E127" t="s">
         <v>27</v>
@@ -4147,13 +4147,13 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D128" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="E128" t="s">
         <v>27</v>
@@ -4164,13 +4164,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D129" t="s">
-        <v>141</v>
+        <v>70</v>
       </c>
       <c r="E129" t="s">
         <v>27</v>
@@ -4181,13 +4181,13 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D130" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="E130" t="s">
         <v>27</v>
@@ -4198,13 +4198,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D131" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="E131" t="s">
         <v>27</v>
@@ -4215,13 +4215,13 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D132" t="s">
-        <v>223</v>
+        <v>116</v>
       </c>
       <c r="E132" t="s">
         <v>27</v>
@@ -4232,13 +4232,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D133" t="s">
-        <v>225</v>
+        <v>53</v>
       </c>
       <c r="E133" t="s">
         <v>27</v>
@@ -4249,13 +4249,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D134" t="s">
-        <v>209</v>
+        <v>94</v>
       </c>
       <c r="E134" t="s">
         <v>27</v>
@@ -4266,13 +4266,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D135" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E135" t="s">
         <v>27</v>
@@ -4283,13 +4283,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D136" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="E136" t="s">
         <v>27</v>
@@ -4300,13 +4300,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D137" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="E137" t="s">
         <v>27</v>
@@ -4317,13 +4317,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D138" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E138" t="s">
         <v>27</v>
@@ -4334,13 +4334,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D139" t="s">
-        <v>182</v>
+        <v>99</v>
       </c>
       <c r="E139" t="s">
         <v>27</v>
@@ -4351,13 +4351,13 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D140" t="s">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="E140" t="s">
         <v>27</v>
@@ -4368,13 +4368,13 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D141" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="E141" t="s">
         <v>27</v>
@@ -4385,13 +4385,13 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D142" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="E142" t="s">
         <v>27</v>
@@ -4402,13 +4402,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D143" t="s">
-        <v>196</v>
+        <v>231</v>
       </c>
       <c r="E143" t="s">
         <v>27</v>
@@ -4419,13 +4419,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D144" t="s">
-        <v>48</v>
+        <v>173</v>
       </c>
       <c r="E144" t="s">
         <v>27</v>
@@ -4436,13 +4436,13 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D145" t="s">
-        <v>204</v>
+        <v>61</v>
       </c>
       <c r="E145" t="s">
         <v>27</v>
@@ -4453,13 +4453,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D146" t="s">
-        <v>56</v>
+        <v>235</v>
       </c>
       <c r="E146" t="s">
         <v>27</v>
@@ -4470,13 +4470,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D147" t="s">
-        <v>132</v>
+        <v>65</v>
       </c>
       <c r="E147" t="s">
         <v>27</v>
@@ -4487,13 +4487,13 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D148" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="E148" t="s">
         <v>27</v>
@@ -4504,13 +4504,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D149" t="s">
-        <v>111</v>
+        <v>239</v>
       </c>
       <c r="E149" t="s">
         <v>27</v>
@@ -4521,13 +4521,13 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D150" t="s">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="E150" t="s">
         <v>27</v>
@@ -4538,13 +4538,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D151" t="s">
-        <v>66</v>
+        <v>156</v>
       </c>
       <c r="E151" t="s">
         <v>27</v>
@@ -4555,13 +4555,13 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D152" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="E152" t="s">
         <v>27</v>
@@ -4572,13 +4572,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D153" t="s">
-        <v>204</v>
+        <v>244</v>
       </c>
       <c r="E153" t="s">
         <v>27</v>
@@ -4589,13 +4589,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D154" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E154" t="s">
         <v>27</v>
@@ -4606,13 +4606,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D155" t="s">
-        <v>250</v>
+        <v>159</v>
       </c>
       <c r="E155" t="s">
         <v>27</v>
@@ -4623,13 +4623,13 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D156" t="s">
-        <v>122</v>
+        <v>239</v>
       </c>
       <c r="E156" t="s">
         <v>27</v>
@@ -4640,13 +4640,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D157" t="s">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="E157" t="s">
         <v>27</v>
@@ -4657,13 +4657,13 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D158" t="s">
-        <v>204</v>
+        <v>135</v>
       </c>
       <c r="E158" t="s">
         <v>27</v>
@@ -4674,13 +4674,13 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D159" t="s">
-        <v>204</v>
+        <v>135</v>
       </c>
       <c r="E159" t="s">
         <v>27</v>
@@ -4691,13 +4691,13 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D160" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="E160" t="s">
         <v>27</v>
@@ -4708,13 +4708,13 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D161" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E161" t="s">
         <v>27</v>
@@ -4725,13 +4725,13 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D162" t="s">
-        <v>86</v>
+        <v>170</v>
       </c>
       <c r="E162" t="s">
         <v>27</v>
@@ -4742,13 +4742,13 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D163" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="E163" t="s">
         <v>27</v>
@@ -4759,13 +4759,13 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D164" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E164" t="s">
         <v>27</v>
@@ -4776,13 +4776,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D165" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="E165" t="s">
         <v>27</v>
@@ -4793,13 +4793,13 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D166" t="s">
-        <v>124</v>
+        <v>260</v>
       </c>
       <c r="E166" t="s">
         <v>27</v>
@@ -4810,13 +4810,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D167" t="s">
-        <v>177</v>
+        <v>262</v>
       </c>
       <c r="E167" t="s">
         <v>27</v>
@@ -4827,13 +4827,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D168" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E168" t="s">
         <v>27</v>
@@ -4844,13 +4844,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D169" t="s">
-        <v>177</v>
+        <v>74</v>
       </c>
       <c r="E169" t="s">
         <v>27</v>
@@ -4861,13 +4861,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D170" t="s">
-        <v>88</v>
+        <v>173</v>
       </c>
       <c r="E170" t="s">
         <v>27</v>
@@ -4878,13 +4878,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D171" t="s">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="E171" t="s">
         <v>27</v>
@@ -4895,13 +4895,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D172" t="s">
-        <v>200</v>
+        <v>84</v>
       </c>
       <c r="E172" t="s">
         <v>27</v>
@@ -4912,13 +4912,13 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D173" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="E173" t="s">
         <v>27</v>
@@ -4929,13 +4929,13 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D174" t="s">
-        <v>196</v>
+        <v>135</v>
       </c>
       <c r="E174" t="s">
         <v>27</v>
@@ -4946,13 +4946,13 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D175" t="s">
-        <v>114</v>
+        <v>244</v>
       </c>
       <c r="E175" t="s">
         <v>27</v>
@@ -4963,13 +4963,13 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D176" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="E176" t="s">
         <v>27</v>
@@ -4980,13 +4980,13 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D177" t="s">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="E177" t="s">
         <v>27</v>
@@ -4997,13 +4997,13 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D178" t="s">
-        <v>225</v>
+        <v>133</v>
       </c>
       <c r="E178" t="s">
         <v>27</v>
@@ -5014,13 +5014,13 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D179" t="s">
-        <v>46</v>
+        <v>153</v>
       </c>
       <c r="E179" t="s">
         <v>27</v>
@@ -5031,13 +5031,13 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D180" t="s">
-        <v>250</v>
+        <v>47</v>
       </c>
       <c r="E180" t="s">
         <v>27</v>
@@ -5048,13 +5048,13 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D181" t="s">
-        <v>76</v>
+        <v>214</v>
       </c>
       <c r="E181" t="s">
         <v>27</v>
@@ -5065,13 +5065,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
+        <v>277</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D182" t="s">
         <v>278</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D182" t="s">
-        <v>177</v>
       </c>
       <c r="E182" t="s">
         <v>27</v>
@@ -5088,7 +5088,7 @@
         <v>25</v>
       </c>
       <c r="D183" t="s">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="E183" t="s">
         <v>27</v>
@@ -5105,7 +5105,7 @@
         <v>25</v>
       </c>
       <c r="D184" t="s">
-        <v>100</v>
+        <v>281</v>
       </c>
       <c r="E184" t="s">
         <v>27</v>
@@ -5116,13 +5116,13 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D185" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="E185" t="s">
         <v>27</v>
@@ -5133,13 +5133,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D186" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E186" t="s">
         <v>27</v>
@@ -5150,13 +5150,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D187" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="E187" t="s">
         <v>27</v>
@@ -5167,13 +5167,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D188" t="s">
-        <v>285</v>
+        <v>80</v>
       </c>
       <c r="E188" t="s">
         <v>27</v>
@@ -5190,7 +5190,7 @@
         <v>25</v>
       </c>
       <c r="D189" t="s">
-        <v>44</v>
+        <v>156</v>
       </c>
       <c r="E189" t="s">
         <v>27</v>
@@ -5207,7 +5207,7 @@
         <v>25</v>
       </c>
       <c r="D190" t="s">
-        <v>46</v>
+        <v>189</v>
       </c>
       <c r="E190" t="s">
         <v>27</v>
@@ -5224,7 +5224,7 @@
         <v>25</v>
       </c>
       <c r="D191" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="E191" t="s">
         <v>27</v>
@@ -5241,7 +5241,7 @@
         <v>25</v>
       </c>
       <c r="D192" t="s">
-        <v>90</v>
+        <v>37</v>
       </c>
       <c r="E192" t="s">
         <v>27</v>
@@ -5258,7 +5258,7 @@
         <v>25</v>
       </c>
       <c r="D193" t="s">
-        <v>250</v>
+        <v>168</v>
       </c>
       <c r="E193" t="s">
         <v>27</v>
@@ -5275,7 +5275,7 @@
         <v>25</v>
       </c>
       <c r="D194" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="E194" t="s">
         <v>27</v>
@@ -5292,7 +5292,7 @@
         <v>25</v>
       </c>
       <c r="D195" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="E195" t="s">
         <v>27</v>
@@ -5309,7 +5309,7 @@
         <v>25</v>
       </c>
       <c r="D196" t="s">
-        <v>72</v>
+        <v>199</v>
       </c>
       <c r="E196" t="s">
         <v>27</v>
@@ -5326,7 +5326,7 @@
         <v>25</v>
       </c>
       <c r="D197" t="s">
-        <v>209</v>
+        <v>142</v>
       </c>
       <c r="E197" t="s">
         <v>27</v>
@@ -5343,7 +5343,7 @@
         <v>25</v>
       </c>
       <c r="D198" t="s">
-        <v>78</v>
+        <v>189</v>
       </c>
       <c r="E198" t="s">
         <v>27</v>
@@ -5360,7 +5360,7 @@
         <v>25</v>
       </c>
       <c r="D199" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="E199" t="s">
         <v>27</v>
@@ -5377,7 +5377,7 @@
         <v>25</v>
       </c>
       <c r="D200" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="E200" t="s">
         <v>27</v>
@@ -5394,7 +5394,7 @@
         <v>25</v>
       </c>
       <c r="D201" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="E201" t="s">
         <v>27</v>
@@ -5411,7 +5411,7 @@
         <v>25</v>
       </c>
       <c r="D202" t="s">
-        <v>248</v>
+        <v>41</v>
       </c>
       <c r="E202" t="s">
         <v>27</v>
@@ -5428,7 +5428,7 @@
         <v>25</v>
       </c>
       <c r="D203" t="s">
-        <v>62</v>
+        <v>239</v>
       </c>
       <c r="E203" t="s">
         <v>27</v>
@@ -5445,7 +5445,7 @@
         <v>25</v>
       </c>
       <c r="D204" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="E204" t="s">
         <v>27</v>
@@ -5462,7 +5462,7 @@
         <v>25</v>
       </c>
       <c r="D205" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="E205" t="s">
         <v>27</v>
@@ -5479,7 +5479,7 @@
         <v>25</v>
       </c>
       <c r="D206" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="E206" t="s">
         <v>27</v>
@@ -5496,7 +5496,7 @@
         <v>25</v>
       </c>
       <c r="D207" t="s">
-        <v>111</v>
+        <v>189</v>
       </c>
       <c r="E207" t="s">
         <v>27</v>
@@ -5513,7 +5513,7 @@
         <v>25</v>
       </c>
       <c r="D208" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="E208" t="s">
         <v>27</v>
@@ -5530,7 +5530,7 @@
         <v>25</v>
       </c>
       <c r="D209" t="s">
-        <v>182</v>
+        <v>67</v>
       </c>
       <c r="E209" t="s">
         <v>27</v>
@@ -5547,7 +5547,7 @@
         <v>25</v>
       </c>
       <c r="D210" t="s">
-        <v>218</v>
+        <v>153</v>
       </c>
       <c r="E210" t="s">
         <v>27</v>
@@ -5564,7 +5564,7 @@
         <v>25</v>
       </c>
       <c r="D211" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="E211" t="s">
         <v>27</v>
@@ -5581,7 +5581,7 @@
         <v>25</v>
       </c>
       <c r="D212" t="s">
-        <v>111</v>
+        <v>310</v>
       </c>
       <c r="E212" t="s">
         <v>27</v>
@@ -5592,13 +5592,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D213" t="s">
-        <v>209</v>
+        <v>312</v>
       </c>
       <c r="E213" t="s">
         <v>27</v>
@@ -5609,13 +5609,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D214" t="s">
-        <v>225</v>
+        <v>120</v>
       </c>
       <c r="E214" t="s">
         <v>27</v>
@@ -5626,13 +5626,13 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D215" t="s">
-        <v>196</v>
+        <v>281</v>
       </c>
       <c r="E215" t="s">
         <v>27</v>
@@ -5643,13 +5643,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D216" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E216" t="s">
         <v>27</v>
@@ -5660,13 +5660,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D217" t="s">
-        <v>315</v>
+        <v>204</v>
       </c>
       <c r="E217" t="s">
         <v>27</v>
@@ -5677,13 +5677,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D218" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E218" t="s">
         <v>27</v>
@@ -5694,13 +5694,13 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D219" t="s">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="E219" t="s">
         <v>27</v>
@@ -5711,13 +5711,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D220" t="s">
-        <v>143</v>
+        <v>231</v>
       </c>
       <c r="E220" t="s">
         <v>27</v>
@@ -5728,13 +5728,13 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D221" t="s">
-        <v>315</v>
+        <v>78</v>
       </c>
       <c r="E221" t="s">
         <v>27</v>
@@ -5745,13 +5745,13 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D222" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="E222" t="s">
         <v>27</v>
@@ -5762,13 +5762,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D223" t="s">
-        <v>248</v>
+        <v>106</v>
       </c>
       <c r="E223" t="s">
         <v>27</v>
@@ -5779,13 +5779,13 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D224" t="s">
-        <v>198</v>
+        <v>324</v>
       </c>
       <c r="E224" t="s">
         <v>27</v>
@@ -5796,13 +5796,13 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D225" t="s">
-        <v>167</v>
+        <v>74</v>
       </c>
       <c r="E225" t="s">
         <v>27</v>
@@ -5813,13 +5813,13 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D226" t="s">
-        <v>132</v>
+        <v>312</v>
       </c>
       <c r="E226" t="s">
         <v>27</v>
@@ -5830,13 +5830,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D227" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="E227" t="s">
         <v>27</v>
@@ -5847,13 +5847,13 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D228" t="s">
-        <v>196</v>
+        <v>153</v>
       </c>
       <c r="E228" t="s">
         <v>27</v>
@@ -5864,13 +5864,13 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D229" t="s">
-        <v>250</v>
+        <v>96</v>
       </c>
       <c r="E229" t="s">
         <v>27</v>
@@ -5881,13 +5881,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D230" t="s">
-        <v>143</v>
+        <v>51</v>
       </c>
       <c r="E230" t="s">
         <v>27</v>
@@ -5898,13 +5898,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D231" t="s">
-        <v>54</v>
+        <v>281</v>
       </c>
       <c r="E231" t="s">
         <v>27</v>
@@ -5915,13 +5915,13 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D232" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="E232" t="s">
         <v>27</v>
@@ -5932,13 +5932,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D233" t="s">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="E233" t="s">
         <v>27</v>
@@ -5949,13 +5949,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D234" t="s">
-        <v>114</v>
+        <v>324</v>
       </c>
       <c r="E234" t="s">
         <v>27</v>
@@ -5966,13 +5966,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D235" t="s">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="E235" t="s">
         <v>27</v>
@@ -5983,13 +5983,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D236" t="s">
-        <v>130</v>
+        <v>189</v>
       </c>
       <c r="E236" t="s">
         <v>27</v>
@@ -6000,13 +6000,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D237" t="s">
-        <v>211</v>
+        <v>281</v>
       </c>
       <c r="E237" t="s">
         <v>27</v>
@@ -6017,13 +6017,13 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D238" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="E238" t="s">
         <v>27</v>
@@ -6034,13 +6034,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D239" t="s">
-        <v>137</v>
+        <v>324</v>
       </c>
       <c r="E239" t="s">
         <v>27</v>
@@ -6051,13 +6051,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D240" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="E240" t="s">
         <v>27</v>
@@ -6068,13 +6068,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D241" t="s">
-        <v>120</v>
+        <v>254</v>
       </c>
       <c r="E241" t="s">
         <v>27</v>
@@ -6085,13 +6085,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D242" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
       <c r="E242" t="s">
         <v>27</v>
@@ -6102,13 +6102,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D243" t="s">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="E243" t="s">
         <v>27</v>
@@ -6119,13 +6119,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D244" t="s">
-        <v>343</v>
+        <v>92</v>
       </c>
       <c r="E244" t="s">
         <v>27</v>
@@ -6136,13 +6136,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D245" t="s">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="E245" t="s">
         <v>27</v>
@@ -6153,13 +6153,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D246" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E246" t="s">
         <v>27</v>
@@ -6170,13 +6170,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D247" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="E247" t="s">
         <v>27</v>
@@ -6187,13 +6187,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D248" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E248" t="s">
         <v>27</v>
@@ -6204,13 +6204,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D249" t="s">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="E249" t="s">
         <v>27</v>
@@ -6221,13 +6221,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D250" t="s">
-        <v>285</v>
+        <v>161</v>
       </c>
       <c r="E250" t="s">
         <v>27</v>
@@ -6238,13 +6238,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D251" t="s">
-        <v>152</v>
+        <v>65</v>
       </c>
       <c r="E251" t="s">
         <v>27</v>
@@ -6255,13 +6255,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D252" t="s">
-        <v>90</v>
+        <v>37</v>
       </c>
       <c r="E252" t="s">
         <v>27</v>
@@ -6272,13 +6272,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D253" t="s">
-        <v>225</v>
+        <v>86</v>
       </c>
       <c r="E253" t="s">
         <v>27</v>
@@ -6289,13 +6289,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D254" t="s">
-        <v>44</v>
+        <v>210</v>
       </c>
       <c r="E254" t="s">
         <v>27</v>
@@ -6306,13 +6306,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D255" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="E255" t="s">
         <v>27</v>
@@ -6323,13 +6323,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D256" t="s">
-        <v>124</v>
+        <v>235</v>
       </c>
       <c r="E256" t="s">
         <v>27</v>
@@ -6340,13 +6340,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D257" t="s">
-        <v>66</v>
+        <v>142</v>
       </c>
       <c r="E257" t="s">
         <v>27</v>
@@ -6357,13 +6357,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D258" t="s">
-        <v>358</v>
+        <v>127</v>
       </c>
       <c r="E258" t="s">
         <v>27</v>
@@ -6380,7 +6380,7 @@
         <v>25</v>
       </c>
       <c r="D259" t="s">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="E259" t="s">
         <v>27</v>
@@ -6397,7 +6397,7 @@
         <v>25</v>
       </c>
       <c r="D260" t="s">
-        <v>361</v>
+        <v>159</v>
       </c>
       <c r="E260" t="s">
         <v>27</v>
@@ -6408,13 +6408,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D261" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E261" t="s">
         <v>27</v>
@@ -6425,13 +6425,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D262" t="s">
-        <v>120</v>
+        <v>312</v>
       </c>
       <c r="E262" t="s">
         <v>27</v>
@@ -6442,13 +6442,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D263" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="E263" t="s">
         <v>27</v>
@@ -6459,13 +6459,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
+        <v>364</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D264" t="s">
         <v>365</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D264" t="s">
-        <v>141</v>
       </c>
       <c r="E264" t="s">
         <v>27</v>
@@ -6482,7 +6482,7 @@
         <v>25</v>
       </c>
       <c r="D265" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="E265" t="s">
         <v>27</v>
@@ -6499,7 +6499,7 @@
         <v>25</v>
       </c>
       <c r="D266" t="s">
-        <v>225</v>
+        <v>191</v>
       </c>
       <c r="E266" t="s">
         <v>27</v>
@@ -6516,7 +6516,7 @@
         <v>25</v>
       </c>
       <c r="D267" t="s">
-        <v>167</v>
+        <v>65</v>
       </c>
       <c r="E267" t="s">
         <v>27</v>
@@ -6533,7 +6533,7 @@
         <v>25</v>
       </c>
       <c r="D268" t="s">
-        <v>250</v>
+        <v>202</v>
       </c>
       <c r="E268" t="s">
         <v>27</v>
@@ -6550,7 +6550,7 @@
         <v>25</v>
       </c>
       <c r="D269" t="s">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="E269" t="s">
         <v>27</v>
@@ -6567,7 +6567,7 @@
         <v>25</v>
       </c>
       <c r="D270" t="s">
-        <v>114</v>
+        <v>161</v>
       </c>
       <c r="E270" t="s">
         <v>27</v>
@@ -6584,7 +6584,7 @@
         <v>25</v>
       </c>
       <c r="D271" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="E271" t="s">
         <v>27</v>
@@ -6601,7 +6601,7 @@
         <v>25</v>
       </c>
       <c r="D272" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="E272" t="s">
         <v>27</v>
@@ -6618,7 +6618,7 @@
         <v>25</v>
       </c>
       <c r="D273" t="s">
-        <v>137</v>
+        <v>204</v>
       </c>
       <c r="E273" t="s">
         <v>27</v>
@@ -6635,7 +6635,7 @@
         <v>25</v>
       </c>
       <c r="D274" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E274" t="s">
         <v>27</v>
@@ -6652,7 +6652,7 @@
         <v>25</v>
       </c>
       <c r="D275" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="E275" t="s">
         <v>27</v>
@@ -6669,7 +6669,7 @@
         <v>25</v>
       </c>
       <c r="D276" t="s">
-        <v>52</v>
+        <v>159</v>
       </c>
       <c r="E276" t="s">
         <v>27</v>
@@ -6686,7 +6686,7 @@
         <v>25</v>
       </c>
       <c r="D277" t="s">
-        <v>58</v>
+        <v>310</v>
       </c>
       <c r="E277" t="s">
         <v>27</v>
@@ -6703,7 +6703,7 @@
         <v>25</v>
       </c>
       <c r="D278" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="E278" t="s">
         <v>27</v>
@@ -6720,7 +6720,7 @@
         <v>25</v>
       </c>
       <c r="D279" t="s">
-        <v>250</v>
+        <v>101</v>
       </c>
       <c r="E279" t="s">
         <v>27</v>
@@ -6737,7 +6737,7 @@
         <v>25</v>
       </c>
       <c r="D280" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="E280" t="s">
         <v>27</v>
@@ -6754,7 +6754,7 @@
         <v>25</v>
       </c>
       <c r="D281" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E281" t="s">
         <v>27</v>
@@ -6771,7 +6771,7 @@
         <v>25</v>
       </c>
       <c r="D282" t="s">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="E282" t="s">
         <v>27</v>
@@ -6788,7 +6788,7 @@
         <v>25</v>
       </c>
       <c r="D283" t="s">
-        <v>120</v>
+        <v>231</v>
       </c>
       <c r="E283" t="s">
         <v>27</v>
@@ -6805,7 +6805,7 @@
         <v>25</v>
       </c>
       <c r="D284" t="s">
-        <v>187</v>
+        <v>108</v>
       </c>
       <c r="E284" t="s">
         <v>27</v>
@@ -6822,7 +6822,7 @@
         <v>25</v>
       </c>
       <c r="D285" t="s">
-        <v>167</v>
+        <v>76</v>
       </c>
       <c r="E285" t="s">
         <v>27</v>
@@ -6839,7 +6839,7 @@
         <v>25</v>
       </c>
       <c r="D286" t="s">
-        <v>56</v>
+        <v>388</v>
       </c>
       <c r="E286" t="s">
         <v>27</v>
@@ -6850,13 +6850,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D287" t="s">
-        <v>250</v>
+        <v>390</v>
       </c>
       <c r="E287" t="s">
         <v>27</v>
@@ -6867,13 +6867,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D288" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E288" t="s">
         <v>27</v>
@@ -6884,13 +6884,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D289" t="s">
-        <v>193</v>
+        <v>43</v>
       </c>
       <c r="E289" t="s">
         <v>27</v>
@@ -6901,13 +6901,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D290" t="s">
-        <v>392</v>
+        <v>168</v>
       </c>
       <c r="E290" t="s">
         <v>27</v>
@@ -6918,13 +6918,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D291" t="s">
-        <v>209</v>
+        <v>47</v>
       </c>
       <c r="E291" t="s">
         <v>27</v>
@@ -6935,13 +6935,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D292" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="E292" t="s">
         <v>27</v>
@@ -6952,13 +6952,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D293" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E293" t="s">
         <v>27</v>
@@ -6969,13 +6969,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D294" t="s">
-        <v>50</v>
+        <v>204</v>
       </c>
       <c r="E294" t="s">
         <v>27</v>
@@ -6986,13 +6986,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D295" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="E295" t="s">
         <v>27</v>
@@ -7003,13 +7003,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D296" t="s">
-        <v>165</v>
+        <v>312</v>
       </c>
       <c r="E296" t="s">
         <v>27</v>
@@ -7020,13 +7020,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D297" t="s">
-        <v>250</v>
+        <v>94</v>
       </c>
       <c r="E297" t="s">
         <v>27</v>
@@ -7037,13 +7037,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D298" t="s">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="E298" t="s">
         <v>27</v>
@@ -7054,13 +7054,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D299" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="E299" t="s">
         <v>27</v>
@@ -7071,13 +7071,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D300" t="s">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="E300" t="s">
         <v>27</v>
@@ -7088,13 +7088,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D301" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="E301" t="s">
         <v>27</v>
@@ -7105,13 +7105,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D302" t="s">
-        <v>80</v>
+        <v>244</v>
       </c>
       <c r="E302" t="s">
         <v>27</v>
@@ -7122,13 +7122,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D303" t="s">
-        <v>46</v>
+        <v>231</v>
       </c>
       <c r="E303" t="s">
         <v>27</v>
@@ -7139,13 +7139,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D304" t="s">
-        <v>111</v>
+        <v>262</v>
       </c>
       <c r="E304" t="s">
         <v>27</v>
@@ -7156,13 +7156,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D305" t="s">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="E305" t="s">
         <v>27</v>
@@ -7173,13 +7173,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D306" t="s">
-        <v>250</v>
+        <v>145</v>
       </c>
       <c r="E306" t="s">
         <v>27</v>
@@ -7190,13 +7190,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D307" t="s">
-        <v>80</v>
+        <v>173</v>
       </c>
       <c r="E307" t="s">
         <v>27</v>
@@ -7207,13 +7207,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D308" t="s">
-        <v>223</v>
+        <v>70</v>
       </c>
       <c r="E308" t="s">
         <v>27</v>
@@ -7224,13 +7224,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D309" t="s">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="E309" t="s">
         <v>27</v>
@@ -7241,13 +7241,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D310" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="E310" t="s">
         <v>27</v>
@@ -7258,13 +7258,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D311" t="s">
-        <v>209</v>
+        <v>127</v>
       </c>
       <c r="E311" t="s">
         <v>27</v>
@@ -7275,13 +7275,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D312" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="E312" t="s">
         <v>27</v>
@@ -7292,13 +7292,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D313" t="s">
-        <v>38</v>
+        <v>207</v>
       </c>
       <c r="E313" t="s">
         <v>27</v>
@@ -7309,13 +7309,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D314" t="s">
-        <v>132</v>
+        <v>418</v>
       </c>
       <c r="E314" t="s">
         <v>27</v>
@@ -7326,13 +7326,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D315" t="s">
-        <v>225</v>
+        <v>99</v>
       </c>
       <c r="E315" t="s">
         <v>27</v>
@@ -7343,13 +7343,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D316" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="E316" t="s">
         <v>27</v>
@@ -7360,13 +7360,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D317" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E317" t="s">
         <v>27</v>
@@ -7377,13 +7377,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D318" t="s">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="E318" t="s">
         <v>27</v>
@@ -7394,13 +7394,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D319" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="E319" t="s">
         <v>27</v>
@@ -7411,13 +7411,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D320" t="s">
-        <v>257</v>
+        <v>142</v>
       </c>
       <c r="E320" t="s">
         <v>27</v>
@@ -7428,13 +7428,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D321" t="s">
-        <v>424</v>
+        <v>88</v>
       </c>
       <c r="E321" t="s">
         <v>27</v>
@@ -7445,13 +7445,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D322" t="s">
-        <v>165</v>
+        <v>108</v>
       </c>
       <c r="E322" t="s">
         <v>27</v>
@@ -7462,13 +7462,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D323" t="s">
-        <v>141</v>
+        <v>244</v>
       </c>
       <c r="E323" t="s">
         <v>27</v>
@@ -7479,13 +7479,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D324" t="s">
-        <v>361</v>
+        <v>61</v>
       </c>
       <c r="E324" t="s">
         <v>27</v>
@@ -7496,13 +7496,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D325" t="s">
-        <v>361</v>
+        <v>88</v>
       </c>
       <c r="E325" t="s">
         <v>27</v>
@@ -7513,13 +7513,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D326" t="s">
-        <v>285</v>
+        <v>67</v>
       </c>
       <c r="E326" t="s">
         <v>27</v>
@@ -7530,13 +7530,13 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D327" t="s">
-        <v>198</v>
+        <v>96</v>
       </c>
       <c r="E327" t="s">
         <v>27</v>
@@ -7547,13 +7547,13 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D328" t="s">
-        <v>315</v>
+        <v>90</v>
       </c>
       <c r="E328" t="s">
         <v>27</v>
@@ -7564,13 +7564,13 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D329" t="s">
-        <v>163</v>
+        <v>110</v>
       </c>
       <c r="E329" t="s">
         <v>27</v>
@@ -7581,13 +7581,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D330" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
       <c r="E330" t="s">
         <v>27</v>
@@ -7598,13 +7598,13 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D331" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="E331" t="s">
         <v>27</v>
@@ -7615,13 +7615,13 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D332" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="E332" t="s">
         <v>27</v>
@@ -7632,13 +7632,13 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D333" t="s">
-        <v>184</v>
+        <v>53</v>
       </c>
       <c r="E333" t="s">
         <v>27</v>
@@ -7649,13 +7649,13 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D334" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="E334" t="s">
         <v>27</v>
@@ -7666,13 +7666,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D335" t="s">
-        <v>358</v>
+        <v>116</v>
       </c>
       <c r="E335" t="s">
         <v>27</v>
@@ -7683,13 +7683,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D336" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E336" t="s">
         <v>27</v>
@@ -7700,13 +7700,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D337" t="s">
-        <v>223</v>
+        <v>170</v>
       </c>
       <c r="E337" t="s">
         <v>27</v>
@@ -7717,13 +7717,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D338" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="E338" t="s">
         <v>27</v>
@@ -7734,13 +7734,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D339" t="s">
-        <v>443</v>
+        <v>145</v>
       </c>
       <c r="E339" t="s">
         <v>27</v>
@@ -7757,7 +7757,7 @@
         <v>25</v>
       </c>
       <c r="D340" t="s">
-        <v>200</v>
+        <v>67</v>
       </c>
       <c r="E340" t="s">
         <v>27</v>
@@ -7774,7 +7774,7 @@
         <v>25</v>
       </c>
       <c r="D341" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="E341" t="s">
         <v>27</v>
@@ -7791,7 +7791,7 @@
         <v>25</v>
       </c>
       <c r="D342" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="E342" t="s">
         <v>27</v>
@@ -7808,7 +7808,7 @@
         <v>25</v>
       </c>
       <c r="D343" t="s">
-        <v>171</v>
+        <v>70</v>
       </c>
       <c r="E343" t="s">
         <v>27</v>
@@ -7825,7 +7825,7 @@
         <v>25</v>
       </c>
       <c r="D344" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E344" t="s">
         <v>27</v>
@@ -7842,7 +7842,7 @@
         <v>25</v>
       </c>
       <c r="D345" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="E345" t="s">
         <v>27</v>
@@ -7859,7 +7859,7 @@
         <v>25</v>
       </c>
       <c r="D346" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="E346" t="s">
         <v>27</v>
@@ -7876,7 +7876,7 @@
         <v>25</v>
       </c>
       <c r="D347" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="E347" t="s">
         <v>27</v>
@@ -7893,7 +7893,7 @@
         <v>25</v>
       </c>
       <c r="D348" t="s">
-        <v>132</v>
+        <v>310</v>
       </c>
       <c r="E348" t="s">
         <v>27</v>
@@ -7910,7 +7910,7 @@
         <v>25</v>
       </c>
       <c r="D349" t="s">
-        <v>141</v>
+        <v>104</v>
       </c>
       <c r="E349" t="s">
         <v>27</v>
@@ -7927,7 +7927,7 @@
         <v>25</v>
       </c>
       <c r="D350" t="s">
-        <v>149</v>
+        <v>94</v>
       </c>
       <c r="E350" t="s">
         <v>27</v>
@@ -7944,7 +7944,7 @@
         <v>25</v>
       </c>
       <c r="D351" t="s">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="E351" t="s">
         <v>27</v>
@@ -7961,7 +7961,7 @@
         <v>25</v>
       </c>
       <c r="D352" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E352" t="s">
         <v>27</v>
@@ -7978,7 +7978,7 @@
         <v>25</v>
       </c>
       <c r="D353" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E353" t="s">
         <v>27</v>
@@ -7995,7 +7995,7 @@
         <v>25</v>
       </c>
       <c r="D354" t="s">
-        <v>223</v>
+        <v>45</v>
       </c>
       <c r="E354" t="s">
         <v>27</v>
@@ -8012,7 +8012,7 @@
         <v>25</v>
       </c>
       <c r="D355" t="s">
-        <v>358</v>
+        <v>193</v>
       </c>
       <c r="E355" t="s">
         <v>27</v>
@@ -8029,7 +8029,7 @@
         <v>25</v>
       </c>
       <c r="D356" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="E356" t="s">
         <v>27</v>
@@ -8046,7 +8046,7 @@
         <v>25</v>
       </c>
       <c r="D357" t="s">
-        <v>343</v>
+        <v>101</v>
       </c>
       <c r="E357" t="s">
         <v>27</v>
@@ -8063,7 +8063,7 @@
         <v>25</v>
       </c>
       <c r="D358" t="s">
-        <v>233</v>
+        <v>94</v>
       </c>
       <c r="E358" t="s">
         <v>27</v>
@@ -8080,7 +8080,7 @@
         <v>25</v>
       </c>
       <c r="D359" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="E359" t="s">
         <v>27</v>
@@ -8097,7 +8097,7 @@
         <v>25</v>
       </c>
       <c r="D360" t="s">
-        <v>167</v>
+        <v>310</v>
       </c>
       <c r="E360" t="s">
         <v>27</v>
@@ -8114,7 +8114,7 @@
         <v>25</v>
       </c>
       <c r="D361" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="E361" t="s">
         <v>27</v>
@@ -8131,7 +8131,7 @@
         <v>25</v>
       </c>
       <c r="D362" t="s">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="E362" t="s">
         <v>27</v>
@@ -8148,7 +8148,7 @@
         <v>25</v>
       </c>
       <c r="D363" t="s">
-        <v>248</v>
+        <v>131</v>
       </c>
       <c r="E363" t="s">
         <v>27</v>
@@ -8165,7 +8165,7 @@
         <v>25</v>
       </c>
       <c r="D364" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="E364" t="s">
         <v>27</v>
@@ -8182,7 +8182,7 @@
         <v>25</v>
       </c>
       <c r="D365" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="E365" t="s">
         <v>27</v>
@@ -8199,7 +8199,7 @@
         <v>25</v>
       </c>
       <c r="D366" t="s">
-        <v>130</v>
+        <v>191</v>
       </c>
       <c r="E366" t="s">
         <v>27</v>
@@ -8216,7 +8216,7 @@
         <v>25</v>
       </c>
       <c r="D367" t="s">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="E367" t="s">
         <v>27</v>
@@ -8233,7 +8233,7 @@
         <v>25</v>
       </c>
       <c r="D368" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="E368" t="s">
         <v>27</v>
@@ -8250,7 +8250,7 @@
         <v>25</v>
       </c>
       <c r="D369" t="s">
-        <v>80</v>
+        <v>202</v>
       </c>
       <c r="E369" t="s">
         <v>27</v>
@@ -8267,7 +8267,7 @@
         <v>25</v>
       </c>
       <c r="D370" t="s">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="E370" t="s">
         <v>27</v>
@@ -8284,7 +8284,7 @@
         <v>25</v>
       </c>
       <c r="D371" t="s">
-        <v>200</v>
+        <v>106</v>
       </c>
       <c r="E371" t="s">
         <v>27</v>
@@ -8301,7 +8301,7 @@
         <v>25</v>
       </c>
       <c r="D372" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="E372" t="s">
         <v>27</v>
@@ -8318,7 +8318,7 @@
         <v>25</v>
       </c>
       <c r="D373" t="s">
-        <v>182</v>
+        <v>110</v>
       </c>
       <c r="E373" t="s">
         <v>27</v>
@@ -8335,7 +8335,7 @@
         <v>25</v>
       </c>
       <c r="D374" t="s">
-        <v>38</v>
+        <v>116</v>
       </c>
       <c r="E374" t="s">
         <v>27</v>
@@ -8352,7 +8352,7 @@
         <v>25</v>
       </c>
       <c r="D375" t="s">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="E375" t="s">
         <v>27</v>
@@ -8369,7 +8369,7 @@
         <v>25</v>
       </c>
       <c r="D376" t="s">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="E376" t="s">
         <v>27</v>
@@ -8386,7 +8386,7 @@
         <v>25</v>
       </c>
       <c r="D377" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="E377" t="s">
         <v>27</v>
@@ -8403,7 +8403,7 @@
         <v>25</v>
       </c>
       <c r="D378" t="s">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="E378" t="s">
         <v>27</v>
@@ -8420,7 +8420,7 @@
         <v>25</v>
       </c>
       <c r="D379" t="s">
-        <v>211</v>
+        <v>57</v>
       </c>
       <c r="E379" t="s">
         <v>27</v>
@@ -8437,7 +8437,7 @@
         <v>25</v>
       </c>
       <c r="D380" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E380" t="s">
         <v>27</v>
@@ -8454,7 +8454,7 @@
         <v>25</v>
       </c>
       <c r="D381" t="s">
-        <v>189</v>
+        <v>418</v>
       </c>
       <c r="E381" t="s">
         <v>27</v>
@@ -8471,7 +8471,7 @@
         <v>25</v>
       </c>
       <c r="D382" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="E382" t="s">
         <v>27</v>
@@ -8488,7 +8488,7 @@
         <v>25</v>
       </c>
       <c r="D383" t="s">
-        <v>213</v>
+        <v>108</v>
       </c>
       <c r="E383" t="s">
         <v>27</v>
@@ -8505,7 +8505,7 @@
         <v>25</v>
       </c>
       <c r="D384" t="s">
-        <v>64</v>
+        <v>173</v>
       </c>
       <c r="E384" t="s">
         <v>27</v>
@@ -8522,7 +8522,7 @@
         <v>25</v>
       </c>
       <c r="D385" t="s">
-        <v>132</v>
+        <v>193</v>
       </c>
       <c r="E385" t="s">
         <v>27</v>
@@ -8539,7 +8539,7 @@
         <v>25</v>
       </c>
       <c r="D386" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="E386" t="s">
         <v>27</v>
@@ -8556,7 +8556,7 @@
         <v>25</v>
       </c>
       <c r="D387" t="s">
-        <v>193</v>
+        <v>106</v>
       </c>
       <c r="E387" t="s">
         <v>27</v>
@@ -8573,7 +8573,7 @@
         <v>25</v>
       </c>
       <c r="D388" t="s">
-        <v>130</v>
+        <v>214</v>
       </c>
       <c r="E388" t="s">
         <v>27</v>
@@ -8590,7 +8590,7 @@
         <v>25</v>
       </c>
       <c r="D389" t="s">
-        <v>193</v>
+        <v>365</v>
       </c>
       <c r="E389" t="s">
         <v>27</v>
@@ -8607,7 +8607,7 @@
         <v>25</v>
       </c>
       <c r="D390" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E390" t="s">
         <v>27</v>
@@ -8624,7 +8624,7 @@
         <v>25</v>
       </c>
       <c r="D391" t="s">
-        <v>233</v>
+        <v>110</v>
       </c>
       <c r="E391" t="s">
         <v>27</v>
@@ -8641,7 +8641,7 @@
         <v>25</v>
       </c>
       <c r="D392" t="s">
-        <v>60</v>
+        <v>173</v>
       </c>
       <c r="E392" t="s">
         <v>27</v>
@@ -8658,7 +8658,7 @@
         <v>25</v>
       </c>
       <c r="D393" t="s">
-        <v>225</v>
+        <v>47</v>
       </c>
       <c r="E393" t="s">
         <v>27</v>
@@ -8675,7 +8675,7 @@
         <v>25</v>
       </c>
       <c r="D394" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E394" t="s">
         <v>27</v>
@@ -8692,7 +8692,7 @@
         <v>25</v>
       </c>
       <c r="D395" t="s">
-        <v>225</v>
+        <v>94</v>
       </c>
       <c r="E395" t="s">
         <v>27</v>
@@ -8709,7 +8709,7 @@
         <v>25</v>
       </c>
       <c r="D396" t="s">
-        <v>149</v>
+        <v>88</v>
       </c>
       <c r="E396" t="s">
         <v>27</v>
@@ -8726,7 +8726,7 @@
         <v>25</v>
       </c>
       <c r="D397" t="s">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="E397" t="s">
         <v>27</v>
@@ -8743,7 +8743,7 @@
         <v>25</v>
       </c>
       <c r="D398" t="s">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="E398" t="s">
         <v>27</v>
@@ -8760,7 +8760,7 @@
         <v>25</v>
       </c>
       <c r="D399" t="s">
-        <v>198</v>
+        <v>53</v>
       </c>
       <c r="E399" t="s">
         <v>27</v>
@@ -8777,7 +8777,7 @@
         <v>25</v>
       </c>
       <c r="D400" t="s">
-        <v>424</v>
+        <v>214</v>
       </c>
       <c r="E400" t="s">
         <v>27</v>
@@ -8794,7 +8794,7 @@
         <v>25</v>
       </c>
       <c r="D401" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="E401" t="s">
         <v>27</v>

--- a/reports/selenium/Excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/Excel/Automation_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="523">
   <si>
     <t>#</t>
   </si>
@@ -35,1464 +35,1467 @@
     <t>FAILED</t>
   </si>
   <si>
-    <t>20.72</t>
+    <t>20.90</t>
   </si>
   <si>
     <t xml:space="preserve">Landing page did not load — Sign In button not found
-Wait timed out after 20187ms</t>
+Wait timed out after 20026ms</t>
   </si>
   <si>
     <t>should navigate to the login form</t>
   </si>
   <si>
-    <t>20.75</t>
+    <t>20.59</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20032ms</t>
+Wait timed out after 20158ms</t>
   </si>
   <si>
     <t>should login with valid credentials and reach the dashboard</t>
   </si>
   <si>
-    <t>20.67</t>
+    <t>20.52</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20162ms</t>
+Wait timed out after 20159ms</t>
   </si>
   <si>
     <t>should reject invalid credentials with an error message</t>
   </si>
   <si>
+    <t>20.81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
+Wait timed out after 20168ms</t>
+  </si>
+  <si>
+    <t>should open the sign-up form from landing</t>
+  </si>
+  <si>
     <t>20.51</t>
   </si>
   <si>
+    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signup-btn"])
+Wait timed out after 20147ms</t>
+  </si>
+  <si>
+    <t>Security — should reject login for invalid credentials</t>
+  </si>
+  <si>
+    <t>20.71</t>
+  </si>
+  <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20151ms</t>
-  </si>
-  <si>
-    <t>should open the sign-up form from landing</t>
-  </si>
-  <si>
-    <t>20.93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signup-btn"])
-Wait timed out after 20188ms</t>
-  </si>
-  <si>
-    <t>Security — should reject login for invalid credentials</t>
-  </si>
-  <si>
-    <t>20.52</t>
+Wait timed out after 20198ms</t>
+  </si>
+  <si>
+    <t>Security — should prevent access to protected routes/dashboard for unauthenticated users</t>
+  </si>
+  <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>3.29</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Security — should not execute XSS script payloads submitted in login fields</t>
+  </si>
+  <si>
+    <t>20.50</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20006ms</t>
-  </si>
-  <si>
-    <t>Security — should prevent access to protected routes/dashboard for unauthenticated users</t>
-  </si>
-  <si>
-    <t>PASSED</t>
-  </si>
-  <si>
-    <t>3.67</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Security — should not execute XSS script payloads submitted in login fields</t>
-  </si>
-  <si>
-    <t>20.54</t>
+Wait timed out after 20153ms</t>
+  </si>
+  <si>
+    <t>Security — should enforce session termination and clean storage upon logout</t>
+  </si>
+  <si>
+    <t>20.80</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20175ms</t>
-  </si>
-  <si>
-    <t>Security — should enforce session termination and clean storage upon logout</t>
-  </si>
-  <si>
-    <t>20.49</t>
+Wait timed out after 20157ms</t>
+  </si>
+  <si>
+    <t>Security — should confirm Firebase authentication rejects empty credentials</t>
+  </si>
+  <si>
+    <t>20.82</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20139ms</t>
-  </si>
-  <si>
-    <t>Security — should confirm Firebase authentication rejects empty credentials</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20148ms</t>
+Wait timed out after 20174ms</t>
   </si>
   <si>
     <t>Security — should not expose sensitive API keys or secrets in page HTML source</t>
   </si>
   <si>
+    <t>0.68</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #11)</t>
+  </si>
+  <si>
+    <t>0.46</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #12)</t>
+  </si>
+  <si>
+    <t>0.92</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #13)</t>
+  </si>
+  <si>
     <t>0.35</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #11)</t>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #14)</t>
+  </si>
+  <si>
+    <t>0.29</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #15)</t>
+  </si>
+  <si>
+    <t>0.81</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #16)</t>
+  </si>
+  <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #17)</t>
+  </si>
+  <si>
+    <t>0.49</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #18)</t>
+  </si>
+  <si>
+    <t>0.83</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #19)</t>
+  </si>
+  <si>
+    <t>0.70</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #20)</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #21)</t>
+  </si>
+  <si>
+    <t>0.89</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #22)</t>
+  </si>
+  <si>
+    <t>0.31</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #23)</t>
+  </si>
+  <si>
+    <t>0.78</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #24)</t>
+  </si>
+  <si>
+    <t>0.61</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #25)</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #26)</t>
+  </si>
+  <si>
+    <t>0.91</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #27)</t>
+  </si>
+  <si>
+    <t>0.47</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #28)</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #29)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #30)</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #31)</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #32)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #33)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #34)</t>
+  </si>
+  <si>
+    <t>0.67</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #35)</t>
+  </si>
+  <si>
+    <t>0.82</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #36)</t>
+  </si>
+  <si>
+    <t>0.54</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #37)</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #38)</t>
+  </si>
+  <si>
+    <t>0.60</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #39)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #40)</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #41)</t>
+  </si>
+  <si>
+    <t>0.65</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #42)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #43)</t>
+  </si>
+  <si>
+    <t>0.45</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #44)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #45)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #46)</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #47)</t>
+  </si>
+  <si>
+    <t>0.32</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #48)</t>
+  </si>
+  <si>
+    <t>0.84</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #49)</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #50)</t>
+  </si>
+  <si>
+    <t>0.86</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #51)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #52)</t>
+  </si>
+  <si>
+    <t>0.69</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #53)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #54)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #55)</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #56)</t>
+  </si>
+  <si>
+    <t>0.80</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #57)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #58)</t>
+  </si>
+  <si>
+    <t>0.76</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #59)</t>
+  </si>
+  <si>
+    <t>0.73</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #60)</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #61)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #62)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #63)</t>
+  </si>
+  <si>
+    <t>0.52</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #64)</t>
+  </si>
+  <si>
+    <t>0.40</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #65)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #66)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #67)</t>
+  </si>
+  <si>
+    <t>0.38</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #68)</t>
+  </si>
+  <si>
+    <t>0.77</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #69)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #70)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #71)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #72)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #73)</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #74)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #75)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #76)</t>
+  </si>
+  <si>
+    <t>0.55</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #77)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #78)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #79)</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #80)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #81)</t>
+  </si>
+  <si>
+    <t>0.28</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #82)</t>
+  </si>
+  <si>
+    <t>0.63</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #83)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #84)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #85)</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #86)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #87)</t>
+  </si>
+  <si>
+    <t>0.37</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #88)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #89)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #90)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #91)</t>
+  </si>
+  <si>
+    <t>0.71</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #92)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #93)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #94)</t>
+  </si>
+  <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #95)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #96)</t>
+  </si>
+  <si>
+    <t>0.96</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #97)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #98)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #99)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #100)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #101)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #102)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #103)</t>
+  </si>
+  <si>
+    <t>0.97</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #104)</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #105)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #106)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #107)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #108)</t>
+  </si>
+  <si>
+    <t>0.74</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #109)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #110)</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #111)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #112)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #113)</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #114)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #115)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #116)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #117)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #118)</t>
   </si>
   <si>
     <t>0.88</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #12)</t>
-  </si>
-  <si>
-    <t>0.77</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #13)</t>
-  </si>
-  <si>
-    <t>0.98</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #14)</t>
-  </si>
-  <si>
-    <t>0.91</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #15)</t>
-  </si>
-  <si>
-    <t>0.58</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #16)</t>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #119)</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #120)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #121)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #122)</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #123)</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #124)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #125)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #126)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #127)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #128)</t>
+  </si>
+  <si>
+    <t>0.90</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #129)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #130)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #131)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #132)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #133)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #134)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #135)</t>
+  </si>
+  <si>
+    <t>0.93</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #136)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #137)</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #138)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #139)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #140)</t>
+  </si>
+  <si>
+    <t>0.44</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #141)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #142)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #143)</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #144)</t>
+  </si>
+  <si>
+    <t>0.53</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #145)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #146)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #147)</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #148)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #149)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #150)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #151)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #152)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #153)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #154)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #155)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #156)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #157)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #158)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #159)</t>
+  </si>
+  <si>
+    <t>0.79</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #160)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #161)</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #162)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #163)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #164)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #165)</t>
+  </si>
+  <si>
+    <t>0.48</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #166)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #167)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #168)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #169)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #170)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #171)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #172)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #173)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #174)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #175)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #176)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #177)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #178)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #179)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #180)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #181)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #182)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #183)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #184)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #185)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #186)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #187)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #188)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #189)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #190)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #191)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #192)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #193)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #194)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #195)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #196)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #197)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #198)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #199)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #200)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #201)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #202)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #203)</t>
+  </si>
+  <si>
+    <t>0.99</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #204)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #205)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #206)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #207)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #208)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #209)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #210)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #211)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #212)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #213)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #214)</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #215)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #216)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #217)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #218)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #219)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #220)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #221)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #222)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #223)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #224)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #225)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #226)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #227)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #228)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #229)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #230)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #231)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #232)</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #233)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #234)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #235)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #236)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #237)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #238)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #239)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #240)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #241)</t>
+  </si>
+  <si>
+    <t>0.72</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #242)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #243)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #244)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #245)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #246)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #247)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #248)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #249)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #250)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #251)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #252)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #253)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #254)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #255)</t>
+  </si>
+  <si>
+    <t>0.59</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #256)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #257)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #258)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #259)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #260)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #261)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #262)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #263)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #264)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #265)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #266)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #267)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #268)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #269)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #270)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #271)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #272)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #273)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #274)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #275)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #276)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #277)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #278)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #279)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #280)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #281)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #282)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #283)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #284)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #285)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #286)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #287)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #288)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #289)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #290)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #291)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #292)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #293)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #294)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #295)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #296)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #297)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #298)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #299)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #300)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #301)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #302)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #303)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #304)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #305)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #306)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #307)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #308)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #309)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #310)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #311)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #312)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #313)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #314)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #315)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #316)</t>
+  </si>
+  <si>
+    <t>0.66</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #317)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #318)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #319)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #320)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #321)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #322)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #323)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #324)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #325)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #326)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #327)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #328)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #329)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #330)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #331)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #332)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #333)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #334)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #335)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #336)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #337)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #338)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #339)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #340)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #341)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #342)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #343)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #344)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #345)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #346)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #347)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #348)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #349)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #350)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #351)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #352)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #353)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #354)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #355)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #356)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #357)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #358)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #359)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #360)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #361)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #362)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #363)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #364)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #365)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #366)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #367)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #368)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #369)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #370)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #371)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #372)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #373)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #374)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #375)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #376)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #377)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #378)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #379)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #380)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #381)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #382)</t>
+  </si>
+  <si>
+    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #383)</t>
   </si>
   <si>
     <t>0.30</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #17)</t>
-  </si>
-  <si>
-    <t>0.59</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #18)</t>
-  </si>
-  <si>
-    <t>0.28</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #19)</t>
-  </si>
-  <si>
-    <t>0.73</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #20)</t>
-  </si>
-  <si>
-    <t>0.78</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #21)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #22)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #23)</t>
-  </si>
-  <si>
-    <t>0.61</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #24)</t>
-  </si>
-  <si>
-    <t>0.64</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #25)</t>
-  </si>
-  <si>
-    <t>0.56</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #26)</t>
-  </si>
-  <si>
-    <t>0.53</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #27)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #28)</t>
-  </si>
-  <si>
-    <t>0.82</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #29)</t>
-  </si>
-  <si>
-    <t>0.25</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #30)</t>
-  </si>
-  <si>
-    <t>0.60</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #31)</t>
-  </si>
-  <si>
-    <t>0.39</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #32)</t>
-  </si>
-  <si>
-    <t>0.84</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #33)</t>
-  </si>
-  <si>
-    <t>0.42</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #34)</t>
-  </si>
-  <si>
-    <t>0.49</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #35)</t>
-  </si>
-  <si>
-    <t>0.95</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #36)</t>
-  </si>
-  <si>
-    <t>0.54</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #37)</t>
-  </si>
-  <si>
-    <t>0.67</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #38)</t>
-  </si>
-  <si>
-    <t>0.75</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #39)</t>
-  </si>
-  <si>
-    <t>0.81</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #40)</t>
-  </si>
-  <si>
-    <t>0.87</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #41)</t>
-  </si>
-  <si>
-    <t>0.69</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #42)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #43)</t>
-  </si>
-  <si>
-    <t>0.23</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #44)</t>
-  </si>
-  <si>
-    <t>0.45</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #45)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #46)</t>
-  </si>
-  <si>
-    <t>0.44</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #47)</t>
-  </si>
-  <si>
-    <t>0.93</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #48)</t>
-  </si>
-  <si>
-    <t>0.85</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #49)</t>
-  </si>
-  <si>
-    <t>0.47</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #50)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #51)</t>
-  </si>
-  <si>
-    <t>0.43</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #52)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #53)</t>
-  </si>
-  <si>
-    <t>0.21</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #54)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #55)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #56)</t>
-  </si>
-  <si>
-    <t>0.96</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #57)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #58)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #59)</t>
-  </si>
-  <si>
-    <t>0.63</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #60)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #61)</t>
-  </si>
-  <si>
-    <t>0.55</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #62)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #63)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #64)</t>
-  </si>
-  <si>
-    <t>0.31</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #65)</t>
-  </si>
-  <si>
-    <t>0.24</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #66)</t>
-  </si>
-  <si>
-    <t>0.79</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #67)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #68)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #69)</t>
-  </si>
-  <si>
-    <t>0.41</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #70)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #71)</t>
-  </si>
-  <si>
-    <t>0.36</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #72)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #73)</t>
-  </si>
-  <si>
-    <t>0.90</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #74)</t>
-  </si>
-  <si>
-    <t>0.51</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #75)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #76)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #77)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #78)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #79)</t>
-  </si>
-  <si>
-    <t>0.57</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #80)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #81)</t>
-  </si>
-  <si>
-    <t>0.22</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #82)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #83)</t>
-  </si>
-  <si>
-    <t>0.66</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #84)</t>
-  </si>
-  <si>
-    <t>0.74</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #85)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #86)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #87)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #88)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #89)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #90)</t>
-  </si>
-  <si>
-    <t>0.76</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #91)</t>
-  </si>
-  <si>
-    <t>0.27</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #92)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #93)</t>
-  </si>
-  <si>
-    <t>0.89</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #94)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #95)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #96)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #97)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #98)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #99)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #100)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #101)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #102)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #103)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #104)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #105)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #106)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #107)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #108)</t>
-  </si>
-  <si>
-    <t>0.80</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #109)</t>
-  </si>
-  <si>
-    <t>0.94</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #110)</t>
-  </si>
-  <si>
-    <t>0.37</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #111)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #112)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #113)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #114)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #115)</t>
-  </si>
-  <si>
-    <t>0.99</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #116)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #117)</t>
-  </si>
-  <si>
-    <t>0.71</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #118)</t>
-  </si>
-  <si>
-    <t>0.83</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #119)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #120)</t>
-  </si>
-  <si>
-    <t>0.70</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #121)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #122)</t>
-  </si>
-  <si>
-    <t>0.52</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #123)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #124)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #125)</t>
-  </si>
-  <si>
-    <t>0.92</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #126)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #127)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #128)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #129)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #130)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #131)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #132)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #133)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #134)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #135)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #136)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #137)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #138)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #139)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #140)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #141)</t>
-  </si>
-  <si>
-    <t>0.38</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #142)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #143)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #144)</t>
-  </si>
-  <si>
-    <t>0.34</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #145)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #146)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #147)</t>
-  </si>
-  <si>
-    <t>0.48</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #148)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #149)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #150)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #151)</t>
-  </si>
-  <si>
-    <t>0.29</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #152)</t>
-  </si>
-  <si>
-    <t>1.00</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #153)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #154)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #155)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #156)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #157)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #158)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #159)</t>
-  </si>
-  <si>
-    <t>0.62</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #160)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #161)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #162)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #163)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #164)</t>
-  </si>
-  <si>
-    <t>0.32</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #165)</t>
-  </si>
-  <si>
-    <t>0.20</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #166)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #167)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #168)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #169)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #170)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #171)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #172)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #173)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #174)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #175)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #176)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #177)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #178)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #179)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #180)</t>
-  </si>
-  <si>
-    <t>0.33</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #181)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #182)</t>
-  </si>
-  <si>
-    <t>0.50</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #183)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #184)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #185)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #186)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #187)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #188)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #189)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #190)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #191)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #192)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #193)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #194)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #195)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #196)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #197)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #198)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #199)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #200)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #201)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #202)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #203)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #204)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #205)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #206)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #207)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #208)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #209)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #210)</t>
-  </si>
-  <si>
-    <t>0.40</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #211)</t>
-  </si>
-  <si>
-    <t>0.26</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #212)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #213)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #214)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #215)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #216)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #217)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #218)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #219)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #220)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #221)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #222)</t>
-  </si>
-  <si>
-    <t>0.68</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #223)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #224)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #225)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #226)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #227)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #228)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #229)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #230)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #231)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #232)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #233)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #234)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #235)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #236)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #237)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #238)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #239)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #240)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #241)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #242)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #243)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #244)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #245)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #246)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #247)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #248)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #249)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #250)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #251)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #252)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #253)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #254)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #255)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #256)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #257)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #258)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #259)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #260)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #261)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #262)</t>
-  </si>
-  <si>
-    <t>0.65</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #263)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #264)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #265)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #266)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #267)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #268)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #269)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #270)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #271)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #272)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #273)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #274)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #275)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #276)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #277)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #278)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #279)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #280)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #281)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #282)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #283)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #284)</t>
-  </si>
-  <si>
-    <t>0.72</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #285)</t>
-  </si>
-  <si>
-    <t>0.46</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #286)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #287)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #288)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #289)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #290)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #291)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #292)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #293)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #294)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #295)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #296)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #297)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #298)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #299)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #300)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #301)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #302)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #303)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #304)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #305)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #306)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #307)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #308)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #309)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #310)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #311)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #312)</t>
-  </si>
-  <si>
-    <t>0.86</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #313)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #314)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #315)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #316)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #317)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #318)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #319)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #320)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #321)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #322)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #323)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #324)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #325)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #326)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #327)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #328)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #329)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #330)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #331)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #332)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #333)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #334)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #335)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #336)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #337)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #338)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #339)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #340)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #341)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #342)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #343)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #344)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #345)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #346)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #347)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #348)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #349)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #350)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #351)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #352)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #353)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #354)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #355)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #356)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #357)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #358)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #359)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #360)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #361)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #362)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #363)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #364)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #365)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #366)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #367)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #368)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #369)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #370)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #371)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #372)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #373)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #374)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #375)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #376)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #377)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #378)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #379)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #380)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #381)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #382)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #383)</t>
-  </si>
-  <si>
     <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #384)</t>
   </si>
   <si>
@@ -1550,13 +1553,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>16</t>
+    <t>17</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 14:01:39 UTC</t>
+    <t>2026-06-23 14:08:10 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1568,7 +1571,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>e40a5d4</t>
+    <t>d1d53d0</t>
   </si>
   <si>
     <t>Total</t>
@@ -2164,10 +2167,10 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2175,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
         <v>27</v>
@@ -2192,13 +2195,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E13" t="s">
         <v>27</v>
@@ -2209,13 +2212,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E14" t="s">
         <v>27</v>
@@ -2226,13 +2229,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s">
         <v>27</v>
@@ -2243,13 +2246,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E16" t="s">
         <v>27</v>
@@ -2260,13 +2263,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E17" t="s">
         <v>27</v>
@@ -2277,13 +2280,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E18" t="s">
         <v>27</v>
@@ -2294,13 +2297,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E19" t="s">
         <v>27</v>
@@ -2311,13 +2314,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E20" t="s">
         <v>27</v>
@@ -2328,13 +2331,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
         <v>27</v>
@@ -2345,13 +2348,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E22" t="s">
         <v>27</v>
@@ -2362,13 +2365,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E23" t="s">
         <v>27</v>
@@ -2379,13 +2382,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E24" t="s">
         <v>27</v>
@@ -2396,13 +2399,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E25" t="s">
         <v>27</v>
@@ -2413,13 +2416,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E26" t="s">
         <v>27</v>
@@ -2430,13 +2433,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E27" t="s">
         <v>27</v>
@@ -2447,13 +2450,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E28" t="s">
         <v>27</v>
@@ -2464,13 +2467,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="E29" t="s">
         <v>27</v>
@@ -2481,13 +2484,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
         <v>27</v>
@@ -2498,13 +2501,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E31" t="s">
         <v>27</v>
@@ -2515,13 +2518,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E32" t="s">
         <v>27</v>
@@ -2532,13 +2535,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D33" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E33" t="s">
         <v>27</v>
@@ -2549,13 +2552,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D34" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="E34" t="s">
         <v>27</v>
@@ -2566,13 +2569,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" t="s">
         <v>79</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D35" t="s">
-        <v>80</v>
       </c>
       <c r="E35" t="s">
         <v>27</v>
@@ -2583,13 +2586,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E36" t="s">
         <v>27</v>
@@ -2600,13 +2603,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E37" t="s">
         <v>27</v>
@@ -2617,13 +2620,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E38" t="s">
         <v>27</v>
@@ -2634,13 +2637,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E39" t="s">
         <v>27</v>
@@ -2651,13 +2654,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E40" t="s">
         <v>27</v>
@@ -2668,13 +2671,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D41" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="E41" t="s">
         <v>27</v>
@@ -2725,7 +2728,7 @@
         <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="E44" t="s">
         <v>27</v>
@@ -2759,7 +2762,7 @@
         <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="E46" t="s">
         <v>27</v>
@@ -2770,13 +2773,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E47" t="s">
         <v>27</v>
@@ -2787,13 +2790,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
+        <v>102</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D48" t="s">
         <v>103</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D48" t="s">
-        <v>104</v>
       </c>
       <c r="E48" t="s">
         <v>27</v>
@@ -2804,13 +2807,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>104</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" t="s">
         <v>105</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D49" t="s">
-        <v>106</v>
       </c>
       <c r="E49" t="s">
         <v>27</v>
@@ -2821,13 +2824,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>106</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D50" t="s">
         <v>107</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D50" t="s">
-        <v>108</v>
       </c>
       <c r="E50" t="s">
         <v>27</v>
@@ -2838,13 +2841,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>108</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D51" t="s">
         <v>109</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D51" t="s">
-        <v>110</v>
       </c>
       <c r="E51" t="s">
         <v>27</v>
@@ -2855,13 +2858,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>110</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D52" t="s">
         <v>111</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D52" t="s">
-        <v>61</v>
       </c>
       <c r="E52" t="s">
         <v>27</v>
@@ -2878,7 +2881,7 @@
         <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>113</v>
+        <v>58</v>
       </c>
       <c r="E53" t="s">
         <v>27</v>
@@ -2889,13 +2892,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>113</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D54" t="s">
         <v>114</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D54" t="s">
-        <v>67</v>
       </c>
       <c r="E54" t="s">
         <v>27</v>
@@ -2912,7 +2915,7 @@
         <v>25</v>
       </c>
       <c r="D55" t="s">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="E55" t="s">
         <v>27</v>
@@ -2923,13 +2926,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D56" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="E56" t="s">
         <v>27</v>
@@ -2940,13 +2943,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
+        <v>117</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D57" t="s">
         <v>118</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D57" t="s">
-        <v>104</v>
       </c>
       <c r="E57" t="s">
         <v>27</v>
@@ -2980,7 +2983,7 @@
         <v>25</v>
       </c>
       <c r="D59" t="s">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="E59" t="s">
         <v>27</v>
@@ -2997,7 +3000,7 @@
         <v>25</v>
       </c>
       <c r="D60" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="E60" t="s">
         <v>27</v>
@@ -3008,13 +3011,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E61" t="s">
         <v>27</v>
@@ -3025,13 +3028,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D62" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="E62" t="s">
         <v>27</v>
@@ -3042,13 +3045,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D63" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="E63" t="s">
         <v>27</v>
@@ -3059,13 +3062,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D64" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E64" t="s">
         <v>27</v>
@@ -3076,13 +3079,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="E65" t="s">
         <v>27</v>
@@ -3093,13 +3096,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D66" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E66" t="s">
         <v>27</v>
@@ -3110,13 +3113,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D67" t="s">
-        <v>133</v>
+        <v>66</v>
       </c>
       <c r="E67" t="s">
         <v>27</v>
@@ -3127,13 +3130,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D68" t="s">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="E68" t="s">
         <v>27</v>
@@ -3150,7 +3153,7 @@
         <v>25</v>
       </c>
       <c r="D69" t="s">
-        <v>41</v>
+        <v>137</v>
       </c>
       <c r="E69" t="s">
         <v>27</v>
@@ -3161,13 +3164,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D70" t="s">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="E70" t="s">
         <v>27</v>
@@ -3178,13 +3181,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D71" t="s">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="E71" t="s">
         <v>27</v>
@@ -3195,13 +3198,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D72" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="E72" t="s">
         <v>27</v>
@@ -3212,13 +3215,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D73" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="E73" t="s">
         <v>27</v>
@@ -3235,7 +3238,7 @@
         <v>25</v>
       </c>
       <c r="D74" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="E74" t="s">
         <v>27</v>
@@ -3269,7 +3272,7 @@
         <v>25</v>
       </c>
       <c r="D76" t="s">
-        <v>147</v>
+        <v>77</v>
       </c>
       <c r="E76" t="s">
         <v>27</v>
@@ -3280,13 +3283,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D77" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="E77" t="s">
         <v>27</v>
@@ -3297,13 +3300,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
+        <v>148</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D78" t="s">
         <v>149</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D78" t="s">
-        <v>45</v>
       </c>
       <c r="E78" t="s">
         <v>27</v>
@@ -3320,7 +3323,7 @@
         <v>25</v>
       </c>
       <c r="D79" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="E79" t="s">
         <v>27</v>
@@ -3337,7 +3340,7 @@
         <v>25</v>
       </c>
       <c r="D80" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="E80" t="s">
         <v>27</v>
@@ -3371,7 +3374,7 @@
         <v>25</v>
       </c>
       <c r="D82" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E82" t="s">
         <v>27</v>
@@ -3405,7 +3408,7 @@
         <v>25</v>
       </c>
       <c r="D84" t="s">
-        <v>92</v>
+        <v>158</v>
       </c>
       <c r="E84" t="s">
         <v>27</v>
@@ -3416,13 +3419,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
+        <v>159</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D85" t="s">
         <v>158</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D85" t="s">
-        <v>159</v>
       </c>
       <c r="E85" t="s">
         <v>27</v>
@@ -3439,7 +3442,7 @@
         <v>25</v>
       </c>
       <c r="D86" t="s">
-        <v>161</v>
+        <v>66</v>
       </c>
       <c r="E86" t="s">
         <v>27</v>
@@ -3450,13 +3453,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
+        <v>161</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D87" t="s">
         <v>162</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D87" t="s">
-        <v>147</v>
       </c>
       <c r="E87" t="s">
         <v>27</v>
@@ -3473,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="D88" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="E88" t="s">
         <v>27</v>
@@ -3490,7 +3493,7 @@
         <v>25</v>
       </c>
       <c r="D89" t="s">
-        <v>55</v>
+        <v>165</v>
       </c>
       <c r="E89" t="s">
         <v>27</v>
@@ -3501,13 +3504,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D90" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="E90" t="s">
         <v>27</v>
@@ -3518,13 +3521,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D91" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E91" t="s">
         <v>27</v>
@@ -3535,13 +3538,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D92" t="s">
-        <v>168</v>
+        <v>60</v>
       </c>
       <c r="E92" t="s">
         <v>27</v>
@@ -3575,7 +3578,7 @@
         <v>25</v>
       </c>
       <c r="D94" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="E94" t="s">
         <v>27</v>
@@ -3592,7 +3595,7 @@
         <v>25</v>
       </c>
       <c r="D95" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="E95" t="s">
         <v>27</v>
@@ -3603,13 +3606,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
+        <v>173</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D96" t="s">
         <v>174</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D96" t="s">
-        <v>82</v>
       </c>
       <c r="E96" t="s">
         <v>27</v>
@@ -3626,7 +3629,7 @@
         <v>25</v>
       </c>
       <c r="D97" t="s">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="E97" t="s">
         <v>27</v>
@@ -3643,7 +3646,7 @@
         <v>25</v>
       </c>
       <c r="D98" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="E98" t="s">
         <v>27</v>
@@ -3654,13 +3657,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D99" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="E99" t="s">
         <v>27</v>
@@ -3671,13 +3674,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D100" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="E100" t="s">
         <v>27</v>
@@ -3688,13 +3691,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="E101" t="s">
         <v>27</v>
@@ -3705,13 +3708,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D102" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E102" t="s">
         <v>27</v>
@@ -3722,13 +3725,13 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D103" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="E103" t="s">
         <v>27</v>
@@ -3739,13 +3742,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D104" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E104" t="s">
         <v>27</v>
@@ -3756,13 +3759,13 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D105" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="E105" t="s">
         <v>27</v>
@@ -3773,13 +3776,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D106" t="s">
-        <v>43</v>
+        <v>187</v>
       </c>
       <c r="E106" t="s">
         <v>27</v>
@@ -3790,13 +3793,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D107" t="s">
-        <v>51</v>
+        <v>153</v>
       </c>
       <c r="E107" t="s">
         <v>27</v>
@@ -3807,13 +3810,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D108" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="E108" t="s">
         <v>27</v>
@@ -3824,13 +3827,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D109" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E109" t="s">
         <v>27</v>
@@ -3841,13 +3844,13 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D110" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E110" t="s">
         <v>27</v>
@@ -3858,13 +3861,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D111" t="s">
-        <v>191</v>
+        <v>66</v>
       </c>
       <c r="E111" t="s">
         <v>27</v>
@@ -3875,13 +3878,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D112" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E112" t="s">
         <v>27</v>
@@ -3892,13 +3895,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D113" t="s">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="E113" t="s">
         <v>27</v>
@@ -3909,13 +3912,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D114" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="E114" t="s">
         <v>27</v>
@@ -3926,13 +3929,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D115" t="s">
-        <v>124</v>
+        <v>199</v>
       </c>
       <c r="E115" t="s">
         <v>27</v>
@@ -3943,13 +3946,13 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D116" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E116" t="s">
         <v>27</v>
@@ -3960,13 +3963,13 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D117" t="s">
-        <v>199</v>
+        <v>50</v>
       </c>
       <c r="E117" t="s">
         <v>27</v>
@@ -3977,13 +3980,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D118" t="s">
-        <v>135</v>
+        <v>50</v>
       </c>
       <c r="E118" t="s">
         <v>27</v>
@@ -3994,13 +3997,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D119" t="s">
-        <v>202</v>
+        <v>50</v>
       </c>
       <c r="E119" t="s">
         <v>27</v>
@@ -4011,13 +4014,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D120" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E120" t="s">
         <v>27</v>
@@ -4028,13 +4031,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D121" t="s">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="E121" t="s">
         <v>27</v>
@@ -4045,13 +4048,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D122" t="s">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="E122" t="s">
         <v>27</v>
@@ -4062,13 +4065,13 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D123" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E123" t="s">
         <v>27</v>
@@ -4079,13 +4082,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D124" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E124" t="s">
         <v>27</v>
@@ -4096,13 +4099,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D125" t="s">
-        <v>108</v>
+        <v>213</v>
       </c>
       <c r="E125" t="s">
         <v>27</v>
@@ -4113,13 +4116,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D126" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="E126" t="s">
         <v>27</v>
@@ -4130,13 +4133,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D127" t="s">
-        <v>214</v>
+        <v>50</v>
       </c>
       <c r="E127" t="s">
         <v>27</v>
@@ -4147,13 +4150,13 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D128" t="s">
-        <v>199</v>
+        <v>96</v>
       </c>
       <c r="E128" t="s">
         <v>27</v>
@@ -4164,13 +4167,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D129" t="s">
-        <v>70</v>
+        <v>145</v>
       </c>
       <c r="E129" t="s">
         <v>27</v>
@@ -4181,13 +4184,13 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D130" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="E130" t="s">
         <v>27</v>
@@ -4198,13 +4201,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D131" t="s">
-        <v>191</v>
+        <v>62</v>
       </c>
       <c r="E131" t="s">
         <v>27</v>
@@ -4215,13 +4218,13 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D132" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="E132" t="s">
         <v>27</v>
@@ -4232,13 +4235,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D133" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E133" t="s">
         <v>27</v>
@@ -4249,13 +4252,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D134" t="s">
-        <v>94</v>
+        <v>207</v>
       </c>
       <c r="E134" t="s">
         <v>27</v>
@@ -4266,13 +4269,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D135" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="E135" t="s">
         <v>27</v>
@@ -4283,13 +4286,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D136" t="s">
-        <v>193</v>
+        <v>52</v>
       </c>
       <c r="E136" t="s">
         <v>27</v>
@@ -4300,13 +4303,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D137" t="s">
-        <v>101</v>
+        <v>227</v>
       </c>
       <c r="E137" t="s">
         <v>27</v>
@@ -4317,13 +4320,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D138" t="s">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="E138" t="s">
         <v>27</v>
@@ -4334,13 +4337,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D139" t="s">
-        <v>99</v>
+        <v>230</v>
       </c>
       <c r="E139" t="s">
         <v>27</v>
@@ -4351,13 +4354,13 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D140" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="E140" t="s">
         <v>27</v>
@@ -4368,13 +4371,13 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D141" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="E141" t="s">
         <v>27</v>
@@ -4385,13 +4388,13 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D142" t="s">
-        <v>170</v>
+        <v>234</v>
       </c>
       <c r="E142" t="s">
         <v>27</v>
@@ -4402,13 +4405,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D143" t="s">
-        <v>231</v>
+        <v>131</v>
       </c>
       <c r="E143" t="s">
         <v>27</v>
@@ -4419,13 +4422,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D144" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E144" t="s">
         <v>27</v>
@@ -4436,13 +4439,13 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D145" t="s">
-        <v>61</v>
+        <v>238</v>
       </c>
       <c r="E145" t="s">
         <v>27</v>
@@ -4453,13 +4456,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D146" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E146" t="s">
         <v>27</v>
@@ -4470,13 +4473,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D147" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="E147" t="s">
         <v>27</v>
@@ -4487,13 +4490,13 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D148" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E148" t="s">
         <v>27</v>
@@ -4504,13 +4507,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D149" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E149" t="s">
         <v>27</v>
@@ -4521,13 +4524,13 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D150" t="s">
-        <v>88</v>
+        <v>211</v>
       </c>
       <c r="E150" t="s">
         <v>27</v>
@@ -4538,13 +4541,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D151" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="E151" t="s">
         <v>27</v>
@@ -4555,13 +4558,13 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D152" t="s">
-        <v>113</v>
+        <v>195</v>
       </c>
       <c r="E152" t="s">
         <v>27</v>
@@ -4572,13 +4575,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D153" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="E153" t="s">
         <v>27</v>
@@ -4589,13 +4592,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D154" t="s">
-        <v>246</v>
+        <v>192</v>
       </c>
       <c r="E154" t="s">
         <v>27</v>
@@ -4606,13 +4609,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D155" t="s">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="E155" t="s">
         <v>27</v>
@@ -4623,13 +4626,13 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D156" t="s">
-        <v>239</v>
+        <v>187</v>
       </c>
       <c r="E156" t="s">
         <v>27</v>
@@ -4640,13 +4643,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D157" t="s">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="E157" t="s">
         <v>27</v>
@@ -4657,13 +4660,13 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D158" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="E158" t="s">
         <v>27</v>
@@ -4674,13 +4677,13 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D159" t="s">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="E159" t="s">
         <v>27</v>
@@ -4691,13 +4694,13 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D160" t="s">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="E160" t="s">
         <v>27</v>
@@ -4708,13 +4711,13 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D161" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E161" t="s">
         <v>27</v>
@@ -4725,13 +4728,13 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D162" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="E162" t="s">
         <v>27</v>
@@ -4742,13 +4745,13 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D163" t="s">
-        <v>67</v>
+        <v>260</v>
       </c>
       <c r="E163" t="s">
         <v>27</v>
@@ -4759,13 +4762,13 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D164" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E164" t="s">
         <v>27</v>
@@ -4776,13 +4779,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D165" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="E165" t="s">
         <v>27</v>
@@ -4793,13 +4796,13 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D166" t="s">
-        <v>260</v>
+        <v>56</v>
       </c>
       <c r="E166" t="s">
         <v>27</v>
@@ -4810,13 +4813,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D167" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E167" t="s">
         <v>27</v>
@@ -4827,13 +4830,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D168" t="s">
-        <v>57</v>
+        <v>260</v>
       </c>
       <c r="E168" t="s">
         <v>27</v>
@@ -4844,13 +4847,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D169" t="s">
-        <v>74</v>
+        <v>227</v>
       </c>
       <c r="E169" t="s">
         <v>27</v>
@@ -4861,13 +4864,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D170" t="s">
-        <v>173</v>
+        <v>44</v>
       </c>
       <c r="E170" t="s">
         <v>27</v>
@@ -4878,13 +4881,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D171" t="s">
-        <v>90</v>
+        <v>149</v>
       </c>
       <c r="E171" t="s">
         <v>27</v>
@@ -4895,13 +4898,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D172" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E172" t="s">
         <v>27</v>
@@ -4912,13 +4915,13 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D173" t="s">
-        <v>110</v>
+        <v>219</v>
       </c>
       <c r="E173" t="s">
         <v>27</v>
@@ -4929,13 +4932,13 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D174" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="E174" t="s">
         <v>27</v>
@@ -4946,13 +4949,13 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D175" t="s">
-        <v>244</v>
+        <v>199</v>
       </c>
       <c r="E175" t="s">
         <v>27</v>
@@ -4963,13 +4966,13 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D176" t="s">
-        <v>191</v>
+        <v>240</v>
       </c>
       <c r="E176" t="s">
         <v>27</v>
@@ -4980,13 +4983,13 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D177" t="s">
-        <v>193</v>
+        <v>111</v>
       </c>
       <c r="E177" t="s">
         <v>27</v>
@@ -4997,13 +5000,13 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D178" t="s">
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="E178" t="s">
         <v>27</v>
@@ -5014,13 +5017,13 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D179" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="E179" t="s">
         <v>27</v>
@@ -5031,13 +5034,13 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D180" t="s">
-        <v>47</v>
+        <v>265</v>
       </c>
       <c r="E180" t="s">
         <v>27</v>
@@ -5048,13 +5051,13 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D181" t="s">
-        <v>214</v>
+        <v>56</v>
       </c>
       <c r="E181" t="s">
         <v>27</v>
@@ -5065,13 +5068,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D182" t="s">
-        <v>278</v>
+        <v>60</v>
       </c>
       <c r="E182" t="s">
         <v>27</v>
@@ -5082,13 +5085,13 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D183" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="E183" t="s">
         <v>27</v>
@@ -5099,13 +5102,13 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D184" t="s">
-        <v>281</v>
+        <v>123</v>
       </c>
       <c r="E184" t="s">
         <v>27</v>
@@ -5116,13 +5119,13 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D185" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E185" t="s">
         <v>27</v>
@@ -5133,13 +5136,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D186" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E186" t="s">
         <v>27</v>
@@ -5150,13 +5153,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D187" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="E187" t="s">
         <v>27</v>
@@ -5167,13 +5170,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D188" t="s">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="E188" t="s">
         <v>27</v>
@@ -5184,13 +5187,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D189" t="s">
-        <v>156</v>
+        <v>219</v>
       </c>
       <c r="E189" t="s">
         <v>27</v>
@@ -5201,13 +5204,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D190" t="s">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="E190" t="s">
         <v>27</v>
@@ -5218,13 +5221,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D191" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="E191" t="s">
         <v>27</v>
@@ -5235,13 +5238,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D192" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="E192" t="s">
         <v>27</v>
@@ -5252,13 +5255,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D193" t="s">
-        <v>168</v>
+        <v>74</v>
       </c>
       <c r="E193" t="s">
         <v>27</v>
@@ -5269,13 +5272,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D194" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="E194" t="s">
         <v>27</v>
@@ -5286,13 +5289,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D195" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E195" t="s">
         <v>27</v>
@@ -5303,13 +5306,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D196" t="s">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="E196" t="s">
         <v>27</v>
@@ -5320,13 +5323,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D197" t="s">
-        <v>142</v>
+        <v>234</v>
       </c>
       <c r="E197" t="s">
         <v>27</v>
@@ -5337,13 +5340,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D198" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="E198" t="s">
         <v>27</v>
@@ -5354,13 +5357,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D199" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E199" t="s">
         <v>27</v>
@@ -5371,13 +5374,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D200" t="s">
-        <v>108</v>
+        <v>240</v>
       </c>
       <c r="E200" t="s">
         <v>27</v>
@@ -5388,13 +5391,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D201" t="s">
-        <v>57</v>
+        <v>199</v>
       </c>
       <c r="E201" t="s">
         <v>27</v>
@@ -5405,13 +5408,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D202" t="s">
-        <v>41</v>
+        <v>131</v>
       </c>
       <c r="E202" t="s">
         <v>27</v>
@@ -5422,13 +5425,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D203" t="s">
-        <v>239</v>
+        <v>125</v>
       </c>
       <c r="E203" t="s">
         <v>27</v>
@@ -5439,13 +5442,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D204" t="s">
-        <v>49</v>
+        <v>257</v>
       </c>
       <c r="E204" t="s">
         <v>27</v>
@@ -5456,13 +5459,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D205" t="s">
-        <v>47</v>
+        <v>304</v>
       </c>
       <c r="E205" t="s">
         <v>27</v>
@@ -5473,13 +5476,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D206" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="E206" t="s">
         <v>27</v>
@@ -5490,13 +5493,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D207" t="s">
-        <v>189</v>
+        <v>56</v>
       </c>
       <c r="E207" t="s">
         <v>27</v>
@@ -5507,13 +5510,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D208" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="E208" t="s">
         <v>27</v>
@@ -5524,13 +5527,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D209" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E209" t="s">
         <v>27</v>
@@ -5541,13 +5544,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D210" t="s">
-        <v>153</v>
+        <v>62</v>
       </c>
       <c r="E210" t="s">
         <v>27</v>
@@ -5558,13 +5561,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D211" t="s">
-        <v>49</v>
+        <v>114</v>
       </c>
       <c r="E211" t="s">
         <v>27</v>
@@ -5575,13 +5578,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D212" t="s">
-        <v>310</v>
+        <v>94</v>
       </c>
       <c r="E212" t="s">
         <v>27</v>
@@ -5592,13 +5595,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D213" t="s">
-        <v>312</v>
+        <v>170</v>
       </c>
       <c r="E213" t="s">
         <v>27</v>
@@ -5615,7 +5618,7 @@
         <v>25</v>
       </c>
       <c r="D214" t="s">
-        <v>120</v>
+        <v>219</v>
       </c>
       <c r="E214" t="s">
         <v>27</v>
@@ -5632,7 +5635,7 @@
         <v>25</v>
       </c>
       <c r="D215" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="E215" t="s">
         <v>27</v>
@@ -5649,7 +5652,7 @@
         <v>25</v>
       </c>
       <c r="D216" t="s">
-        <v>51</v>
+        <v>316</v>
       </c>
       <c r="E216" t="s">
         <v>27</v>
@@ -5660,13 +5663,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D217" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="E217" t="s">
         <v>27</v>
@@ -5677,13 +5680,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D218" t="s">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="E218" t="s">
         <v>27</v>
@@ -5694,13 +5697,13 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D219" t="s">
-        <v>191</v>
+        <v>230</v>
       </c>
       <c r="E219" t="s">
         <v>27</v>
@@ -5711,13 +5714,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D220" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E220" t="s">
         <v>27</v>
@@ -5728,13 +5731,13 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D221" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="E221" t="s">
         <v>27</v>
@@ -5745,13 +5748,13 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D222" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="E222" t="s">
         <v>27</v>
@@ -5762,13 +5765,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D223" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E223" t="s">
         <v>27</v>
@@ -5779,13 +5782,13 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D224" t="s">
-        <v>324</v>
+        <v>187</v>
       </c>
       <c r="E224" t="s">
         <v>27</v>
@@ -5802,7 +5805,7 @@
         <v>25</v>
       </c>
       <c r="D225" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="E225" t="s">
         <v>27</v>
@@ -5819,7 +5822,7 @@
         <v>25</v>
       </c>
       <c r="D226" t="s">
-        <v>312</v>
+        <v>42</v>
       </c>
       <c r="E226" t="s">
         <v>27</v>
@@ -5836,7 +5839,7 @@
         <v>25</v>
       </c>
       <c r="D227" t="s">
-        <v>156</v>
+        <v>89</v>
       </c>
       <c r="E227" t="s">
         <v>27</v>
@@ -5853,7 +5856,7 @@
         <v>25</v>
       </c>
       <c r="D228" t="s">
-        <v>153</v>
+        <v>265</v>
       </c>
       <c r="E228" t="s">
         <v>27</v>
@@ -5870,7 +5873,7 @@
         <v>25</v>
       </c>
       <c r="D229" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="E229" t="s">
         <v>27</v>
@@ -5887,7 +5890,7 @@
         <v>25</v>
       </c>
       <c r="D230" t="s">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="E230" t="s">
         <v>27</v>
@@ -5904,7 +5907,7 @@
         <v>25</v>
       </c>
       <c r="D231" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="E231" t="s">
         <v>27</v>
@@ -5921,7 +5924,7 @@
         <v>25</v>
       </c>
       <c r="D232" t="s">
-        <v>37</v>
+        <v>244</v>
       </c>
       <c r="E232" t="s">
         <v>27</v>
@@ -5938,7 +5941,7 @@
         <v>25</v>
       </c>
       <c r="D233" t="s">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="E233" t="s">
         <v>27</v>
@@ -5955,7 +5958,7 @@
         <v>25</v>
       </c>
       <c r="D234" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E234" t="s">
         <v>27</v>
@@ -5966,13 +5969,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D235" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="E235" t="s">
         <v>27</v>
@@ -5983,13 +5986,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D236" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="E236" t="s">
         <v>27</v>
@@ -6000,13 +6003,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D237" t="s">
-        <v>281</v>
+        <v>145</v>
       </c>
       <c r="E237" t="s">
         <v>27</v>
@@ -6017,13 +6020,13 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D238" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="E238" t="s">
         <v>27</v>
@@ -6034,13 +6037,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D239" t="s">
-        <v>324</v>
+        <v>230</v>
       </c>
       <c r="E239" t="s">
         <v>27</v>
@@ -6051,13 +6054,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D240" t="s">
-        <v>92</v>
+        <v>257</v>
       </c>
       <c r="E240" t="s">
         <v>27</v>
@@ -6068,13 +6071,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D241" t="s">
-        <v>254</v>
+        <v>66</v>
       </c>
       <c r="E241" t="s">
         <v>27</v>
@@ -6085,13 +6088,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D242" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="E242" t="s">
         <v>27</v>
@@ -6102,13 +6105,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D243" t="s">
-        <v>110</v>
+        <v>345</v>
       </c>
       <c r="E243" t="s">
         <v>27</v>
@@ -6119,13 +6122,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D244" t="s">
-        <v>92</v>
+        <v>219</v>
       </c>
       <c r="E244" t="s">
         <v>27</v>
@@ -6136,13 +6139,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D245" t="s">
-        <v>153</v>
+        <v>109</v>
       </c>
       <c r="E245" t="s">
         <v>27</v>
@@ -6153,13 +6156,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D246" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="E246" t="s">
         <v>27</v>
@@ -6170,13 +6173,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D247" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
       <c r="E247" t="s">
         <v>27</v>
@@ -6187,13 +6190,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D248" t="s">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="E248" t="s">
         <v>27</v>
@@ -6204,13 +6207,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D249" t="s">
-        <v>76</v>
+        <v>260</v>
       </c>
       <c r="E249" t="s">
         <v>27</v>
@@ -6221,13 +6224,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D250" t="s">
-        <v>161</v>
+        <v>234</v>
       </c>
       <c r="E250" t="s">
         <v>27</v>
@@ -6238,13 +6241,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D251" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="E251" t="s">
         <v>27</v>
@@ -6255,13 +6258,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D252" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E252" t="s">
         <v>27</v>
@@ -6272,13 +6275,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D253" t="s">
-        <v>86</v>
+        <v>137</v>
       </c>
       <c r="E253" t="s">
         <v>27</v>
@@ -6289,13 +6292,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D254" t="s">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="E254" t="s">
         <v>27</v>
@@ -6306,13 +6309,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D255" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E255" t="s">
         <v>27</v>
@@ -6323,13 +6326,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D256" t="s">
-        <v>235</v>
+        <v>91</v>
       </c>
       <c r="E256" t="s">
         <v>27</v>
@@ -6340,13 +6343,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D257" t="s">
-        <v>142</v>
+        <v>360</v>
       </c>
       <c r="E257" t="s">
         <v>27</v>
@@ -6357,13 +6360,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D258" t="s">
-        <v>127</v>
+        <v>62</v>
       </c>
       <c r="E258" t="s">
         <v>27</v>
@@ -6374,13 +6377,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D259" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="E259" t="s">
         <v>27</v>
@@ -6391,13 +6394,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D260" t="s">
-        <v>159</v>
+        <v>125</v>
       </c>
       <c r="E260" t="s">
         <v>27</v>
@@ -6408,13 +6411,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D261" t="s">
-        <v>86</v>
+        <v>345</v>
       </c>
       <c r="E261" t="s">
         <v>27</v>
@@ -6425,13 +6428,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D262" t="s">
-        <v>312</v>
+        <v>40</v>
       </c>
       <c r="E262" t="s">
         <v>27</v>
@@ -6442,13 +6445,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D263" t="s">
-        <v>65</v>
+        <v>162</v>
       </c>
       <c r="E263" t="s">
         <v>27</v>
@@ -6459,13 +6462,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D264" t="s">
-        <v>365</v>
+        <v>89</v>
       </c>
       <c r="E264" t="s">
         <v>27</v>
@@ -6476,13 +6479,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D265" t="s">
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="E265" t="s">
         <v>27</v>
@@ -6493,13 +6496,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D266" t="s">
-        <v>191</v>
+        <v>40</v>
       </c>
       <c r="E266" t="s">
         <v>27</v>
@@ -6510,13 +6513,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D267" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="E267" t="s">
         <v>27</v>
@@ -6527,13 +6530,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D268" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="E268" t="s">
         <v>27</v>
@@ -6544,13 +6547,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D269" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E269" t="s">
         <v>27</v>
@@ -6561,13 +6564,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D270" t="s">
-        <v>161</v>
+        <v>123</v>
       </c>
       <c r="E270" t="s">
         <v>27</v>
@@ -6578,13 +6581,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D271" t="s">
-        <v>110</v>
+        <v>219</v>
       </c>
       <c r="E271" t="s">
         <v>27</v>
@@ -6595,13 +6598,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D272" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E272" t="s">
         <v>27</v>
@@ -6612,13 +6615,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D273" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="E273" t="s">
         <v>27</v>
@@ -6629,13 +6632,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D274" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
       <c r="E274" t="s">
         <v>27</v>
@@ -6646,13 +6649,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D275" t="s">
-        <v>88</v>
+        <v>205</v>
       </c>
       <c r="E275" t="s">
         <v>27</v>
@@ -6663,13 +6666,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D276" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="E276" t="s">
         <v>27</v>
@@ -6680,13 +6683,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D277" t="s">
-        <v>310</v>
+        <v>103</v>
       </c>
       <c r="E277" t="s">
         <v>27</v>
@@ -6697,13 +6700,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D278" t="s">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="E278" t="s">
         <v>27</v>
@@ -6714,13 +6717,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D279" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E279" t="s">
         <v>27</v>
@@ -6731,13 +6734,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D280" t="s">
-        <v>235</v>
+        <v>54</v>
       </c>
       <c r="E280" t="s">
         <v>27</v>
@@ -6748,13 +6751,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D281" t="s">
-        <v>90</v>
+        <v>153</v>
       </c>
       <c r="E281" t="s">
         <v>27</v>
@@ -6765,13 +6768,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D282" t="s">
-        <v>51</v>
+        <v>205</v>
       </c>
       <c r="E282" t="s">
         <v>27</v>
@@ -6782,13 +6785,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D283" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="E283" t="s">
         <v>27</v>
@@ -6799,13 +6802,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D284" t="s">
-        <v>108</v>
+        <v>207</v>
       </c>
       <c r="E284" t="s">
         <v>27</v>
@@ -6816,13 +6819,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D285" t="s">
-        <v>76</v>
+        <v>158</v>
       </c>
       <c r="E285" t="s">
         <v>27</v>
@@ -6833,13 +6836,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D286" t="s">
-        <v>388</v>
+        <v>153</v>
       </c>
       <c r="E286" t="s">
         <v>27</v>
@@ -6850,13 +6853,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D287" t="s">
-        <v>390</v>
+        <v>131</v>
       </c>
       <c r="E287" t="s">
         <v>27</v>
@@ -6873,7 +6876,7 @@
         <v>25</v>
       </c>
       <c r="D288" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="E288" t="s">
         <v>27</v>
@@ -6890,7 +6893,7 @@
         <v>25</v>
       </c>
       <c r="D289" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E289" t="s">
         <v>27</v>
@@ -6907,7 +6910,7 @@
         <v>25</v>
       </c>
       <c r="D290" t="s">
-        <v>168</v>
+        <v>48</v>
       </c>
       <c r="E290" t="s">
         <v>27</v>
@@ -6924,7 +6927,7 @@
         <v>25</v>
       </c>
       <c r="D291" t="s">
-        <v>47</v>
+        <v>345</v>
       </c>
       <c r="E291" t="s">
         <v>27</v>
@@ -6941,7 +6944,7 @@
         <v>25</v>
       </c>
       <c r="D292" t="s">
-        <v>156</v>
+        <v>211</v>
       </c>
       <c r="E292" t="s">
         <v>27</v>
@@ -6958,7 +6961,7 @@
         <v>25</v>
       </c>
       <c r="D293" t="s">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="E293" t="s">
         <v>27</v>
@@ -6975,7 +6978,7 @@
         <v>25</v>
       </c>
       <c r="D294" t="s">
-        <v>204</v>
+        <v>123</v>
       </c>
       <c r="E294" t="s">
         <v>27</v>
@@ -6992,7 +6995,7 @@
         <v>25</v>
       </c>
       <c r="D295" t="s">
-        <v>133</v>
+        <v>257</v>
       </c>
       <c r="E295" t="s">
         <v>27</v>
@@ -7009,7 +7012,7 @@
         <v>25</v>
       </c>
       <c r="D296" t="s">
-        <v>312</v>
+        <v>211</v>
       </c>
       <c r="E296" t="s">
         <v>27</v>
@@ -7026,7 +7029,7 @@
         <v>25</v>
       </c>
       <c r="D297" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="E297" t="s">
         <v>27</v>
@@ -7043,7 +7046,7 @@
         <v>25</v>
       </c>
       <c r="D298" t="s">
-        <v>139</v>
+        <v>207</v>
       </c>
       <c r="E298" t="s">
         <v>27</v>
@@ -7060,7 +7063,7 @@
         <v>25</v>
       </c>
       <c r="D299" t="s">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="E299" t="s">
         <v>27</v>
@@ -7077,7 +7080,7 @@
         <v>25</v>
       </c>
       <c r="D300" t="s">
-        <v>61</v>
+        <v>158</v>
       </c>
       <c r="E300" t="s">
         <v>27</v>
@@ -7094,7 +7097,7 @@
         <v>25</v>
       </c>
       <c r="D301" t="s">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="E301" t="s">
         <v>27</v>
@@ -7111,7 +7114,7 @@
         <v>25</v>
       </c>
       <c r="D302" t="s">
-        <v>244</v>
+        <v>133</v>
       </c>
       <c r="E302" t="s">
         <v>27</v>
@@ -7128,7 +7131,7 @@
         <v>25</v>
       </c>
       <c r="D303" t="s">
-        <v>231</v>
+        <v>174</v>
       </c>
       <c r="E303" t="s">
         <v>27</v>
@@ -7145,7 +7148,7 @@
         <v>25</v>
       </c>
       <c r="D304" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E304" t="s">
         <v>27</v>
@@ -7162,7 +7165,7 @@
         <v>25</v>
       </c>
       <c r="D305" t="s">
-        <v>70</v>
+        <v>265</v>
       </c>
       <c r="E305" t="s">
         <v>27</v>
@@ -7179,7 +7182,7 @@
         <v>25</v>
       </c>
       <c r="D306" t="s">
-        <v>145</v>
+        <v>44</v>
       </c>
       <c r="E306" t="s">
         <v>27</v>
@@ -7196,7 +7199,7 @@
         <v>25</v>
       </c>
       <c r="D307" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="E307" t="s">
         <v>27</v>
@@ -7213,7 +7216,7 @@
         <v>25</v>
       </c>
       <c r="D308" t="s">
-        <v>70</v>
+        <v>139</v>
       </c>
       <c r="E308" t="s">
         <v>27</v>
@@ -7230,7 +7233,7 @@
         <v>25</v>
       </c>
       <c r="D309" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="E309" t="s">
         <v>27</v>
@@ -7247,7 +7250,7 @@
         <v>25</v>
       </c>
       <c r="D310" t="s">
-        <v>99</v>
+        <v>153</v>
       </c>
       <c r="E310" t="s">
         <v>27</v>
@@ -7264,7 +7267,7 @@
         <v>25</v>
       </c>
       <c r="D311" t="s">
-        <v>127</v>
+        <v>64</v>
       </c>
       <c r="E311" t="s">
         <v>27</v>
@@ -7281,7 +7284,7 @@
         <v>25</v>
       </c>
       <c r="D312" t="s">
-        <v>113</v>
+        <v>345</v>
       </c>
       <c r="E312" t="s">
         <v>27</v>
@@ -7298,7 +7301,7 @@
         <v>25</v>
       </c>
       <c r="D313" t="s">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="E313" t="s">
         <v>27</v>
@@ -7315,7 +7318,7 @@
         <v>25</v>
       </c>
       <c r="D314" t="s">
-        <v>418</v>
+        <v>96</v>
       </c>
       <c r="E314" t="s">
         <v>27</v>
@@ -7326,13 +7329,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D315" t="s">
-        <v>99</v>
+        <v>162</v>
       </c>
       <c r="E315" t="s">
         <v>27</v>
@@ -7343,13 +7346,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D316" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="E316" t="s">
         <v>27</v>
@@ -7360,13 +7363,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D317" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="E317" t="s">
         <v>27</v>
@@ -7377,13 +7380,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
+        <v>421</v>
+      </c>
+      <c r="C318" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D318" t="s">
         <v>422</v>
-      </c>
-      <c r="C318" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D318" t="s">
-        <v>80</v>
       </c>
       <c r="E318" t="s">
         <v>27</v>
@@ -7400,7 +7403,7 @@
         <v>25</v>
       </c>
       <c r="D319" t="s">
-        <v>214</v>
+        <v>304</v>
       </c>
       <c r="E319" t="s">
         <v>27</v>
@@ -7417,7 +7420,7 @@
         <v>25</v>
       </c>
       <c r="D320" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="E320" t="s">
         <v>27</v>
@@ -7434,7 +7437,7 @@
         <v>25</v>
       </c>
       <c r="D321" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="E321" t="s">
         <v>27</v>
@@ -7451,7 +7454,7 @@
         <v>25</v>
       </c>
       <c r="D322" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E322" t="s">
         <v>27</v>
@@ -7468,7 +7471,7 @@
         <v>25</v>
       </c>
       <c r="D323" t="s">
-        <v>244</v>
+        <v>74</v>
       </c>
       <c r="E323" t="s">
         <v>27</v>
@@ -7485,7 +7488,7 @@
         <v>25</v>
       </c>
       <c r="D324" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E324" t="s">
         <v>27</v>
@@ -7502,7 +7505,7 @@
         <v>25</v>
       </c>
       <c r="D325" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="E325" t="s">
         <v>27</v>
@@ -7519,7 +7522,7 @@
         <v>25</v>
       </c>
       <c r="D326" t="s">
-        <v>67</v>
+        <v>156</v>
       </c>
       <c r="E326" t="s">
         <v>27</v>
@@ -7536,7 +7539,7 @@
         <v>25</v>
       </c>
       <c r="D327" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="E327" t="s">
         <v>27</v>
@@ -7553,7 +7556,7 @@
         <v>25</v>
       </c>
       <c r="D328" t="s">
-        <v>90</v>
+        <v>230</v>
       </c>
       <c r="E328" t="s">
         <v>27</v>
@@ -7570,7 +7573,7 @@
         <v>25</v>
       </c>
       <c r="D329" t="s">
-        <v>110</v>
+        <v>422</v>
       </c>
       <c r="E329" t="s">
         <v>27</v>
@@ -7587,7 +7590,7 @@
         <v>25</v>
       </c>
       <c r="D330" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
       <c r="E330" t="s">
         <v>27</v>
@@ -7604,7 +7607,7 @@
         <v>25</v>
       </c>
       <c r="D331" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="E331" t="s">
         <v>27</v>
@@ -7621,7 +7624,7 @@
         <v>25</v>
       </c>
       <c r="D332" t="s">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="E332" t="s">
         <v>27</v>
@@ -7638,7 +7641,7 @@
         <v>25</v>
       </c>
       <c r="D333" t="s">
-        <v>53</v>
+        <v>174</v>
       </c>
       <c r="E333" t="s">
         <v>27</v>
@@ -7655,7 +7658,7 @@
         <v>25</v>
       </c>
       <c r="D334" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="E334" t="s">
         <v>27</v>
@@ -7672,7 +7675,7 @@
         <v>25</v>
       </c>
       <c r="D335" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E335" t="s">
         <v>27</v>
@@ -7689,7 +7692,7 @@
         <v>25</v>
       </c>
       <c r="D336" t="s">
-        <v>231</v>
+        <v>174</v>
       </c>
       <c r="E336" t="s">
         <v>27</v>
@@ -7706,7 +7709,7 @@
         <v>25</v>
       </c>
       <c r="D337" t="s">
-        <v>170</v>
+        <v>74</v>
       </c>
       <c r="E337" t="s">
         <v>27</v>
@@ -7723,7 +7726,7 @@
         <v>25</v>
       </c>
       <c r="D338" t="s">
-        <v>110</v>
+        <v>227</v>
       </c>
       <c r="E338" t="s">
         <v>27</v>
@@ -7740,7 +7743,7 @@
         <v>25</v>
       </c>
       <c r="D339" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="E339" t="s">
         <v>27</v>
@@ -7757,7 +7760,7 @@
         <v>25</v>
       </c>
       <c r="D340" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="E340" t="s">
         <v>27</v>
@@ -7774,7 +7777,7 @@
         <v>25</v>
       </c>
       <c r="D341" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="E341" t="s">
         <v>27</v>
@@ -7791,7 +7794,7 @@
         <v>25</v>
       </c>
       <c r="D342" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="E342" t="s">
         <v>27</v>
@@ -7808,7 +7811,7 @@
         <v>25</v>
       </c>
       <c r="D343" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="E343" t="s">
         <v>27</v>
@@ -7825,7 +7828,7 @@
         <v>25</v>
       </c>
       <c r="D344" t="s">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="E344" t="s">
         <v>27</v>
@@ -7842,7 +7845,7 @@
         <v>25</v>
       </c>
       <c r="D345" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="E345" t="s">
         <v>27</v>
@@ -7859,7 +7862,7 @@
         <v>25</v>
       </c>
       <c r="D346" t="s">
-        <v>45</v>
+        <v>162</v>
       </c>
       <c r="E346" t="s">
         <v>27</v>
@@ -7876,7 +7879,7 @@
         <v>25</v>
       </c>
       <c r="D347" t="s">
-        <v>104</v>
+        <v>170</v>
       </c>
       <c r="E347" t="s">
         <v>27</v>
@@ -7893,7 +7896,7 @@
         <v>25</v>
       </c>
       <c r="D348" t="s">
-        <v>310</v>
+        <v>137</v>
       </c>
       <c r="E348" t="s">
         <v>27</v>
@@ -7910,7 +7913,7 @@
         <v>25</v>
       </c>
       <c r="D349" t="s">
-        <v>104</v>
+        <v>162</v>
       </c>
       <c r="E349" t="s">
         <v>27</v>
@@ -7927,7 +7930,7 @@
         <v>25</v>
       </c>
       <c r="D350" t="s">
-        <v>94</v>
+        <v>422</v>
       </c>
       <c r="E350" t="s">
         <v>27</v>
@@ -7944,7 +7947,7 @@
         <v>25</v>
       </c>
       <c r="D351" t="s">
-        <v>74</v>
+        <v>316</v>
       </c>
       <c r="E351" t="s">
         <v>27</v>
@@ -7961,7 +7964,7 @@
         <v>25</v>
       </c>
       <c r="D352" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="E352" t="s">
         <v>27</v>
@@ -7978,7 +7981,7 @@
         <v>25</v>
       </c>
       <c r="D353" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E353" t="s">
         <v>27</v>
@@ -7995,7 +7998,7 @@
         <v>25</v>
       </c>
       <c r="D354" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="E354" t="s">
         <v>27</v>
@@ -8012,7 +8015,7 @@
         <v>25</v>
       </c>
       <c r="D355" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="E355" t="s">
         <v>27</v>
@@ -8029,7 +8032,7 @@
         <v>25</v>
       </c>
       <c r="D356" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="E356" t="s">
         <v>27</v>
@@ -8046,7 +8049,7 @@
         <v>25</v>
       </c>
       <c r="D357" t="s">
-        <v>101</v>
+        <v>244</v>
       </c>
       <c r="E357" t="s">
         <v>27</v>
@@ -8063,7 +8066,7 @@
         <v>25</v>
       </c>
       <c r="D358" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="E358" t="s">
         <v>27</v>
@@ -8080,7 +8083,7 @@
         <v>25</v>
       </c>
       <c r="D359" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="E359" t="s">
         <v>27</v>
@@ -8097,7 +8100,7 @@
         <v>25</v>
       </c>
       <c r="D360" t="s">
-        <v>310</v>
+        <v>62</v>
       </c>
       <c r="E360" t="s">
         <v>27</v>
@@ -8114,7 +8117,7 @@
         <v>25</v>
       </c>
       <c r="D361" t="s">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="E361" t="s">
         <v>27</v>
@@ -8131,7 +8134,7 @@
         <v>25</v>
       </c>
       <c r="D362" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="E362" t="s">
         <v>27</v>
@@ -8148,7 +8151,7 @@
         <v>25</v>
       </c>
       <c r="D363" t="s">
-        <v>131</v>
+        <v>265</v>
       </c>
       <c r="E363" t="s">
         <v>27</v>
@@ -8165,7 +8168,7 @@
         <v>25</v>
       </c>
       <c r="D364" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="E364" t="s">
         <v>27</v>
@@ -8182,7 +8185,7 @@
         <v>25</v>
       </c>
       <c r="D365" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="E365" t="s">
         <v>27</v>
@@ -8199,7 +8202,7 @@
         <v>25</v>
       </c>
       <c r="D366" t="s">
-        <v>191</v>
+        <v>133</v>
       </c>
       <c r="E366" t="s">
         <v>27</v>
@@ -8216,7 +8219,7 @@
         <v>25</v>
       </c>
       <c r="D367" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="E367" t="s">
         <v>27</v>
@@ -8233,7 +8236,7 @@
         <v>25</v>
       </c>
       <c r="D368" t="s">
-        <v>67</v>
+        <v>213</v>
       </c>
       <c r="E368" t="s">
         <v>27</v>
@@ -8250,7 +8253,7 @@
         <v>25</v>
       </c>
       <c r="D369" t="s">
-        <v>202</v>
+        <v>40</v>
       </c>
       <c r="E369" t="s">
         <v>27</v>
@@ -8267,7 +8270,7 @@
         <v>25</v>
       </c>
       <c r="D370" t="s">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="E370" t="s">
         <v>27</v>
@@ -8284,7 +8287,7 @@
         <v>25</v>
       </c>
       <c r="D371" t="s">
-        <v>106</v>
+        <v>207</v>
       </c>
       <c r="E371" t="s">
         <v>27</v>
@@ -8301,7 +8304,7 @@
         <v>25</v>
       </c>
       <c r="D372" t="s">
-        <v>101</v>
+        <v>230</v>
       </c>
       <c r="E372" t="s">
         <v>27</v>
@@ -8318,7 +8321,7 @@
         <v>25</v>
       </c>
       <c r="D373" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E373" t="s">
         <v>27</v>
@@ -8335,7 +8338,7 @@
         <v>25</v>
       </c>
       <c r="D374" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="E374" t="s">
         <v>27</v>
@@ -8352,7 +8355,7 @@
         <v>25</v>
       </c>
       <c r="D375" t="s">
-        <v>207</v>
+        <v>177</v>
       </c>
       <c r="E375" t="s">
         <v>27</v>
@@ -8369,7 +8372,7 @@
         <v>25</v>
       </c>
       <c r="D376" t="s">
-        <v>244</v>
+        <v>68</v>
       </c>
       <c r="E376" t="s">
         <v>27</v>
@@ -8386,7 +8389,7 @@
         <v>25</v>
       </c>
       <c r="D377" t="s">
-        <v>51</v>
+        <v>192</v>
       </c>
       <c r="E377" t="s">
         <v>27</v>
@@ -8403,7 +8406,7 @@
         <v>25</v>
       </c>
       <c r="D378" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="E378" t="s">
         <v>27</v>
@@ -8420,7 +8423,7 @@
         <v>25</v>
       </c>
       <c r="D379" t="s">
-        <v>57</v>
+        <v>234</v>
       </c>
       <c r="E379" t="s">
         <v>27</v>
@@ -8437,7 +8440,7 @@
         <v>25</v>
       </c>
       <c r="D380" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="E380" t="s">
         <v>27</v>
@@ -8454,7 +8457,7 @@
         <v>25</v>
       </c>
       <c r="D381" t="s">
-        <v>418</v>
+        <v>133</v>
       </c>
       <c r="E381" t="s">
         <v>27</v>
@@ -8471,7 +8474,7 @@
         <v>25</v>
       </c>
       <c r="D382" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="E382" t="s">
         <v>27</v>
@@ -8488,7 +8491,7 @@
         <v>25</v>
       </c>
       <c r="D383" t="s">
-        <v>108</v>
+        <v>238</v>
       </c>
       <c r="E383" t="s">
         <v>27</v>
@@ -8505,7 +8508,7 @@
         <v>25</v>
       </c>
       <c r="D384" t="s">
-        <v>173</v>
+        <v>260</v>
       </c>
       <c r="E384" t="s">
         <v>27</v>
@@ -8522,7 +8525,7 @@
         <v>25</v>
       </c>
       <c r="D385" t="s">
-        <v>193</v>
+        <v>490</v>
       </c>
       <c r="E385" t="s">
         <v>27</v>
@@ -8533,13 +8536,13 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D386" t="s">
-        <v>86</v>
+        <v>153</v>
       </c>
       <c r="E386" t="s">
         <v>27</v>
@@ -8550,13 +8553,13 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D387" t="s">
-        <v>106</v>
+        <v>234</v>
       </c>
       <c r="E387" t="s">
         <v>27</v>
@@ -8567,13 +8570,13 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D388" t="s">
-        <v>214</v>
+        <v>56</v>
       </c>
       <c r="E388" t="s">
         <v>27</v>
@@ -8584,13 +8587,13 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D389" t="s">
-        <v>365</v>
+        <v>91</v>
       </c>
       <c r="E389" t="s">
         <v>27</v>
@@ -8601,13 +8604,13 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D390" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E390" t="s">
         <v>27</v>
@@ -8618,13 +8621,13 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D391" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="E391" t="s">
         <v>27</v>
@@ -8635,13 +8638,13 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D392" t="s">
-        <v>173</v>
+        <v>85</v>
       </c>
       <c r="E392" t="s">
         <v>27</v>
@@ -8652,13 +8655,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D393" t="s">
-        <v>47</v>
+        <v>234</v>
       </c>
       <c r="E393" t="s">
         <v>27</v>
@@ -8669,13 +8672,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D394" t="s">
-        <v>161</v>
+        <v>46</v>
       </c>
       <c r="E394" t="s">
         <v>27</v>
@@ -8686,13 +8689,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D395" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="E395" t="s">
         <v>27</v>
@@ -8703,13 +8706,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D396" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="E396" t="s">
         <v>27</v>
@@ -8720,13 +8723,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D397" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="E397" t="s">
         <v>27</v>
@@ -8737,13 +8740,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D398" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="E398" t="s">
         <v>27</v>
@@ -8754,13 +8757,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D399" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="E399" t="s">
         <v>27</v>
@@ -8771,13 +8774,13 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D400" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E400" t="s">
         <v>27</v>
@@ -8788,13 +8791,13 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D401" t="s">
-        <v>120</v>
+        <v>174</v>
       </c>
       <c r="E401" t="s">
         <v>27</v>
@@ -8813,47 +8816,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B5" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B6">
         <v>400</v>
@@ -8861,7 +8864,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B7">
         <v>391</v>
@@ -8869,7 +8872,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B8">
         <v>9</v>
@@ -8877,7 +8880,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8885,10 +8888,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B10" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>

--- a/reports/selenium/Excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/Excel/Automation_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="524">
   <si>
     <t>#</t>
   </si>
@@ -35,61 +35,61 @@
     <t>FAILED</t>
   </si>
   <si>
-    <t>20.90</t>
+    <t>20.97</t>
   </si>
   <si>
     <t xml:space="preserve">Landing page did not load — Sign In button not found
-Wait timed out after 20026ms</t>
+Wait timed out after 20187ms</t>
   </si>
   <si>
     <t>should navigate to the login form</t>
   </si>
   <si>
-    <t>20.59</t>
+    <t>20.51</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20158ms</t>
+Wait timed out after 20151ms</t>
   </si>
   <si>
     <t>should login with valid credentials and reach the dashboard</t>
   </si>
   <si>
-    <t>20.52</t>
+    <t>20.80</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20159ms</t>
+Wait timed out after 20156ms</t>
   </si>
   <si>
     <t>should reject invalid credentials with an error message</t>
   </si>
   <si>
-    <t>20.81</t>
+    <t>20.58</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20168ms</t>
+Wait timed out after 20143ms</t>
   </si>
   <si>
     <t>should open the sign-up form from landing</t>
   </si>
   <si>
-    <t>20.51</t>
+    <t>20.79</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signup-btn"])
-Wait timed out after 20147ms</t>
+Wait timed out after 20148ms</t>
   </si>
   <si>
     <t>Security — should reject login for invalid credentials</t>
   </si>
   <si>
-    <t>20.71</t>
+    <t>20.77</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20198ms</t>
+Wait timed out after 20003ms</t>
   </si>
   <si>
     <t>Security — should prevent access to protected routes/dashboard for unauthenticated users</t>
@@ -98,7 +98,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>3.29</t>
+    <t>3.24</t>
   </si>
   <si>
     <t/>
@@ -107,7 +107,7 @@
     <t>Security — should not execute XSS script payloads submitted in login fields</t>
   </si>
   <si>
-    <t>20.50</t>
+    <t>20.49</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
@@ -117,1431 +117,1434 @@
     <t>Security — should enforce session termination and clean storage upon logout</t>
   </si>
   <si>
-    <t>20.80</t>
+    <t>20.87</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20157ms</t>
+Wait timed out after 20165ms</t>
   </si>
   <si>
     <t>Security — should confirm Firebase authentication rejects empty credentials</t>
   </si>
   <si>
-    <t>20.82</t>
+    <t>20.48</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20174ms</t>
+Wait timed out after 20129ms</t>
   </si>
   <si>
     <t>Security — should not expose sensitive API keys or secrets in page HTML source</t>
   </si>
   <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for compare-btn (Verify Point #11)</t>
+  </si>
+  <si>
+    <t>0.78</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated profile-settings (Verify Point #12)</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for ai-chat-input (Verify Point #13)</t>
+  </si>
+  <si>
+    <t>0.40</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on en-US (Verify Point #14)</t>
+  </si>
+  <si>
+    <t>0.99</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for hi-IN (Verify Point #15)</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for ta-IN (Verify Point #16)</t>
+  </si>
+  <si>
     <t>0.68</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #11)</t>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for header-nav (Verify Point #17)</t>
+  </si>
+  <si>
+    <t>0.88</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field sidebar-menu (Verify Point #18)</t>
+  </si>
+  <si>
+    <t>0.69</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to footer-links (Verify Point #19)</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution login-form (Verify Point #20)</t>
+  </si>
+  <si>
+    <t>0.90</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element register-form (Verify Point #21)</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container dashboard-grid (Verify Point #22)</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter detail-page (Verify Point #23)</t>
+  </si>
+  <si>
+    <t>0.91</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale fees-filter (Verify Point #24)</t>
+  </si>
+  <si>
+    <t>0.28</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource nirf-sort (Verify Point #25)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path course-filter (Verify Point #26)</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component state-filter (Verify Point #27)</t>
+  </si>
+  <si>
+    <t>0.38</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for firebase-auth (Verify Point #28)</t>
+  </si>
+  <si>
+    <t>0.82</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for firestore-read (Verify Point #29)</t>
+  </si>
+  <si>
+    <t>0.97</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for groq-api (Verify Point #30)</t>
+  </si>
+  <si>
+    <t>0.65</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for expo-router (Verify Point #31)</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated college-list (Verify Point #32)</t>
   </si>
   <si>
     <t>0.46</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #12)</t>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for saved-list (Verify Point #33)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on comparison-list (Verify Point #34)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for chat-history (Verify Point #35)</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for avatar-upload (Verify Point #36)</t>
+  </si>
+  <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for theme-toggle (Verify Point #37)</t>
+  </si>
+  <si>
+    <t>0.93</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field notification-prefs (Verify Point #38)</t>
+  </si>
+  <si>
+    <t>0.49</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to session-token (Verify Point #39)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution XSS-injection (Verify Point #40)</t>
+  </si>
+  <si>
+    <t>0.44</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element SQL-injection (Verify Point #41)</t>
+  </si>
+  <si>
+    <t>0.54</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container CSRF-token (Verify Point #42)</t>
+  </si>
+  <si>
+    <t>0.84</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter CORS-origin (Verify Point #43)</t>
+  </si>
+  <si>
+    <t>0.59</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale CSP-header (Verify Point #44)</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource X-Frame-Options (Verify Point #45)</t>
+  </si>
+  <si>
+    <t>0.30</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path primary-font (Verify Point #46)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component accent-color (Verify Point #47)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for glassmorphic-transparency (Verify Point #48)</t>
+  </si>
+  <si>
+    <t>0.76</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for border-radius (Verify Point #49)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for bundle-size (Verify Point #50)</t>
+  </si>
+  <si>
+    <t>0.55</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for first-meaningful-paint (Verify Point #51)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated time-to-interactive (Verify Point #52)</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for dom-depth (Verify Point #53)</t>
+  </si>
+  <si>
+    <t>0.74</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on lost-item-card (Verify Point #54)</t>
+  </si>
+  <si>
+    <t>0.81</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for users-ref (Verify Point #55)</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for items-ref (Verify Point #56)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for de-DE (Verify Point #57)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field fr-FR (Verify Point #58)</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to ja-JP (Verify Point #59)</t>
+  </si>
+  <si>
+    <t>0.80</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution pt-BR (Verify Point #60)</t>
+  </si>
+  <si>
+    <t>0.79</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element it-IT (Verify Point #61)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container 1920x1080 (Verify Point #62)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter 1440x900 (Verify Point #63)</t>
+  </si>
+  <si>
+    <t>0.53</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale 1280x800 (Verify Point #64)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource 1024x768 (Verify Point #65)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path 768x1024 (Verify Point #66)</t>
+  </si>
+  <si>
+    <t>0.73</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component 375x812 (Verify Point #67)</t>
+  </si>
+  <si>
+    <t>0.37</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for sign-in-button (Verify Point #68)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for email-input (Verify Point #69)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for password-field (Verify Point #70)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for search-bar (Verify Point #71)</t>
+  </si>
+  <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated college-card (Verify Point #72)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for compare-btn (Verify Point #73)</t>
+  </si>
+  <si>
+    <t>0.47</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on profile-settings (Verify Point #74)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for ai-chat-input (Verify Point #75)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for en-US (Verify Point #76)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for hi-IN (Verify Point #77)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field ta-IN (Verify Point #78)</t>
+  </si>
+  <si>
+    <t>0.32</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to header-nav (Verify Point #79)</t>
+  </si>
+  <si>
+    <t>0.67</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution sidebar-menu (Verify Point #80)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element footer-links (Verify Point #81)</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container login-form (Verify Point #82)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter register-form (Verify Point #83)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale dashboard-grid (Verify Point #84)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource detail-page (Verify Point #85)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path fees-filter (Verify Point #86)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component nirf-sort (Verify Point #87)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for course-filter (Verify Point #88)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for state-filter (Verify Point #89)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for firebase-auth (Verify Point #90)</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for firestore-read (Verify Point #91)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #92)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for expo-router (Verify Point #93)</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on college-list (Verify Point #94)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for saved-list (Verify Point #95)</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for comparison-list (Verify Point #96)</t>
+  </si>
+  <si>
+    <t>0.63</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for chat-history (Verify Point #97)</t>
+  </si>
+  <si>
+    <t>0.87</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field avatar-upload (Verify Point #98)</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to theme-toggle (Verify Point #99)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution notification-prefs (Verify Point #100)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element session-token (Verify Point #101)</t>
+  </si>
+  <si>
+    <t>0.29</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container XSS-injection (Verify Point #102)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter SQL-injection (Verify Point #103)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale CSRF-token (Verify Point #104)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource CORS-origin (Verify Point #105)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path CSP-header (Verify Point #106)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component X-Frame-Options (Verify Point #107)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for primary-font (Verify Point #108)</t>
+  </si>
+  <si>
+    <t>0.96</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for accent-color (Verify Point #109)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for glassmorphic-transparency (Verify Point #110)</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for border-radius (Verify Point #111)</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated bundle-size (Verify Point #112)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for first-meaningful-paint (Verify Point #113)</t>
+  </si>
+  <si>
+    <t>0.60</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on time-to-interactive (Verify Point #114)</t>
+  </si>
+  <si>
+    <t>0.72</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for dom-depth (Verify Point #115)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for lost-item-card (Verify Point #116)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for users-ref (Verify Point #117)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field items-ref (Verify Point #118)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to de-DE (Verify Point #119)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution fr-FR (Verify Point #120)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element ja-JP (Verify Point #121)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container pt-BR (Verify Point #122)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter it-IT (Verify Point #123)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #124)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #125)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #126)</t>
   </si>
   <si>
     <t>0.92</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #13)</t>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #127)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #128)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for 375x812 (Verify Point #129)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for sign-in-button (Verify Point #130)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for email-input (Verify Point #131)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated password-field (Verify Point #132)</t>
+  </si>
+  <si>
+    <t>0.71</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for search-bar (Verify Point #133)</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on college-card (Verify Point #134)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for compare-btn (Verify Point #135)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for profile-settings (Verify Point #136)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for ai-chat-input (Verify Point #137)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field en-US (Verify Point #138)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to hi-IN (Verify Point #139)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution ta-IN (Verify Point #140)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element header-nav (Verify Point #141)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container sidebar-menu (Verify Point #142)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter footer-links (Verify Point #143)</t>
+  </si>
+  <si>
+    <t>0.48</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale login-form (Verify Point #144)</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource register-form (Verify Point #145)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path dashboard-grid (Verify Point #146)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component detail-page (Verify Point #147)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for fees-filter (Verify Point #148)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for nirf-sort (Verify Point #149)</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for course-filter (Verify Point #150)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for state-filter (Verify Point #151)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated firebase-auth (Verify Point #152)</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for firestore-read (Verify Point #153)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on groq-api (Verify Point #154)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for expo-router (Verify Point #155)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for college-list (Verify Point #156)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for saved-list (Verify Point #157)</t>
+  </si>
+  <si>
+    <t>0.45</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field comparison-list (Verify Point #158)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to chat-history (Verify Point #159)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution avatar-upload (Verify Point #160)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element theme-toggle (Verify Point #161)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container notification-prefs (Verify Point #162)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter session-token (Verify Point #163)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale XSS-injection (Verify Point #164)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #165)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path CSRF-token (Verify Point #166)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component CORS-origin (Verify Point #167)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for CSP-header (Verify Point #168)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for X-Frame-Options (Verify Point #169)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for primary-font (Verify Point #170)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for accent-color (Verify Point #171)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated glassmorphic-transparency (Verify Point #172)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for border-radius (Verify Point #173)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on bundle-size (Verify Point #174)</t>
+  </si>
+  <si>
+    <t>0.86</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for first-meaningful-paint (Verify Point #175)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for time-to-interactive (Verify Point #176)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for dom-depth (Verify Point #177)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field lost-item-card (Verify Point #178)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to users-ref (Verify Point #179)</t>
+  </si>
+  <si>
+    <t>0.31</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution items-ref (Verify Point #180)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element de-DE (Verify Point #181)</t>
+  </si>
+  <si>
+    <t>0.77</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container fr-FR (Verify Point #182)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter ja-JP (Verify Point #183)</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale pt-BR (Verify Point #184)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource it-IT (Verify Point #185)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path 1920x1080 (Verify Point #186)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component 1440x900 (Verify Point #187)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for 1280x800 (Verify Point #188)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for 1024x768 (Verify Point #189)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for 768x1024 (Verify Point #190)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for 375x812 (Verify Point #191)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated sign-in-button (Verify Point #192)</t>
+  </si>
+  <si>
+    <t>0.83</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for email-input (Verify Point #193)</t>
+  </si>
+  <si>
+    <t>0.89</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on password-field (Verify Point #194)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for search-bar (Verify Point #195)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for college-card (Verify Point #196)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for compare-btn (Verify Point #197)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field profile-settings (Verify Point #198)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to ai-chat-input (Verify Point #199)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution en-US (Verify Point #200)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element hi-IN (Verify Point #201)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container ta-IN (Verify Point #202)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter header-nav (Verify Point #203)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale sidebar-menu (Verify Point #204)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource footer-links (Verify Point #205)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path login-form (Verify Point #206)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component register-form (Verify Point #207)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for dashboard-grid (Verify Point #208)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for detail-page (Verify Point #209)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for fees-filter (Verify Point #210)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for nirf-sort (Verify Point #211)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated course-filter (Verify Point #212)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for state-filter (Verify Point #213)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on firebase-auth (Verify Point #214)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for firestore-read (Verify Point #215)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for groq-api (Verify Point #216)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for expo-router (Verify Point #217)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field college-list (Verify Point #218)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to saved-list (Verify Point #219)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution comparison-list (Verify Point #220)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element chat-history (Verify Point #221)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container avatar-upload (Verify Point #222)</t>
+  </si>
+  <si>
+    <t>0.70</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter theme-toggle (Verify Point #223)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale notification-prefs (Verify Point #224)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource session-token (Verify Point #225)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path XSS-injection (Verify Point #226)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component SQL-injection (Verify Point #227)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for CSRF-token (Verify Point #228)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for CORS-origin (Verify Point #229)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for CSP-header (Verify Point #230)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for X-Frame-Options (Verify Point #231)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated primary-font (Verify Point #232)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for accent-color (Verify Point #233)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on glassmorphic-transparency (Verify Point #234)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for border-radius (Verify Point #235)</t>
+  </si>
+  <si>
+    <t>0.52</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for bundle-size (Verify Point #236)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for first-meaningful-paint (Verify Point #237)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field time-to-interactive (Verify Point #238)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to dom-depth (Verify Point #239)</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution lost-item-card (Verify Point #240)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element users-ref (Verify Point #241)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container items-ref (Verify Point #242)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter de-DE (Verify Point #243)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale fr-FR (Verify Point #244)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource ja-JP (Verify Point #245)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path pt-BR (Verify Point #246)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component it-IT (Verify Point #247)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #248)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #249)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #250)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #251)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #252)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for 375x812 (Verify Point #253)</t>
+  </si>
+  <si>
+    <t>0.61</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on sign-in-button (Verify Point #254)</t>
+  </si>
+  <si>
+    <t>0.66</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for email-input (Verify Point #255)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for password-field (Verify Point #256)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for search-bar (Verify Point #257)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field college-card (Verify Point #258)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to compare-btn (Verify Point #259)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution profile-settings (Verify Point #260)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element ai-chat-input (Verify Point #261)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container en-US (Verify Point #262)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter hi-IN (Verify Point #263)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale ta-IN (Verify Point #264)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource header-nav (Verify Point #265)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path sidebar-menu (Verify Point #266)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component footer-links (Verify Point #267)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for login-form (Verify Point #268)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for register-form (Verify Point #269)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for dashboard-grid (Verify Point #270)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for detail-page (Verify Point #271)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated fees-filter (Verify Point #272)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for nirf-sort (Verify Point #273)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on course-filter (Verify Point #274)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for state-filter (Verify Point #275)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for firebase-auth (Verify Point #276)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for firestore-read (Verify Point #277)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field groq-api (Verify Point #278)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to expo-router (Verify Point #279)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution college-list (Verify Point #280)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element saved-list (Verify Point #281)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container comparison-list (Verify Point #282)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter chat-history (Verify Point #283)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale avatar-upload (Verify Point #284)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource theme-toggle (Verify Point #285)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path notification-prefs (Verify Point #286)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component session-token (Verify Point #287)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for XSS-injection (Verify Point #288)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for SQL-injection (Verify Point #289)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for CSRF-token (Verify Point #290)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for CORS-origin (Verify Point #291)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated CSP-header (Verify Point #292)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for X-Frame-Options (Verify Point #293)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on primary-font (Verify Point #294)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for accent-color (Verify Point #295)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for glassmorphic-transparency (Verify Point #296)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for border-radius (Verify Point #297)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field bundle-size (Verify Point #298)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to first-meaningful-paint (Verify Point #299)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution time-to-interactive (Verify Point #300)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element dom-depth (Verify Point #301)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container lost-item-card (Verify Point #302)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter users-ref (Verify Point #303)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale items-ref (Verify Point #304)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource de-DE (Verify Point #305)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path fr-FR (Verify Point #306)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component ja-JP (Verify Point #307)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for pt-BR (Verify Point #308)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for it-IT (Verify Point #309)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for 1920x1080 (Verify Point #310)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for 1440x900 (Verify Point #311)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated 1280x800 (Verify Point #312)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for 1024x768 (Verify Point #313)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on 768x1024 (Verify Point #314)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for 375x812 (Verify Point #315)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for sign-in-button (Verify Point #316)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for email-input (Verify Point #317)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field password-field (Verify Point #318)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to search-bar (Verify Point #319)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution college-card (Verify Point #320)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element compare-btn (Verify Point #321)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container profile-settings (Verify Point #322)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter ai-chat-input (Verify Point #323)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale en-US (Verify Point #324)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource hi-IN (Verify Point #325)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path ta-IN (Verify Point #326)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component header-nav (Verify Point #327)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for sidebar-menu (Verify Point #328)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for footer-links (Verify Point #329)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for login-form (Verify Point #330)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for register-form (Verify Point #331)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated dashboard-grid (Verify Point #332)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for detail-page (Verify Point #333)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on fees-filter (Verify Point #334)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for nirf-sort (Verify Point #335)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for course-filter (Verify Point #336)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for state-filter (Verify Point #337)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field firebase-auth (Verify Point #338)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to firestore-read (Verify Point #339)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution groq-api (Verify Point #340)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element expo-router (Verify Point #341)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container college-list (Verify Point #342)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter saved-list (Verify Point #343)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale comparison-list (Verify Point #344)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource chat-history (Verify Point #345)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path avatar-upload (Verify Point #346)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component theme-toggle (Verify Point #347)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for notification-prefs (Verify Point #348)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for session-token (Verify Point #349)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for XSS-injection (Verify Point #350)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for SQL-injection (Verify Point #351)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated CSRF-token (Verify Point #352)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for CORS-origin (Verify Point #353)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on CSP-header (Verify Point #354)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for X-Frame-Options (Verify Point #355)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for primary-font (Verify Point #356)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for accent-color (Verify Point #357)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field glassmorphic-transparency (Verify Point #358)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to border-radius (Verify Point #359)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution bundle-size (Verify Point #360)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element first-meaningful-paint (Verify Point #361)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container time-to-interactive (Verify Point #362)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter dom-depth (Verify Point #363)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale lost-item-card (Verify Point #364)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource users-ref (Verify Point #365)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path items-ref (Verify Point #366)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component de-DE (Verify Point #367)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for fr-FR (Verify Point #368)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for ja-JP (Verify Point #369)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for pt-BR (Verify Point #370)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for it-IT (Verify Point #371)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #372)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #373)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #374)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #375)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #376)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for 375x812 (Verify Point #377)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field sign-in-button (Verify Point #378)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to email-input (Verify Point #379)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution password-field (Verify Point #380)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element search-bar (Verify Point #381)</t>
   </si>
   <si>
     <t>0.35</t>
   </si>
   <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #14)</t>
-  </si>
-  <si>
-    <t>0.29</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #15)</t>
-  </si>
-  <si>
-    <t>0.81</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #16)</t>
-  </si>
-  <si>
-    <t>0.39</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #17)</t>
-  </si>
-  <si>
-    <t>0.49</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #18)</t>
-  </si>
-  <si>
-    <t>0.83</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #19)</t>
-  </si>
-  <si>
-    <t>0.70</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #20)</t>
-  </si>
-  <si>
-    <t>0.33</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #21)</t>
-  </si>
-  <si>
-    <t>0.89</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #22)</t>
-  </si>
-  <si>
-    <t>0.31</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #23)</t>
-  </si>
-  <si>
-    <t>0.78</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #24)</t>
-  </si>
-  <si>
-    <t>0.61</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #25)</t>
-  </si>
-  <si>
-    <t>0.75</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #26)</t>
-  </si>
-  <si>
-    <t>0.91</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #27)</t>
-  </si>
-  <si>
-    <t>0.47</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #28)</t>
-  </si>
-  <si>
-    <t>0.21</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #29)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #30)</t>
-  </si>
-  <si>
-    <t>0.27</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #31)</t>
-  </si>
-  <si>
-    <t>0.62</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #32)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #33)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #34)</t>
-  </si>
-  <si>
-    <t>0.67</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #35)</t>
-  </si>
-  <si>
-    <t>0.82</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #36)</t>
-  </si>
-  <si>
-    <t>0.54</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #37)</t>
-  </si>
-  <si>
-    <t>0.41</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #38)</t>
-  </si>
-  <si>
-    <t>0.60</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #39)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #40)</t>
-  </si>
-  <si>
-    <t>0.57</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #41)</t>
-  </si>
-  <si>
-    <t>0.65</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #42)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #43)</t>
-  </si>
-  <si>
-    <t>0.45</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #44)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #45)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #46)</t>
-  </si>
-  <si>
-    <t>0.23</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #47)</t>
-  </si>
-  <si>
-    <t>0.32</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #48)</t>
-  </si>
-  <si>
-    <t>0.84</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #49)</t>
-  </si>
-  <si>
-    <t>0.58</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #50)</t>
-  </si>
-  <si>
-    <t>0.86</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #51)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #52)</t>
-  </si>
-  <si>
-    <t>0.69</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #53)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #54)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #55)</t>
-  </si>
-  <si>
-    <t>0.34</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #56)</t>
-  </si>
-  <si>
-    <t>0.80</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #57)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #58)</t>
-  </si>
-  <si>
-    <t>0.76</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #59)</t>
-  </si>
-  <si>
-    <t>0.73</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #60)</t>
-  </si>
-  <si>
-    <t>0.64</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #61)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #62)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #63)</t>
-  </si>
-  <si>
-    <t>0.52</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #64)</t>
-  </si>
-  <si>
-    <t>0.40</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #65)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #66)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #67)</t>
-  </si>
-  <si>
-    <t>0.38</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #68)</t>
-  </si>
-  <si>
-    <t>0.77</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #69)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #70)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #71)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #72)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #73)</t>
-  </si>
-  <si>
-    <t>0.85</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #74)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #75)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #76)</t>
-  </si>
-  <si>
-    <t>0.55</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #77)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #78)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #79)</t>
-  </si>
-  <si>
-    <t>0.98</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #80)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #81)</t>
-  </si>
-  <si>
-    <t>0.28</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #82)</t>
-  </si>
-  <si>
-    <t>0.63</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #83)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #84)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #85)</t>
-  </si>
-  <si>
-    <t>0.24</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #86)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #87)</t>
-  </si>
-  <si>
-    <t>0.37</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #88)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #89)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #90)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #91)</t>
-  </si>
-  <si>
-    <t>0.71</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #92)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #93)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #94)</t>
-  </si>
-  <si>
-    <t>0.36</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #95)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #96)</t>
-  </si>
-  <si>
-    <t>0.96</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #97)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #98)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #99)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #100)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #101)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #102)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #103)</t>
-  </si>
-  <si>
-    <t>0.97</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #104)</t>
-  </si>
-  <si>
-    <t>0.43</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #105)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #106)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #107)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #108)</t>
-  </si>
-  <si>
-    <t>0.74</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #109)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #110)</t>
-  </si>
-  <si>
-    <t>0.94</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #111)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #112)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #113)</t>
-  </si>
-  <si>
-    <t>1.00</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #114)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #115)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #116)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #117)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #118)</t>
-  </si>
-  <si>
-    <t>0.88</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #119)</t>
-  </si>
-  <si>
-    <t>0.26</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #120)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #121)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #122)</t>
-  </si>
-  <si>
-    <t>0.56</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #123)</t>
-  </si>
-  <si>
-    <t>0.25</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #124)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #125)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #126)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #127)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #128)</t>
-  </si>
-  <si>
-    <t>0.90</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #129)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #130)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #131)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #132)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #133)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #134)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #135)</t>
-  </si>
-  <si>
-    <t>0.93</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #136)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #137)</t>
-  </si>
-  <si>
-    <t>0.42</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #138)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #139)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #140)</t>
-  </si>
-  <si>
-    <t>0.44</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #141)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #142)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #143)</t>
-  </si>
-  <si>
-    <t>0.50</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #144)</t>
-  </si>
-  <si>
-    <t>0.53</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #145)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #146)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #147)</t>
-  </si>
-  <si>
-    <t>0.95</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #148)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #149)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #150)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #151)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #152)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #153)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #154)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #155)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #156)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #157)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #158)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #159)</t>
-  </si>
-  <si>
-    <t>0.79</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #160)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #161)</t>
-  </si>
-  <si>
-    <t>0.51</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #162)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #163)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #164)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #165)</t>
-  </si>
-  <si>
-    <t>0.48</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #166)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #167)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #168)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #169)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #170)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #171)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #172)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #173)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #174)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #175)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #176)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #177)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #178)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #179)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #180)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #181)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #182)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #183)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #184)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #185)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #186)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #187)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #188)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #189)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #190)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #191)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #192)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #193)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #194)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #195)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #196)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #197)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #198)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #199)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #200)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #201)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #202)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #203)</t>
-  </si>
-  <si>
-    <t>0.99</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #204)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #205)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #206)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #207)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #208)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #209)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #210)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #211)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #212)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #213)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #214)</t>
-  </si>
-  <si>
-    <t>0.22</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #215)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #216)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #217)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #218)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #219)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #220)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #221)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #222)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #223)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #224)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #225)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #226)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #227)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #228)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #229)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #230)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #231)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #232)</t>
-  </si>
-  <si>
-    <t>0.20</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #233)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #234)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #235)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #236)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #237)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #238)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #239)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #240)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #241)</t>
-  </si>
-  <si>
-    <t>0.72</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #242)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #243)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #244)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #245)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #246)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #247)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #248)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #249)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #250)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #251)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #252)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #253)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #254)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #255)</t>
-  </si>
-  <si>
-    <t>0.59</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #256)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #257)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #258)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #259)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #260)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #261)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #262)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #263)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #264)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #265)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #266)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #267)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #268)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #269)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #270)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #271)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #272)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #273)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #274)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #275)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #276)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #277)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #278)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #279)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #280)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #281)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #282)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #283)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #284)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #285)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #286)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #287)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #288)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #289)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #290)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #291)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #292)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #293)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #294)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #295)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #296)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #297)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #298)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #299)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #300)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #301)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #302)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #303)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #304)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #305)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #306)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #307)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #308)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #309)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #310)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #311)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #312)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #313)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #314)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #315)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #316)</t>
-  </si>
-  <si>
-    <t>0.66</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #317)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #318)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #319)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 1920x1080 (Verify Point #320)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element 1440x900 (Verify Point #321)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container 1280x800 (Verify Point #322)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter 1024x768 (Verify Point #323)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 768x1024 (Verify Point #324)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource sign-in-button (Verify Point #325)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #326)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component password-field (Verify Point #327)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for search-bar (Verify Point #328)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for college-card (Verify Point #329)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for compare-btn (Verify Point #330)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for profile-settings (Verify Point #331)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated ai-chat-input (Verify Point #332)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for en-US (Verify Point #333)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on header-nav (Verify Point #334)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for sidebar-menu (Verify Point #335)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 1920x1080 (Verify Point #336)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for 1440x900 (Verify Point #337)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field 1280x800 (Verify Point #338)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step 1024x768 (Verify Point #339)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #340)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element sign-in-button (Verify Point #341)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container email-input (Verify Point #342)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter password-field (Verify Point #343)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale search-bar (Verify Point #344)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource college-card (Verify Point #345)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path compare-btn (Verify Point #346)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #347)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for ai-chat-input (Verify Point #348)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for en-US (Verify Point #349)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for header-nav (Verify Point #350)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for sidebar-menu (Verify Point #351)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 1920x1080 (Verify Point #352)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for 1440x900 (Verify Point #353)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on 1280x800 (Verify Point #354)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for 1024x768 (Verify Point #355)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for 768x1024 (Verify Point #356)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for sign-in-button (Verify Point #357)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field email-input (Verify Point #358)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step password-field (Verify Point #359)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution search-bar (Verify Point #360)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element college-card (Verify Point #361)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container compare-btn (Verify Point #362)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #363)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale ai-chat-input (Verify Point #364)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #365)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #366)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #367)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #368)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #369)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #370)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #371)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #372)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for sign-in-button (Verify Point #373)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on email-input (Verify Point #374)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for password-field (Verify Point #375)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for search-bar (Verify Point #376)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for college-card (Verify Point #377)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field compare-btn (Verify Point #378)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step profile-settings (Verify Point #379)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [UI]: Verify page responsiveness for resolution ai-chat-input (Verify Point #380)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #381)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [DOM]: Verify DOM integrity for container header-nav (Verify Point #382)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Validation]: Verify form field validation with parameter sidebar-menu (Verify Point #383)</t>
-  </si>
-  <si>
-    <t>0.30</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #384)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #385)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #386)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #387)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #388)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Dashboard]: Verify college card rendering for sign-in-button (Verify Point #389)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Details]: Verify college detail page fields for email-input (Verify Point #390)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Search]: Verify search results filtering for password-field (Verify Point #391)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Auth Guard]: Verify route protection for unauthenticated search-bar (Verify Point #392)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Session]: Verify session cookie flags for college-card (Verify Point #393)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [XSS]: Verify XSS payload encoding on compare-btn (Verify Point #394)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [AI Chat]: Verify AI chat response rendering for profile-settings (Verify Point #395)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Comparison]: Verify college comparison table for ai-chat-input (Verify Point #396)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Saved Items]: Verify saved colleges list persistence for en-US (Verify Point #397)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Profile]: Verify user profile update for field header-nav (Verify Point #398)</t>
-  </si>
-  <si>
-    <t>Smart Admission Web — E2E [Onboarding]: Verify onboarding flow step sidebar-menu (Verify Point #399)</t>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container college-card (Verify Point #382)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter compare-btn (Verify Point #383)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale profile-settings (Verify Point #384)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource ai-chat-input (Verify Point #385)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path en-US (Verify Point #386)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component hi-IN (Verify Point #387)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for ta-IN (Verify Point #388)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for header-nav (Verify Point #389)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for sidebar-menu (Verify Point #390)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for footer-links (Verify Point #391)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated login-form (Verify Point #392)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for register-form (Verify Point #393)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on dashboard-grid (Verify Point #394)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for detail-page (Verify Point #395)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for fees-filter (Verify Point #396)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for nirf-sort (Verify Point #397)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field course-filter (Verify Point #398)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to state-filter (Verify Point #399)</t>
   </si>
   <si>
     <t>Field</t>
@@ -1553,13 +1556,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>17</t>
+    <t>18</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 14:08:10 UTC</t>
+    <t>2026-06-23 14:30:52 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1571,7 +1574,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>d1d53d0</t>
+    <t>04fd2d2</t>
   </si>
   <si>
     <t>Total</t>
@@ -2439,7 +2442,7 @@
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E27" t="s">
         <v>27</v>
@@ -2450,13 +2453,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" t="s">
         <v>69</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" t="s">
-        <v>70</v>
       </c>
       <c r="E28" t="s">
         <v>27</v>
@@ -2467,13 +2470,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" t="s">
         <v>71</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29" t="s">
-        <v>72</v>
       </c>
       <c r="E29" t="s">
         <v>27</v>
@@ -2484,13 +2487,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" t="s">
         <v>73</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D30" t="s">
-        <v>74</v>
       </c>
       <c r="E30" t="s">
         <v>27</v>
@@ -2501,13 +2504,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" t="s">
         <v>75</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D31" t="s">
-        <v>38</v>
       </c>
       <c r="E31" t="s">
         <v>27</v>
@@ -2558,7 +2561,7 @@
         <v>25</v>
       </c>
       <c r="D34" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="E34" t="s">
         <v>27</v>
@@ -2569,13 +2572,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="E35" t="s">
         <v>27</v>
@@ -2586,13 +2589,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="E36" t="s">
         <v>27</v>
@@ -2677,7 +2680,7 @@
         <v>25</v>
       </c>
       <c r="D41" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="E41" t="s">
         <v>27</v>
@@ -2728,7 +2731,7 @@
         <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="E44" t="s">
         <v>27</v>
@@ -2739,13 +2742,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E45" t="s">
         <v>27</v>
@@ -2756,13 +2759,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="E46" t="s">
         <v>27</v>
@@ -2773,13 +2776,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E47" t="s">
         <v>27</v>
@@ -2790,13 +2793,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E48" t="s">
         <v>27</v>
@@ -2807,13 +2810,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="E49" t="s">
         <v>27</v>
@@ -2824,13 +2827,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E50" t="s">
         <v>27</v>
@@ -2841,13 +2844,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D51" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="E51" t="s">
         <v>27</v>
@@ -2881,7 +2884,7 @@
         <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E53" t="s">
         <v>27</v>
@@ -2915,7 +2918,7 @@
         <v>25</v>
       </c>
       <c r="D55" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="E55" t="s">
         <v>27</v>
@@ -2926,13 +2929,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D56" t="s">
-        <v>46</v>
+        <v>118</v>
       </c>
       <c r="E56" t="s">
         <v>27</v>
@@ -2943,13 +2946,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D57" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E57" t="s">
         <v>27</v>
@@ -2960,13 +2963,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D58" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E58" t="s">
         <v>27</v>
@@ -2977,13 +2980,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D59" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E59" t="s">
         <v>27</v>
@@ -2994,13 +2997,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D60" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E60" t="s">
         <v>27</v>
@@ -3011,13 +3014,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E61" t="s">
         <v>27</v>
@@ -3028,13 +3031,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D62" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E62" t="s">
         <v>27</v>
@@ -3045,13 +3048,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D63" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="E63" t="s">
         <v>27</v>
@@ -3062,13 +3065,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D64" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="E64" t="s">
         <v>27</v>
@@ -3079,13 +3082,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E65" t="s">
         <v>27</v>
@@ -3096,13 +3099,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D66" t="s">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="E66" t="s">
         <v>27</v>
@@ -3119,7 +3122,7 @@
         <v>25</v>
       </c>
       <c r="D67" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E67" t="s">
         <v>27</v>
@@ -3136,7 +3139,7 @@
         <v>25</v>
       </c>
       <c r="D68" t="s">
-        <v>52</v>
+        <v>136</v>
       </c>
       <c r="E68" t="s">
         <v>27</v>
@@ -3147,13 +3150,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D69" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E69" t="s">
         <v>27</v>
@@ -3164,13 +3167,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D70" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="E70" t="s">
         <v>27</v>
@@ -3187,7 +3190,7 @@
         <v>25</v>
       </c>
       <c r="D71" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="E71" t="s">
         <v>27</v>
@@ -3204,7 +3207,7 @@
         <v>25</v>
       </c>
       <c r="D72" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E72" t="s">
         <v>27</v>
@@ -3221,7 +3224,7 @@
         <v>25</v>
       </c>
       <c r="D73" t="s">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="E73" t="s">
         <v>27</v>
@@ -3232,13 +3235,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D74" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="E74" t="s">
         <v>27</v>
@@ -3249,13 +3252,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D75" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E75" t="s">
         <v>27</v>
@@ -3266,13 +3269,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D76" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="E76" t="s">
         <v>27</v>
@@ -3283,13 +3286,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D77" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="E77" t="s">
         <v>27</v>
@@ -3300,13 +3303,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="E78" t="s">
         <v>27</v>
@@ -3323,7 +3326,7 @@
         <v>25</v>
       </c>
       <c r="D79" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E79" t="s">
         <v>27</v>
@@ -3340,7 +3343,7 @@
         <v>25</v>
       </c>
       <c r="D80" t="s">
-        <v>99</v>
+        <v>152</v>
       </c>
       <c r="E80" t="s">
         <v>27</v>
@@ -3351,13 +3354,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D81" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E81" t="s">
         <v>27</v>
@@ -3368,13 +3371,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D82" t="s">
-        <v>62</v>
+        <v>126</v>
       </c>
       <c r="E82" t="s">
         <v>27</v>
@@ -3385,13 +3388,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D83" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E83" t="s">
         <v>27</v>
@@ -3402,13 +3405,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
+        <v>158</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D84" t="s">
         <v>157</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D84" t="s">
-        <v>158</v>
       </c>
       <c r="E84" t="s">
         <v>27</v>
@@ -3425,7 +3428,7 @@
         <v>25</v>
       </c>
       <c r="D85" t="s">
-        <v>158</v>
+        <v>52</v>
       </c>
       <c r="E85" t="s">
         <v>27</v>
@@ -3442,7 +3445,7 @@
         <v>25</v>
       </c>
       <c r="D86" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="E86" t="s">
         <v>27</v>
@@ -3459,7 +3462,7 @@
         <v>25</v>
       </c>
       <c r="D87" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="E87" t="s">
         <v>27</v>
@@ -3470,13 +3473,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D88" t="s">
-        <v>125</v>
+        <v>54</v>
       </c>
       <c r="E88" t="s">
         <v>27</v>
@@ -3487,13 +3490,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D89" t="s">
-        <v>165</v>
+        <v>108</v>
       </c>
       <c r="E89" t="s">
         <v>27</v>
@@ -3504,13 +3507,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D90" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="E90" t="s">
         <v>27</v>
@@ -3521,13 +3524,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D91" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E91" t="s">
         <v>27</v>
@@ -3538,13 +3541,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D92" t="s">
-        <v>60</v>
+        <v>167</v>
       </c>
       <c r="E92" t="s">
         <v>27</v>
@@ -3555,13 +3558,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D93" t="s">
-        <v>170</v>
+        <v>71</v>
       </c>
       <c r="E93" t="s">
         <v>27</v>
@@ -3572,13 +3575,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D94" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="E94" t="s">
         <v>27</v>
@@ -3589,13 +3592,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D95" t="s">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="E95" t="s">
         <v>27</v>
@@ -3606,13 +3609,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D96" t="s">
-        <v>174</v>
+        <v>62</v>
       </c>
       <c r="E96" t="s">
         <v>27</v>
@@ -3623,13 +3626,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D97" t="s">
-        <v>56</v>
+        <v>174</v>
       </c>
       <c r="E97" t="s">
         <v>27</v>
@@ -3640,13 +3643,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
+        <v>175</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D98" t="s">
         <v>176</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D98" t="s">
-        <v>177</v>
       </c>
       <c r="E98" t="s">
         <v>27</v>
@@ -3657,13 +3660,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
+        <v>177</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D99" t="s">
         <v>178</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D99" t="s">
-        <v>114</v>
       </c>
       <c r="E99" t="s">
         <v>27</v>
@@ -3680,7 +3683,7 @@
         <v>25</v>
       </c>
       <c r="D100" t="s">
-        <v>66</v>
+        <v>180</v>
       </c>
       <c r="E100" t="s">
         <v>27</v>
@@ -3691,13 +3694,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>96</v>
+        <v>171</v>
       </c>
       <c r="E101" t="s">
         <v>27</v>
@@ -3708,13 +3711,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D102" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="E102" t="s">
         <v>27</v>
@@ -3725,13 +3728,13 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D103" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="E103" t="s">
         <v>27</v>
@@ -3742,13 +3745,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D104" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="E104" t="s">
         <v>27</v>
@@ -3759,13 +3762,13 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
+        <v>186</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D105" t="s">
         <v>184</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D105" t="s">
-        <v>185</v>
       </c>
       <c r="E105" t="s">
         <v>27</v>
@@ -3776,13 +3779,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D106" t="s">
-        <v>187</v>
+        <v>124</v>
       </c>
       <c r="E106" t="s">
         <v>27</v>
@@ -3799,7 +3802,7 @@
         <v>25</v>
       </c>
       <c r="D107" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E107" t="s">
         <v>27</v>
@@ -3816,7 +3819,7 @@
         <v>25</v>
       </c>
       <c r="D108" t="s">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c r="E108" t="s">
         <v>27</v>
@@ -3833,7 +3836,7 @@
         <v>25</v>
       </c>
       <c r="D109" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="E109" t="s">
         <v>27</v>
@@ -3867,7 +3870,7 @@
         <v>25</v>
       </c>
       <c r="D111" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="E111" t="s">
         <v>27</v>
@@ -3901,7 +3904,7 @@
         <v>25</v>
       </c>
       <c r="D113" t="s">
-        <v>107</v>
+        <v>197</v>
       </c>
       <c r="E113" t="s">
         <v>27</v>
@@ -3912,13 +3915,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D114" t="s">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="E114" t="s">
         <v>27</v>
@@ -3929,13 +3932,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D115" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E115" t="s">
         <v>27</v>
@@ -3946,13 +3949,13 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D116" t="s">
-        <v>56</v>
+        <v>202</v>
       </c>
       <c r="E116" t="s">
         <v>27</v>
@@ -3963,13 +3966,13 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D117" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="E117" t="s">
         <v>27</v>
@@ -3980,13 +3983,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D118" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E118" t="s">
         <v>27</v>
@@ -3997,13 +4000,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D119" t="s">
-        <v>50</v>
+        <v>146</v>
       </c>
       <c r="E119" t="s">
         <v>27</v>
@@ -4014,13 +4017,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D120" t="s">
-        <v>205</v>
+        <v>40</v>
       </c>
       <c r="E120" t="s">
         <v>27</v>
@@ -4031,13 +4034,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D121" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="E121" t="s">
         <v>27</v>
@@ -4054,7 +4057,7 @@
         <v>25</v>
       </c>
       <c r="D122" t="s">
-        <v>174</v>
+        <v>64</v>
       </c>
       <c r="E122" t="s">
         <v>27</v>
@@ -4071,7 +4074,7 @@
         <v>25</v>
       </c>
       <c r="D123" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="E123" t="s">
         <v>27</v>
@@ -4088,7 +4091,7 @@
         <v>25</v>
       </c>
       <c r="D124" t="s">
-        <v>211</v>
+        <v>58</v>
       </c>
       <c r="E124" t="s">
         <v>27</v>
@@ -4099,13 +4102,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D125" t="s">
-        <v>213</v>
+        <v>50</v>
       </c>
       <c r="E125" t="s">
         <v>27</v>
@@ -4116,13 +4119,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D126" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="E126" t="s">
         <v>27</v>
@@ -4133,13 +4136,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D127" t="s">
-        <v>50</v>
+        <v>171</v>
       </c>
       <c r="E127" t="s">
         <v>27</v>
@@ -4150,13 +4153,13 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D128" t="s">
-        <v>96</v>
+        <v>215</v>
       </c>
       <c r="E128" t="s">
         <v>27</v>
@@ -4167,13 +4170,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D129" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E129" t="s">
         <v>27</v>
@@ -4184,13 +4187,13 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D130" t="s">
-        <v>219</v>
+        <v>118</v>
       </c>
       <c r="E130" t="s">
         <v>27</v>
@@ -4201,13 +4204,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D131" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="E131" t="s">
         <v>27</v>
@@ -4218,13 +4221,13 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D132" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="E132" t="s">
         <v>27</v>
@@ -4235,13 +4238,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D133" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E133" t="s">
         <v>27</v>
@@ -4252,13 +4255,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D134" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="E134" t="s">
         <v>27</v>
@@ -4269,13 +4272,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
+        <v>223</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D135" t="s">
         <v>224</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D135" t="s">
-        <v>38</v>
       </c>
       <c r="E135" t="s">
         <v>27</v>
@@ -4292,7 +4295,7 @@
         <v>25</v>
       </c>
       <c r="D136" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E136" t="s">
         <v>27</v>
@@ -4309,7 +4312,7 @@
         <v>25</v>
       </c>
       <c r="D137" t="s">
-        <v>227</v>
+        <v>118</v>
       </c>
       <c r="E137" t="s">
         <v>27</v>
@@ -4320,13 +4323,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D138" t="s">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="E138" t="s">
         <v>27</v>
@@ -4337,13 +4340,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D139" t="s">
-        <v>230</v>
+        <v>62</v>
       </c>
       <c r="E139" t="s">
         <v>27</v>
@@ -4354,13 +4357,13 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D140" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="E140" t="s">
         <v>27</v>
@@ -4371,13 +4374,13 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D141" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="E141" t="s">
         <v>27</v>
@@ -4388,13 +4391,13 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D142" t="s">
-        <v>234</v>
+        <v>157</v>
       </c>
       <c r="E142" t="s">
         <v>27</v>
@@ -4405,13 +4408,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D143" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="E143" t="s">
         <v>27</v>
@@ -4422,13 +4425,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D144" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E144" t="s">
         <v>27</v>
@@ -4439,13 +4442,13 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D145" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E145" t="s">
         <v>27</v>
@@ -4456,13 +4459,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D146" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E146" t="s">
         <v>27</v>
@@ -4473,13 +4476,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D147" t="s">
-        <v>96</v>
+        <v>167</v>
       </c>
       <c r="E147" t="s">
         <v>27</v>
@@ -4490,13 +4493,13 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D148" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E148" t="s">
         <v>27</v>
@@ -4507,13 +4510,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D149" t="s">
-        <v>244</v>
+        <v>69</v>
       </c>
       <c r="E149" t="s">
         <v>27</v>
@@ -4524,13 +4527,13 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D150" t="s">
-        <v>211</v>
+        <v>69</v>
       </c>
       <c r="E150" t="s">
         <v>27</v>
@@ -4541,13 +4544,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D151" t="s">
-        <v>145</v>
+        <v>243</v>
       </c>
       <c r="E151" t="s">
         <v>27</v>
@@ -4558,13 +4561,13 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D152" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="E152" t="s">
         <v>27</v>
@@ -4575,13 +4578,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D153" t="s">
-        <v>211</v>
+        <v>81</v>
       </c>
       <c r="E153" t="s">
         <v>27</v>
@@ -4592,13 +4595,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D154" t="s">
-        <v>192</v>
+        <v>247</v>
       </c>
       <c r="E154" t="s">
         <v>27</v>
@@ -4609,13 +4612,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D155" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="E155" t="s">
         <v>27</v>
@@ -4626,13 +4629,13 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D156" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E156" t="s">
         <v>27</v>
@@ -4643,13 +4646,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D157" t="s">
-        <v>244</v>
+        <v>126</v>
       </c>
       <c r="E157" t="s">
         <v>27</v>
@@ -4660,13 +4663,13 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D158" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="E158" t="s">
         <v>27</v>
@@ -4677,13 +4680,13 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D159" t="s">
-        <v>48</v>
+        <v>253</v>
       </c>
       <c r="E159" t="s">
         <v>27</v>
@@ -4694,13 +4697,13 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D160" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="E160" t="s">
         <v>27</v>
@@ -4711,13 +4714,13 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D161" t="s">
-        <v>257</v>
+        <v>56</v>
       </c>
       <c r="E161" t="s">
         <v>27</v>
@@ -4728,13 +4731,13 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D162" t="s">
-        <v>156</v>
+        <v>44</v>
       </c>
       <c r="E162" t="s">
         <v>27</v>
@@ -4745,13 +4748,13 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D163" t="s">
-        <v>260</v>
+        <v>171</v>
       </c>
       <c r="E163" t="s">
         <v>27</v>
@@ -4762,13 +4765,13 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D164" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="E164" t="s">
         <v>27</v>
@@ -4779,13 +4782,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D165" t="s">
-        <v>87</v>
+        <v>174</v>
       </c>
       <c r="E165" t="s">
         <v>27</v>
@@ -4796,13 +4799,13 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D166" t="s">
-        <v>56</v>
+        <v>176</v>
       </c>
       <c r="E166" t="s">
         <v>27</v>
@@ -4813,13 +4816,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D167" t="s">
-        <v>265</v>
+        <v>111</v>
       </c>
       <c r="E167" t="s">
         <v>27</v>
@@ -4830,13 +4833,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D168" t="s">
-        <v>260</v>
+        <v>157</v>
       </c>
       <c r="E168" t="s">
         <v>27</v>
@@ -4847,13 +4850,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D169" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E169" t="s">
         <v>27</v>
@@ -4864,13 +4867,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D170" t="s">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="E170" t="s">
         <v>27</v>
@@ -4881,13 +4884,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D171" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="E171" t="s">
         <v>27</v>
@@ -4898,13 +4901,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D172" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="E172" t="s">
         <v>27</v>
@@ -4915,13 +4918,13 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D173" t="s">
-        <v>219</v>
+        <v>143</v>
       </c>
       <c r="E173" t="s">
         <v>27</v>
@@ -4932,13 +4935,13 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D174" t="s">
-        <v>99</v>
+        <v>224</v>
       </c>
       <c r="E174" t="s">
         <v>27</v>
@@ -4949,13 +4952,13 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D175" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="E175" t="s">
         <v>27</v>
@@ -4966,13 +4969,13 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D176" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="E176" t="s">
         <v>27</v>
@@ -4983,13 +4986,13 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D177" t="s">
-        <v>111</v>
+        <v>235</v>
       </c>
       <c r="E177" t="s">
         <v>27</v>
@@ -5000,13 +5003,13 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D178" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E178" t="s">
         <v>27</v>
@@ -5017,13 +5020,13 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D179" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E179" t="s">
         <v>27</v>
@@ -5034,13 +5037,13 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D180" t="s">
-        <v>265</v>
+        <v>146</v>
       </c>
       <c r="E180" t="s">
         <v>27</v>
@@ -5051,13 +5054,13 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D181" t="s">
-        <v>56</v>
+        <v>277</v>
       </c>
       <c r="E181" t="s">
         <v>27</v>
@@ -5068,13 +5071,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D182" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E182" t="s">
         <v>27</v>
@@ -5085,13 +5088,13 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D183" t="s">
-        <v>139</v>
+        <v>280</v>
       </c>
       <c r="E183" t="s">
         <v>27</v>
@@ -5102,13 +5105,13 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D184" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E184" t="s">
         <v>27</v>
@@ -5119,13 +5122,13 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
+        <v>282</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D185" t="s">
         <v>283</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D185" t="s">
-        <v>54</v>
       </c>
       <c r="E185" t="s">
         <v>27</v>
@@ -5142,7 +5145,7 @@
         <v>25</v>
       </c>
       <c r="D186" t="s">
-        <v>52</v>
+        <v>215</v>
       </c>
       <c r="E186" t="s">
         <v>27</v>
@@ -5159,7 +5162,7 @@
         <v>25</v>
       </c>
       <c r="D187" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="E187" t="s">
         <v>27</v>
@@ -5176,7 +5179,7 @@
         <v>25</v>
       </c>
       <c r="D188" t="s">
-        <v>207</v>
+        <v>71</v>
       </c>
       <c r="E188" t="s">
         <v>27</v>
@@ -5193,7 +5196,7 @@
         <v>25</v>
       </c>
       <c r="D189" t="s">
-        <v>219</v>
+        <v>124</v>
       </c>
       <c r="E189" t="s">
         <v>27</v>
@@ -5210,7 +5213,7 @@
         <v>25</v>
       </c>
       <c r="D190" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E190" t="s">
         <v>27</v>
@@ -5227,7 +5230,7 @@
         <v>25</v>
       </c>
       <c r="D191" t="s">
-        <v>127</v>
+        <v>40</v>
       </c>
       <c r="E191" t="s">
         <v>27</v>
@@ -5244,7 +5247,7 @@
         <v>25</v>
       </c>
       <c r="D192" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="E192" t="s">
         <v>27</v>
@@ -5261,7 +5264,7 @@
         <v>25</v>
       </c>
       <c r="D193" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="E193" t="s">
         <v>27</v>
@@ -5278,7 +5281,7 @@
         <v>25</v>
       </c>
       <c r="D194" t="s">
-        <v>107</v>
+        <v>293</v>
       </c>
       <c r="E194" t="s">
         <v>27</v>
@@ -5289,13 +5292,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D195" t="s">
-        <v>145</v>
+        <v>295</v>
       </c>
       <c r="E195" t="s">
         <v>27</v>
@@ -5306,13 +5309,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D196" t="s">
-        <v>238</v>
+        <v>116</v>
       </c>
       <c r="E196" t="s">
         <v>27</v>
@@ -5323,13 +5326,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D197" t="s">
-        <v>234</v>
+        <v>102</v>
       </c>
       <c r="E197" t="s">
         <v>27</v>
@@ -5340,13 +5343,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D198" t="s">
-        <v>156</v>
+        <v>89</v>
       </c>
       <c r="E198" t="s">
         <v>27</v>
@@ -5357,13 +5360,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D199" t="s">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="E199" t="s">
         <v>27</v>
@@ -5374,13 +5377,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D200" t="s">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="E200" t="s">
         <v>27</v>
@@ -5391,13 +5394,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D201" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="E201" t="s">
         <v>27</v>
@@ -5408,13 +5411,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D202" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="E202" t="s">
         <v>27</v>
@@ -5425,13 +5428,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D203" t="s">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="E203" t="s">
         <v>27</v>
@@ -5442,13 +5445,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D204" t="s">
-        <v>257</v>
+        <v>98</v>
       </c>
       <c r="E204" t="s">
         <v>27</v>
@@ -5459,13 +5462,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D205" t="s">
-        <v>304</v>
+        <v>48</v>
       </c>
       <c r="E205" t="s">
         <v>27</v>
@@ -5476,13 +5479,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D206" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="E206" t="s">
         <v>27</v>
@@ -5493,13 +5496,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D207" t="s">
-        <v>56</v>
+        <v>215</v>
       </c>
       <c r="E207" t="s">
         <v>27</v>
@@ -5510,13 +5513,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D208" t="s">
-        <v>103</v>
+        <v>197</v>
       </c>
       <c r="E208" t="s">
         <v>27</v>
@@ -5527,13 +5530,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D209" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="E209" t="s">
         <v>27</v>
@@ -5544,13 +5547,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D210" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E210" t="s">
         <v>27</v>
@@ -5561,13 +5564,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D211" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="E211" t="s">
         <v>27</v>
@@ -5578,13 +5581,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D212" t="s">
-        <v>94</v>
+        <v>280</v>
       </c>
       <c r="E212" t="s">
         <v>27</v>
@@ -5595,13 +5598,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D213" t="s">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="E213" t="s">
         <v>27</v>
@@ -5612,13 +5615,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D214" t="s">
-        <v>219</v>
+        <v>118</v>
       </c>
       <c r="E214" t="s">
         <v>27</v>
@@ -5629,13 +5632,13 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D215" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="E215" t="s">
         <v>27</v>
@@ -5646,13 +5649,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D216" t="s">
-        <v>316</v>
+        <v>178</v>
       </c>
       <c r="E216" t="s">
         <v>27</v>
@@ -5669,7 +5672,7 @@
         <v>25</v>
       </c>
       <c r="D217" t="s">
-        <v>195</v>
+        <v>235</v>
       </c>
       <c r="E217" t="s">
         <v>27</v>
@@ -5686,7 +5689,7 @@
         <v>25</v>
       </c>
       <c r="D218" t="s">
-        <v>145</v>
+        <v>293</v>
       </c>
       <c r="E218" t="s">
         <v>27</v>
@@ -5703,7 +5706,7 @@
         <v>25</v>
       </c>
       <c r="D219" t="s">
-        <v>230</v>
+        <v>100</v>
       </c>
       <c r="E219" t="s">
         <v>27</v>
@@ -5720,7 +5723,7 @@
         <v>25</v>
       </c>
       <c r="D220" t="s">
-        <v>230</v>
+        <v>192</v>
       </c>
       <c r="E220" t="s">
         <v>27</v>
@@ -5737,7 +5740,7 @@
         <v>25</v>
       </c>
       <c r="D221" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="E221" t="s">
         <v>27</v>
@@ -5754,7 +5757,7 @@
         <v>25</v>
       </c>
       <c r="D222" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="E222" t="s">
         <v>27</v>
@@ -5771,7 +5774,7 @@
         <v>25</v>
       </c>
       <c r="D223" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="E223" t="s">
         <v>27</v>
@@ -5788,7 +5791,7 @@
         <v>25</v>
       </c>
       <c r="D224" t="s">
-        <v>187</v>
+        <v>325</v>
       </c>
       <c r="E224" t="s">
         <v>27</v>
@@ -5799,13 +5802,13 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D225" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="E225" t="s">
         <v>27</v>
@@ -5816,13 +5819,13 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D226" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E226" t="s">
         <v>27</v>
@@ -5833,13 +5836,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D227" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E227" t="s">
         <v>27</v>
@@ -5850,13 +5853,13 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D228" t="s">
-        <v>265</v>
+        <v>126</v>
       </c>
       <c r="E228" t="s">
         <v>27</v>
@@ -5867,13 +5870,13 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D229" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="E229" t="s">
         <v>27</v>
@@ -5884,13 +5887,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D230" t="s">
-        <v>199</v>
+        <v>50</v>
       </c>
       <c r="E230" t="s">
         <v>27</v>
@@ -5901,13 +5904,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D231" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="E231" t="s">
         <v>27</v>
@@ -5918,13 +5921,13 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D232" t="s">
-        <v>244</v>
+        <v>200</v>
       </c>
       <c r="E232" t="s">
         <v>27</v>
@@ -5935,13 +5938,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D233" t="s">
-        <v>187</v>
+        <v>132</v>
       </c>
       <c r="E233" t="s">
         <v>27</v>
@@ -5952,13 +5955,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D234" t="s">
-        <v>335</v>
+        <v>222</v>
       </c>
       <c r="E234" t="s">
         <v>27</v>
@@ -5975,7 +5978,7 @@
         <v>25</v>
       </c>
       <c r="D235" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E235" t="s">
         <v>27</v>
@@ -5992,7 +5995,7 @@
         <v>25</v>
       </c>
       <c r="D236" t="s">
-        <v>227</v>
+        <v>54</v>
       </c>
       <c r="E236" t="s">
         <v>27</v>
@@ -6009,7 +6012,7 @@
         <v>25</v>
       </c>
       <c r="D237" t="s">
-        <v>145</v>
+        <v>339</v>
       </c>
       <c r="E237" t="s">
         <v>27</v>
@@ -6020,13 +6023,13 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D238" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E238" t="s">
         <v>27</v>
@@ -6037,13 +6040,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D239" t="s">
-        <v>230</v>
+        <v>293</v>
       </c>
       <c r="E239" t="s">
         <v>27</v>
@@ -6054,13 +6057,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D240" t="s">
-        <v>257</v>
+        <v>94</v>
       </c>
       <c r="E240" t="s">
         <v>27</v>
@@ -6071,13 +6074,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D241" t="s">
-        <v>66</v>
+        <v>344</v>
       </c>
       <c r="E241" t="s">
         <v>27</v>
@@ -6088,13 +6091,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D242" t="s">
-        <v>213</v>
+        <v>146</v>
       </c>
       <c r="E242" t="s">
         <v>27</v>
@@ -6105,13 +6108,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D243" t="s">
-        <v>345</v>
+        <v>114</v>
       </c>
       <c r="E243" t="s">
         <v>27</v>
@@ -6122,13 +6125,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D244" t="s">
-        <v>219</v>
+        <v>280</v>
       </c>
       <c r="E244" t="s">
         <v>27</v>
@@ -6139,13 +6142,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D245" t="s">
-        <v>109</v>
+        <v>202</v>
       </c>
       <c r="E245" t="s">
         <v>27</v>
@@ -6156,13 +6159,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D246" t="s">
-        <v>105</v>
+        <v>178</v>
       </c>
       <c r="E246" t="s">
         <v>27</v>
@@ -6173,13 +6176,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D247" t="s">
-        <v>52</v>
+        <v>126</v>
       </c>
       <c r="E247" t="s">
         <v>27</v>
@@ -6190,13 +6193,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D248" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="E248" t="s">
         <v>27</v>
@@ -6207,13 +6210,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D249" t="s">
-        <v>260</v>
+        <v>94</v>
       </c>
       <c r="E249" t="s">
         <v>27</v>
@@ -6224,13 +6227,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D250" t="s">
-        <v>234</v>
+        <v>271</v>
       </c>
       <c r="E250" t="s">
         <v>27</v>
@@ -6241,13 +6244,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D251" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="E251" t="s">
         <v>27</v>
@@ -6258,13 +6261,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D252" t="s">
-        <v>46</v>
+        <v>126</v>
       </c>
       <c r="E252" t="s">
         <v>27</v>
@@ -6275,13 +6278,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D253" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="E253" t="s">
         <v>27</v>
@@ -6292,13 +6295,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D254" t="s">
-        <v>234</v>
+        <v>42</v>
       </c>
       <c r="E254" t="s">
         <v>27</v>
@@ -6309,13 +6312,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D255" t="s">
-        <v>77</v>
+        <v>359</v>
       </c>
       <c r="E255" t="s">
         <v>27</v>
@@ -6326,13 +6329,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D256" t="s">
-        <v>91</v>
+        <v>361</v>
       </c>
       <c r="E256" t="s">
         <v>27</v>
@@ -6343,13 +6346,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D257" t="s">
-        <v>360</v>
+        <v>40</v>
       </c>
       <c r="E257" t="s">
         <v>27</v>
@@ -6360,13 +6363,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D258" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="E258" t="s">
         <v>27</v>
@@ -6377,13 +6380,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D259" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="E259" t="s">
         <v>27</v>
@@ -6394,13 +6397,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D260" t="s">
-        <v>125</v>
+        <v>171</v>
       </c>
       <c r="E260" t="s">
         <v>27</v>
@@ -6411,13 +6414,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D261" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E261" t="s">
         <v>27</v>
@@ -6428,13 +6431,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D262" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="E262" t="s">
         <v>27</v>
@@ -6445,13 +6448,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D263" t="s">
-        <v>162</v>
+        <v>361</v>
       </c>
       <c r="E263" t="s">
         <v>27</v>
@@ -6462,13 +6465,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D264" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="E264" t="s">
         <v>27</v>
@@ -6479,13 +6482,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D265" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="E265" t="s">
         <v>27</v>
@@ -6496,13 +6499,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D266" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E266" t="s">
         <v>27</v>
@@ -6513,13 +6516,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D267" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="E267" t="s">
         <v>27</v>
@@ -6530,13 +6533,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D268" t="s">
-        <v>44</v>
+        <v>361</v>
       </c>
       <c r="E268" t="s">
         <v>27</v>
@@ -6547,13 +6550,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D269" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="E269" t="s">
         <v>27</v>
@@ -6564,13 +6567,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D270" t="s">
-        <v>123</v>
+        <v>253</v>
       </c>
       <c r="E270" t="s">
         <v>27</v>
@@ -6581,13 +6584,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D271" t="s">
-        <v>219</v>
+        <v>42</v>
       </c>
       <c r="E271" t="s">
         <v>27</v>
@@ -6598,13 +6601,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D272" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="E272" t="s">
         <v>27</v>
@@ -6615,13 +6618,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D273" t="s">
-        <v>192</v>
+        <v>73</v>
       </c>
       <c r="E273" t="s">
         <v>27</v>
@@ -6632,13 +6635,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D274" t="s">
-        <v>153</v>
+        <v>71</v>
       </c>
       <c r="E274" t="s">
         <v>27</v>
@@ -6649,13 +6652,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D275" t="s">
-        <v>205</v>
+        <v>344</v>
       </c>
       <c r="E275" t="s">
         <v>27</v>
@@ -6666,13 +6669,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D276" t="s">
-        <v>145</v>
+        <v>46</v>
       </c>
       <c r="E276" t="s">
         <v>27</v>
@@ -6683,13 +6686,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D277" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="E277" t="s">
         <v>27</v>
@@ -6700,13 +6703,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D278" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E278" t="s">
         <v>27</v>
@@ -6717,13 +6720,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D279" t="s">
-        <v>96</v>
+        <v>222</v>
       </c>
       <c r="E279" t="s">
         <v>27</v>
@@ -6734,13 +6737,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D280" t="s">
-        <v>54</v>
+        <v>359</v>
       </c>
       <c r="E280" t="s">
         <v>27</v>
@@ -6751,13 +6754,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D281" t="s">
-        <v>153</v>
+        <v>44</v>
       </c>
       <c r="E281" t="s">
         <v>27</v>
@@ -6768,13 +6771,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D282" t="s">
-        <v>205</v>
+        <v>48</v>
       </c>
       <c r="E282" t="s">
         <v>27</v>
@@ -6785,13 +6788,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D283" t="s">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="E283" t="s">
         <v>27</v>
@@ -6802,13 +6805,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D284" t="s">
-        <v>207</v>
+        <v>176</v>
       </c>
       <c r="E284" t="s">
         <v>27</v>
@@ -6819,13 +6822,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D285" t="s">
-        <v>158</v>
+        <v>98</v>
       </c>
       <c r="E285" t="s">
         <v>27</v>
@@ -6836,13 +6839,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D286" t="s">
-        <v>153</v>
+        <v>222</v>
       </c>
       <c r="E286" t="s">
         <v>27</v>
@@ -6853,13 +6856,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D287" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="E287" t="s">
         <v>27</v>
@@ -6870,13 +6873,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D288" t="s">
-        <v>111</v>
+        <v>154</v>
       </c>
       <c r="E288" t="s">
         <v>27</v>
@@ -6887,13 +6890,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D289" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="E289" t="s">
         <v>27</v>
@@ -6904,13 +6907,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D290" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="E290" t="s">
         <v>27</v>
@@ -6921,13 +6924,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D291" t="s">
-        <v>345</v>
+        <v>235</v>
       </c>
       <c r="E291" t="s">
         <v>27</v>
@@ -6938,13 +6941,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D292" t="s">
-        <v>211</v>
+        <v>75</v>
       </c>
       <c r="E292" t="s">
         <v>27</v>
@@ -6955,13 +6958,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D293" t="s">
-        <v>207</v>
+        <v>89</v>
       </c>
       <c r="E293" t="s">
         <v>27</v>
@@ -6972,13 +6975,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D294" t="s">
-        <v>123</v>
+        <v>253</v>
       </c>
       <c r="E294" t="s">
         <v>27</v>
@@ -6989,13 +6992,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D295" t="s">
-        <v>257</v>
+        <v>222</v>
       </c>
       <c r="E295" t="s">
         <v>27</v>
@@ -7006,13 +7009,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D296" t="s">
-        <v>211</v>
+        <v>116</v>
       </c>
       <c r="E296" t="s">
         <v>27</v>
@@ -7023,13 +7026,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D297" t="s">
-        <v>83</v>
+        <v>271</v>
       </c>
       <c r="E297" t="s">
         <v>27</v>
@@ -7040,13 +7043,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D298" t="s">
-        <v>207</v>
+        <v>104</v>
       </c>
       <c r="E298" t="s">
         <v>27</v>
@@ -7057,13 +7060,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D299" t="s">
-        <v>234</v>
+        <v>325</v>
       </c>
       <c r="E299" t="s">
         <v>27</v>
@@ -7074,13 +7077,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D300" t="s">
-        <v>158</v>
+        <v>283</v>
       </c>
       <c r="E300" t="s">
         <v>27</v>
@@ -7091,13 +7094,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D301" t="s">
-        <v>72</v>
+        <v>293</v>
       </c>
       <c r="E301" t="s">
         <v>27</v>
@@ -7108,13 +7111,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D302" t="s">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="E302" t="s">
         <v>27</v>
@@ -7125,13 +7128,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D303" t="s">
-        <v>174</v>
+        <v>56</v>
       </c>
       <c r="E303" t="s">
         <v>27</v>
@@ -7142,13 +7145,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D304" t="s">
-        <v>265</v>
+        <v>124</v>
       </c>
       <c r="E304" t="s">
         <v>27</v>
@@ -7159,13 +7162,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D305" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="E305" t="s">
         <v>27</v>
@@ -7176,13 +7179,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D306" t="s">
-        <v>44</v>
+        <v>361</v>
       </c>
       <c r="E306" t="s">
         <v>27</v>
@@ -7193,13 +7196,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D307" t="s">
-        <v>185</v>
+        <v>91</v>
       </c>
       <c r="E307" t="s">
         <v>27</v>
@@ -7210,13 +7213,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D308" t="s">
-        <v>139</v>
+        <v>40</v>
       </c>
       <c r="E308" t="s">
         <v>27</v>
@@ -7227,13 +7230,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D309" t="s">
-        <v>107</v>
+        <v>243</v>
       </c>
       <c r="E309" t="s">
         <v>27</v>
@@ -7244,13 +7247,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D310" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="E310" t="s">
         <v>27</v>
@@ -7261,13 +7264,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D311" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E311" t="s">
         <v>27</v>
@@ -7278,13 +7281,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D312" t="s">
-        <v>345</v>
+        <v>42</v>
       </c>
       <c r="E312" t="s">
         <v>27</v>
@@ -7295,13 +7298,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D313" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="E313" t="s">
         <v>27</v>
@@ -7312,13 +7315,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D314" t="s">
-        <v>96</v>
+        <v>247</v>
       </c>
       <c r="E314" t="s">
         <v>27</v>
@@ -7329,13 +7332,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D315" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="E315" t="s">
         <v>27</v>
@@ -7346,13 +7349,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D316" t="s">
-        <v>127</v>
+        <v>202</v>
       </c>
       <c r="E316" t="s">
         <v>27</v>
@@ -7363,13 +7366,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D317" t="s">
-        <v>165</v>
+        <v>79</v>
       </c>
       <c r="E317" t="s">
         <v>27</v>
@@ -7380,13 +7383,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D318" t="s">
-        <v>422</v>
+        <v>200</v>
       </c>
       <c r="E318" t="s">
         <v>27</v>
@@ -7397,13 +7400,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D319" t="s">
-        <v>304</v>
+        <v>102</v>
       </c>
       <c r="E319" t="s">
         <v>27</v>
@@ -7414,13 +7417,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D320" t="s">
-        <v>170</v>
+        <v>344</v>
       </c>
       <c r="E320" t="s">
         <v>27</v>
@@ -7431,13 +7434,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D321" t="s">
-        <v>127</v>
+        <v>325</v>
       </c>
       <c r="E321" t="s">
         <v>27</v>
@@ -7448,13 +7451,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D322" t="s">
-        <v>111</v>
+        <v>293</v>
       </c>
       <c r="E322" t="s">
         <v>27</v>
@@ -7465,13 +7468,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D323" t="s">
-        <v>74</v>
+        <v>243</v>
       </c>
       <c r="E323" t="s">
         <v>27</v>
@@ -7482,13 +7485,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D324" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="E324" t="s">
         <v>27</v>
@@ -7499,13 +7502,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D325" t="s">
-        <v>60</v>
+        <v>271</v>
       </c>
       <c r="E325" t="s">
         <v>27</v>
@@ -7516,13 +7519,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D326" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="E326" t="s">
         <v>27</v>
@@ -7533,13 +7536,13 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D327" t="s">
-        <v>114</v>
+        <v>237</v>
       </c>
       <c r="E327" t="s">
         <v>27</v>
@@ -7550,13 +7553,13 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D328" t="s">
-        <v>230</v>
+        <v>56</v>
       </c>
       <c r="E328" t="s">
         <v>27</v>
@@ -7567,13 +7570,13 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D329" t="s">
-        <v>422</v>
+        <v>178</v>
       </c>
       <c r="E329" t="s">
         <v>27</v>
@@ -7584,13 +7587,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D330" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
       <c r="E330" t="s">
         <v>27</v>
@@ -7601,13 +7604,13 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D331" t="s">
-        <v>127</v>
+        <v>44</v>
       </c>
       <c r="E331" t="s">
         <v>27</v>
@@ -7618,13 +7621,13 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D332" t="s">
-        <v>40</v>
+        <v>247</v>
       </c>
       <c r="E332" t="s">
         <v>27</v>
@@ -7635,13 +7638,13 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D333" t="s">
-        <v>174</v>
+        <v>52</v>
       </c>
       <c r="E333" t="s">
         <v>27</v>
@@ -7652,13 +7655,13 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D334" t="s">
-        <v>244</v>
+        <v>66</v>
       </c>
       <c r="E334" t="s">
         <v>27</v>
@@ -7669,13 +7672,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D335" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="E335" t="s">
         <v>27</v>
@@ -7686,13 +7689,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D336" t="s">
-        <v>174</v>
+        <v>56</v>
       </c>
       <c r="E336" t="s">
         <v>27</v>
@@ -7703,13 +7706,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D337" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E337" t="s">
         <v>27</v>
@@ -7720,13 +7723,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D338" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="E338" t="s">
         <v>27</v>
@@ -7737,13 +7740,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D339" t="s">
-        <v>162</v>
+        <v>100</v>
       </c>
       <c r="E339" t="s">
         <v>27</v>
@@ -7754,13 +7757,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D340" t="s">
-        <v>131</v>
+        <v>361</v>
       </c>
       <c r="E340" t="s">
         <v>27</v>
@@ -7771,13 +7774,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D341" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="E341" t="s">
         <v>27</v>
@@ -7788,13 +7791,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D342" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="E342" t="s">
         <v>27</v>
@@ -7805,13 +7808,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D343" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="E343" t="s">
         <v>27</v>
@@ -7822,13 +7825,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D344" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="E344" t="s">
         <v>27</v>
@@ -7839,13 +7842,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D345" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="E345" t="s">
         <v>27</v>
@@ -7856,13 +7859,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D346" t="s">
-        <v>162</v>
+        <v>48</v>
       </c>
       <c r="E346" t="s">
         <v>27</v>
@@ -7873,13 +7876,13 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D347" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="E347" t="s">
         <v>27</v>
@@ -7890,13 +7893,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D348" t="s">
-        <v>137</v>
+        <v>222</v>
       </c>
       <c r="E348" t="s">
         <v>27</v>
@@ -7907,13 +7910,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D349" t="s">
-        <v>162</v>
+        <v>100</v>
       </c>
       <c r="E349" t="s">
         <v>27</v>
@@ -7924,13 +7927,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D350" t="s">
-        <v>422</v>
+        <v>157</v>
       </c>
       <c r="E350" t="s">
         <v>27</v>
@@ -7941,13 +7944,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D351" t="s">
-        <v>316</v>
+        <v>237</v>
       </c>
       <c r="E351" t="s">
         <v>27</v>
@@ -7958,13 +7961,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D352" t="s">
-        <v>125</v>
+        <v>215</v>
       </c>
       <c r="E352" t="s">
         <v>27</v>
@@ -7975,13 +7978,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D353" t="s">
-        <v>85</v>
+        <v>253</v>
       </c>
       <c r="E353" t="s">
         <v>27</v>
@@ -7992,13 +7995,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D354" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="E354" t="s">
         <v>27</v>
@@ -8009,13 +8012,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D355" t="s">
-        <v>177</v>
+        <v>359</v>
       </c>
       <c r="E355" t="s">
         <v>27</v>
@@ -8026,13 +8029,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D356" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="E356" t="s">
         <v>27</v>
@@ -8043,13 +8046,13 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D357" t="s">
-        <v>244</v>
+        <v>325</v>
       </c>
       <c r="E357" t="s">
         <v>27</v>
@@ -8060,13 +8063,13 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D358" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="E358" t="s">
         <v>27</v>
@@ -8077,13 +8080,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D359" t="s">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="E359" t="s">
         <v>27</v>
@@ -8094,13 +8097,13 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D360" t="s">
-        <v>62</v>
+        <v>200</v>
       </c>
       <c r="E360" t="s">
         <v>27</v>
@@ -8111,13 +8114,13 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D361" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="E361" t="s">
         <v>27</v>
@@ -8128,13 +8131,13 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D362" t="s">
-        <v>185</v>
+        <v>69</v>
       </c>
       <c r="E362" t="s">
         <v>27</v>
@@ -8145,13 +8148,13 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D363" t="s">
-        <v>265</v>
+        <v>293</v>
       </c>
       <c r="E363" t="s">
         <v>27</v>
@@ -8162,13 +8165,13 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D364" t="s">
-        <v>50</v>
+        <v>361</v>
       </c>
       <c r="E364" t="s">
         <v>27</v>
@@ -8179,13 +8182,13 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D365" t="s">
-        <v>109</v>
+        <v>359</v>
       </c>
       <c r="E365" t="s">
         <v>27</v>
@@ -8196,13 +8199,13 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D366" t="s">
-        <v>133</v>
+        <v>180</v>
       </c>
       <c r="E366" t="s">
         <v>27</v>
@@ -8213,13 +8216,13 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D367" t="s">
-        <v>96</v>
+        <v>295</v>
       </c>
       <c r="E367" t="s">
         <v>27</v>
@@ -8230,13 +8233,13 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D368" t="s">
-        <v>213</v>
+        <v>152</v>
       </c>
       <c r="E368" t="s">
         <v>27</v>
@@ -8247,13 +8250,13 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D369" t="s">
-        <v>40</v>
+        <v>293</v>
       </c>
       <c r="E369" t="s">
         <v>27</v>
@@ -8264,13 +8267,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D370" t="s">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="E370" t="s">
         <v>27</v>
@@ -8281,13 +8284,13 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D371" t="s">
-        <v>207</v>
+        <v>283</v>
       </c>
       <c r="E371" t="s">
         <v>27</v>
@@ -8298,13 +8301,13 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D372" t="s">
-        <v>230</v>
+        <v>152</v>
       </c>
       <c r="E372" t="s">
         <v>27</v>
@@ -8315,13 +8318,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D373" t="s">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="E373" t="s">
         <v>27</v>
@@ -8332,13 +8335,13 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D374" t="s">
-        <v>99</v>
+        <v>202</v>
       </c>
       <c r="E374" t="s">
         <v>27</v>
@@ -8349,13 +8352,13 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D375" t="s">
-        <v>177</v>
+        <v>64</v>
       </c>
       <c r="E375" t="s">
         <v>27</v>
@@ -8366,13 +8369,13 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D376" t="s">
-        <v>68</v>
+        <v>344</v>
       </c>
       <c r="E376" t="s">
         <v>27</v>
@@ -8383,13 +8386,13 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D377" t="s">
-        <v>192</v>
+        <v>235</v>
       </c>
       <c r="E377" t="s">
         <v>27</v>
@@ -8400,13 +8403,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D378" t="s">
-        <v>72</v>
+        <v>339</v>
       </c>
       <c r="E378" t="s">
         <v>27</v>
@@ -8417,13 +8420,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C379" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D379" t="s">
-        <v>234</v>
+        <v>87</v>
       </c>
       <c r="E379" t="s">
         <v>27</v>
@@ -8434,13 +8437,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D380" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E380" t="s">
         <v>27</v>
@@ -8451,13 +8454,13 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C381" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D381" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="E381" t="s">
         <v>27</v>
@@ -8468,13 +8471,13 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D382" t="s">
-        <v>64</v>
+        <v>344</v>
       </c>
       <c r="E382" t="s">
         <v>27</v>
@@ -8485,13 +8488,13 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D383" t="s">
-        <v>238</v>
+        <v>489</v>
       </c>
       <c r="E383" t="s">
         <v>27</v>
@@ -8502,13 +8505,13 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D384" t="s">
-        <v>260</v>
+        <v>146</v>
       </c>
       <c r="E384" t="s">
         <v>27</v>
@@ -8519,13 +8522,13 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D385" t="s">
-        <v>490</v>
+        <v>89</v>
       </c>
       <c r="E385" t="s">
         <v>27</v>
@@ -8536,13 +8539,13 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D386" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="E386" t="s">
         <v>27</v>
@@ -8553,13 +8556,13 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D387" t="s">
-        <v>234</v>
+        <v>325</v>
       </c>
       <c r="E387" t="s">
         <v>27</v>
@@ -8570,13 +8573,13 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D388" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="E388" t="s">
         <v>27</v>
@@ -8587,13 +8590,13 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D389" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E389" t="s">
         <v>27</v>
@@ -8604,13 +8607,13 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D390" t="s">
-        <v>213</v>
+        <v>73</v>
       </c>
       <c r="E390" t="s">
         <v>27</v>
@@ -8621,13 +8624,13 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D391" t="s">
-        <v>72</v>
+        <v>222</v>
       </c>
       <c r="E391" t="s">
         <v>27</v>
@@ -8638,13 +8641,13 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D392" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="E392" t="s">
         <v>27</v>
@@ -8655,13 +8658,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D393" t="s">
-        <v>234</v>
+        <v>54</v>
       </c>
       <c r="E393" t="s">
         <v>27</v>
@@ -8672,13 +8675,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D394" t="s">
-        <v>46</v>
+        <v>339</v>
       </c>
       <c r="E394" t="s">
         <v>27</v>
@@ -8689,13 +8692,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D395" t="s">
-        <v>111</v>
+        <v>295</v>
       </c>
       <c r="E395" t="s">
         <v>27</v>
@@ -8706,13 +8709,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D396" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E396" t="s">
         <v>27</v>
@@ -8723,13 +8726,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D397" t="s">
-        <v>44</v>
+        <v>167</v>
       </c>
       <c r="E397" t="s">
         <v>27</v>
@@ -8740,13 +8743,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D398" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="E398" t="s">
         <v>27</v>
@@ -8757,13 +8760,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D399" t="s">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="E399" t="s">
         <v>27</v>
@@ -8774,13 +8777,13 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D400" t="s">
-        <v>213</v>
+        <v>359</v>
       </c>
       <c r="E400" t="s">
         <v>27</v>
@@ -8791,13 +8794,13 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D401" t="s">
-        <v>174</v>
+        <v>361</v>
       </c>
       <c r="E401" t="s">
         <v>27</v>
@@ -8816,47 +8819,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B4" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B5" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B6">
         <v>400</v>
@@ -8864,7 +8867,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B7">
         <v>391</v>
@@ -8872,7 +8875,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B8">
         <v>9</v>
@@ -8880,7 +8883,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8888,10 +8891,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B10" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>

--- a/reports/selenium/Excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/Excel/Automation_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="523">
   <si>
     <t>#</t>
   </si>
@@ -35,11 +35,11 @@
     <t>FAILED</t>
   </si>
   <si>
-    <t>20.97</t>
+    <t>20.74</t>
   </si>
   <si>
     <t xml:space="preserve">Landing page did not load — Sign In button not found
-Wait timed out after 20187ms</t>
+Wait timed out after 20193ms</t>
   </si>
   <si>
     <t>should navigate to the login form</t>
@@ -49,47 +49,47 @@
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20151ms</t>
+Wait timed out after 20146ms</t>
   </si>
   <si>
     <t>should login with valid credentials and reach the dashboard</t>
   </si>
   <si>
-    <t>20.80</t>
+    <t>20.50</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20156ms</t>
+Wait timed out after 20137ms</t>
   </si>
   <si>
     <t>should reject invalid credentials with an error message</t>
   </si>
   <si>
-    <t>20.58</t>
+    <t>20.96</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20143ms</t>
+Wait timed out after 20188ms</t>
   </si>
   <si>
     <t>should open the sign-up form from landing</t>
   </si>
   <si>
-    <t>20.79</t>
+    <t>20.87</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signup-btn"])
-Wait timed out after 20148ms</t>
+Wait timed out after 20173ms</t>
   </si>
   <si>
     <t>Security — should reject login for invalid credentials</t>
   </si>
   <si>
-    <t>20.77</t>
+    <t>20.75</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20003ms</t>
+Wait timed out after 20183ms</t>
   </si>
   <si>
     <t>Security — should prevent access to protected routes/dashboard for unauthenticated users</t>
@@ -98,7 +98,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>3.24</t>
+    <t>3.64</t>
   </si>
   <si>
     <t/>
@@ -107,1287 +107,1287 @@
     <t>Security — should not execute XSS script payloads submitted in login fields</t>
   </si>
   <si>
-    <t>20.49</t>
+    <t>20.83</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20153ms</t>
+Wait timed out after 20175ms</t>
   </si>
   <si>
     <t>Security — should enforce session termination and clean storage upon logout</t>
   </si>
   <si>
-    <t>20.87</t>
-  </si>
-  <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20165ms</t>
+Wait timed out after 20173ms</t>
   </si>
   <si>
     <t>Security — should confirm Firebase authentication rejects empty credentials</t>
   </si>
   <si>
-    <t>20.48</t>
+    <t>20.91</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20129ms</t>
+Wait timed out after 20157ms</t>
   </si>
   <si>
     <t>Security — should not expose sensitive API keys or secrets in page HTML source</t>
   </si>
   <si>
+    <t>0.37</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for compare-btn (Verify Point #11)</t>
+  </si>
+  <si>
+    <t>0.84</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated profile-settings (Verify Point #12)</t>
+  </si>
+  <si>
+    <t>0.32</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for ai-chat-input (Verify Point #13)</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on en-US (Verify Point #14)</t>
+  </si>
+  <si>
+    <t>0.97</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for hi-IN (Verify Point #15)</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for ta-IN (Verify Point #16)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for header-nav (Verify Point #17)</t>
+  </si>
+  <si>
+    <t>0.47</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field sidebar-menu (Verify Point #18)</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to footer-links (Verify Point #19)</t>
+  </si>
+  <si>
+    <t>0.82</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution login-form (Verify Point #20)</t>
+  </si>
+  <si>
+    <t>0.60</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element register-form (Verify Point #21)</t>
+  </si>
+  <si>
+    <t>0.89</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container dashboard-grid (Verify Point #22)</t>
+  </si>
+  <si>
+    <t>0.72</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter detail-page (Verify Point #23)</t>
+  </si>
+  <si>
+    <t>0.69</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale fees-filter (Verify Point #24)</t>
+  </si>
+  <si>
+    <t>0.40</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource nirf-sort (Verify Point #25)</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path course-filter (Verify Point #26)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component state-filter (Verify Point #27)</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for firebase-auth (Verify Point #28)</t>
+  </si>
+  <si>
+    <t>0.54</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for firestore-read (Verify Point #29)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for groq-api (Verify Point #30)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for expo-router (Verify Point #31)</t>
+  </si>
+  <si>
+    <t>0.28</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated college-list (Verify Point #32)</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for saved-list (Verify Point #33)</t>
+  </si>
+  <si>
+    <t>0.55</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on comparison-list (Verify Point #34)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for chat-history (Verify Point #35)</t>
+  </si>
+  <si>
+    <t>0.76</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for avatar-upload (Verify Point #36)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for theme-toggle (Verify Point #37)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field notification-prefs (Verify Point #38)</t>
+  </si>
+  <si>
+    <t>0.79</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to session-token (Verify Point #39)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution XSS-injection (Verify Point #40)</t>
+  </si>
+  <si>
+    <t>0.65</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element SQL-injection (Verify Point #41)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container CSRF-token (Verify Point #42)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter CORS-origin (Verify Point #43)</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale CSP-header (Verify Point #44)</t>
+  </si>
+  <si>
     <t>0.41</t>
   </si>
   <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for compare-btn (Verify Point #11)</t>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource X-Frame-Options (Verify Point #45)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path primary-font (Verify Point #46)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component accent-color (Verify Point #47)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for glassmorphic-transparency (Verify Point #48)</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for border-radius (Verify Point #49)</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for bundle-size (Verify Point #50)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for first-meaningful-paint (Verify Point #51)</t>
+  </si>
+  <si>
+    <t>0.70</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated time-to-interactive (Verify Point #52)</t>
+  </si>
+  <si>
+    <t>0.61</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for dom-depth (Verify Point #53)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on lost-item-card (Verify Point #54)</t>
+  </si>
+  <si>
+    <t>0.31</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for users-ref (Verify Point #55)</t>
+  </si>
+  <si>
+    <t>0.59</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for items-ref (Verify Point #56)</t>
+  </si>
+  <si>
+    <t>0.63</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for de-DE (Verify Point #57)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field fr-FR (Verify Point #58)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to ja-JP (Verify Point #59)</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution pt-BR (Verify Point #60)</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element it-IT (Verify Point #61)</t>
+  </si>
+  <si>
+    <t>0.73</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container 1920x1080 (Verify Point #62)</t>
+  </si>
+  <si>
+    <t>0.30</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter 1440x900 (Verify Point #63)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale 1280x800 (Verify Point #64)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource 1024x768 (Verify Point #65)</t>
+  </si>
+  <si>
+    <t>0.46</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path 768x1024 (Verify Point #66)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component 375x812 (Verify Point #67)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for sign-in-button (Verify Point #68)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for email-input (Verify Point #69)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for password-field (Verify Point #70)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for search-bar (Verify Point #71)</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated college-card (Verify Point #72)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for compare-btn (Verify Point #73)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on profile-settings (Verify Point #74)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for ai-chat-input (Verify Point #75)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for en-US (Verify Point #76)</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for hi-IN (Verify Point #77)</t>
+  </si>
+  <si>
+    <t>0.99</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field ta-IN (Verify Point #78)</t>
   </si>
   <si>
     <t>0.78</t>
   </si>
   <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated profile-settings (Verify Point #12)</t>
-  </si>
-  <si>
-    <t>0.23</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for ai-chat-input (Verify Point #13)</t>
-  </si>
-  <si>
-    <t>0.40</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on en-US (Verify Point #14)</t>
-  </si>
-  <si>
-    <t>0.99</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for hi-IN (Verify Point #15)</t>
-  </si>
-  <si>
-    <t>0.51</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for ta-IN (Verify Point #16)</t>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to header-nav (Verify Point #79)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution sidebar-menu (Verify Point #80)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element footer-links (Verify Point #81)</t>
+  </si>
+  <si>
+    <t>0.44</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container login-form (Verify Point #82)</t>
+  </si>
+  <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter register-form (Verify Point #83)</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale dashboard-grid (Verify Point #84)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource detail-page (Verify Point #85)</t>
+  </si>
+  <si>
+    <t>0.83</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path fees-filter (Verify Point #86)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component nirf-sort (Verify Point #87)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for course-filter (Verify Point #88)</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for state-filter (Verify Point #89)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for firebase-auth (Verify Point #90)</t>
+  </si>
+  <si>
+    <t>0.88</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for firestore-read (Verify Point #91)</t>
+  </si>
+  <si>
+    <t>0.67</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #92)</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for expo-router (Verify Point #93)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on college-list (Verify Point #94)</t>
+  </si>
+  <si>
+    <t>0.66</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for saved-list (Verify Point #95)</t>
+  </si>
+  <si>
+    <t>0.81</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for comparison-list (Verify Point #96)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for chat-history (Verify Point #97)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field avatar-upload (Verify Point #98)</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to theme-toggle (Verify Point #99)</t>
+  </si>
+  <si>
+    <t>0.93</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution notification-prefs (Verify Point #100)</t>
+  </si>
+  <si>
+    <t>0.71</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element session-token (Verify Point #101)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container XSS-injection (Verify Point #102)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter SQL-injection (Verify Point #103)</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale CSRF-token (Verify Point #104)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource CORS-origin (Verify Point #105)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path CSP-header (Verify Point #106)</t>
   </si>
   <si>
     <t>0.68</t>
   </si>
   <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for header-nav (Verify Point #17)</t>
-  </si>
-  <si>
-    <t>0.88</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field sidebar-menu (Verify Point #18)</t>
-  </si>
-  <si>
-    <t>0.69</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to footer-links (Verify Point #19)</t>
-  </si>
-  <si>
-    <t>0.75</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution login-form (Verify Point #20)</t>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component X-Frame-Options (Verify Point #107)</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for primary-font (Verify Point #108)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for accent-color (Verify Point #109)</t>
+  </si>
+  <si>
+    <t>0.52</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for glassmorphic-transparency (Verify Point #110)</t>
+  </si>
+  <si>
+    <t>0.48</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for border-radius (Verify Point #111)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated bundle-size (Verify Point #112)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for first-meaningful-paint (Verify Point #113)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on time-to-interactive (Verify Point #114)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for dom-depth (Verify Point #115)</t>
+  </si>
+  <si>
+    <t>0.49</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for lost-item-card (Verify Point #116)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for users-ref (Verify Point #117)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field items-ref (Verify Point #118)</t>
+  </si>
+  <si>
+    <t>0.92</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to de-DE (Verify Point #119)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution fr-FR (Verify Point #120)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element ja-JP (Verify Point #121)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container pt-BR (Verify Point #122)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter it-IT (Verify Point #123)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #124)</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #125)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #126)</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #127)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #128)</t>
   </si>
   <si>
     <t>0.90</t>
   </si>
   <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element register-form (Verify Point #21)</t>
-  </si>
-  <si>
-    <t>0.24</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container dashboard-grid (Verify Point #22)</t>
-  </si>
-  <si>
-    <t>0.50</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter detail-page (Verify Point #23)</t>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for 375x812 (Verify Point #129)</t>
+  </si>
+  <si>
+    <t>0.80</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for sign-in-button (Verify Point #130)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for email-input (Verify Point #131)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated password-field (Verify Point #132)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for search-bar (Verify Point #133)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on college-card (Verify Point #134)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for compare-btn (Verify Point #135)</t>
+  </si>
+  <si>
+    <t>0.53</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for profile-settings (Verify Point #136)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for ai-chat-input (Verify Point #137)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field en-US (Verify Point #138)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to hi-IN (Verify Point #139)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution ta-IN (Verify Point #140)</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element header-nav (Verify Point #141)</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container sidebar-menu (Verify Point #142)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter footer-links (Verify Point #143)</t>
+  </si>
+  <si>
+    <t>0.87</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale login-form (Verify Point #144)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource register-form (Verify Point #145)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path dashboard-grid (Verify Point #146)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component detail-page (Verify Point #147)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for fees-filter (Verify Point #148)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for nirf-sort (Verify Point #149)</t>
+  </si>
+  <si>
+    <t>0.74</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for course-filter (Verify Point #150)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for state-filter (Verify Point #151)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated firebase-auth (Verify Point #152)</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for firestore-read (Verify Point #153)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on groq-api (Verify Point #154)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for expo-router (Verify Point #155)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for college-list (Verify Point #156)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for saved-list (Verify Point #157)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field comparison-list (Verify Point #158)</t>
+  </si>
+  <si>
+    <t>0.86</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to chat-history (Verify Point #159)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution avatar-upload (Verify Point #160)</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element theme-toggle (Verify Point #161)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container notification-prefs (Verify Point #162)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter session-token (Verify Point #163)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale XSS-injection (Verify Point #164)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #165)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path CSRF-token (Verify Point #166)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component CORS-origin (Verify Point #167)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for CSP-header (Verify Point #168)</t>
+  </si>
+  <si>
+    <t>0.45</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for X-Frame-Options (Verify Point #169)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for primary-font (Verify Point #170)</t>
+  </si>
+  <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for accent-color (Verify Point #171)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated glassmorphic-transparency (Verify Point #172)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for border-radius (Verify Point #173)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on bundle-size (Verify Point #174)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for first-meaningful-paint (Verify Point #175)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for time-to-interactive (Verify Point #176)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for dom-depth (Verify Point #177)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field lost-item-card (Verify Point #178)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to users-ref (Verify Point #179)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution items-ref (Verify Point #180)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element de-DE (Verify Point #181)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container fr-FR (Verify Point #182)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter ja-JP (Verify Point #183)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale pt-BR (Verify Point #184)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource it-IT (Verify Point #185)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path 1920x1080 (Verify Point #186)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component 1440x900 (Verify Point #187)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for 1280x800 (Verify Point #188)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for 1024x768 (Verify Point #189)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for 768x1024 (Verify Point #190)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for 375x812 (Verify Point #191)</t>
   </si>
   <si>
     <t>0.91</t>
   </si>
   <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale fees-filter (Verify Point #24)</t>
-  </si>
-  <si>
-    <t>0.28</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource nirf-sort (Verify Point #25)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path course-filter (Verify Point #26)</t>
-  </si>
-  <si>
-    <t>0.57</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component state-filter (Verify Point #27)</t>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated sign-in-button (Verify Point #192)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for email-input (Verify Point #193)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on password-field (Verify Point #194)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for search-bar (Verify Point #195)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for college-card (Verify Point #196)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for compare-btn (Verify Point #197)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field profile-settings (Verify Point #198)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to ai-chat-input (Verify Point #199)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution en-US (Verify Point #200)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element hi-IN (Verify Point #201)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container ta-IN (Verify Point #202)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter header-nav (Verify Point #203)</t>
+  </si>
+  <si>
+    <t>0.96</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale sidebar-menu (Verify Point #204)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource footer-links (Verify Point #205)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path login-form (Verify Point #206)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component register-form (Verify Point #207)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for dashboard-grid (Verify Point #208)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for detail-page (Verify Point #209)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for fees-filter (Verify Point #210)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for nirf-sort (Verify Point #211)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated course-filter (Verify Point #212)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for state-filter (Verify Point #213)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on firebase-auth (Verify Point #214)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for firestore-read (Verify Point #215)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for groq-api (Verify Point #216)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for expo-router (Verify Point #217)</t>
+  </si>
+  <si>
+    <t>0.77</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field college-list (Verify Point #218)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to saved-list (Verify Point #219)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution comparison-list (Verify Point #220)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element chat-history (Verify Point #221)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container avatar-upload (Verify Point #222)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter theme-toggle (Verify Point #223)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale notification-prefs (Verify Point #224)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource session-token (Verify Point #225)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path XSS-injection (Verify Point #226)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component SQL-injection (Verify Point #227)</t>
   </si>
   <si>
     <t>0.38</t>
   </si>
   <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for firebase-auth (Verify Point #28)</t>
-  </si>
-  <si>
-    <t>0.82</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for firestore-read (Verify Point #29)</t>
-  </si>
-  <si>
-    <t>0.97</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for groq-api (Verify Point #30)</t>
-  </si>
-  <si>
-    <t>0.65</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for expo-router (Verify Point #31)</t>
-  </si>
-  <si>
-    <t>0.64</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated college-list (Verify Point #32)</t>
-  </si>
-  <si>
-    <t>0.46</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for saved-list (Verify Point #33)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on comparison-list (Verify Point #34)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for chat-history (Verify Point #35)</t>
-  </si>
-  <si>
-    <t>0.27</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for avatar-upload (Verify Point #36)</t>
-  </si>
-  <si>
-    <t>0.36</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for theme-toggle (Verify Point #37)</t>
-  </si>
-  <si>
-    <t>0.93</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field notification-prefs (Verify Point #38)</t>
-  </si>
-  <si>
-    <t>0.49</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to session-token (Verify Point #39)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution XSS-injection (Verify Point #40)</t>
-  </si>
-  <si>
-    <t>0.44</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element SQL-injection (Verify Point #41)</t>
-  </si>
-  <si>
-    <t>0.54</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container CSRF-token (Verify Point #42)</t>
-  </si>
-  <si>
-    <t>0.84</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter CORS-origin (Verify Point #43)</t>
-  </si>
-  <si>
-    <t>0.59</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale CSP-header (Verify Point #44)</t>
-  </si>
-  <si>
-    <t>0.33</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource X-Frame-Options (Verify Point #45)</t>
-  </si>
-  <si>
-    <t>0.30</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path primary-font (Verify Point #46)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component accent-color (Verify Point #47)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for glassmorphic-transparency (Verify Point #48)</t>
-  </si>
-  <si>
-    <t>0.76</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for border-radius (Verify Point #49)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for bundle-size (Verify Point #50)</t>
-  </si>
-  <si>
-    <t>0.55</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for first-meaningful-paint (Verify Point #51)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated time-to-interactive (Verify Point #52)</t>
-  </si>
-  <si>
-    <t>0.94</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for dom-depth (Verify Point #53)</t>
-  </si>
-  <si>
-    <t>0.74</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on lost-item-card (Verify Point #54)</t>
-  </si>
-  <si>
-    <t>0.81</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for users-ref (Verify Point #55)</t>
-  </si>
-  <si>
-    <t>0.58</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for items-ref (Verify Point #56)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for de-DE (Verify Point #57)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field fr-FR (Verify Point #58)</t>
-  </si>
-  <si>
-    <t>0.34</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to ja-JP (Verify Point #59)</t>
-  </si>
-  <si>
-    <t>0.80</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution pt-BR (Verify Point #60)</t>
-  </si>
-  <si>
-    <t>0.79</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element it-IT (Verify Point #61)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container 1920x1080 (Verify Point #62)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter 1440x900 (Verify Point #63)</t>
-  </si>
-  <si>
-    <t>0.53</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale 1280x800 (Verify Point #64)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource 1024x768 (Verify Point #65)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path 768x1024 (Verify Point #66)</t>
-  </si>
-  <si>
-    <t>0.73</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component 375x812 (Verify Point #67)</t>
-  </si>
-  <si>
-    <t>0.37</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for sign-in-button (Verify Point #68)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for email-input (Verify Point #69)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for password-field (Verify Point #70)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for search-bar (Verify Point #71)</t>
-  </si>
-  <si>
-    <t>0.39</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated college-card (Verify Point #72)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for compare-btn (Verify Point #73)</t>
-  </si>
-  <si>
-    <t>0.47</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on profile-settings (Verify Point #74)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for ai-chat-input (Verify Point #75)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for en-US (Verify Point #76)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for hi-IN (Verify Point #77)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field ta-IN (Verify Point #78)</t>
-  </si>
-  <si>
-    <t>0.32</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to header-nav (Verify Point #79)</t>
-  </si>
-  <si>
-    <t>0.67</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution sidebar-menu (Verify Point #80)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element footer-links (Verify Point #81)</t>
-  </si>
-  <si>
-    <t>0.56</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container login-form (Verify Point #82)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter register-form (Verify Point #83)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale dashboard-grid (Verify Point #84)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource detail-page (Verify Point #85)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path fees-filter (Verify Point #86)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component nirf-sort (Verify Point #87)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for course-filter (Verify Point #88)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for state-filter (Verify Point #89)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for firebase-auth (Verify Point #90)</t>
-  </si>
-  <si>
-    <t>0.20</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for firestore-read (Verify Point #91)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #92)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for expo-router (Verify Point #93)</t>
-  </si>
-  <si>
-    <t>0.25</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on college-list (Verify Point #94)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for saved-list (Verify Point #95)</t>
-  </si>
-  <si>
-    <t>0.42</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for comparison-list (Verify Point #96)</t>
-  </si>
-  <si>
-    <t>0.63</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for chat-history (Verify Point #97)</t>
-  </si>
-  <si>
-    <t>0.87</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field avatar-upload (Verify Point #98)</t>
-  </si>
-  <si>
-    <t>0.21</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to theme-toggle (Verify Point #99)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution notification-prefs (Verify Point #100)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element session-token (Verify Point #101)</t>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for CSRF-token (Verify Point #228)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for CORS-origin (Verify Point #229)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for CSP-header (Verify Point #230)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for X-Frame-Options (Verify Point #231)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated primary-font (Verify Point #232)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for accent-color (Verify Point #233)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on glassmorphic-transparency (Verify Point #234)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for border-radius (Verify Point #235)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for bundle-size (Verify Point #236)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for first-meaningful-paint (Verify Point #237)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field time-to-interactive (Verify Point #238)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to dom-depth (Verify Point #239)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution lost-item-card (Verify Point #240)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element users-ref (Verify Point #241)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container items-ref (Verify Point #242)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter de-DE (Verify Point #243)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale fr-FR (Verify Point #244)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource ja-JP (Verify Point #245)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path pt-BR (Verify Point #246)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component it-IT (Verify Point #247)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #248)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #249)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #250)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #251)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #252)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for 375x812 (Verify Point #253)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on sign-in-button (Verify Point #254)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for email-input (Verify Point #255)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for password-field (Verify Point #256)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for search-bar (Verify Point #257)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field college-card (Verify Point #258)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to compare-btn (Verify Point #259)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution profile-settings (Verify Point #260)</t>
   </si>
   <si>
     <t>0.29</t>
   </si>
   <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container XSS-injection (Verify Point #102)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter SQL-injection (Verify Point #103)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale CSRF-token (Verify Point #104)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource CORS-origin (Verify Point #105)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path CSP-header (Verify Point #106)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component X-Frame-Options (Verify Point #107)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for primary-font (Verify Point #108)</t>
-  </si>
-  <si>
-    <t>0.96</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for accent-color (Verify Point #109)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for glassmorphic-transparency (Verify Point #110)</t>
-  </si>
-  <si>
-    <t>1.00</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for border-radius (Verify Point #111)</t>
-  </si>
-  <si>
-    <t>0.22</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated bundle-size (Verify Point #112)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for first-meaningful-paint (Verify Point #113)</t>
-  </si>
-  <si>
-    <t>0.60</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on time-to-interactive (Verify Point #114)</t>
-  </si>
-  <si>
-    <t>0.72</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for dom-depth (Verify Point #115)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for lost-item-card (Verify Point #116)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for users-ref (Verify Point #117)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field items-ref (Verify Point #118)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to de-DE (Verify Point #119)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution fr-FR (Verify Point #120)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element ja-JP (Verify Point #121)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container pt-BR (Verify Point #122)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter it-IT (Verify Point #123)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #124)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #125)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #126)</t>
-  </si>
-  <si>
-    <t>0.92</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #127)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #128)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for 375x812 (Verify Point #129)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for sign-in-button (Verify Point #130)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for email-input (Verify Point #131)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated password-field (Verify Point #132)</t>
-  </si>
-  <si>
-    <t>0.71</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for search-bar (Verify Point #133)</t>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element ai-chat-input (Verify Point #261)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container en-US (Verify Point #262)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter hi-IN (Verify Point #263)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale ta-IN (Verify Point #264)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource header-nav (Verify Point #265)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path sidebar-menu (Verify Point #266)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component footer-links (Verify Point #267)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for login-form (Verify Point #268)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for register-form (Verify Point #269)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for dashboard-grid (Verify Point #270)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for detail-page (Verify Point #271)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated fees-filter (Verify Point #272)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for nirf-sort (Verify Point #273)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on course-filter (Verify Point #274)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for state-filter (Verify Point #275)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for firebase-auth (Verify Point #276)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for firestore-read (Verify Point #277)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field groq-api (Verify Point #278)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to expo-router (Verify Point #279)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution college-list (Verify Point #280)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element saved-list (Verify Point #281)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container comparison-list (Verify Point #282)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter chat-history (Verify Point #283)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale avatar-upload (Verify Point #284)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource theme-toggle (Verify Point #285)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path notification-prefs (Verify Point #286)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component session-token (Verify Point #287)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for XSS-injection (Verify Point #288)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for SQL-injection (Verify Point #289)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for CSRF-token (Verify Point #290)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for CORS-origin (Verify Point #291)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated CSP-header (Verify Point #292)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for X-Frame-Options (Verify Point #293)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on primary-font (Verify Point #294)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for accent-color (Verify Point #295)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for glassmorphic-transparency (Verify Point #296)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for border-radius (Verify Point #297)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field bundle-size (Verify Point #298)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to first-meaningful-paint (Verify Point #299)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution time-to-interactive (Verify Point #300)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element dom-depth (Verify Point #301)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container lost-item-card (Verify Point #302)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter users-ref (Verify Point #303)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale items-ref (Verify Point #304)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource de-DE (Verify Point #305)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path fr-FR (Verify Point #306)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component ja-JP (Verify Point #307)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for pt-BR (Verify Point #308)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for it-IT (Verify Point #309)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for 1920x1080 (Verify Point #310)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for 1440x900 (Verify Point #311)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated 1280x800 (Verify Point #312)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for 1024x768 (Verify Point #313)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on 768x1024 (Verify Point #314)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for 375x812 (Verify Point #315)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for sign-in-button (Verify Point #316)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for email-input (Verify Point #317)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field password-field (Verify Point #318)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to search-bar (Verify Point #319)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution college-card (Verify Point #320)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element compare-btn (Verify Point #321)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container profile-settings (Verify Point #322)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter ai-chat-input (Verify Point #323)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale en-US (Verify Point #324)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource hi-IN (Verify Point #325)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path ta-IN (Verify Point #326)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component header-nav (Verify Point #327)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for sidebar-menu (Verify Point #328)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for footer-links (Verify Point #329)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for login-form (Verify Point #330)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for register-form (Verify Point #331)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated dashboard-grid (Verify Point #332)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for detail-page (Verify Point #333)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on fees-filter (Verify Point #334)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for nirf-sort (Verify Point #335)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for course-filter (Verify Point #336)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for state-filter (Verify Point #337)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field firebase-auth (Verify Point #338)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to firestore-read (Verify Point #339)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution groq-api (Verify Point #340)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element expo-router (Verify Point #341)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container college-list (Verify Point #342)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter saved-list (Verify Point #343)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale comparison-list (Verify Point #344)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource chat-history (Verify Point #345)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path avatar-upload (Verify Point #346)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component theme-toggle (Verify Point #347)</t>
   </si>
   <si>
     <t>0.26</t>
   </si>
   <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on college-card (Verify Point #134)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for compare-btn (Verify Point #135)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for profile-settings (Verify Point #136)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for ai-chat-input (Verify Point #137)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field en-US (Verify Point #138)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to hi-IN (Verify Point #139)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution ta-IN (Verify Point #140)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element header-nav (Verify Point #141)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container sidebar-menu (Verify Point #142)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter footer-links (Verify Point #143)</t>
-  </si>
-  <si>
-    <t>0.48</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale login-form (Verify Point #144)</t>
-  </si>
-  <si>
-    <t>0.43</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource register-form (Verify Point #145)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path dashboard-grid (Verify Point #146)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component detail-page (Verify Point #147)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for fees-filter (Verify Point #148)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for nirf-sort (Verify Point #149)</t>
-  </si>
-  <si>
-    <t>0.98</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for course-filter (Verify Point #150)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for state-filter (Verify Point #151)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated firebase-auth (Verify Point #152)</t>
-  </si>
-  <si>
-    <t>0.95</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for firestore-read (Verify Point #153)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on groq-api (Verify Point #154)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for expo-router (Verify Point #155)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for college-list (Verify Point #156)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for saved-list (Verify Point #157)</t>
-  </si>
-  <si>
-    <t>0.45</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field comparison-list (Verify Point #158)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to chat-history (Verify Point #159)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution avatar-upload (Verify Point #160)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element theme-toggle (Verify Point #161)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container notification-prefs (Verify Point #162)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter session-token (Verify Point #163)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale XSS-injection (Verify Point #164)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #165)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path CSRF-token (Verify Point #166)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component CORS-origin (Verify Point #167)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for CSP-header (Verify Point #168)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for X-Frame-Options (Verify Point #169)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for primary-font (Verify Point #170)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for accent-color (Verify Point #171)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated glassmorphic-transparency (Verify Point #172)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for border-radius (Verify Point #173)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on bundle-size (Verify Point #174)</t>
-  </si>
-  <si>
-    <t>0.86</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for first-meaningful-paint (Verify Point #175)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for time-to-interactive (Verify Point #176)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for dom-depth (Verify Point #177)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field lost-item-card (Verify Point #178)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to users-ref (Verify Point #179)</t>
-  </si>
-  <si>
-    <t>0.31</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution items-ref (Verify Point #180)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element de-DE (Verify Point #181)</t>
-  </si>
-  <si>
-    <t>0.77</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container fr-FR (Verify Point #182)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter ja-JP (Verify Point #183)</t>
-  </si>
-  <si>
-    <t>0.62</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale pt-BR (Verify Point #184)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource it-IT (Verify Point #185)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path 1920x1080 (Verify Point #186)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component 1440x900 (Verify Point #187)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for 1280x800 (Verify Point #188)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for 1024x768 (Verify Point #189)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for 768x1024 (Verify Point #190)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for 375x812 (Verify Point #191)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated sign-in-button (Verify Point #192)</t>
-  </si>
-  <si>
-    <t>0.83</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for email-input (Verify Point #193)</t>
-  </si>
-  <si>
-    <t>0.89</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on password-field (Verify Point #194)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for search-bar (Verify Point #195)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for college-card (Verify Point #196)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for compare-btn (Verify Point #197)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field profile-settings (Verify Point #198)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to ai-chat-input (Verify Point #199)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution en-US (Verify Point #200)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element hi-IN (Verify Point #201)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container ta-IN (Verify Point #202)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter header-nav (Verify Point #203)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale sidebar-menu (Verify Point #204)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource footer-links (Verify Point #205)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path login-form (Verify Point #206)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component register-form (Verify Point #207)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for dashboard-grid (Verify Point #208)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for detail-page (Verify Point #209)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for fees-filter (Verify Point #210)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for nirf-sort (Verify Point #211)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated course-filter (Verify Point #212)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for state-filter (Verify Point #213)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on firebase-auth (Verify Point #214)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for firestore-read (Verify Point #215)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for groq-api (Verify Point #216)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for expo-router (Verify Point #217)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field college-list (Verify Point #218)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to saved-list (Verify Point #219)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution comparison-list (Verify Point #220)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element chat-history (Verify Point #221)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container avatar-upload (Verify Point #222)</t>
-  </si>
-  <si>
-    <t>0.70</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter theme-toggle (Verify Point #223)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale notification-prefs (Verify Point #224)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource session-token (Verify Point #225)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path XSS-injection (Verify Point #226)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component SQL-injection (Verify Point #227)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for CSRF-token (Verify Point #228)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for CORS-origin (Verify Point #229)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for CSP-header (Verify Point #230)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for X-Frame-Options (Verify Point #231)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated primary-font (Verify Point #232)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for accent-color (Verify Point #233)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on glassmorphic-transparency (Verify Point #234)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for border-radius (Verify Point #235)</t>
-  </si>
-  <si>
-    <t>0.52</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for bundle-size (Verify Point #236)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for first-meaningful-paint (Verify Point #237)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field time-to-interactive (Verify Point #238)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to dom-depth (Verify Point #239)</t>
-  </si>
-  <si>
-    <t>0.85</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution lost-item-card (Verify Point #240)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element users-ref (Verify Point #241)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container items-ref (Verify Point #242)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter de-DE (Verify Point #243)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale fr-FR (Verify Point #244)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource ja-JP (Verify Point #245)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path pt-BR (Verify Point #246)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component it-IT (Verify Point #247)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #248)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #249)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #250)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #251)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #252)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for 375x812 (Verify Point #253)</t>
-  </si>
-  <si>
-    <t>0.61</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on sign-in-button (Verify Point #254)</t>
-  </si>
-  <si>
-    <t>0.66</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for email-input (Verify Point #255)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for password-field (Verify Point #256)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for search-bar (Verify Point #257)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field college-card (Verify Point #258)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to compare-btn (Verify Point #259)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution profile-settings (Verify Point #260)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element ai-chat-input (Verify Point #261)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container en-US (Verify Point #262)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter hi-IN (Verify Point #263)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale ta-IN (Verify Point #264)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource header-nav (Verify Point #265)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path sidebar-menu (Verify Point #266)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component footer-links (Verify Point #267)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for login-form (Verify Point #268)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for register-form (Verify Point #269)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for dashboard-grid (Verify Point #270)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for detail-page (Verify Point #271)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated fees-filter (Verify Point #272)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for nirf-sort (Verify Point #273)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on course-filter (Verify Point #274)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for state-filter (Verify Point #275)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for firebase-auth (Verify Point #276)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for firestore-read (Verify Point #277)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field groq-api (Verify Point #278)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to expo-router (Verify Point #279)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution college-list (Verify Point #280)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element saved-list (Verify Point #281)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container comparison-list (Verify Point #282)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter chat-history (Verify Point #283)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale avatar-upload (Verify Point #284)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource theme-toggle (Verify Point #285)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path notification-prefs (Verify Point #286)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component session-token (Verify Point #287)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for XSS-injection (Verify Point #288)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for SQL-injection (Verify Point #289)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for CSRF-token (Verify Point #290)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for CORS-origin (Verify Point #291)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated CSP-header (Verify Point #292)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for X-Frame-Options (Verify Point #293)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on primary-font (Verify Point #294)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for accent-color (Verify Point #295)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for glassmorphic-transparency (Verify Point #296)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for border-radius (Verify Point #297)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field bundle-size (Verify Point #298)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to first-meaningful-paint (Verify Point #299)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution time-to-interactive (Verify Point #300)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element dom-depth (Verify Point #301)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container lost-item-card (Verify Point #302)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter users-ref (Verify Point #303)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale items-ref (Verify Point #304)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource de-DE (Verify Point #305)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path fr-FR (Verify Point #306)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component ja-JP (Verify Point #307)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for pt-BR (Verify Point #308)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for it-IT (Verify Point #309)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for 1920x1080 (Verify Point #310)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for 1440x900 (Verify Point #311)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated 1280x800 (Verify Point #312)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for 1024x768 (Verify Point #313)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on 768x1024 (Verify Point #314)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for 375x812 (Verify Point #315)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for sign-in-button (Verify Point #316)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for email-input (Verify Point #317)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field password-field (Verify Point #318)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to search-bar (Verify Point #319)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution college-card (Verify Point #320)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element compare-btn (Verify Point #321)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container profile-settings (Verify Point #322)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter ai-chat-input (Verify Point #323)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale en-US (Verify Point #324)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource hi-IN (Verify Point #325)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path ta-IN (Verify Point #326)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component header-nav (Verify Point #327)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for sidebar-menu (Verify Point #328)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for footer-links (Verify Point #329)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for login-form (Verify Point #330)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for register-form (Verify Point #331)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated dashboard-grid (Verify Point #332)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for detail-page (Verify Point #333)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on fees-filter (Verify Point #334)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for nirf-sort (Verify Point #335)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for course-filter (Verify Point #336)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for state-filter (Verify Point #337)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field firebase-auth (Verify Point #338)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to firestore-read (Verify Point #339)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution groq-api (Verify Point #340)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element expo-router (Verify Point #341)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container college-list (Verify Point #342)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter saved-list (Verify Point #343)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale comparison-list (Verify Point #344)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource chat-history (Verify Point #345)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path avatar-upload (Verify Point #346)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component theme-toggle (Verify Point #347)</t>
-  </si>
-  <si>
     <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for notification-prefs (Verify Point #348)</t>
   </si>
   <si>
@@ -1490,9 +1490,6 @@
     <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element search-bar (Verify Point #381)</t>
   </si>
   <si>
-    <t>0.35</t>
-  </si>
-  <si>
     <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container college-card (Verify Point #382)</t>
   </si>
   <si>
@@ -1556,13 +1553,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>18</t>
+    <t>19</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 14:30:52 UTC</t>
+    <t>2026-06-23 14:43:49 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -1574,7 +1571,7 @@
     <t>Commit</t>
   </si>
   <si>
-    <t>04fd2d2</t>
+    <t>af530d5</t>
   </si>
   <si>
     <t>Total</t>
@@ -2153,10 +2150,10 @@
         <v>6</v>
       </c>
       <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
         <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2164,16 +2161,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
         <v>35</v>
-      </c>
-      <c r="E11" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2181,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
         <v>37</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" t="s">
-        <v>38</v>
       </c>
       <c r="E12" t="s">
         <v>27</v>
@@ -2198,13 +2195,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
         <v>39</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" t="s">
-        <v>40</v>
       </c>
       <c r="E13" t="s">
         <v>27</v>
@@ -2215,13 +2212,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
         <v>41</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" t="s">
-        <v>42</v>
       </c>
       <c r="E14" t="s">
         <v>27</v>
@@ -2232,13 +2229,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" t="s">
         <v>43</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" t="s">
-        <v>44</v>
       </c>
       <c r="E15" t="s">
         <v>27</v>
@@ -2249,13 +2246,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" t="s">
         <v>45</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" t="s">
-        <v>46</v>
       </c>
       <c r="E16" t="s">
         <v>27</v>
@@ -2266,13 +2263,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" t="s">
         <v>47</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" t="s">
-        <v>48</v>
       </c>
       <c r="E17" t="s">
         <v>27</v>
@@ -2283,13 +2280,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E18" t="s">
         <v>27</v>
@@ -2300,13 +2297,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E19" t="s">
         <v>27</v>
@@ -2317,13 +2314,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E20" t="s">
         <v>27</v>
@@ -2334,13 +2331,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E21" t="s">
         <v>27</v>
@@ -2351,13 +2348,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
         <v>27</v>
@@ -2368,13 +2365,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" t="s">
         <v>27</v>
@@ -2385,13 +2382,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E24" t="s">
         <v>27</v>
@@ -2402,13 +2399,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E25" t="s">
         <v>27</v>
@@ -2419,13 +2416,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E26" t="s">
         <v>27</v>
@@ -2436,13 +2433,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E27" t="s">
         <v>27</v>
@@ -2453,13 +2450,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E28" t="s">
         <v>27</v>
@@ -2470,13 +2467,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E29" t="s">
         <v>27</v>
@@ -2487,13 +2484,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E30" t="s">
         <v>27</v>
@@ -2504,13 +2501,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="E31" t="s">
         <v>27</v>
@@ -2521,13 +2518,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="E32" t="s">
         <v>27</v>
@@ -2538,13 +2535,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D33" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E33" t="s">
         <v>27</v>
@@ -2555,13 +2552,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D34" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E34" t="s">
         <v>27</v>
@@ -2572,13 +2569,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E35" t="s">
         <v>27</v>
@@ -2589,13 +2586,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="E36" t="s">
         <v>27</v>
@@ -2606,13 +2603,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E37" t="s">
         <v>27</v>
@@ -2623,13 +2620,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D38" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E38" t="s">
         <v>27</v>
@@ -2640,13 +2637,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="E39" t="s">
         <v>27</v>
@@ -2657,13 +2654,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E40" t="s">
         <v>27</v>
@@ -2674,13 +2671,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D41" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="E41" t="s">
         <v>27</v>
@@ -2691,13 +2688,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D42" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E42" t="s">
         <v>27</v>
@@ -2708,13 +2705,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="E43" t="s">
         <v>27</v>
@@ -2725,13 +2722,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="E44" t="s">
         <v>27</v>
@@ -2742,13 +2739,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E45" t="s">
         <v>27</v>
@@ -2759,13 +2756,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E46" t="s">
         <v>27</v>
@@ -2776,13 +2773,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="E47" t="s">
         <v>27</v>
@@ -2793,13 +2790,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="E48" t="s">
         <v>27</v>
@@ -2810,13 +2807,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E49" t="s">
         <v>27</v>
@@ -2827,13 +2824,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E50" t="s">
         <v>27</v>
@@ -2844,13 +2841,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D51" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="E51" t="s">
         <v>27</v>
@@ -2861,13 +2858,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="E52" t="s">
         <v>27</v>
@@ -2878,13 +2875,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="E53" t="s">
         <v>27</v>
@@ -2895,13 +2892,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E54" t="s">
         <v>27</v>
@@ -2912,13 +2909,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D55" t="s">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="E55" t="s">
         <v>27</v>
@@ -2929,13 +2926,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D56" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E56" t="s">
         <v>27</v>
@@ -2946,13 +2943,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D57" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E57" t="s">
         <v>27</v>
@@ -2963,7 +2960,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>25</v>
@@ -2980,13 +2977,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D59" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="E59" t="s">
         <v>27</v>
@@ -2997,13 +2994,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D60" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="E60" t="s">
         <v>27</v>
@@ -3014,13 +3011,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E61" t="s">
         <v>27</v>
@@ -3031,13 +3028,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D62" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E62" t="s">
         <v>27</v>
@@ -3048,13 +3045,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D63" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E63" t="s">
         <v>27</v>
@@ -3065,13 +3062,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D64" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="E64" t="s">
         <v>27</v>
@@ -3082,13 +3079,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="E65" t="s">
         <v>27</v>
@@ -3099,13 +3096,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D66" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E66" t="s">
         <v>27</v>
@@ -3116,13 +3113,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D67" t="s">
-        <v>62</v>
+        <v>128</v>
       </c>
       <c r="E67" t="s">
         <v>27</v>
@@ -3133,13 +3130,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D68" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="E68" t="s">
         <v>27</v>
@@ -3150,13 +3147,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D69" t="s">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="E69" t="s">
         <v>27</v>
@@ -3167,13 +3164,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D70" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="E70" t="s">
         <v>27</v>
@@ -3184,13 +3181,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D71" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="E71" t="s">
         <v>27</v>
@@ -3201,13 +3198,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D72" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="E72" t="s">
         <v>27</v>
@@ -3218,13 +3215,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D73" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E73" t="s">
         <v>27</v>
@@ -3235,13 +3232,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D74" t="s">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="E74" t="s">
         <v>27</v>
@@ -3252,13 +3249,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D75" t="s">
-        <v>146</v>
+        <v>58</v>
       </c>
       <c r="E75" t="s">
         <v>27</v>
@@ -3269,13 +3266,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D76" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="E76" t="s">
         <v>27</v>
@@ -3286,13 +3283,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D77" t="s">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E77" t="s">
         <v>27</v>
@@ -3303,13 +3300,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="E78" t="s">
         <v>27</v>
@@ -3320,13 +3317,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D79" t="s">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="E79" t="s">
         <v>27</v>
@@ -3337,13 +3334,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D80" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E80" t="s">
         <v>27</v>
@@ -3354,13 +3351,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D81" t="s">
-        <v>154</v>
+        <v>102</v>
       </c>
       <c r="E81" t="s">
         <v>27</v>
@@ -3371,13 +3368,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D82" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="E82" t="s">
         <v>27</v>
@@ -3388,13 +3385,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D83" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E83" t="s">
         <v>27</v>
@@ -3405,13 +3402,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D84" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E84" t="s">
         <v>27</v>
@@ -3422,13 +3419,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D85" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="E85" t="s">
         <v>27</v>
@@ -3439,13 +3436,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D86" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="E86" t="s">
         <v>27</v>
@@ -3456,13 +3453,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D87" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="E87" t="s">
         <v>27</v>
@@ -3473,13 +3470,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D88" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E88" t="s">
         <v>27</v>
@@ -3490,13 +3487,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D89" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="E89" t="s">
         <v>27</v>
@@ -3507,13 +3504,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D90" t="s">
-        <v>114</v>
+        <v>160</v>
       </c>
       <c r="E90" t="s">
         <v>27</v>
@@ -3524,13 +3521,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D91" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="E91" t="s">
         <v>27</v>
@@ -3541,13 +3538,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D92" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E92" t="s">
         <v>27</v>
@@ -3558,13 +3555,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D93" t="s">
-        <v>71</v>
+        <v>165</v>
       </c>
       <c r="E93" t="s">
         <v>27</v>
@@ -3575,13 +3572,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D94" t="s">
-        <v>104</v>
+        <v>167</v>
       </c>
       <c r="E94" t="s">
         <v>27</v>
@@ -3592,13 +3589,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D95" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="E95" t="s">
         <v>27</v>
@@ -3609,13 +3606,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D96" t="s">
-        <v>62</v>
+        <v>170</v>
       </c>
       <c r="E96" t="s">
         <v>27</v>
@@ -3626,13 +3623,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D97" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E97" t="s">
         <v>27</v>
@@ -3643,13 +3640,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D98" t="s">
-        <v>176</v>
+        <v>43</v>
       </c>
       <c r="E98" t="s">
         <v>27</v>
@@ -3660,13 +3657,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D99" t="s">
-        <v>178</v>
+        <v>100</v>
       </c>
       <c r="E99" t="s">
         <v>27</v>
@@ -3677,13 +3674,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D100" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E100" t="s">
         <v>27</v>
@@ -3694,13 +3691,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="E101" t="s">
         <v>27</v>
@@ -3711,13 +3708,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D102" t="s">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="E102" t="s">
         <v>27</v>
@@ -3728,13 +3725,13 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D103" t="s">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="E103" t="s">
         <v>27</v>
@@ -3745,13 +3742,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D104" t="s">
-        <v>132</v>
+        <v>45</v>
       </c>
       <c r="E104" t="s">
         <v>27</v>
@@ -3762,7 +3759,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>25</v>
@@ -3779,13 +3776,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D106" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E106" t="s">
         <v>27</v>
@@ -3796,13 +3793,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D107" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="E107" t="s">
         <v>27</v>
@@ -3813,13 +3810,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D108" t="s">
-        <v>38</v>
+        <v>188</v>
       </c>
       <c r="E108" t="s">
         <v>27</v>
@@ -3830,13 +3827,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
+        <v>189</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D109" t="s">
         <v>190</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D109" t="s">
-        <v>118</v>
       </c>
       <c r="E109" t="s">
         <v>27</v>
@@ -3853,7 +3850,7 @@
         <v>25</v>
       </c>
       <c r="D110" t="s">
-        <v>192</v>
+        <v>62</v>
       </c>
       <c r="E110" t="s">
         <v>27</v>
@@ -3864,13 +3861,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
+        <v>192</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D111" t="s">
         <v>193</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D111" t="s">
-        <v>44</v>
       </c>
       <c r="E111" t="s">
         <v>27</v>
@@ -3904,7 +3901,7 @@
         <v>25</v>
       </c>
       <c r="D113" t="s">
-        <v>197</v>
+        <v>114</v>
       </c>
       <c r="E113" t="s">
         <v>27</v>
@@ -3915,13 +3912,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D114" t="s">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="E114" t="s">
         <v>27</v>
@@ -3932,13 +3929,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D115" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="E115" t="s">
         <v>27</v>
@@ -3949,13 +3946,13 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D116" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="E116" t="s">
         <v>27</v>
@@ -3966,13 +3963,13 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D117" t="s">
-        <v>71</v>
+        <v>201</v>
       </c>
       <c r="E117" t="s">
         <v>27</v>
@@ -3983,13 +3980,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D118" t="s">
-        <v>64</v>
+        <v>156</v>
       </c>
       <c r="E118" t="s">
         <v>27</v>
@@ -4000,13 +3997,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D119" t="s">
-        <v>146</v>
+        <v>93</v>
       </c>
       <c r="E119" t="s">
         <v>27</v>
@@ -4017,13 +4014,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D120" t="s">
-        <v>40</v>
+        <v>205</v>
       </c>
       <c r="E120" t="s">
         <v>27</v>
@@ -4034,13 +4031,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D121" t="s">
-        <v>192</v>
+        <v>86</v>
       </c>
       <c r="E121" t="s">
         <v>27</v>
@@ -4051,13 +4048,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D122" t="s">
-        <v>64</v>
+        <v>149</v>
       </c>
       <c r="E122" t="s">
         <v>27</v>
@@ -4068,13 +4065,13 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D123" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
       <c r="E123" t="s">
         <v>27</v>
@@ -4085,13 +4082,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D124" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="E124" t="s">
         <v>27</v>
@@ -4102,13 +4099,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D125" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="E125" t="s">
         <v>27</v>
@@ -4119,13 +4116,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
+        <v>211</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D126" t="s">
         <v>212</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D126" t="s">
-        <v>46</v>
       </c>
       <c r="E126" t="s">
         <v>27</v>
@@ -4142,7 +4139,7 @@
         <v>25</v>
       </c>
       <c r="D127" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="E127" t="s">
         <v>27</v>
@@ -4176,7 +4173,7 @@
         <v>25</v>
       </c>
       <c r="D129" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="E129" t="s">
         <v>27</v>
@@ -4193,7 +4190,7 @@
         <v>25</v>
       </c>
       <c r="D130" t="s">
-        <v>118</v>
+        <v>218</v>
       </c>
       <c r="E130" t="s">
         <v>27</v>
@@ -4204,13 +4201,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D131" t="s">
-        <v>108</v>
+        <v>220</v>
       </c>
       <c r="E131" t="s">
         <v>27</v>
@@ -4221,13 +4218,13 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D132" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="E132" t="s">
         <v>27</v>
@@ -4238,13 +4235,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D133" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E133" t="s">
         <v>27</v>
@@ -4255,13 +4252,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D134" t="s">
-        <v>222</v>
+        <v>153</v>
       </c>
       <c r="E134" t="s">
         <v>27</v>
@@ -4272,13 +4269,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D135" t="s">
-        <v>224</v>
+        <v>86</v>
       </c>
       <c r="E135" t="s">
         <v>27</v>
@@ -4295,7 +4292,7 @@
         <v>25</v>
       </c>
       <c r="D136" t="s">
-        <v>60</v>
+        <v>195</v>
       </c>
       <c r="E136" t="s">
         <v>27</v>
@@ -4312,7 +4309,7 @@
         <v>25</v>
       </c>
       <c r="D137" t="s">
-        <v>118</v>
+        <v>227</v>
       </c>
       <c r="E137" t="s">
         <v>27</v>
@@ -4323,13 +4320,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D138" t="s">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="E138" t="s">
         <v>27</v>
@@ -4340,13 +4337,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D139" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="E139" t="s">
         <v>27</v>
@@ -4357,13 +4354,13 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D140" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="E140" t="s">
         <v>27</v>
@@ -4374,13 +4371,13 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D141" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="E141" t="s">
         <v>27</v>
@@ -4391,13 +4388,13 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D142" t="s">
-        <v>157</v>
+        <v>233</v>
       </c>
       <c r="E142" t="s">
         <v>27</v>
@@ -4408,13 +4405,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D143" t="s">
-        <v>79</v>
+        <v>235</v>
       </c>
       <c r="E143" t="s">
         <v>27</v>
@@ -4425,13 +4422,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D144" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="E144" t="s">
         <v>27</v>
@@ -4442,13 +4439,13 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D145" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E145" t="s">
         <v>27</v>
@@ -4459,13 +4456,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D146" t="s">
-        <v>237</v>
+        <v>112</v>
       </c>
       <c r="E146" t="s">
         <v>27</v>
@@ -4476,13 +4473,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D147" t="s">
-        <v>167</v>
+        <v>86</v>
       </c>
       <c r="E147" t="s">
         <v>27</v>
@@ -4493,13 +4490,13 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D148" t="s">
-        <v>44</v>
+        <v>149</v>
       </c>
       <c r="E148" t="s">
         <v>27</v>
@@ -4510,13 +4507,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D149" t="s">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="E149" t="s">
         <v>27</v>
@@ -4527,13 +4524,13 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D150" t="s">
-        <v>69</v>
+        <v>141</v>
       </c>
       <c r="E150" t="s">
         <v>27</v>
@@ -4544,13 +4541,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D151" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E151" t="s">
         <v>27</v>
@@ -4561,13 +4558,13 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D152" t="s">
-        <v>184</v>
+        <v>245</v>
       </c>
       <c r="E152" t="s">
         <v>27</v>
@@ -4578,13 +4575,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D153" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E153" t="s">
         <v>27</v>
@@ -4595,13 +4592,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D154" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E154" t="s">
         <v>27</v>
@@ -4612,13 +4609,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D155" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="E155" t="s">
         <v>27</v>
@@ -4629,13 +4626,13 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D156" t="s">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="E156" t="s">
         <v>27</v>
@@ -4646,13 +4643,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D157" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="E157" t="s">
         <v>27</v>
@@ -4663,7 +4660,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>25</v>
@@ -4680,13 +4677,13 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D159" t="s">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="E159" t="s">
         <v>27</v>
@@ -4697,13 +4694,13 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D160" t="s">
-        <v>114</v>
+        <v>256</v>
       </c>
       <c r="E160" t="s">
         <v>27</v>
@@ -4714,13 +4711,13 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D161" t="s">
-        <v>56</v>
+        <v>220</v>
       </c>
       <c r="E161" t="s">
         <v>27</v>
@@ -4731,13 +4728,13 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D162" t="s">
-        <v>44</v>
+        <v>259</v>
       </c>
       <c r="E162" t="s">
         <v>27</v>
@@ -4748,13 +4745,13 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D163" t="s">
-        <v>171</v>
+        <v>107</v>
       </c>
       <c r="E163" t="s">
         <v>27</v>
@@ -4765,13 +4762,13 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D164" t="s">
-        <v>96</v>
+        <v>235</v>
       </c>
       <c r="E164" t="s">
         <v>27</v>
@@ -4782,13 +4779,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D165" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="E165" t="s">
         <v>27</v>
@@ -4799,13 +4796,13 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D166" t="s">
-        <v>176</v>
+        <v>215</v>
       </c>
       <c r="E166" t="s">
         <v>27</v>
@@ -4816,13 +4813,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D167" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="E167" t="s">
         <v>27</v>
@@ -4833,13 +4830,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D168" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="E168" t="s">
         <v>27</v>
@@ -4850,13 +4847,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D169" t="s">
-        <v>224</v>
+        <v>135</v>
       </c>
       <c r="E169" t="s">
         <v>27</v>
@@ -4867,13 +4864,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D170" t="s">
-        <v>102</v>
+        <v>268</v>
       </c>
       <c r="E170" t="s">
         <v>27</v>
@@ -4884,13 +4881,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D171" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="E171" t="s">
         <v>27</v>
@@ -4901,13 +4898,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D172" t="s">
-        <v>44</v>
+        <v>271</v>
       </c>
       <c r="E172" t="s">
         <v>27</v>
@@ -4918,13 +4915,13 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D173" t="s">
-        <v>143</v>
+        <v>100</v>
       </c>
       <c r="E173" t="s">
         <v>27</v>
@@ -4935,13 +4932,13 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D174" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E174" t="s">
         <v>27</v>
@@ -4952,13 +4949,13 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D175" t="s">
-        <v>167</v>
+        <v>75</v>
       </c>
       <c r="E175" t="s">
         <v>27</v>
@@ -4969,13 +4966,13 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D176" t="s">
-        <v>271</v>
+        <v>149</v>
       </c>
       <c r="E176" t="s">
         <v>27</v>
@@ -4986,13 +4983,13 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D177" t="s">
-        <v>235</v>
+        <v>188</v>
       </c>
       <c r="E177" t="s">
         <v>27</v>
@@ -5003,13 +5000,13 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D178" t="s">
-        <v>146</v>
+        <v>256</v>
       </c>
       <c r="E178" t="s">
         <v>27</v>
@@ -5020,13 +5017,13 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D179" t="s">
-        <v>120</v>
+        <v>215</v>
       </c>
       <c r="E179" t="s">
         <v>27</v>
@@ -5037,13 +5034,13 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D180" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="E180" t="s">
         <v>27</v>
@@ -5054,13 +5051,13 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D181" t="s">
-        <v>277</v>
+        <v>245</v>
       </c>
       <c r="E181" t="s">
         <v>27</v>
@@ -5071,13 +5068,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D182" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="E182" t="s">
         <v>27</v>
@@ -5088,13 +5085,13 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D183" t="s">
-        <v>280</v>
+        <v>105</v>
       </c>
       <c r="E183" t="s">
         <v>27</v>
@@ -5105,13 +5102,13 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D184" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="E184" t="s">
         <v>27</v>
@@ -5122,13 +5119,13 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D185" t="s">
-        <v>283</v>
+        <v>190</v>
       </c>
       <c r="E185" t="s">
         <v>27</v>
@@ -5139,13 +5136,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D186" t="s">
-        <v>215</v>
+        <v>95</v>
       </c>
       <c r="E186" t="s">
         <v>27</v>
@@ -5156,13 +5153,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D187" t="s">
-        <v>54</v>
+        <v>190</v>
       </c>
       <c r="E187" t="s">
         <v>27</v>
@@ -5173,13 +5170,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D188" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="E188" t="s">
         <v>27</v>
@@ -5190,13 +5187,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D189" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="E189" t="s">
         <v>27</v>
@@ -5207,13 +5204,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D190" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="E190" t="s">
         <v>27</v>
@@ -5224,13 +5221,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D191" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E191" t="s">
         <v>27</v>
@@ -5241,13 +5238,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D192" t="s">
-        <v>108</v>
+        <v>184</v>
       </c>
       <c r="E192" t="s">
         <v>27</v>
@@ -5258,13 +5255,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D193" t="s">
-        <v>102</v>
+        <v>293</v>
       </c>
       <c r="E193" t="s">
         <v>27</v>
@@ -5275,13 +5272,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D194" t="s">
-        <v>293</v>
+        <v>178</v>
       </c>
       <c r="E194" t="s">
         <v>27</v>
@@ -5292,13 +5289,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D195" t="s">
-        <v>295</v>
+        <v>50</v>
       </c>
       <c r="E195" t="s">
         <v>27</v>
@@ -5315,7 +5312,7 @@
         <v>25</v>
       </c>
       <c r="D196" t="s">
-        <v>116</v>
+        <v>271</v>
       </c>
       <c r="E196" t="s">
         <v>27</v>
@@ -5332,7 +5329,7 @@
         <v>25</v>
       </c>
       <c r="D197" t="s">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="E197" t="s">
         <v>27</v>
@@ -5349,7 +5346,7 @@
         <v>25</v>
       </c>
       <c r="D198" t="s">
-        <v>89</v>
+        <v>293</v>
       </c>
       <c r="E198" t="s">
         <v>27</v>
@@ -5366,7 +5363,7 @@
         <v>25</v>
       </c>
       <c r="D199" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="E199" t="s">
         <v>27</v>
@@ -5383,7 +5380,7 @@
         <v>25</v>
       </c>
       <c r="D200" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E200" t="s">
         <v>27</v>
@@ -5400,7 +5397,7 @@
         <v>25</v>
       </c>
       <c r="D201" t="s">
-        <v>235</v>
+        <v>45</v>
       </c>
       <c r="E201" t="s">
         <v>27</v>
@@ -5417,7 +5414,7 @@
         <v>25</v>
       </c>
       <c r="D202" t="s">
-        <v>167</v>
+        <v>64</v>
       </c>
       <c r="E202" t="s">
         <v>27</v>
@@ -5434,7 +5431,7 @@
         <v>25</v>
       </c>
       <c r="D203" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="E203" t="s">
         <v>27</v>
@@ -5451,7 +5448,7 @@
         <v>25</v>
       </c>
       <c r="D204" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="E204" t="s">
         <v>27</v>
@@ -5468,7 +5465,7 @@
         <v>25</v>
       </c>
       <c r="D205" t="s">
-        <v>48</v>
+        <v>306</v>
       </c>
       <c r="E205" t="s">
         <v>27</v>
@@ -5479,13 +5476,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D206" t="s">
-        <v>73</v>
+        <v>172</v>
       </c>
       <c r="E206" t="s">
         <v>27</v>
@@ -5496,13 +5493,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D207" t="s">
-        <v>215</v>
+        <v>62</v>
       </c>
       <c r="E207" t="s">
         <v>27</v>
@@ -5513,13 +5510,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D208" t="s">
-        <v>197</v>
+        <v>62</v>
       </c>
       <c r="E208" t="s">
         <v>27</v>
@@ -5530,13 +5527,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D209" t="s">
-        <v>108</v>
+        <v>245</v>
       </c>
       <c r="E209" t="s">
         <v>27</v>
@@ -5547,13 +5544,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D210" t="s">
-        <v>50</v>
+        <v>149</v>
       </c>
       <c r="E210" t="s">
         <v>27</v>
@@ -5564,13 +5561,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D211" t="s">
-        <v>85</v>
+        <v>178</v>
       </c>
       <c r="E211" t="s">
         <v>27</v>
@@ -5581,13 +5578,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D212" t="s">
-        <v>280</v>
+        <v>212</v>
       </c>
       <c r="E212" t="s">
         <v>27</v>
@@ -5598,13 +5595,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D213" t="s">
-        <v>50</v>
+        <v>201</v>
       </c>
       <c r="E213" t="s">
         <v>27</v>
@@ -5615,13 +5612,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D214" t="s">
-        <v>118</v>
+        <v>268</v>
       </c>
       <c r="E214" t="s">
         <v>27</v>
@@ -5632,13 +5629,13 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D215" t="s">
-        <v>224</v>
+        <v>306</v>
       </c>
       <c r="E215" t="s">
         <v>27</v>
@@ -5649,7 +5646,7 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>25</v>
@@ -5666,13 +5663,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D217" t="s">
-        <v>235</v>
+        <v>167</v>
       </c>
       <c r="E217" t="s">
         <v>27</v>
@@ -5683,13 +5680,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D218" t="s">
-        <v>293</v>
+        <v>233</v>
       </c>
       <c r="E218" t="s">
         <v>27</v>
@@ -5700,13 +5697,13 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D219" t="s">
-        <v>100</v>
+        <v>321</v>
       </c>
       <c r="E219" t="s">
         <v>27</v>
@@ -5717,13 +5714,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D220" t="s">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="E220" t="s">
         <v>27</v>
@@ -5734,13 +5731,13 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D221" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="E221" t="s">
         <v>27</v>
@@ -5751,13 +5748,13 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D222" t="s">
-        <v>277</v>
+        <v>43</v>
       </c>
       <c r="E222" t="s">
         <v>27</v>
@@ -5768,13 +5765,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D223" t="s">
-        <v>132</v>
+        <v>259</v>
       </c>
       <c r="E223" t="s">
         <v>27</v>
@@ -5785,13 +5782,13 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D224" t="s">
-        <v>325</v>
+        <v>77</v>
       </c>
       <c r="E224" t="s">
         <v>27</v>
@@ -5802,13 +5799,13 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D225" t="s">
-        <v>60</v>
+        <v>184</v>
       </c>
       <c r="E225" t="s">
         <v>27</v>
@@ -5819,13 +5816,13 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D226" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E226" t="s">
         <v>27</v>
@@ -5836,13 +5833,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D227" t="s">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="E227" t="s">
         <v>27</v>
@@ -5853,13 +5850,13 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D228" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="E228" t="s">
         <v>27</v>
@@ -5870,13 +5867,13 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D229" t="s">
-        <v>136</v>
+        <v>332</v>
       </c>
       <c r="E229" t="s">
         <v>27</v>
@@ -5887,13 +5884,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D230" t="s">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="E230" t="s">
         <v>27</v>
@@ -5904,13 +5901,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D231" t="s">
-        <v>192</v>
+        <v>227</v>
       </c>
       <c r="E231" t="s">
         <v>27</v>
@@ -5921,13 +5918,13 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D232" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="E232" t="s">
         <v>27</v>
@@ -5938,13 +5935,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D233" t="s">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E233" t="s">
         <v>27</v>
@@ -5955,13 +5952,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D234" t="s">
-        <v>222</v>
+        <v>160</v>
       </c>
       <c r="E234" t="s">
         <v>27</v>
@@ -5972,13 +5969,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D235" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="E235" t="s">
         <v>27</v>
@@ -5989,13 +5986,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D236" t="s">
-        <v>54</v>
+        <v>176</v>
       </c>
       <c r="E236" t="s">
         <v>27</v>
@@ -6006,13 +6003,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D237" t="s">
-        <v>339</v>
+        <v>227</v>
       </c>
       <c r="E237" t="s">
         <v>27</v>
@@ -6023,13 +6020,13 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D238" t="s">
-        <v>124</v>
+        <v>245</v>
       </c>
       <c r="E238" t="s">
         <v>27</v>
@@ -6040,13 +6037,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D239" t="s">
-        <v>293</v>
+        <v>66</v>
       </c>
       <c r="E239" t="s">
         <v>27</v>
@@ -6057,13 +6054,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D240" t="s">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="E240" t="s">
         <v>27</v>
@@ -6074,13 +6071,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D241" t="s">
-        <v>344</v>
+        <v>128</v>
       </c>
       <c r="E241" t="s">
         <v>27</v>
@@ -6097,7 +6094,7 @@
         <v>25</v>
       </c>
       <c r="D242" t="s">
-        <v>146</v>
+        <v>39</v>
       </c>
       <c r="E242" t="s">
         <v>27</v>
@@ -6114,7 +6111,7 @@
         <v>25</v>
       </c>
       <c r="D243" t="s">
-        <v>114</v>
+        <v>271</v>
       </c>
       <c r="E243" t="s">
         <v>27</v>
@@ -6131,7 +6128,7 @@
         <v>25</v>
       </c>
       <c r="D244" t="s">
-        <v>280</v>
+        <v>43</v>
       </c>
       <c r="E244" t="s">
         <v>27</v>
@@ -6148,7 +6145,7 @@
         <v>25</v>
       </c>
       <c r="D245" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="E245" t="s">
         <v>27</v>
@@ -6165,7 +6162,7 @@
         <v>25</v>
       </c>
       <c r="D246" t="s">
-        <v>178</v>
+        <v>256</v>
       </c>
       <c r="E246" t="s">
         <v>27</v>
@@ -6182,7 +6179,7 @@
         <v>25</v>
       </c>
       <c r="D247" t="s">
-        <v>126</v>
+        <v>245</v>
       </c>
       <c r="E247" t="s">
         <v>27</v>
@@ -6199,7 +6196,7 @@
         <v>25</v>
       </c>
       <c r="D248" t="s">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="E248" t="s">
         <v>27</v>
@@ -6216,7 +6213,7 @@
         <v>25</v>
       </c>
       <c r="D249" t="s">
-        <v>94</v>
+        <v>306</v>
       </c>
       <c r="E249" t="s">
         <v>27</v>
@@ -6233,7 +6230,7 @@
         <v>25</v>
       </c>
       <c r="D250" t="s">
-        <v>271</v>
+        <v>135</v>
       </c>
       <c r="E250" t="s">
         <v>27</v>
@@ -6250,7 +6247,7 @@
         <v>25</v>
       </c>
       <c r="D251" t="s">
-        <v>143</v>
+        <v>321</v>
       </c>
       <c r="E251" t="s">
         <v>27</v>
@@ -6267,7 +6264,7 @@
         <v>25</v>
       </c>
       <c r="D252" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E252" t="s">
         <v>27</v>
@@ -6284,7 +6281,7 @@
         <v>25</v>
       </c>
       <c r="D253" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="E253" t="s">
         <v>27</v>
@@ -6301,7 +6298,7 @@
         <v>25</v>
       </c>
       <c r="D254" t="s">
-        <v>42</v>
+        <v>220</v>
       </c>
       <c r="E254" t="s">
         <v>27</v>
@@ -6318,7 +6315,7 @@
         <v>25</v>
       </c>
       <c r="D255" t="s">
-        <v>359</v>
+        <v>256</v>
       </c>
       <c r="E255" t="s">
         <v>27</v>
@@ -6329,13 +6326,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D256" t="s">
-        <v>361</v>
+        <v>306</v>
       </c>
       <c r="E256" t="s">
         <v>27</v>
@@ -6346,13 +6343,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D257" t="s">
-        <v>40</v>
+        <v>201</v>
       </c>
       <c r="E257" t="s">
         <v>27</v>
@@ -6363,13 +6360,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D258" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="E258" t="s">
         <v>27</v>
@@ -6380,13 +6377,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D259" t="s">
-        <v>146</v>
+        <v>64</v>
       </c>
       <c r="E259" t="s">
         <v>27</v>
@@ -6397,13 +6394,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D260" t="s">
-        <v>171</v>
+        <v>249</v>
       </c>
       <c r="E260" t="s">
         <v>27</v>
@@ -6414,13 +6411,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D261" t="s">
-        <v>344</v>
+        <v>195</v>
       </c>
       <c r="E261" t="s">
         <v>27</v>
@@ -6431,13 +6428,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D262" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="E262" t="s">
         <v>27</v>
@@ -6448,13 +6445,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D263" t="s">
-        <v>361</v>
+        <v>256</v>
       </c>
       <c r="E263" t="s">
         <v>27</v>
@@ -6465,13 +6462,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D264" t="s">
-        <v>40</v>
+        <v>188</v>
       </c>
       <c r="E264" t="s">
         <v>27</v>
@@ -6482,13 +6479,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D265" t="s">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="E265" t="s">
         <v>27</v>
@@ -6499,13 +6496,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D266" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E266" t="s">
         <v>27</v>
@@ -6516,13 +6513,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D267" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="E267" t="s">
         <v>27</v>
@@ -6533,13 +6530,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D268" t="s">
-        <v>361</v>
+        <v>201</v>
       </c>
       <c r="E268" t="s">
         <v>27</v>
@@ -6550,13 +6547,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D269" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="E269" t="s">
         <v>27</v>
@@ -6567,13 +6564,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D270" t="s">
-        <v>253</v>
+        <v>47</v>
       </c>
       <c r="E270" t="s">
         <v>27</v>
@@ -6584,13 +6581,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D271" t="s">
-        <v>42</v>
+        <v>184</v>
       </c>
       <c r="E271" t="s">
         <v>27</v>
@@ -6601,13 +6598,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D272" t="s">
-        <v>58</v>
+        <v>293</v>
       </c>
       <c r="E272" t="s">
         <v>27</v>
@@ -6618,13 +6615,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D273" t="s">
-        <v>73</v>
+        <v>218</v>
       </c>
       <c r="E273" t="s">
         <v>27</v>
@@ -6635,13 +6632,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D274" t="s">
-        <v>71</v>
+        <v>165</v>
       </c>
       <c r="E274" t="s">
         <v>27</v>
@@ -6652,13 +6649,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D275" t="s">
-        <v>344</v>
+        <v>93</v>
       </c>
       <c r="E275" t="s">
         <v>27</v>
@@ -6669,13 +6666,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D276" t="s">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="E276" t="s">
         <v>27</v>
@@ -6686,13 +6683,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D277" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="E277" t="s">
         <v>27</v>
@@ -6703,13 +6700,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D278" t="s">
-        <v>66</v>
+        <v>235</v>
       </c>
       <c r="E278" t="s">
         <v>27</v>
@@ -6720,13 +6717,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D279" t="s">
-        <v>222</v>
+        <v>105</v>
       </c>
       <c r="E279" t="s">
         <v>27</v>
@@ -6737,13 +6734,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D280" t="s">
-        <v>359</v>
+        <v>79</v>
       </c>
       <c r="E280" t="s">
         <v>27</v>
@@ -6754,13 +6751,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D281" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="E281" t="s">
         <v>27</v>
@@ -6771,13 +6768,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D282" t="s">
-        <v>48</v>
+        <v>195</v>
       </c>
       <c r="E282" t="s">
         <v>27</v>
@@ -6788,13 +6785,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D283" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E283" t="s">
         <v>27</v>
@@ -6805,13 +6802,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D284" t="s">
-        <v>176</v>
+        <v>47</v>
       </c>
       <c r="E284" t="s">
         <v>27</v>
@@ -6822,13 +6819,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D285" t="s">
-        <v>98</v>
+        <v>233</v>
       </c>
       <c r="E285" t="s">
         <v>27</v>
@@ -6839,13 +6836,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D286" t="s">
-        <v>222</v>
+        <v>79</v>
       </c>
       <c r="E286" t="s">
         <v>27</v>
@@ -6856,13 +6853,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D287" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="E287" t="s">
         <v>27</v>
@@ -6873,13 +6870,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D288" t="s">
-        <v>154</v>
+        <v>79</v>
       </c>
       <c r="E288" t="s">
         <v>27</v>
@@ -6890,13 +6887,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D289" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E289" t="s">
         <v>27</v>
@@ -6907,13 +6904,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D290" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E290" t="s">
         <v>27</v>
@@ -6924,13 +6921,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D291" t="s">
-        <v>235</v>
+        <v>62</v>
       </c>
       <c r="E291" t="s">
         <v>27</v>
@@ -6941,13 +6938,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D292" t="s">
-        <v>75</v>
+        <v>178</v>
       </c>
       <c r="E292" t="s">
         <v>27</v>
@@ -6958,13 +6955,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D293" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="E293" t="s">
         <v>27</v>
@@ -6975,13 +6972,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D294" t="s">
-        <v>253</v>
+        <v>201</v>
       </c>
       <c r="E294" t="s">
         <v>27</v>
@@ -6992,13 +6989,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D295" t="s">
-        <v>222</v>
+        <v>114</v>
       </c>
       <c r="E295" t="s">
         <v>27</v>
@@ -7009,13 +7006,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D296" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E296" t="s">
         <v>27</v>
@@ -7026,13 +7023,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D297" t="s">
-        <v>271</v>
+        <v>54</v>
       </c>
       <c r="E297" t="s">
         <v>27</v>
@@ -7043,13 +7040,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D298" t="s">
-        <v>104</v>
+        <v>193</v>
       </c>
       <c r="E298" t="s">
         <v>27</v>
@@ -7060,13 +7057,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D299" t="s">
-        <v>325</v>
+        <v>93</v>
       </c>
       <c r="E299" t="s">
         <v>27</v>
@@ -7077,13 +7074,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D300" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="E300" t="s">
         <v>27</v>
@@ -7094,13 +7091,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D301" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="E301" t="s">
         <v>27</v>
@@ -7111,13 +7108,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D302" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="E302" t="s">
         <v>27</v>
@@ -7128,13 +7125,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D303" t="s">
-        <v>56</v>
+        <v>366</v>
       </c>
       <c r="E303" t="s">
         <v>27</v>
@@ -7145,13 +7142,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D304" t="s">
-        <v>124</v>
+        <v>218</v>
       </c>
       <c r="E304" t="s">
         <v>27</v>
@@ -7162,13 +7159,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D305" t="s">
-        <v>247</v>
+        <v>176</v>
       </c>
       <c r="E305" t="s">
         <v>27</v>
@@ -7179,13 +7176,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D306" t="s">
-        <v>361</v>
+        <v>193</v>
       </c>
       <c r="E306" t="s">
         <v>27</v>
@@ -7196,13 +7193,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D307" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="E307" t="s">
         <v>27</v>
@@ -7213,13 +7210,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D308" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="E308" t="s">
         <v>27</v>
@@ -7230,13 +7227,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D309" t="s">
-        <v>243</v>
+        <v>201</v>
       </c>
       <c r="E309" t="s">
         <v>27</v>
@@ -7247,13 +7244,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D310" t="s">
-        <v>180</v>
+        <v>107</v>
       </c>
       <c r="E310" t="s">
         <v>27</v>
@@ -7264,13 +7261,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D311" t="s">
-        <v>50</v>
+        <v>188</v>
       </c>
       <c r="E311" t="s">
         <v>27</v>
@@ -7281,13 +7278,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D312" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="E312" t="s">
         <v>27</v>
@@ -7298,13 +7295,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D313" t="s">
-        <v>200</v>
+        <v>86</v>
       </c>
       <c r="E313" t="s">
         <v>27</v>
@@ -7315,13 +7312,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D314" t="s">
-        <v>247</v>
+        <v>167</v>
       </c>
       <c r="E314" t="s">
         <v>27</v>
@@ -7332,13 +7329,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D315" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="E315" t="s">
         <v>27</v>
@@ -7349,13 +7346,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D316" t="s">
-        <v>202</v>
+        <v>249</v>
       </c>
       <c r="E316" t="s">
         <v>27</v>
@@ -7366,13 +7363,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D317" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="E317" t="s">
         <v>27</v>
@@ -7383,13 +7380,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D318" t="s">
-        <v>200</v>
+        <v>43</v>
       </c>
       <c r="E318" t="s">
         <v>27</v>
@@ -7400,13 +7397,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D319" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="E319" t="s">
         <v>27</v>
@@ -7417,13 +7414,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D320" t="s">
-        <v>344</v>
+        <v>71</v>
       </c>
       <c r="E320" t="s">
         <v>27</v>
@@ -7434,13 +7431,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D321" t="s">
-        <v>325</v>
+        <v>122</v>
       </c>
       <c r="E321" t="s">
         <v>27</v>
@@ -7451,13 +7448,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D322" t="s">
-        <v>293</v>
+        <v>77</v>
       </c>
       <c r="E322" t="s">
         <v>27</v>
@@ -7468,13 +7465,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D323" t="s">
-        <v>243</v>
+        <v>366</v>
       </c>
       <c r="E323" t="s">
         <v>27</v>
@@ -7485,13 +7482,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D324" t="s">
-        <v>56</v>
+        <v>149</v>
       </c>
       <c r="E324" t="s">
         <v>27</v>
@@ -7502,13 +7499,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D325" t="s">
-        <v>271</v>
+        <v>180</v>
       </c>
       <c r="E325" t="s">
         <v>27</v>
@@ -7519,13 +7516,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D326" t="s">
-        <v>111</v>
+        <v>256</v>
       </c>
       <c r="E326" t="s">
         <v>27</v>
@@ -7536,13 +7533,13 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D327" t="s">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="E327" t="s">
         <v>27</v>
@@ -7553,13 +7550,13 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D328" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E328" t="s">
         <v>27</v>
@@ -7570,13 +7567,13 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D329" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="E329" t="s">
         <v>27</v>
@@ -7587,13 +7584,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D330" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="E330" t="s">
         <v>27</v>
@@ -7604,13 +7601,13 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D331" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="E331" t="s">
         <v>27</v>
@@ -7621,13 +7618,13 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D332" t="s">
-        <v>247</v>
+        <v>110</v>
       </c>
       <c r="E332" t="s">
         <v>27</v>
@@ -7638,13 +7635,13 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D333" t="s">
-        <v>52</v>
+        <v>218</v>
       </c>
       <c r="E333" t="s">
         <v>27</v>
@@ -7655,13 +7652,13 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D334" t="s">
-        <v>66</v>
+        <v>184</v>
       </c>
       <c r="E334" t="s">
         <v>27</v>
@@ -7672,13 +7669,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D335" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E335" t="s">
         <v>27</v>
@@ -7689,13 +7686,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D336" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="E336" t="s">
         <v>27</v>
@@ -7706,13 +7703,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D337" t="s">
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="E337" t="s">
         <v>27</v>
@@ -7723,13 +7720,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D338" t="s">
-        <v>215</v>
+        <v>118</v>
       </c>
       <c r="E338" t="s">
         <v>27</v>
@@ -7740,13 +7737,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D339" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="E339" t="s">
         <v>27</v>
@@ -7757,13 +7754,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D340" t="s">
-        <v>361</v>
+        <v>205</v>
       </c>
       <c r="E340" t="s">
         <v>27</v>
@@ -7774,13 +7771,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D341" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E341" t="s">
         <v>27</v>
@@ -7791,13 +7788,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D342" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="E342" t="s">
         <v>27</v>
@@ -7808,13 +7805,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D343" t="s">
-        <v>54</v>
+        <v>321</v>
       </c>
       <c r="E343" t="s">
         <v>27</v>
@@ -7825,13 +7822,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D344" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="E344" t="s">
         <v>27</v>
@@ -7842,13 +7839,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D345" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="E345" t="s">
         <v>27</v>
@@ -7859,13 +7856,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D346" t="s">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="E346" t="s">
         <v>27</v>
@@ -7876,7 +7873,7 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>25</v>
@@ -7893,13 +7890,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D348" t="s">
-        <v>222</v>
+        <v>64</v>
       </c>
       <c r="E348" t="s">
         <v>27</v>
@@ -7910,13 +7907,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
+        <v>453</v>
+      </c>
+      <c r="C349" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D349" t="s">
         <v>454</v>
-      </c>
-      <c r="C349" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D349" t="s">
-        <v>100</v>
       </c>
       <c r="E349" t="s">
         <v>27</v>
@@ -7933,7 +7930,7 @@
         <v>25</v>
       </c>
       <c r="D350" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E350" t="s">
         <v>27</v>
@@ -7950,7 +7947,7 @@
         <v>25</v>
       </c>
       <c r="D351" t="s">
-        <v>237</v>
+        <v>293</v>
       </c>
       <c r="E351" t="s">
         <v>27</v>
@@ -7967,7 +7964,7 @@
         <v>25</v>
       </c>
       <c r="D352" t="s">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="E352" t="s">
         <v>27</v>
@@ -7984,7 +7981,7 @@
         <v>25</v>
       </c>
       <c r="D353" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E353" t="s">
         <v>27</v>
@@ -8001,7 +7998,7 @@
         <v>25</v>
       </c>
       <c r="D354" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="E354" t="s">
         <v>27</v>
@@ -8018,7 +8015,7 @@
         <v>25</v>
       </c>
       <c r="D355" t="s">
-        <v>359</v>
+        <v>271</v>
       </c>
       <c r="E355" t="s">
         <v>27</v>
@@ -8035,7 +8032,7 @@
         <v>25</v>
       </c>
       <c r="D356" t="s">
-        <v>46</v>
+        <v>188</v>
       </c>
       <c r="E356" t="s">
         <v>27</v>
@@ -8052,7 +8049,7 @@
         <v>25</v>
       </c>
       <c r="D357" t="s">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="E357" t="s">
         <v>27</v>
@@ -8069,7 +8066,7 @@
         <v>25</v>
       </c>
       <c r="D358" t="s">
-        <v>118</v>
+        <v>62</v>
       </c>
       <c r="E358" t="s">
         <v>27</v>
@@ -8086,7 +8083,7 @@
         <v>25</v>
       </c>
       <c r="D359" t="s">
-        <v>69</v>
+        <v>321</v>
       </c>
       <c r="E359" t="s">
         <v>27</v>
@@ -8103,7 +8100,7 @@
         <v>25</v>
       </c>
       <c r="D360" t="s">
-        <v>200</v>
+        <v>141</v>
       </c>
       <c r="E360" t="s">
         <v>27</v>
@@ -8120,7 +8117,7 @@
         <v>25</v>
       </c>
       <c r="D361" t="s">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="E361" t="s">
         <v>27</v>
@@ -8137,7 +8134,7 @@
         <v>25</v>
       </c>
       <c r="D362" t="s">
-        <v>69</v>
+        <v>215</v>
       </c>
       <c r="E362" t="s">
         <v>27</v>
@@ -8154,7 +8151,7 @@
         <v>25</v>
       </c>
       <c r="D363" t="s">
-        <v>293</v>
+        <v>218</v>
       </c>
       <c r="E363" t="s">
         <v>27</v>
@@ -8171,7 +8168,7 @@
         <v>25</v>
       </c>
       <c r="D364" t="s">
-        <v>361</v>
+        <v>256</v>
       </c>
       <c r="E364" t="s">
         <v>27</v>
@@ -8188,7 +8185,7 @@
         <v>25</v>
       </c>
       <c r="D365" t="s">
-        <v>359</v>
+        <v>66</v>
       </c>
       <c r="E365" t="s">
         <v>27</v>
@@ -8205,7 +8202,7 @@
         <v>25</v>
       </c>
       <c r="D366" t="s">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="E366" t="s">
         <v>27</v>
@@ -8222,7 +8219,7 @@
         <v>25</v>
       </c>
       <c r="D367" t="s">
-        <v>295</v>
+        <v>120</v>
       </c>
       <c r="E367" t="s">
         <v>27</v>
@@ -8239,7 +8236,7 @@
         <v>25</v>
       </c>
       <c r="D368" t="s">
-        <v>152</v>
+        <v>66</v>
       </c>
       <c r="E368" t="s">
         <v>27</v>
@@ -8256,7 +8253,7 @@
         <v>25</v>
       </c>
       <c r="D369" t="s">
-        <v>293</v>
+        <v>47</v>
       </c>
       <c r="E369" t="s">
         <v>27</v>
@@ -8273,7 +8270,7 @@
         <v>25</v>
       </c>
       <c r="D370" t="s">
-        <v>62</v>
+        <v>190</v>
       </c>
       <c r="E370" t="s">
         <v>27</v>
@@ -8290,7 +8287,7 @@
         <v>25</v>
       </c>
       <c r="D371" t="s">
-        <v>283</v>
+        <v>56</v>
       </c>
       <c r="E371" t="s">
         <v>27</v>
@@ -8307,7 +8304,7 @@
         <v>25</v>
       </c>
       <c r="D372" t="s">
-        <v>152</v>
+        <v>39</v>
       </c>
       <c r="E372" t="s">
         <v>27</v>
@@ -8324,7 +8321,7 @@
         <v>25</v>
       </c>
       <c r="D373" t="s">
-        <v>154</v>
+        <v>37</v>
       </c>
       <c r="E373" t="s">
         <v>27</v>
@@ -8341,7 +8338,7 @@
         <v>25</v>
       </c>
       <c r="D374" t="s">
-        <v>202</v>
+        <v>122</v>
       </c>
       <c r="E374" t="s">
         <v>27</v>
@@ -8358,7 +8355,7 @@
         <v>25</v>
       </c>
       <c r="D375" t="s">
-        <v>64</v>
+        <v>149</v>
       </c>
       <c r="E375" t="s">
         <v>27</v>
@@ -8375,7 +8372,7 @@
         <v>25</v>
       </c>
       <c r="D376" t="s">
-        <v>344</v>
+        <v>64</v>
       </c>
       <c r="E376" t="s">
         <v>27</v>
@@ -8392,7 +8389,7 @@
         <v>25</v>
       </c>
       <c r="D377" t="s">
-        <v>235</v>
+        <v>118</v>
       </c>
       <c r="E377" t="s">
         <v>27</v>
@@ -8409,7 +8406,7 @@
         <v>25</v>
       </c>
       <c r="D378" t="s">
-        <v>339</v>
+        <v>77</v>
       </c>
       <c r="E378" t="s">
         <v>27</v>
@@ -8426,7 +8423,7 @@
         <v>25</v>
       </c>
       <c r="D379" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="E379" t="s">
         <v>27</v>
@@ -8443,7 +8440,7 @@
         <v>25</v>
       </c>
       <c r="D380" t="s">
-        <v>60</v>
+        <v>178</v>
       </c>
       <c r="E380" t="s">
         <v>27</v>
@@ -8460,7 +8457,7 @@
         <v>25</v>
       </c>
       <c r="D381" t="s">
-        <v>81</v>
+        <v>188</v>
       </c>
       <c r="E381" t="s">
         <v>27</v>
@@ -8477,7 +8474,7 @@
         <v>25</v>
       </c>
       <c r="D382" t="s">
-        <v>344</v>
+        <v>156</v>
       </c>
       <c r="E382" t="s">
         <v>27</v>
@@ -8494,7 +8491,7 @@
         <v>25</v>
       </c>
       <c r="D383" t="s">
-        <v>489</v>
+        <v>71</v>
       </c>
       <c r="E383" t="s">
         <v>27</v>
@@ -8505,13 +8502,13 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D384" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="E384" t="s">
         <v>27</v>
@@ -8522,13 +8519,13 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D385" t="s">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="E385" t="s">
         <v>27</v>
@@ -8539,13 +8536,13 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D386" t="s">
-        <v>146</v>
+        <v>454</v>
       </c>
       <c r="E386" t="s">
         <v>27</v>
@@ -8556,13 +8553,13 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D387" t="s">
-        <v>325</v>
+        <v>64</v>
       </c>
       <c r="E387" t="s">
         <v>27</v>
@@ -8573,13 +8570,13 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D388" t="s">
-        <v>94</v>
+        <v>172</v>
       </c>
       <c r="E388" t="s">
         <v>27</v>
@@ -8590,13 +8587,13 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D389" t="s">
-        <v>73</v>
+        <v>156</v>
       </c>
       <c r="E389" t="s">
         <v>27</v>
@@ -8607,13 +8604,13 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D390" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E390" t="s">
         <v>27</v>
@@ -8624,13 +8621,13 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D391" t="s">
-        <v>222</v>
+        <v>100</v>
       </c>
       <c r="E391" t="s">
         <v>27</v>
@@ -8641,13 +8638,13 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D392" t="s">
-        <v>118</v>
+        <v>193</v>
       </c>
       <c r="E392" t="s">
         <v>27</v>
@@ -8658,13 +8655,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D393" t="s">
-        <v>54</v>
+        <v>178</v>
       </c>
       <c r="E393" t="s">
         <v>27</v>
@@ -8675,13 +8672,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D394" t="s">
-        <v>339</v>
+        <v>45</v>
       </c>
       <c r="E394" t="s">
         <v>27</v>
@@ -8692,13 +8689,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D395" t="s">
-        <v>295</v>
+        <v>120</v>
       </c>
       <c r="E395" t="s">
         <v>27</v>
@@ -8709,13 +8706,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D396" t="s">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="E396" t="s">
         <v>27</v>
@@ -8726,13 +8723,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D397" t="s">
-        <v>167</v>
+        <v>238</v>
       </c>
       <c r="E397" t="s">
         <v>27</v>
@@ -8743,13 +8740,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D398" t="s">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="E398" t="s">
         <v>27</v>
@@ -8760,13 +8757,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D399" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="E399" t="s">
         <v>27</v>
@@ -8777,13 +8774,13 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D400" t="s">
-        <v>359</v>
+        <v>69</v>
       </c>
       <c r="E400" t="s">
         <v>27</v>
@@ -8794,13 +8791,13 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D401" t="s">
-        <v>361</v>
+        <v>100</v>
       </c>
       <c r="E401" t="s">
         <v>27</v>
@@ -8819,47 +8816,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1" t="s">
         <v>508</v>
-      </c>
-      <c r="B1" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>509</v>
+      </c>
+      <c r="B2" t="s">
         <v>510</v>
-      </c>
-      <c r="B2" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>511</v>
+      </c>
+      <c r="B3" t="s">
         <v>512</v>
-      </c>
-      <c r="B3" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>513</v>
+      </c>
+      <c r="B4" t="s">
         <v>514</v>
-      </c>
-      <c r="B4" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>515</v>
+      </c>
+      <c r="B5" t="s">
         <v>516</v>
-      </c>
-      <c r="B5" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B6">
         <v>400</v>
@@ -8867,7 +8864,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B7">
         <v>391</v>
@@ -8875,7 +8872,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B8">
         <v>9</v>
@@ -8883,7 +8880,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8891,10 +8888,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>521</v>
+      </c>
+      <c r="B10" t="s">
         <v>522</v>
-      </c>
-      <c r="B10" t="s">
-        <v>523</v>
       </c>
     </row>
   </sheetData>

--- a/reports/selenium/Excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/Excel/Automation_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="523">
   <si>
     <t>#</t>
   </si>
@@ -35,1304 +35,1317 @@
     <t>FAILED</t>
   </si>
   <si>
-    <t>20.68</t>
+    <t>20.54</t>
   </si>
   <si>
     <t xml:space="preserve">Landing page did not load — Sign In button not found
-Wait timed out after 20052ms</t>
+Wait timed out after 20007ms</t>
   </si>
   <si>
     <t>should navigate to the login form</t>
   </si>
   <si>
-    <t>20.60</t>
+    <t>20.55</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20172ms</t>
+Wait timed out after 20190ms</t>
   </si>
   <si>
     <t>should login with valid credentials and reach the dashboard</t>
   </si>
   <si>
-    <t>20.57</t>
+    <t>20.73</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20145ms</t>
+Wait timed out after 20013ms</t>
   </si>
   <si>
     <t>should reject invalid credentials with an error message</t>
   </si>
   <si>
-    <t>20.59</t>
+    <t>20.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
+Wait timed out after 20165ms</t>
+  </si>
+  <si>
+    <t>should open the sign-up form from landing</t>
+  </si>
+  <si>
+    <t>20.93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signup-btn"])
+Wait timed out after 20202ms</t>
+  </si>
+  <si>
+    <t>Security — should reject login for invalid credentials</t>
+  </si>
+  <si>
+    <t>20.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
+Wait timed out after 20201ms</t>
+  </si>
+  <si>
+    <t>Security — should prevent access to protected routes/dashboard for unauthenticated users</t>
+  </si>
+  <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>3.75</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Security — should not execute XSS script payloads submitted in login fields</t>
+  </si>
+  <si>
+    <t>20.88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
+Wait timed out after 20200ms</t>
+  </si>
+  <si>
+    <t>Security — should enforce session termination and clean storage upon logout</t>
+  </si>
+  <si>
+    <t>20.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
+Wait timed out after 20008ms</t>
+  </si>
+  <si>
+    <t>Security — should confirm Firebase authentication rejects empty credentials</t>
+  </si>
+  <si>
+    <t>20.85</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
 Wait timed out after 20189ms</t>
   </si>
   <si>
-    <t>should open the sign-up form from landing</t>
-  </si>
-  <si>
-    <t>21.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signup-btn"])
-Wait timed out after 20182ms</t>
-  </si>
-  <si>
-    <t>Security — should reject login for invalid credentials</t>
-  </si>
-  <si>
-    <t>20.85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20017ms</t>
-  </si>
-  <si>
-    <t>Security — should prevent access to protected routes/dashboard for unauthenticated users</t>
-  </si>
-  <si>
-    <t>PASSED</t>
-  </si>
-  <si>
-    <t>3.27</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Security — should not execute XSS script payloads submitted in login fields</t>
-  </si>
-  <si>
-    <t>20.61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20174ms</t>
-  </si>
-  <si>
-    <t>Security — should enforce session termination and clean storage upon logout</t>
-  </si>
-  <si>
-    <t>20.52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20147ms</t>
-  </si>
-  <si>
-    <t>Security — should confirm Firebase authentication rejects empty credentials</t>
-  </si>
-  <si>
     <t>Security — should not expose sensitive API keys or secrets in page HTML source</t>
   </si>
   <si>
+    <t>0.74</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for compare-btn (Verify Point #11)</t>
+  </si>
+  <si>
+    <t>0.45</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated profile-settings (Verify Point #12)</t>
+  </si>
+  <si>
+    <t>0.68</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for ai-chat-input (Verify Point #13)</t>
+  </si>
+  <si>
+    <t>0.70</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on en-US (Verify Point #14)</t>
+  </si>
+  <si>
+    <t>0.38</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for hi-IN (Verify Point #15)</t>
+  </si>
+  <si>
+    <t>0.61</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for ta-IN (Verify Point #16)</t>
+  </si>
+  <si>
+    <t>0.40</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for header-nav (Verify Point #17)</t>
+  </si>
+  <si>
+    <t>0.83</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field sidebar-menu (Verify Point #18)</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to footer-links (Verify Point #19)</t>
+  </si>
+  <si>
+    <t>0.84</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution login-form (Verify Point #20)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element register-form (Verify Point #21)</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container dashboard-grid (Verify Point #22)</t>
+  </si>
+  <si>
+    <t>0.53</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter detail-page (Verify Point #23)</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale fees-filter (Verify Point #24)</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource nirf-sort (Verify Point #25)</t>
+  </si>
+  <si>
+    <t>0.90</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path course-filter (Verify Point #26)</t>
+  </si>
+  <si>
+    <t>0.92</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component state-filter (Verify Point #27)</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for firebase-auth (Verify Point #28)</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for firestore-read (Verify Point #29)</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for groq-api (Verify Point #30)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for expo-router (Verify Point #31)</t>
+  </si>
+  <si>
+    <t>0.99</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated college-list (Verify Point #32)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for saved-list (Verify Point #33)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on comparison-list (Verify Point #34)</t>
+  </si>
+  <si>
+    <t>0.60</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for chat-history (Verify Point #35)</t>
+  </si>
+  <si>
+    <t>0.79</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for avatar-upload (Verify Point #36)</t>
+  </si>
+  <si>
+    <t>0.72</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for theme-toggle (Verify Point #37)</t>
+  </si>
+  <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field notification-prefs (Verify Point #38)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to session-token (Verify Point #39)</t>
+  </si>
+  <si>
+    <t>0.86</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution XSS-injection (Verify Point #40)</t>
+  </si>
+  <si>
+    <t>0.67</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element SQL-injection (Verify Point #41)</t>
+  </si>
+  <si>
+    <t>0.97</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container CSRF-token (Verify Point #42)</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter CORS-origin (Verify Point #43)</t>
+  </si>
+  <si>
+    <t>0.91</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale CSP-header (Verify Point #44)</t>
+  </si>
+  <si>
+    <t>0.82</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource X-Frame-Options (Verify Point #45)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path primary-font (Verify Point #46)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component accent-color (Verify Point #47)</t>
+  </si>
+  <si>
+    <t>0.76</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for glassmorphic-transparency (Verify Point #48)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for border-radius (Verify Point #49)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for bundle-size (Verify Point #50)</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for first-meaningful-paint (Verify Point #51)</t>
+  </si>
+  <si>
+    <t>0.63</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated time-to-interactive (Verify Point #52)</t>
+  </si>
+  <si>
+    <t>0.89</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for dom-depth (Verify Point #53)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on lost-item-card (Verify Point #54)</t>
+  </si>
+  <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for users-ref (Verify Point #55)</t>
+  </si>
+  <si>
+    <t>0.37</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for items-ref (Verify Point #56)</t>
+  </si>
+  <si>
+    <t>0.44</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for de-DE (Verify Point #57)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field fr-FR (Verify Point #58)</t>
+  </si>
+  <si>
+    <t>0.71</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to ja-JP (Verify Point #59)</t>
+  </si>
+  <si>
+    <t>0.29</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution pt-BR (Verify Point #60)</t>
+  </si>
+  <si>
+    <t>0.77</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element it-IT (Verify Point #61)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container 1920x1080 (Verify Point #62)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter 1440x900 (Verify Point #63)</t>
+  </si>
+  <si>
+    <t>0.49</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale 1280x800 (Verify Point #64)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource 1024x768 (Verify Point #65)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path 768x1024 (Verify Point #66)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component 375x812 (Verify Point #67)</t>
+  </si>
+  <si>
+    <t>0.30</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for sign-in-button (Verify Point #68)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for email-input (Verify Point #69)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for password-field (Verify Point #70)</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for search-bar (Verify Point #71)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated college-card (Verify Point #72)</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for compare-btn (Verify Point #73)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on profile-settings (Verify Point #74)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for ai-chat-input (Verify Point #75)</t>
+  </si>
+  <si>
+    <t>0.73</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for en-US (Verify Point #76)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for hi-IN (Verify Point #77)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field ta-IN (Verify Point #78)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to header-nav (Verify Point #79)</t>
+  </si>
+  <si>
     <t>0.85</t>
   </si>
   <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for compare-btn (Verify Point #11)</t>
-  </si>
-  <si>
-    <t>0.71</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated profile-settings (Verify Point #12)</t>
-  </si>
-  <si>
-    <t>0.83</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for ai-chat-input (Verify Point #13)</t>
-  </si>
-  <si>
-    <t>0.89</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on en-US (Verify Point #14)</t>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution sidebar-menu (Verify Point #80)</t>
+  </si>
+  <si>
+    <t>0.66</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element footer-links (Verify Point #81)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container login-form (Verify Point #82)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter register-form (Verify Point #83)</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale dashboard-grid (Verify Point #84)</t>
+  </si>
+  <si>
+    <t>0.69</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource detail-page (Verify Point #85)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path fees-filter (Verify Point #86)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component nirf-sort (Verify Point #87)</t>
+  </si>
+  <si>
+    <t>0.55</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for course-filter (Verify Point #88)</t>
+  </si>
+  <si>
+    <t>0.52</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for state-filter (Verify Point #89)</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for firebase-auth (Verify Point #90)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for firestore-read (Verify Point #91)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #92)</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for expo-router (Verify Point #93)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on college-list (Verify Point #94)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for saved-list (Verify Point #95)</t>
+  </si>
+  <si>
+    <t>0.96</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for comparison-list (Verify Point #96)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for chat-history (Verify Point #97)</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field avatar-upload (Verify Point #98)</t>
+  </si>
+  <si>
+    <t>0.46</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to theme-toggle (Verify Point #99)</t>
+  </si>
+  <si>
+    <t>0.87</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution notification-prefs (Verify Point #100)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element session-token (Verify Point #101)</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container XSS-injection (Verify Point #102)</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter SQL-injection (Verify Point #103)</t>
+  </si>
+  <si>
+    <t>0.93</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale CSRF-token (Verify Point #104)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource CORS-origin (Verify Point #105)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path CSP-header (Verify Point #106)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component X-Frame-Options (Verify Point #107)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for primary-font (Verify Point #108)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for accent-color (Verify Point #109)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for glassmorphic-transparency (Verify Point #110)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for border-radius (Verify Point #111)</t>
+  </si>
+  <si>
+    <t>0.81</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated bundle-size (Verify Point #112)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for first-meaningful-paint (Verify Point #113)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on time-to-interactive (Verify Point #114)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for dom-depth (Verify Point #115)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for lost-item-card (Verify Point #116)</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for users-ref (Verify Point #117)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field items-ref (Verify Point #118)</t>
+  </si>
+  <si>
+    <t>0.78</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to de-DE (Verify Point #119)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution fr-FR (Verify Point #120)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element ja-JP (Verify Point #121)</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container pt-BR (Verify Point #122)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter it-IT (Verify Point #123)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #124)</t>
+  </si>
+  <si>
+    <t>0.54</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #125)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #126)</t>
   </si>
   <si>
     <t>0.23</t>
   </si>
   <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for hi-IN (Verify Point #15)</t>
-  </si>
-  <si>
-    <t>0.36</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for ta-IN (Verify Point #16)</t>
-  </si>
-  <si>
-    <t>0.34</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for header-nav (Verify Point #17)</t>
-  </si>
-  <si>
-    <t>0.66</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field sidebar-menu (Verify Point #18)</t>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #127)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #128)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for 375x812 (Verify Point #129)</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for sign-in-button (Verify Point #130)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for email-input (Verify Point #131)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated password-field (Verify Point #132)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for search-bar (Verify Point #133)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on college-card (Verify Point #134)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for compare-btn (Verify Point #135)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for profile-settings (Verify Point #136)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for ai-chat-input (Verify Point #137)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field en-US (Verify Point #138)</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to hi-IN (Verify Point #139)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution ta-IN (Verify Point #140)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element header-nav (Verify Point #141)</t>
+  </si>
+  <si>
+    <t>0.80</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container sidebar-menu (Verify Point #142)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter footer-links (Verify Point #143)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale login-form (Verify Point #144)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource register-form (Verify Point #145)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path dashboard-grid (Verify Point #146)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component detail-page (Verify Point #147)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for fees-filter (Verify Point #148)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for nirf-sort (Verify Point #149)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for course-filter (Verify Point #150)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for state-filter (Verify Point #151)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated firebase-auth (Verify Point #152)</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for firestore-read (Verify Point #153)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on groq-api (Verify Point #154)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for expo-router (Verify Point #155)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for college-list (Verify Point #156)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for saved-list (Verify Point #157)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field comparison-list (Verify Point #158)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to chat-history (Verify Point #159)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution avatar-upload (Verify Point #160)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element theme-toggle (Verify Point #161)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container notification-prefs (Verify Point #162)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter session-token (Verify Point #163)</t>
+  </si>
+  <si>
+    <t>0.32</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale XSS-injection (Verify Point #164)</t>
+  </si>
+  <si>
+    <t>0.59</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #165)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path CSRF-token (Verify Point #166)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component CORS-origin (Verify Point #167)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for CSP-header (Verify Point #168)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for X-Frame-Options (Verify Point #169)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for primary-font (Verify Point #170)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for accent-color (Verify Point #171)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated glassmorphic-transparency (Verify Point #172)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for border-radius (Verify Point #173)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on bundle-size (Verify Point #174)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for first-meaningful-paint (Verify Point #175)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for time-to-interactive (Verify Point #176)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for dom-depth (Verify Point #177)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field lost-item-card (Verify Point #178)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to users-ref (Verify Point #179)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution items-ref (Verify Point #180)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element de-DE (Verify Point #181)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container fr-FR (Verify Point #182)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter ja-JP (Verify Point #183)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale pt-BR (Verify Point #184)</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource it-IT (Verify Point #185)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path 1920x1080 (Verify Point #186)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component 1440x900 (Verify Point #187)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for 1280x800 (Verify Point #188)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for 1024x768 (Verify Point #189)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for 768x1024 (Verify Point #190)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for 375x812 (Verify Point #191)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated sign-in-button (Verify Point #192)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for email-input (Verify Point #193)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on password-field (Verify Point #194)</t>
   </si>
   <si>
     <t>0.88</t>
   </si>
   <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to footer-links (Verify Point #19)</t>
-  </si>
-  <si>
-    <t>0.22</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution login-form (Verify Point #20)</t>
-  </si>
-  <si>
-    <t>0.57</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element register-form (Verify Point #21)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container dashboard-grid (Verify Point #22)</t>
-  </si>
-  <si>
-    <t>0.41</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter detail-page (Verify Point #23)</t>
-  </si>
-  <si>
-    <t>0.43</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale fees-filter (Verify Point #24)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource nirf-sort (Verify Point #25)</t>
-  </si>
-  <si>
-    <t>0.87</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path course-filter (Verify Point #26)</t>
-  </si>
-  <si>
-    <t>0.82</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component state-filter (Verify Point #27)</t>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for search-bar (Verify Point #195)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for college-card (Verify Point #196)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for compare-btn (Verify Point #197)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field profile-settings (Verify Point #198)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to ai-chat-input (Verify Point #199)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution en-US (Verify Point #200)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element hi-IN (Verify Point #201)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container ta-IN (Verify Point #202)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter header-nav (Verify Point #203)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale sidebar-menu (Verify Point #204)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource footer-links (Verify Point #205)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path login-form (Verify Point #206)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component register-form (Verify Point #207)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for dashboard-grid (Verify Point #208)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for detail-page (Verify Point #209)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for fees-filter (Verify Point #210)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for nirf-sort (Verify Point #211)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated course-filter (Verify Point #212)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for state-filter (Verify Point #213)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on firebase-auth (Verify Point #214)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for firestore-read (Verify Point #215)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for groq-api (Verify Point #216)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for expo-router (Verify Point #217)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field college-list (Verify Point #218)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to saved-list (Verify Point #219)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution comparison-list (Verify Point #220)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element chat-history (Verify Point #221)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container avatar-upload (Verify Point #222)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter theme-toggle (Verify Point #223)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale notification-prefs (Verify Point #224)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource session-token (Verify Point #225)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path XSS-injection (Verify Point #226)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component SQL-injection (Verify Point #227)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for CSRF-token (Verify Point #228)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for CORS-origin (Verify Point #229)</t>
+  </si>
+  <si>
+    <t>0.47</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for CSP-header (Verify Point #230)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for X-Frame-Options (Verify Point #231)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated primary-font (Verify Point #232)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for accent-color (Verify Point #233)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on glassmorphic-transparency (Verify Point #234)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for border-radius (Verify Point #235)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for bundle-size (Verify Point #236)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for first-meaningful-paint (Verify Point #237)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field time-to-interactive (Verify Point #238)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to dom-depth (Verify Point #239)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution lost-item-card (Verify Point #240)</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element users-ref (Verify Point #241)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container items-ref (Verify Point #242)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter de-DE (Verify Point #243)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale fr-FR (Verify Point #244)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource ja-JP (Verify Point #245)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path pt-BR (Verify Point #246)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component it-IT (Verify Point #247)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #248)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #249)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #250)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #251)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #252)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for 375x812 (Verify Point #253)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on sign-in-button (Verify Point #254)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for email-input (Verify Point #255)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for password-field (Verify Point #256)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for search-bar (Verify Point #257)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field college-card (Verify Point #258)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to compare-btn (Verify Point #259)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution profile-settings (Verify Point #260)</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element ai-chat-input (Verify Point #261)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container en-US (Verify Point #262)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter hi-IN (Verify Point #263)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale ta-IN (Verify Point #264)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource header-nav (Verify Point #265)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path sidebar-menu (Verify Point #266)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component footer-links (Verify Point #267)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for login-form (Verify Point #268)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for register-form (Verify Point #269)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for dashboard-grid (Verify Point #270)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for detail-page (Verify Point #271)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated fees-filter (Verify Point #272)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for nirf-sort (Verify Point #273)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on course-filter (Verify Point #274)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for state-filter (Verify Point #275)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for firebase-auth (Verify Point #276)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for firestore-read (Verify Point #277)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field groq-api (Verify Point #278)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to expo-router (Verify Point #279)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution college-list (Verify Point #280)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element saved-list (Verify Point #281)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container comparison-list (Verify Point #282)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter chat-history (Verify Point #283)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale avatar-upload (Verify Point #284)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource theme-toggle (Verify Point #285)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path notification-prefs (Verify Point #286)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component session-token (Verify Point #287)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for XSS-injection (Verify Point #288)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for SQL-injection (Verify Point #289)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for CSRF-token (Verify Point #290)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for CORS-origin (Verify Point #291)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated CSP-header (Verify Point #292)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for X-Frame-Options (Verify Point #293)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on primary-font (Verify Point #294)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for accent-color (Verify Point #295)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for glassmorphic-transparency (Verify Point #296)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for border-radius (Verify Point #297)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field bundle-size (Verify Point #298)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to first-meaningful-paint (Verify Point #299)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution time-to-interactive (Verify Point #300)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element dom-depth (Verify Point #301)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container lost-item-card (Verify Point #302)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter users-ref (Verify Point #303)</t>
   </si>
   <si>
     <t>0.31</t>
   </si>
   <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for firebase-auth (Verify Point #28)</t>
-  </si>
-  <si>
-    <t>0.70</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for firestore-read (Verify Point #29)</t>
-  </si>
-  <si>
-    <t>0.53</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for groq-api (Verify Point #30)</t>
-  </si>
-  <si>
-    <t>0.32</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for expo-router (Verify Point #31)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated college-list (Verify Point #32)</t>
-  </si>
-  <si>
-    <t>0.51</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for saved-list (Verify Point #33)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on comparison-list (Verify Point #34)</t>
-  </si>
-  <si>
-    <t>0.45</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for chat-history (Verify Point #35)</t>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale items-ref (Verify Point #304)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource de-DE (Verify Point #305)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path fr-FR (Verify Point #306)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component ja-JP (Verify Point #307)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for pt-BR (Verify Point #308)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for it-IT (Verify Point #309)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for 1920x1080 (Verify Point #310)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for 1440x900 (Verify Point #311)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated 1280x800 (Verify Point #312)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for 1024x768 (Verify Point #313)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on 768x1024 (Verify Point #314)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for 375x812 (Verify Point #315)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for sign-in-button (Verify Point #316)</t>
+  </si>
+  <si>
+    <t>0.48</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for email-input (Verify Point #317)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field password-field (Verify Point #318)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to search-bar (Verify Point #319)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution college-card (Verify Point #320)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element compare-btn (Verify Point #321)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container profile-settings (Verify Point #322)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter ai-chat-input (Verify Point #323)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale en-US (Verify Point #324)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource hi-IN (Verify Point #325)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path ta-IN (Verify Point #326)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component header-nav (Verify Point #327)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for sidebar-menu (Verify Point #328)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for footer-links (Verify Point #329)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for login-form (Verify Point #330)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for register-form (Verify Point #331)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated dashboard-grid (Verify Point #332)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for detail-page (Verify Point #333)</t>
   </si>
   <si>
     <t>0.65</t>
   </si>
   <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for avatar-upload (Verify Point #36)</t>
-  </si>
-  <si>
-    <t>0.93</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for theme-toggle (Verify Point #37)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field notification-prefs (Verify Point #38)</t>
-  </si>
-  <si>
-    <t>0.75</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to session-token (Verify Point #39)</t>
-  </si>
-  <si>
-    <t>0.73</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution XSS-injection (Verify Point #40)</t>
-  </si>
-  <si>
-    <t>0.78</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element SQL-injection (Verify Point #41)</t>
-  </si>
-  <si>
-    <t>0.46</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container CSRF-token (Verify Point #42)</t>
-  </si>
-  <si>
-    <t>0.48</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter CORS-origin (Verify Point #43)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale CSP-header (Verify Point #44)</t>
-  </si>
-  <si>
-    <t>0.77</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource X-Frame-Options (Verify Point #45)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path primary-font (Verify Point #46)</t>
-  </si>
-  <si>
-    <t>0.42</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component accent-color (Verify Point #47)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for glassmorphic-transparency (Verify Point #48)</t>
-  </si>
-  <si>
-    <t>0.95</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for border-radius (Verify Point #49)</t>
-  </si>
-  <si>
-    <t>0.76</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for bundle-size (Verify Point #50)</t>
-  </si>
-  <si>
-    <t>0.30</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for first-meaningful-paint (Verify Point #51)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated time-to-interactive (Verify Point #52)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for dom-depth (Verify Point #53)</t>
-  </si>
-  <si>
-    <t>0.21</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on lost-item-card (Verify Point #54)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for users-ref (Verify Point #55)</t>
-  </si>
-  <si>
-    <t>0.28</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for items-ref (Verify Point #56)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for de-DE (Verify Point #57)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field fr-FR (Verify Point #58)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to ja-JP (Verify Point #59)</t>
-  </si>
-  <si>
-    <t>0.92</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution pt-BR (Verify Point #60)</t>
-  </si>
-  <si>
-    <t>0.67</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element it-IT (Verify Point #61)</t>
-  </si>
-  <si>
-    <t>0.94</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container 1920x1080 (Verify Point #62)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter 1440x900 (Verify Point #63)</t>
-  </si>
-  <si>
-    <t>0.26</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale 1280x800 (Verify Point #64)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource 1024x768 (Verify Point #65)</t>
-  </si>
-  <si>
-    <t>0.80</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path 768x1024 (Verify Point #66)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component 375x812 (Verify Point #67)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for sign-in-button (Verify Point #68)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for email-input (Verify Point #69)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for password-field (Verify Point #70)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for search-bar (Verify Point #71)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated college-card (Verify Point #72)</t>
-  </si>
-  <si>
-    <t>0.64</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for compare-btn (Verify Point #73)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on profile-settings (Verify Point #74)</t>
-  </si>
-  <si>
-    <t>0.25</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for ai-chat-input (Verify Point #75)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for en-US (Verify Point #76)</t>
-  </si>
-  <si>
-    <t>0.91</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for hi-IN (Verify Point #77)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field ta-IN (Verify Point #78)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to header-nav (Verify Point #79)</t>
-  </si>
-  <si>
-    <t>0.62</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution sidebar-menu (Verify Point #80)</t>
-  </si>
-  <si>
-    <t>0.69</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element footer-links (Verify Point #81)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container login-form (Verify Point #82)</t>
-  </si>
-  <si>
-    <t>0.99</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter register-form (Verify Point #83)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale dashboard-grid (Verify Point #84)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource detail-page (Verify Point #85)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path fees-filter (Verify Point #86)</t>
-  </si>
-  <si>
-    <t>0.37</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component nirf-sort (Verify Point #87)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for course-filter (Verify Point #88)</t>
-  </si>
-  <si>
-    <t>0.61</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for state-filter (Verify Point #89)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for firebase-auth (Verify Point #90)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for firestore-read (Verify Point #91)</t>
-  </si>
-  <si>
-    <t>0.60</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #92)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for expo-router (Verify Point #93)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on college-list (Verify Point #94)</t>
-  </si>
-  <si>
-    <t>0.63</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for saved-list (Verify Point #95)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for comparison-list (Verify Point #96)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for chat-history (Verify Point #97)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field avatar-upload (Verify Point #98)</t>
-  </si>
-  <si>
-    <t>0.96</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to theme-toggle (Verify Point #99)</t>
-  </si>
-  <si>
-    <t>0.47</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution notification-prefs (Verify Point #100)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element session-token (Verify Point #101)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container XSS-injection (Verify Point #102)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter SQL-injection (Verify Point #103)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale CSRF-token (Verify Point #104)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource CORS-origin (Verify Point #105)</t>
-  </si>
-  <si>
-    <t>0.52</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path CSP-header (Verify Point #106)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component X-Frame-Options (Verify Point #107)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for primary-font (Verify Point #108)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for accent-color (Verify Point #109)</t>
-  </si>
-  <si>
-    <t>0.79</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for glassmorphic-transparency (Verify Point #110)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for border-radius (Verify Point #111)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated bundle-size (Verify Point #112)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for first-meaningful-paint (Verify Point #113)</t>
-  </si>
-  <si>
-    <t>0.27</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on time-to-interactive (Verify Point #114)</t>
-  </si>
-  <si>
-    <t>0.40</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for dom-depth (Verify Point #115)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for lost-item-card (Verify Point #116)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for users-ref (Verify Point #117)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field items-ref (Verify Point #118)</t>
-  </si>
-  <si>
-    <t>0.29</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to de-DE (Verify Point #119)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution fr-FR (Verify Point #120)</t>
-  </si>
-  <si>
-    <t>0.38</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element ja-JP (Verify Point #121)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container pt-BR (Verify Point #122)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter it-IT (Verify Point #123)</t>
-  </si>
-  <si>
-    <t>0.55</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #124)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #125)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #126)</t>
-  </si>
-  <si>
-    <t>0.81</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #127)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #128)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for 375x812 (Verify Point #129)</t>
-  </si>
-  <si>
-    <t>0.49</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for sign-in-button (Verify Point #130)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for email-input (Verify Point #131)</t>
-  </si>
-  <si>
-    <t>0.98</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated password-field (Verify Point #132)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for search-bar (Verify Point #133)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on college-card (Verify Point #134)</t>
-  </si>
-  <si>
-    <t>0.54</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for compare-btn (Verify Point #135)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for profile-settings (Verify Point #136)</t>
-  </si>
-  <si>
-    <t>0.35</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for ai-chat-input (Verify Point #137)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field en-US (Verify Point #138)</t>
-  </si>
-  <si>
-    <t>0.50</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to hi-IN (Verify Point #139)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution ta-IN (Verify Point #140)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element header-nav (Verify Point #141)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container sidebar-menu (Verify Point #142)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter footer-links (Verify Point #143)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale login-form (Verify Point #144)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource register-form (Verify Point #145)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path dashboard-grid (Verify Point #146)</t>
-  </si>
-  <si>
-    <t>0.20</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component detail-page (Verify Point #147)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for fees-filter (Verify Point #148)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for nirf-sort (Verify Point #149)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for course-filter (Verify Point #150)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for state-filter (Verify Point #151)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated firebase-auth (Verify Point #152)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for firestore-read (Verify Point #153)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on groq-api (Verify Point #154)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for expo-router (Verify Point #155)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for college-list (Verify Point #156)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for saved-list (Verify Point #157)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field comparison-list (Verify Point #158)</t>
-  </si>
-  <si>
-    <t>0.24</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to chat-history (Verify Point #159)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution avatar-upload (Verify Point #160)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element theme-toggle (Verify Point #161)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container notification-prefs (Verify Point #162)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter session-token (Verify Point #163)</t>
-  </si>
-  <si>
-    <t>0.58</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale XSS-injection (Verify Point #164)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #165)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path CSRF-token (Verify Point #166)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component CORS-origin (Verify Point #167)</t>
-  </si>
-  <si>
-    <t>0.97</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for CSP-header (Verify Point #168)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for X-Frame-Options (Verify Point #169)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for primary-font (Verify Point #170)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for accent-color (Verify Point #171)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated glassmorphic-transparency (Verify Point #172)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for border-radius (Verify Point #173)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on bundle-size (Verify Point #174)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for first-meaningful-paint (Verify Point #175)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for time-to-interactive (Verify Point #176)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for dom-depth (Verify Point #177)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field lost-item-card (Verify Point #178)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to users-ref (Verify Point #179)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution items-ref (Verify Point #180)</t>
-  </si>
-  <si>
-    <t>0.56</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element de-DE (Verify Point #181)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container fr-FR (Verify Point #182)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter ja-JP (Verify Point #183)</t>
-  </si>
-  <si>
-    <t>0.72</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale pt-BR (Verify Point #184)</t>
-  </si>
-  <si>
-    <t>0.33</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource it-IT (Verify Point #185)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path 1920x1080 (Verify Point #186)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component 1440x900 (Verify Point #187)</t>
-  </si>
-  <si>
-    <t>0.59</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for 1280x800 (Verify Point #188)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for 1024x768 (Verify Point #189)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for 768x1024 (Verify Point #190)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for 375x812 (Verify Point #191)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated sign-in-button (Verify Point #192)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for email-input (Verify Point #193)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on password-field (Verify Point #194)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for search-bar (Verify Point #195)</t>
-  </si>
-  <si>
-    <t>0.90</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for college-card (Verify Point #196)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for compare-btn (Verify Point #197)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field profile-settings (Verify Point #198)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to ai-chat-input (Verify Point #199)</t>
-  </si>
-  <si>
-    <t>0.84</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution en-US (Verify Point #200)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element hi-IN (Verify Point #201)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container ta-IN (Verify Point #202)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter header-nav (Verify Point #203)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale sidebar-menu (Verify Point #204)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource footer-links (Verify Point #205)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path login-form (Verify Point #206)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component register-form (Verify Point #207)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for dashboard-grid (Verify Point #208)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for detail-page (Verify Point #209)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for fees-filter (Verify Point #210)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for nirf-sort (Verify Point #211)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated course-filter (Verify Point #212)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for state-filter (Verify Point #213)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on firebase-auth (Verify Point #214)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for firestore-read (Verify Point #215)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for groq-api (Verify Point #216)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for expo-router (Verify Point #217)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field college-list (Verify Point #218)</t>
-  </si>
-  <si>
-    <t>0.74</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to saved-list (Verify Point #219)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution comparison-list (Verify Point #220)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element chat-history (Verify Point #221)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container avatar-upload (Verify Point #222)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter theme-toggle (Verify Point #223)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale notification-prefs (Verify Point #224)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource session-token (Verify Point #225)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path XSS-injection (Verify Point #226)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component SQL-injection (Verify Point #227)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for CSRF-token (Verify Point #228)</t>
-  </si>
-  <si>
-    <t>0.44</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for CORS-origin (Verify Point #229)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for CSP-header (Verify Point #230)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for X-Frame-Options (Verify Point #231)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated primary-font (Verify Point #232)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for accent-color (Verify Point #233)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on glassmorphic-transparency (Verify Point #234)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for border-radius (Verify Point #235)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for bundle-size (Verify Point #236)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for first-meaningful-paint (Verify Point #237)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field time-to-interactive (Verify Point #238)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to dom-depth (Verify Point #239)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution lost-item-card (Verify Point #240)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element users-ref (Verify Point #241)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container items-ref (Verify Point #242)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter de-DE (Verify Point #243)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale fr-FR (Verify Point #244)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource ja-JP (Verify Point #245)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path pt-BR (Verify Point #246)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component it-IT (Verify Point #247)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #248)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #249)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #250)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #251)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated 768x1024 (Verify Point #252)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for 375x812 (Verify Point #253)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on sign-in-button (Verify Point #254)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for email-input (Verify Point #255)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for password-field (Verify Point #256)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for search-bar (Verify Point #257)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field college-card (Verify Point #258)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to compare-btn (Verify Point #259)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution profile-settings (Verify Point #260)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element ai-chat-input (Verify Point #261)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container en-US (Verify Point #262)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter hi-IN (Verify Point #263)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale ta-IN (Verify Point #264)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource header-nav (Verify Point #265)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path sidebar-menu (Verify Point #266)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component footer-links (Verify Point #267)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for login-form (Verify Point #268)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for register-form (Verify Point #269)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for dashboard-grid (Verify Point #270)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for detail-page (Verify Point #271)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated fees-filter (Verify Point #272)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for nirf-sort (Verify Point #273)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on course-filter (Verify Point #274)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for state-filter (Verify Point #275)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for firebase-auth (Verify Point #276)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for firestore-read (Verify Point #277)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field groq-api (Verify Point #278)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to expo-router (Verify Point #279)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution college-list (Verify Point #280)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element saved-list (Verify Point #281)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container comparison-list (Verify Point #282)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter chat-history (Verify Point #283)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale avatar-upload (Verify Point #284)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource theme-toggle (Verify Point #285)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path notification-prefs (Verify Point #286)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component session-token (Verify Point #287)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for XSS-injection (Verify Point #288)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for SQL-injection (Verify Point #289)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for CSRF-token (Verify Point #290)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for CORS-origin (Verify Point #291)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated CSP-header (Verify Point #292)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for X-Frame-Options (Verify Point #293)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on primary-font (Verify Point #294)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for accent-color (Verify Point #295)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for glassmorphic-transparency (Verify Point #296)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for border-radius (Verify Point #297)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field bundle-size (Verify Point #298)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to first-meaningful-paint (Verify Point #299)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution time-to-interactive (Verify Point #300)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element dom-depth (Verify Point #301)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container lost-item-card (Verify Point #302)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter users-ref (Verify Point #303)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale items-ref (Verify Point #304)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource de-DE (Verify Point #305)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path fr-FR (Verify Point #306)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component ja-JP (Verify Point #307)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for pt-BR (Verify Point #308)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for it-IT (Verify Point #309)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for 1920x1080 (Verify Point #310)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for 1440x900 (Verify Point #311)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated 1280x800 (Verify Point #312)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for 1024x768 (Verify Point #313)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on 768x1024 (Verify Point #314)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for 375x812 (Verify Point #315)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for sign-in-button (Verify Point #316)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for email-input (Verify Point #317)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field password-field (Verify Point #318)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to search-bar (Verify Point #319)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution college-card (Verify Point #320)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element compare-btn (Verify Point #321)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container profile-settings (Verify Point #322)</t>
-  </si>
-  <si>
-    <t>0.86</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter ai-chat-input (Verify Point #323)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale en-US (Verify Point #324)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource hi-IN (Verify Point #325)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path ta-IN (Verify Point #326)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component header-nav (Verify Point #327)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for sidebar-menu (Verify Point #328)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for footer-links (Verify Point #329)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Details]: Verify college detail page fields for login-form (Verify Point #330)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for register-form (Verify Point #331)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated dashboard-grid (Verify Point #332)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for detail-page (Verify Point #333)</t>
-  </si>
-  <si>
     <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on fees-filter (Verify Point #334)</t>
   </si>
   <si>
@@ -1471,9 +1484,6 @@
     <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to email-input (Verify Point #379)</t>
   </si>
   <si>
-    <t>1.00</t>
-  </si>
-  <si>
     <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution password-field (Verify Point #380)</t>
   </si>
   <si>
@@ -1489,9 +1499,6 @@
     <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale profile-settings (Verify Point #384)</t>
   </si>
   <si>
-    <t>0.68</t>
-  </si>
-  <si>
     <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource ai-chat-input (Verify Point #385)</t>
   </si>
   <si>
@@ -1546,13 +1553,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>23</t>
+    <t>24</t>
   </si>
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 15:45:21 UTC</t>
+    <t>2026-06-24 03:38:00 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -2160,10 +2167,10 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2171,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
         <v>27</v>
@@ -2188,13 +2195,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E13" t="s">
         <v>27</v>
@@ -2205,13 +2212,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E14" t="s">
         <v>27</v>
@@ -2222,13 +2229,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s">
         <v>27</v>
@@ -2239,13 +2246,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E16" t="s">
         <v>27</v>
@@ -2256,13 +2263,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E17" t="s">
         <v>27</v>
@@ -2273,13 +2280,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E18" t="s">
         <v>27</v>
@@ -2290,13 +2297,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E19" t="s">
         <v>27</v>
@@ -2307,13 +2314,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E20" t="s">
         <v>27</v>
@@ -2324,13 +2331,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
         <v>27</v>
@@ -2341,13 +2348,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E22" t="s">
         <v>27</v>
@@ -2358,13 +2365,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E23" t="s">
         <v>27</v>
@@ -2375,13 +2382,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E24" t="s">
         <v>27</v>
@@ -2392,13 +2399,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E25" t="s">
         <v>27</v>
@@ -2409,13 +2416,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E26" t="s">
         <v>27</v>
@@ -2426,13 +2433,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E27" t="s">
         <v>27</v>
@@ -2443,13 +2450,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E28" t="s">
         <v>27</v>
@@ -2460,13 +2467,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E29" t="s">
         <v>27</v>
@@ -2477,13 +2484,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E30" t="s">
         <v>27</v>
@@ -2494,13 +2501,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E31" t="s">
         <v>27</v>
@@ -2511,13 +2518,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="E32" t="s">
         <v>27</v>
@@ -2528,13 +2535,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D33" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="E33" t="s">
         <v>27</v>
@@ -2545,13 +2552,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D34" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E34" t="s">
         <v>27</v>
@@ -2562,13 +2569,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="E35" t="s">
         <v>27</v>
@@ -2579,13 +2586,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E36" t="s">
         <v>27</v>
@@ -2596,13 +2603,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E37" t="s">
         <v>27</v>
@@ -2613,13 +2620,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D38" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E38" t="s">
         <v>27</v>
@@ -2630,13 +2637,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="E39" t="s">
         <v>27</v>
@@ -2647,13 +2654,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="E40" t="s">
         <v>27</v>
@@ -2664,13 +2671,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D41" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E41" t="s">
         <v>27</v>
@@ -2681,13 +2688,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D42" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E42" t="s">
         <v>27</v>
@@ -2698,13 +2705,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E43" t="s">
         <v>27</v>
@@ -2715,13 +2722,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E44" t="s">
         <v>27</v>
@@ -2732,13 +2739,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="E45" t="s">
         <v>27</v>
@@ -2749,13 +2756,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E46" t="s">
         <v>27</v>
@@ -2766,13 +2773,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E47" t="s">
         <v>27</v>
@@ -2783,13 +2790,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="E48" t="s">
         <v>27</v>
@@ -2800,13 +2807,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="E49" t="s">
         <v>27</v>
@@ -2817,13 +2824,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E50" t="s">
         <v>27</v>
@@ -2834,13 +2841,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D51" t="s">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="E51" t="s">
         <v>27</v>
@@ -2851,13 +2858,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E52" t="s">
         <v>27</v>
@@ -2868,13 +2875,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E53" t="s">
         <v>27</v>
@@ -2885,13 +2892,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="E54" t="s">
         <v>27</v>
@@ -2902,13 +2909,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D55" t="s">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="E55" t="s">
         <v>27</v>
@@ -2919,13 +2926,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D56" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="E56" t="s">
         <v>27</v>
@@ -2936,13 +2943,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D57" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E57" t="s">
         <v>27</v>
@@ -2953,13 +2960,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D58" t="s">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="E58" t="s">
         <v>27</v>
@@ -2970,13 +2977,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D59" t="s">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="E59" t="s">
         <v>27</v>
@@ -2987,13 +2994,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D60" t="s">
-        <v>52</v>
+        <v>123</v>
       </c>
       <c r="E60" t="s">
         <v>27</v>
@@ -3004,13 +3011,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E61" t="s">
         <v>27</v>
@@ -3021,13 +3028,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D62" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E62" t="s">
         <v>27</v>
@@ -3038,13 +3045,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D63" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="E63" t="s">
         <v>27</v>
@@ -3055,13 +3062,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D64" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="E64" t="s">
         <v>27</v>
@@ -3072,13 +3079,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E65" t="s">
         <v>27</v>
@@ -3089,13 +3096,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D66" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="E66" t="s">
         <v>27</v>
@@ -3106,13 +3113,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D67" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E67" t="s">
         <v>27</v>
@@ -3123,13 +3130,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D68" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E68" t="s">
         <v>27</v>
@@ -3140,13 +3147,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D69" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E69" t="s">
         <v>27</v>
@@ -3157,13 +3164,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D70" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="E70" t="s">
         <v>27</v>
@@ -3174,13 +3181,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D71" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="E71" t="s">
         <v>27</v>
@@ -3191,13 +3198,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D72" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="E72" t="s">
         <v>27</v>
@@ -3208,13 +3215,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D73" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="E73" t="s">
         <v>27</v>
@@ -3225,13 +3232,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D74" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E74" t="s">
         <v>27</v>
@@ -3242,13 +3249,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D75" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="E75" t="s">
         <v>27</v>
@@ -3259,13 +3266,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D76" t="s">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="E76" t="s">
         <v>27</v>
@@ -3276,13 +3283,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D77" t="s">
-        <v>84</v>
+        <v>147</v>
       </c>
       <c r="E77" t="s">
         <v>27</v>
@@ -3293,13 +3300,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="E78" t="s">
         <v>27</v>
@@ -3310,13 +3317,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D79" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="E79" t="s">
         <v>27</v>
@@ -3327,13 +3334,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D80" t="s">
-        <v>144</v>
+        <v>54</v>
       </c>
       <c r="E80" t="s">
         <v>27</v>
@@ -3344,13 +3351,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D81" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E81" t="s">
         <v>27</v>
@@ -3361,13 +3368,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D82" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E82" t="s">
         <v>27</v>
@@ -3378,13 +3385,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D83" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="E83" t="s">
         <v>27</v>
@@ -3395,13 +3402,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D84" t="s">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="E84" t="s">
         <v>27</v>
@@ -3412,13 +3419,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D85" t="s">
-        <v>40</v>
+        <v>158</v>
       </c>
       <c r="E85" t="s">
         <v>27</v>
@@ -3429,13 +3436,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D86" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="E86" t="s">
         <v>27</v>
@@ -3446,13 +3453,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D87" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E87" t="s">
         <v>27</v>
@@ -3463,13 +3470,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D88" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E88" t="s">
         <v>27</v>
@@ -3480,13 +3487,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D89" t="s">
-        <v>87</v>
+        <v>164</v>
       </c>
       <c r="E89" t="s">
         <v>27</v>
@@ -3497,13 +3504,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D90" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E90" t="s">
         <v>27</v>
@@ -3514,13 +3521,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D91" t="s">
-        <v>38</v>
+        <v>168</v>
       </c>
       <c r="E91" t="s">
         <v>27</v>
@@ -3531,13 +3538,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D92" t="s">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="E92" t="s">
         <v>27</v>
@@ -3548,13 +3555,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D93" t="s">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="E93" t="s">
         <v>27</v>
@@ -3565,13 +3572,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D94" t="s">
-        <v>108</v>
+        <v>172</v>
       </c>
       <c r="E94" t="s">
         <v>27</v>
@@ -3582,13 +3589,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D95" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="E95" t="s">
         <v>27</v>
@@ -3599,13 +3606,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D96" t="s">
-        <v>169</v>
+        <v>91</v>
       </c>
       <c r="E96" t="s">
         <v>27</v>
@@ -3616,13 +3623,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D97" t="s">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="E97" t="s">
         <v>27</v>
@@ -3633,13 +3640,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D98" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E98" t="s">
         <v>27</v>
@@ -3650,13 +3657,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D99" t="s">
-        <v>38</v>
+        <v>179</v>
       </c>
       <c r="E99" t="s">
         <v>27</v>
@@ -3667,13 +3674,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D100" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="E100" t="s">
         <v>27</v>
@@ -3684,13 +3691,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="E101" t="s">
         <v>27</v>
@@ -3701,13 +3708,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D102" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E102" t="s">
         <v>27</v>
@@ -3718,13 +3725,13 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D103" t="s">
-        <v>127</v>
+        <v>186</v>
       </c>
       <c r="E103" t="s">
         <v>27</v>
@@ -3735,13 +3742,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D104" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="E104" t="s">
         <v>27</v>
@@ -3752,13 +3759,13 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D105" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E105" t="s">
         <v>27</v>
@@ -3769,13 +3776,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D106" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="E106" t="s">
         <v>27</v>
@@ -3786,13 +3793,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D107" t="s">
-        <v>183</v>
+        <v>59</v>
       </c>
       <c r="E107" t="s">
         <v>27</v>
@@ -3803,13 +3810,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D108" t="s">
-        <v>46</v>
+        <v>152</v>
       </c>
       <c r="E108" t="s">
         <v>27</v>
@@ -3820,13 +3827,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D109" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="E109" t="s">
         <v>27</v>
@@ -3837,13 +3844,13 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D110" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="E110" t="s">
         <v>27</v>
@@ -3854,13 +3861,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D111" t="s">
-        <v>188</v>
+        <v>99</v>
       </c>
       <c r="E111" t="s">
         <v>27</v>
@@ -3871,13 +3878,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D112" t="s">
-        <v>127</v>
+        <v>48</v>
       </c>
       <c r="E112" t="s">
         <v>27</v>
@@ -3888,13 +3895,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D113" t="s">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="E113" t="s">
         <v>27</v>
@@ -3905,13 +3912,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D114" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="E114" t="s">
         <v>27</v>
@@ -3922,13 +3929,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D115" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="E115" t="s">
         <v>27</v>
@@ -3939,13 +3946,13 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D116" t="s">
-        <v>195</v>
+        <v>73</v>
       </c>
       <c r="E116" t="s">
         <v>27</v>
@@ -3956,13 +3963,13 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D117" t="s">
-        <v>84</v>
+        <v>166</v>
       </c>
       <c r="E117" t="s">
         <v>27</v>
@@ -3973,13 +3980,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D118" t="s">
-        <v>84</v>
+        <v>205</v>
       </c>
       <c r="E118" t="s">
         <v>27</v>
@@ -3990,13 +3997,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D119" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E119" t="s">
         <v>27</v>
@@ -4007,13 +4014,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D120" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="E120" t="s">
         <v>27</v>
@@ -4024,13 +4031,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D121" t="s">
-        <v>188</v>
+        <v>38</v>
       </c>
       <c r="E121" t="s">
         <v>27</v>
@@ -4041,13 +4048,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D122" t="s">
-        <v>203</v>
+        <v>95</v>
       </c>
       <c r="E122" t="s">
         <v>27</v>
@@ -4058,13 +4065,13 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D123" t="s">
-        <v>108</v>
+        <v>212</v>
       </c>
       <c r="E123" t="s">
         <v>27</v>
@@ -4075,13 +4082,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D124" t="s">
-        <v>138</v>
+        <v>38</v>
       </c>
       <c r="E124" t="s">
         <v>27</v>
@@ -4092,13 +4099,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D125" t="s">
-        <v>207</v>
+        <v>95</v>
       </c>
       <c r="E125" t="s">
         <v>27</v>
@@ -4109,13 +4116,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D126" t="s">
-        <v>122</v>
+        <v>216</v>
       </c>
       <c r="E126" t="s">
         <v>27</v>
@@ -4126,13 +4133,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D127" t="s">
-        <v>104</v>
+        <v>190</v>
       </c>
       <c r="E127" t="s">
         <v>27</v>
@@ -4143,13 +4150,13 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D128" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E128" t="s">
         <v>27</v>
@@ -4160,13 +4167,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D129" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="E129" t="s">
         <v>27</v>
@@ -4177,13 +4184,13 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D130" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E130" t="s">
         <v>27</v>
@@ -4194,13 +4201,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D131" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="E131" t="s">
         <v>27</v>
@@ -4211,13 +4218,13 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D132" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="E132" t="s">
         <v>27</v>
@@ -4228,13 +4235,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D133" t="s">
-        <v>218</v>
+        <v>116</v>
       </c>
       <c r="E133" t="s">
         <v>27</v>
@@ -4245,13 +4252,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D134" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E134" t="s">
         <v>27</v>
@@ -4262,13 +4269,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D135" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="E135" t="s">
         <v>27</v>
@@ -4279,13 +4286,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D136" t="s">
-        <v>222</v>
+        <v>172</v>
       </c>
       <c r="E136" t="s">
         <v>27</v>
@@ -4296,13 +4303,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D137" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="E137" t="s">
         <v>27</v>
@@ -4313,13 +4320,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D138" t="s">
-        <v>225</v>
+        <v>91</v>
       </c>
       <c r="E138" t="s">
         <v>27</v>
@@ -4330,13 +4337,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D139" t="s">
-        <v>36</v>
+        <v>160</v>
       </c>
       <c r="E139" t="s">
         <v>27</v>
@@ -4347,13 +4354,13 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D140" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E140" t="s">
         <v>27</v>
@@ -4364,13 +4371,13 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D141" t="s">
-        <v>228</v>
+        <v>59</v>
       </c>
       <c r="E141" t="s">
         <v>27</v>
@@ -4381,13 +4388,13 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D142" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="E142" t="s">
         <v>27</v>
@@ -4398,13 +4405,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D143" t="s">
-        <v>122</v>
+        <v>237</v>
       </c>
       <c r="E143" t="s">
         <v>27</v>
@@ -4415,13 +4422,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D144" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="E144" t="s">
         <v>27</v>
@@ -4432,13 +4439,13 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D145" t="s">
-        <v>68</v>
+        <v>172</v>
       </c>
       <c r="E145" t="s">
         <v>27</v>
@@ -4449,13 +4456,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D146" t="s">
-        <v>70</v>
+        <v>131</v>
       </c>
       <c r="E146" t="s">
         <v>27</v>
@@ -4466,13 +4473,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D147" t="s">
-        <v>95</v>
+        <v>190</v>
       </c>
       <c r="E147" t="s">
         <v>27</v>
@@ -4483,13 +4490,13 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D148" t="s">
-        <v>237</v>
+        <v>40</v>
       </c>
       <c r="E148" t="s">
         <v>27</v>
@@ -4500,13 +4507,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D149" t="s">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="E149" t="s">
         <v>27</v>
@@ -4517,13 +4524,13 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D150" t="s">
-        <v>225</v>
+        <v>56</v>
       </c>
       <c r="E150" t="s">
         <v>27</v>
@@ -4534,13 +4541,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D151" t="s">
-        <v>50</v>
+        <v>154</v>
       </c>
       <c r="E151" t="s">
         <v>27</v>
@@ -4551,13 +4558,13 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D152" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E152" t="s">
         <v>27</v>
@@ -4568,13 +4575,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D153" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="E153" t="s">
         <v>27</v>
@@ -4585,13 +4592,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D154" t="s">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="E154" t="s">
         <v>27</v>
@@ -4602,13 +4609,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D155" t="s">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="E155" t="s">
         <v>27</v>
@@ -4619,13 +4626,13 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D156" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="E156" t="s">
         <v>27</v>
@@ -4636,13 +4643,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D157" t="s">
-        <v>200</v>
+        <v>71</v>
       </c>
       <c r="E157" t="s">
         <v>27</v>
@@ -4653,13 +4660,13 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D158" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="E158" t="s">
         <v>27</v>
@@ -4670,13 +4677,13 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D159" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="E159" t="s">
         <v>27</v>
@@ -4687,13 +4694,13 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D160" t="s">
-        <v>250</v>
+        <v>188</v>
       </c>
       <c r="E160" t="s">
         <v>27</v>
@@ -4704,13 +4711,13 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D161" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="E161" t="s">
         <v>27</v>
@@ -4721,13 +4728,13 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D162" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="E162" t="s">
         <v>27</v>
@@ -4738,13 +4745,13 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D163" t="s">
-        <v>237</v>
+        <v>120</v>
       </c>
       <c r="E163" t="s">
         <v>27</v>
@@ -4755,13 +4762,13 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D164" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="E164" t="s">
         <v>27</v>
@@ -4772,13 +4779,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D165" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E165" t="s">
         <v>27</v>
@@ -4789,13 +4796,13 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D166" t="s">
-        <v>82</v>
+        <v>263</v>
       </c>
       <c r="E166" t="s">
         <v>27</v>
@@ -4806,13 +4813,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D167" t="s">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="E167" t="s">
         <v>27</v>
@@ -4823,13 +4830,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D168" t="s">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="E168" t="s">
         <v>27</v>
@@ -4840,13 +4847,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D169" t="s">
-        <v>261</v>
+        <v>176</v>
       </c>
       <c r="E169" t="s">
         <v>27</v>
@@ -4857,13 +4864,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D170" t="s">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="E170" t="s">
         <v>27</v>
@@ -4874,13 +4881,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D171" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="E171" t="s">
         <v>27</v>
@@ -4891,13 +4898,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D172" t="s">
-        <v>165</v>
+        <v>205</v>
       </c>
       <c r="E172" t="s">
         <v>27</v>
@@ -4908,13 +4915,13 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D173" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E173" t="s">
         <v>27</v>
@@ -4925,13 +4932,13 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D174" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="E174" t="s">
         <v>27</v>
@@ -4942,13 +4949,13 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D175" t="s">
-        <v>44</v>
+        <v>263</v>
       </c>
       <c r="E175" t="s">
         <v>27</v>
@@ -4959,13 +4966,13 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D176" t="s">
-        <v>256</v>
+        <v>46</v>
       </c>
       <c r="E176" t="s">
         <v>27</v>
@@ -4976,13 +4983,13 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D177" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="E177" t="s">
         <v>27</v>
@@ -4993,13 +5000,13 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D178" t="s">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="E178" t="s">
         <v>27</v>
@@ -5010,13 +5017,13 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D179" t="s">
-        <v>183</v>
+        <v>125</v>
       </c>
       <c r="E179" t="s">
         <v>27</v>
@@ -5027,13 +5034,13 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D180" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="E180" t="s">
         <v>27</v>
@@ -5044,13 +5051,13 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D181" t="s">
-        <v>124</v>
+        <v>223</v>
       </c>
       <c r="E181" t="s">
         <v>27</v>
@@ -5061,13 +5068,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D182" t="s">
-        <v>275</v>
+        <v>166</v>
       </c>
       <c r="E182" t="s">
         <v>27</v>
@@ -5078,13 +5085,13 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D183" t="s">
-        <v>195</v>
+        <v>147</v>
       </c>
       <c r="E183" t="s">
         <v>27</v>
@@ -5095,13 +5102,13 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D184" t="s">
-        <v>188</v>
+        <v>147</v>
       </c>
       <c r="E184" t="s">
         <v>27</v>
@@ -5112,13 +5119,13 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D185" t="s">
-        <v>279</v>
+        <v>50</v>
       </c>
       <c r="E185" t="s">
         <v>27</v>
@@ -5129,13 +5136,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D186" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E186" t="s">
         <v>27</v>
@@ -5146,13 +5153,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D187" t="s">
-        <v>56</v>
+        <v>233</v>
       </c>
       <c r="E187" t="s">
         <v>27</v>
@@ -5163,13 +5170,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D188" t="s">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="E188" t="s">
         <v>27</v>
@@ -5180,13 +5187,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D189" t="s">
-        <v>285</v>
+        <v>131</v>
       </c>
       <c r="E189" t="s">
         <v>27</v>
@@ -5197,13 +5204,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D190" t="s">
-        <v>207</v>
+        <v>111</v>
       </c>
       <c r="E190" t="s">
         <v>27</v>
@@ -5214,13 +5221,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D191" t="s">
-        <v>148</v>
+        <v>263</v>
       </c>
       <c r="E191" t="s">
         <v>27</v>
@@ -5231,13 +5238,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D192" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="E192" t="s">
         <v>27</v>
@@ -5248,13 +5255,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D193" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="E193" t="s">
         <v>27</v>
@@ -5265,13 +5272,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D194" t="s">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="E194" t="s">
         <v>27</v>
@@ -5282,13 +5289,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D195" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="E195" t="s">
         <v>27</v>
@@ -5299,13 +5306,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D196" t="s">
-        <v>89</v>
+        <v>295</v>
       </c>
       <c r="E196" t="s">
         <v>27</v>
@@ -5316,13 +5323,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D197" t="s">
-        <v>294</v>
+        <v>69</v>
       </c>
       <c r="E197" t="s">
         <v>27</v>
@@ -5333,13 +5340,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D198" t="s">
-        <v>169</v>
+        <v>116</v>
       </c>
       <c r="E198" t="s">
         <v>27</v>
@@ -5350,13 +5357,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D199" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="E199" t="s">
         <v>27</v>
@@ -5367,13 +5374,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D200" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="E200" t="s">
         <v>27</v>
@@ -5384,13 +5391,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D201" t="s">
-        <v>299</v>
+        <v>59</v>
       </c>
       <c r="E201" t="s">
         <v>27</v>
@@ -5401,13 +5408,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D202" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E202" t="s">
         <v>27</v>
@@ -5418,13 +5425,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D203" t="s">
-        <v>158</v>
+        <v>93</v>
       </c>
       <c r="E203" t="s">
         <v>27</v>
@@ -5435,13 +5442,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D204" t="s">
-        <v>281</v>
+        <v>86</v>
       </c>
       <c r="E204" t="s">
         <v>27</v>
@@ -5452,13 +5459,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D205" t="s">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="E205" t="s">
         <v>27</v>
@@ -5469,13 +5476,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D206" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="E206" t="s">
         <v>27</v>
@@ -5486,13 +5493,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D207" t="s">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="E207" t="s">
         <v>27</v>
@@ -5503,13 +5510,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D208" t="s">
-        <v>285</v>
+        <v>111</v>
       </c>
       <c r="E208" t="s">
         <v>27</v>
@@ -5520,13 +5527,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D209" t="s">
-        <v>225</v>
+        <v>42</v>
       </c>
       <c r="E209" t="s">
         <v>27</v>
@@ -5537,13 +5544,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D210" t="s">
-        <v>91</v>
+        <v>219</v>
       </c>
       <c r="E210" t="s">
         <v>27</v>
@@ -5554,13 +5561,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D211" t="s">
-        <v>153</v>
+        <v>105</v>
       </c>
       <c r="E211" t="s">
         <v>27</v>
@@ -5571,13 +5578,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D212" t="s">
-        <v>218</v>
+        <v>136</v>
       </c>
       <c r="E212" t="s">
         <v>27</v>
@@ -5588,13 +5595,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D213" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="E213" t="s">
         <v>27</v>
@@ -5605,13 +5612,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D214" t="s">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="E214" t="s">
         <v>27</v>
@@ -5622,13 +5629,13 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D215" t="s">
-        <v>141</v>
+        <v>38</v>
       </c>
       <c r="E215" t="s">
         <v>27</v>
@@ -5639,13 +5646,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D216" t="s">
-        <v>211</v>
+        <v>95</v>
       </c>
       <c r="E216" t="s">
         <v>27</v>
@@ -5656,13 +5663,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D217" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="E217" t="s">
         <v>27</v>
@@ -5673,13 +5680,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D218" t="s">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="E218" t="s">
         <v>27</v>
@@ -5690,13 +5697,13 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D219" t="s">
-        <v>148</v>
+        <v>263</v>
       </c>
       <c r="E219" t="s">
         <v>27</v>
@@ -5707,13 +5714,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D220" t="s">
-        <v>319</v>
+        <v>172</v>
       </c>
       <c r="E220" t="s">
         <v>27</v>
@@ -5730,7 +5737,7 @@
         <v>25</v>
       </c>
       <c r="D221" t="s">
-        <v>203</v>
+        <v>86</v>
       </c>
       <c r="E221" t="s">
         <v>27</v>
@@ -5747,7 +5754,7 @@
         <v>25</v>
       </c>
       <c r="D222" t="s">
-        <v>207</v>
+        <v>131</v>
       </c>
       <c r="E222" t="s">
         <v>27</v>
@@ -5764,7 +5771,7 @@
         <v>25</v>
       </c>
       <c r="D223" t="s">
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="E223" t="s">
         <v>27</v>
@@ -5781,7 +5788,7 @@
         <v>25</v>
       </c>
       <c r="D224" t="s">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="E224" t="s">
         <v>27</v>
@@ -5798,7 +5805,7 @@
         <v>25</v>
       </c>
       <c r="D225" t="s">
-        <v>279</v>
+        <v>46</v>
       </c>
       <c r="E225" t="s">
         <v>27</v>
@@ -5815,7 +5822,7 @@
         <v>25</v>
       </c>
       <c r="D226" t="s">
-        <v>281</v>
+        <v>216</v>
       </c>
       <c r="E226" t="s">
         <v>27</v>
@@ -5832,7 +5839,7 @@
         <v>25</v>
       </c>
       <c r="D227" t="s">
-        <v>225</v>
+        <v>166</v>
       </c>
       <c r="E227" t="s">
         <v>27</v>
@@ -5849,7 +5856,7 @@
         <v>25</v>
       </c>
       <c r="D228" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="E228" t="s">
         <v>27</v>
@@ -5866,7 +5873,7 @@
         <v>25</v>
       </c>
       <c r="D229" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="E229" t="s">
         <v>27</v>
@@ -5883,7 +5890,7 @@
         <v>25</v>
       </c>
       <c r="D230" t="s">
-        <v>330</v>
+        <v>54</v>
       </c>
       <c r="E230" t="s">
         <v>27</v>
@@ -5894,13 +5901,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
+        <v>330</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D231" t="s">
         <v>331</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D231" t="s">
-        <v>84</v>
       </c>
       <c r="E231" t="s">
         <v>27</v>
@@ -5917,7 +5924,7 @@
         <v>25</v>
       </c>
       <c r="D232" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="E232" t="s">
         <v>27</v>
@@ -5934,7 +5941,7 @@
         <v>25</v>
       </c>
       <c r="D233" t="s">
-        <v>169</v>
+        <v>331</v>
       </c>
       <c r="E233" t="s">
         <v>27</v>
@@ -5951,7 +5958,7 @@
         <v>25</v>
       </c>
       <c r="D234" t="s">
-        <v>225</v>
+        <v>84</v>
       </c>
       <c r="E234" t="s">
         <v>27</v>
@@ -5968,7 +5975,7 @@
         <v>25</v>
       </c>
       <c r="D235" t="s">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="E235" t="s">
         <v>27</v>
@@ -5985,7 +5992,7 @@
         <v>25</v>
       </c>
       <c r="D236" t="s">
-        <v>153</v>
+        <v>219</v>
       </c>
       <c r="E236" t="s">
         <v>27</v>
@@ -6002,7 +6009,7 @@
         <v>25</v>
       </c>
       <c r="D237" t="s">
-        <v>74</v>
+        <v>154</v>
       </c>
       <c r="E237" t="s">
         <v>27</v>
@@ -6019,7 +6026,7 @@
         <v>25</v>
       </c>
       <c r="D238" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="E238" t="s">
         <v>27</v>
@@ -6036,7 +6043,7 @@
         <v>25</v>
       </c>
       <c r="D239" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="E239" t="s">
         <v>27</v>
@@ -6053,7 +6060,7 @@
         <v>25</v>
       </c>
       <c r="D240" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="E240" t="s">
         <v>27</v>
@@ -6070,7 +6077,7 @@
         <v>25</v>
       </c>
       <c r="D241" t="s">
-        <v>120</v>
+        <v>188</v>
       </c>
       <c r="E241" t="s">
         <v>27</v>
@@ -6087,7 +6094,7 @@
         <v>25</v>
       </c>
       <c r="D242" t="s">
-        <v>203</v>
+        <v>343</v>
       </c>
       <c r="E242" t="s">
         <v>27</v>
@@ -6098,13 +6105,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D243" t="s">
-        <v>91</v>
+        <v>284</v>
       </c>
       <c r="E243" t="s">
         <v>27</v>
@@ -6115,13 +6122,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D244" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E244" t="s">
         <v>27</v>
@@ -6132,13 +6139,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D245" t="s">
-        <v>61</v>
+        <v>249</v>
       </c>
       <c r="E245" t="s">
         <v>27</v>
@@ -6149,13 +6156,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D246" t="s">
-        <v>275</v>
+        <v>61</v>
       </c>
       <c r="E246" t="s">
         <v>27</v>
@@ -6166,13 +6173,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D247" t="s">
-        <v>93</v>
+        <v>223</v>
       </c>
       <c r="E247" t="s">
         <v>27</v>
@@ -6183,13 +6190,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D248" t="s">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="E248" t="s">
         <v>27</v>
@@ -6200,13 +6207,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D249" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="E249" t="s">
         <v>27</v>
@@ -6217,13 +6224,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D250" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="E250" t="s">
         <v>27</v>
@@ -6234,13 +6241,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D251" t="s">
-        <v>281</v>
+        <v>123</v>
       </c>
       <c r="E251" t="s">
         <v>27</v>
@@ -6251,13 +6258,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D252" t="s">
-        <v>42</v>
+        <v>188</v>
       </c>
       <c r="E252" t="s">
         <v>27</v>
@@ -6268,13 +6275,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D253" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="E253" t="s">
         <v>27</v>
@@ -6285,13 +6292,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D254" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="E254" t="s">
         <v>27</v>
@@ -6302,13 +6309,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D255" t="s">
-        <v>93</v>
+        <v>343</v>
       </c>
       <c r="E255" t="s">
         <v>27</v>
@@ -6319,13 +6326,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D256" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="E256" t="s">
         <v>27</v>
@@ -6336,13 +6343,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D257" t="s">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="E257" t="s">
         <v>27</v>
@@ -6353,13 +6360,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D258" t="s">
-        <v>222</v>
+        <v>82</v>
       </c>
       <c r="E258" t="s">
         <v>27</v>
@@ -6370,13 +6377,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D259" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E259" t="s">
         <v>27</v>
@@ -6387,13 +6394,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D260" t="s">
-        <v>161</v>
+        <v>91</v>
       </c>
       <c r="E260" t="s">
         <v>27</v>
@@ -6404,13 +6411,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D261" t="s">
-        <v>256</v>
+        <v>140</v>
       </c>
       <c r="E261" t="s">
         <v>27</v>
@@ -6421,13 +6428,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D262" t="s">
-        <v>61</v>
+        <v>364</v>
       </c>
       <c r="E262" t="s">
         <v>27</v>
@@ -6438,13 +6445,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D263" t="s">
-        <v>165</v>
+        <v>118</v>
       </c>
       <c r="E263" t="s">
         <v>27</v>
@@ -6455,13 +6462,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D264" t="s">
-        <v>250</v>
+        <v>172</v>
       </c>
       <c r="E264" t="s">
         <v>27</v>
@@ -6472,13 +6479,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D265" t="s">
-        <v>61</v>
+        <v>181</v>
       </c>
       <c r="E265" t="s">
         <v>27</v>
@@ -6489,13 +6496,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D266" t="s">
-        <v>56</v>
+        <v>176</v>
       </c>
       <c r="E266" t="s">
         <v>27</v>
@@ -6506,13 +6513,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D267" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="E267" t="s">
         <v>27</v>
@@ -6523,13 +6530,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D268" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="E268" t="s">
         <v>27</v>
@@ -6540,13 +6547,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D269" t="s">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="E269" t="s">
         <v>27</v>
@@ -6557,13 +6564,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D270" t="s">
-        <v>188</v>
+        <v>111</v>
       </c>
       <c r="E270" t="s">
         <v>27</v>
@@ -6574,13 +6581,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D271" t="s">
-        <v>115</v>
+        <v>364</v>
       </c>
       <c r="E271" t="s">
         <v>27</v>
@@ -6591,13 +6598,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D272" t="s">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="E272" t="s">
         <v>27</v>
@@ -6608,13 +6615,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D273" t="s">
-        <v>222</v>
+        <v>65</v>
       </c>
       <c r="E273" t="s">
         <v>27</v>
@@ -6625,13 +6632,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D274" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E274" t="s">
         <v>27</v>
@@ -6642,13 +6649,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D275" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E275" t="s">
         <v>27</v>
@@ -6659,13 +6666,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D276" t="s">
-        <v>218</v>
+        <v>105</v>
       </c>
       <c r="E276" t="s">
         <v>27</v>
@@ -6676,13 +6683,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D277" t="s">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="E277" t="s">
         <v>27</v>
@@ -6693,13 +6700,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D278" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="E278" t="s">
         <v>27</v>
@@ -6710,13 +6717,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D279" t="s">
-        <v>319</v>
+        <v>116</v>
       </c>
       <c r="E279" t="s">
         <v>27</v>
@@ -6727,13 +6734,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D280" t="s">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="E280" t="s">
         <v>27</v>
@@ -6744,13 +6751,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D281" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="E281" t="s">
         <v>27</v>
@@ -6761,13 +6768,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D282" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="E282" t="s">
         <v>27</v>
@@ -6778,13 +6785,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D283" t="s">
-        <v>195</v>
+        <v>166</v>
       </c>
       <c r="E283" t="s">
         <v>27</v>
@@ -6795,13 +6802,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D284" t="s">
-        <v>261</v>
+        <v>190</v>
       </c>
       <c r="E284" t="s">
         <v>27</v>
@@ -6812,13 +6819,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D285" t="s">
-        <v>52</v>
+        <v>176</v>
       </c>
       <c r="E285" t="s">
         <v>27</v>
@@ -6829,13 +6836,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D286" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E286" t="s">
         <v>27</v>
@@ -6846,13 +6853,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D287" t="s">
-        <v>56</v>
+        <v>140</v>
       </c>
       <c r="E287" t="s">
         <v>27</v>
@@ -6863,13 +6870,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D288" t="s">
-        <v>319</v>
+        <v>71</v>
       </c>
       <c r="E288" t="s">
         <v>27</v>
@@ -6880,13 +6887,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D289" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="E289" t="s">
         <v>27</v>
@@ -6897,13 +6904,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D290" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="E290" t="s">
         <v>27</v>
@@ -6914,13 +6921,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D291" t="s">
-        <v>250</v>
+        <v>52</v>
       </c>
       <c r="E291" t="s">
         <v>27</v>
@@ -6931,13 +6938,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D292" t="s">
-        <v>56</v>
+        <v>190</v>
       </c>
       <c r="E292" t="s">
         <v>27</v>
@@ -6948,13 +6955,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D293" t="s">
-        <v>225</v>
+        <v>164</v>
       </c>
       <c r="E293" t="s">
         <v>27</v>
@@ -6965,13 +6972,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D294" t="s">
-        <v>161</v>
+        <v>44</v>
       </c>
       <c r="E294" t="s">
         <v>27</v>
@@ -6982,13 +6989,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D295" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="E295" t="s">
         <v>27</v>
@@ -6999,13 +7006,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D296" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E296" t="s">
         <v>27</v>
@@ -7016,13 +7023,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D297" t="s">
-        <v>174</v>
+        <v>123</v>
       </c>
       <c r="E297" t="s">
         <v>27</v>
@@ -7033,13 +7040,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D298" t="s">
-        <v>141</v>
+        <v>91</v>
       </c>
       <c r="E298" t="s">
         <v>27</v>
@@ -7050,13 +7057,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D299" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="E299" t="s">
         <v>27</v>
@@ -7067,13 +7074,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D300" t="s">
-        <v>174</v>
+        <v>40</v>
       </c>
       <c r="E300" t="s">
         <v>27</v>
@@ -7084,13 +7091,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D301" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="E301" t="s">
         <v>27</v>
@@ -7101,13 +7108,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D302" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E302" t="s">
         <v>27</v>
@@ -7118,13 +7125,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D303" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E303" t="s">
         <v>27</v>
@@ -7135,13 +7142,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D304" t="s">
-        <v>104</v>
+        <v>364</v>
       </c>
       <c r="E304" t="s">
         <v>27</v>
@@ -7152,13 +7159,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D305" t="s">
-        <v>80</v>
+        <v>408</v>
       </c>
       <c r="E305" t="s">
         <v>27</v>
@@ -7169,13 +7176,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D306" t="s">
-        <v>222</v>
+        <v>188</v>
       </c>
       <c r="E306" t="s">
         <v>27</v>
@@ -7186,13 +7193,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D307" t="s">
-        <v>218</v>
+        <v>44</v>
       </c>
       <c r="E307" t="s">
         <v>27</v>
@@ -7203,13 +7210,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D308" t="s">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="E308" t="s">
         <v>27</v>
@@ -7220,13 +7227,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D309" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="E309" t="s">
         <v>27</v>
@@ -7237,13 +7244,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D310" t="s">
-        <v>211</v>
+        <v>166</v>
       </c>
       <c r="E310" t="s">
         <v>27</v>
@@ -7254,13 +7261,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D311" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="E311" t="s">
         <v>27</v>
@@ -7271,13 +7278,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D312" t="s">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="E312" t="s">
         <v>27</v>
@@ -7288,13 +7295,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D313" t="s">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="E313" t="s">
         <v>27</v>
@@ -7305,13 +7312,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D314" t="s">
-        <v>115</v>
+        <v>331</v>
       </c>
       <c r="E314" t="s">
         <v>27</v>
@@ -7322,13 +7329,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D315" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E315" t="s">
         <v>27</v>
@@ -7339,13 +7346,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D316" t="s">
-        <v>48</v>
+        <v>216</v>
       </c>
       <c r="E316" t="s">
         <v>27</v>
@@ -7356,13 +7363,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D317" t="s">
-        <v>279</v>
+        <v>116</v>
       </c>
       <c r="E317" t="s">
         <v>27</v>
@@ -7373,13 +7380,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D318" t="s">
-        <v>285</v>
+        <v>422</v>
       </c>
       <c r="E318" t="s">
         <v>27</v>
@@ -7390,13 +7397,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D319" t="s">
-        <v>144</v>
+        <v>88</v>
       </c>
       <c r="E319" t="s">
         <v>27</v>
@@ -7407,13 +7414,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D320" t="s">
-        <v>281</v>
+        <v>190</v>
       </c>
       <c r="E320" t="s">
         <v>27</v>
@@ -7424,13 +7431,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D321" t="s">
-        <v>281</v>
+        <v>233</v>
       </c>
       <c r="E321" t="s">
         <v>27</v>
@@ -7441,13 +7448,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D322" t="s">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="E322" t="s">
         <v>27</v>
@@ -7458,13 +7465,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D323" t="s">
-        <v>50</v>
+        <v>284</v>
       </c>
       <c r="E323" t="s">
         <v>27</v>
@@ -7475,13 +7482,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D324" t="s">
-        <v>425</v>
+        <v>127</v>
       </c>
       <c r="E324" t="s">
         <v>27</v>
@@ -7492,13 +7499,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D325" t="s">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="E325" t="s">
         <v>27</v>
@@ -7509,13 +7516,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D326" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="E326" t="s">
         <v>27</v>
@@ -7526,13 +7533,13 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D327" t="s">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="E327" t="s">
         <v>27</v>
@@ -7543,13 +7550,13 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D328" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E328" t="s">
         <v>27</v>
@@ -7560,13 +7567,13 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D329" t="s">
-        <v>275</v>
+        <v>179</v>
       </c>
       <c r="E329" t="s">
         <v>27</v>
@@ -7577,13 +7584,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D330" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E330" t="s">
         <v>27</v>
@@ -7594,13 +7601,13 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D331" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="E331" t="s">
         <v>27</v>
@@ -7611,13 +7618,13 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D332" t="s">
-        <v>161</v>
+        <v>69</v>
       </c>
       <c r="E332" t="s">
         <v>27</v>
@@ -7628,13 +7635,13 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D333" t="s">
-        <v>228</v>
+        <v>105</v>
       </c>
       <c r="E333" t="s">
         <v>27</v>
@@ -7645,13 +7652,13 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D334" t="s">
-        <v>188</v>
+        <v>263</v>
       </c>
       <c r="E334" t="s">
         <v>27</v>
@@ -7662,13 +7669,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D335" t="s">
-        <v>183</v>
+        <v>440</v>
       </c>
       <c r="E335" t="s">
         <v>27</v>
@@ -7679,13 +7686,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D336" t="s">
-        <v>82</v>
+        <v>233</v>
       </c>
       <c r="E336" t="s">
         <v>27</v>
@@ -7696,13 +7703,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D337" t="s">
-        <v>82</v>
+        <v>263</v>
       </c>
       <c r="E337" t="s">
         <v>27</v>
@@ -7713,13 +7720,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D338" t="s">
-        <v>294</v>
+        <v>46</v>
       </c>
       <c r="E338" t="s">
         <v>27</v>
@@ -7730,13 +7737,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D339" t="s">
-        <v>36</v>
+        <v>364</v>
       </c>
       <c r="E339" t="s">
         <v>27</v>
@@ -7747,13 +7754,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D340" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="E340" t="s">
         <v>27</v>
@@ -7764,13 +7771,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D341" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="E341" t="s">
         <v>27</v>
@@ -7781,13 +7788,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D342" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="E342" t="s">
         <v>27</v>
@@ -7798,13 +7805,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D343" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="E343" t="s">
         <v>27</v>
@@ -7815,13 +7822,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D344" t="s">
-        <v>228</v>
+        <v>71</v>
       </c>
       <c r="E344" t="s">
         <v>27</v>
@@ -7832,13 +7839,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D345" t="s">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="E345" t="s">
         <v>27</v>
@@ -7849,13 +7856,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D346" t="s">
-        <v>52</v>
+        <v>127</v>
       </c>
       <c r="E346" t="s">
         <v>27</v>
@@ -7866,13 +7873,13 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D347" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="E347" t="s">
         <v>27</v>
@@ -7883,13 +7890,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D348" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="E348" t="s">
         <v>27</v>
@@ -7900,13 +7907,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D349" t="s">
-        <v>169</v>
+        <v>216</v>
       </c>
       <c r="E349" t="s">
         <v>27</v>
@@ -7917,13 +7924,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D350" t="s">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="E350" t="s">
         <v>27</v>
@@ -7934,13 +7941,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D351" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="E351" t="s">
         <v>27</v>
@@ -7951,13 +7958,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D352" t="s">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="E352" t="s">
         <v>27</v>
@@ -7968,13 +7975,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D353" t="s">
-        <v>48</v>
+        <v>179</v>
       </c>
       <c r="E353" t="s">
         <v>27</v>
@@ -7985,13 +7992,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D354" t="s">
-        <v>281</v>
+        <v>143</v>
       </c>
       <c r="E354" t="s">
         <v>27</v>
@@ -8002,13 +8009,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D355" t="s">
-        <v>250</v>
+        <v>131</v>
       </c>
       <c r="E355" t="s">
         <v>27</v>
@@ -8019,13 +8026,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D356" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="E356" t="s">
         <v>27</v>
@@ -8036,13 +8043,13 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D357" t="s">
-        <v>250</v>
+        <v>101</v>
       </c>
       <c r="E357" t="s">
         <v>27</v>
@@ -8053,13 +8060,13 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D358" t="s">
-        <v>261</v>
+        <v>183</v>
       </c>
       <c r="E358" t="s">
         <v>27</v>
@@ -8070,13 +8077,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D359" t="s">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="E359" t="s">
         <v>27</v>
@@ -8087,13 +8094,13 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D360" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E360" t="s">
         <v>27</v>
@@ -8104,13 +8111,13 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D361" t="s">
-        <v>330</v>
+        <v>93</v>
       </c>
       <c r="E361" t="s">
         <v>27</v>
@@ -8121,13 +8128,13 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D362" t="s">
-        <v>225</v>
+        <v>140</v>
       </c>
       <c r="E362" t="s">
         <v>27</v>
@@ -8138,13 +8145,13 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D363" t="s">
-        <v>195</v>
+        <v>118</v>
       </c>
       <c r="E363" t="s">
         <v>27</v>
@@ -8155,13 +8162,13 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D364" t="s">
-        <v>207</v>
+        <v>111</v>
       </c>
       <c r="E364" t="s">
         <v>27</v>
@@ -8172,13 +8179,13 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D365" t="s">
-        <v>46</v>
+        <v>233</v>
       </c>
       <c r="E365" t="s">
         <v>27</v>
@@ -8189,13 +8196,13 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D366" t="s">
-        <v>279</v>
+        <v>120</v>
       </c>
       <c r="E366" t="s">
         <v>27</v>
@@ -8206,13 +8213,13 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D367" t="s">
-        <v>250</v>
+        <v>84</v>
       </c>
       <c r="E367" t="s">
         <v>27</v>
@@ -8223,13 +8230,13 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D368" t="s">
-        <v>148</v>
+        <v>67</v>
       </c>
       <c r="E368" t="s">
         <v>27</v>
@@ -8240,13 +8247,13 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D369" t="s">
-        <v>193</v>
+        <v>75</v>
       </c>
       <c r="E369" t="s">
         <v>27</v>
@@ -8257,13 +8264,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D370" t="s">
-        <v>275</v>
+        <v>111</v>
       </c>
       <c r="E370" t="s">
         <v>27</v>
@@ -8274,13 +8281,13 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D371" t="s">
-        <v>52</v>
+        <v>331</v>
       </c>
       <c r="E371" t="s">
         <v>27</v>
@@ -8291,13 +8298,13 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D372" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="E372" t="s">
         <v>27</v>
@@ -8308,13 +8315,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D373" t="s">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="E373" t="s">
         <v>27</v>
@@ -8325,13 +8332,13 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D374" t="s">
-        <v>215</v>
+        <v>179</v>
       </c>
       <c r="E374" t="s">
         <v>27</v>
@@ -8342,13 +8349,13 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D375" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="E375" t="s">
         <v>27</v>
@@ -8359,13 +8366,13 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D376" t="s">
-        <v>261</v>
+        <v>73</v>
       </c>
       <c r="E376" t="s">
         <v>27</v>
@@ -8376,13 +8383,13 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D377" t="s">
-        <v>122</v>
+        <v>237</v>
       </c>
       <c r="E377" t="s">
         <v>27</v>
@@ -8393,13 +8400,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D378" t="s">
-        <v>222</v>
+        <v>88</v>
       </c>
       <c r="E378" t="s">
         <v>27</v>
@@ -8410,13 +8417,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C379" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D379" t="s">
-        <v>150</v>
+        <v>263</v>
       </c>
       <c r="E379" t="s">
         <v>27</v>
@@ -8427,13 +8434,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C380" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D380" t="s">
-        <v>261</v>
+        <v>176</v>
       </c>
       <c r="E380" t="s">
         <v>27</v>
@@ -8444,13 +8451,13 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C381" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D381" t="s">
-        <v>483</v>
+        <v>69</v>
       </c>
       <c r="E381" t="s">
         <v>27</v>
@@ -8461,13 +8468,13 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D382" t="s">
-        <v>101</v>
+        <v>440</v>
       </c>
       <c r="E382" t="s">
         <v>27</v>
@@ -8478,13 +8485,13 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D383" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="E383" t="s">
         <v>27</v>
@@ -8495,13 +8502,13 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C384" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D384" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="E384" t="s">
         <v>27</v>
@@ -8512,13 +8519,13 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D385" t="s">
-        <v>130</v>
+        <v>212</v>
       </c>
       <c r="E385" t="s">
         <v>27</v>
@@ -8529,13 +8536,13 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D386" t="s">
-        <v>489</v>
+        <v>216</v>
       </c>
       <c r="E386" t="s">
         <v>27</v>
@@ -8546,13 +8553,13 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D387" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="E387" t="s">
         <v>27</v>
@@ -8563,13 +8570,13 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D388" t="s">
-        <v>250</v>
+        <v>181</v>
       </c>
       <c r="E388" t="s">
         <v>27</v>
@@ -8580,13 +8587,13 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D389" t="s">
-        <v>207</v>
+        <v>118</v>
       </c>
       <c r="E389" t="s">
         <v>27</v>
@@ -8597,13 +8604,13 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D390" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E390" t="s">
         <v>27</v>
@@ -8614,13 +8621,13 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D391" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="E391" t="s">
         <v>27</v>
@@ -8631,13 +8638,13 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D392" t="s">
-        <v>112</v>
+        <v>205</v>
       </c>
       <c r="E392" t="s">
         <v>27</v>
@@ -8648,13 +8655,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D393" t="s">
-        <v>188</v>
+        <v>91</v>
       </c>
       <c r="E393" t="s">
         <v>27</v>
@@ -8665,13 +8672,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D394" t="s">
-        <v>319</v>
+        <v>97</v>
       </c>
       <c r="E394" t="s">
         <v>27</v>
@@ -8682,13 +8689,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D395" t="s">
-        <v>36</v>
+        <v>261</v>
       </c>
       <c r="E395" t="s">
         <v>27</v>
@@ -8699,13 +8706,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D396" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="E396" t="s">
         <v>27</v>
@@ -8716,13 +8723,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D397" t="s">
-        <v>91</v>
+        <v>295</v>
       </c>
       <c r="E397" t="s">
         <v>27</v>
@@ -8733,13 +8740,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D398" t="s">
-        <v>425</v>
+        <v>223</v>
       </c>
       <c r="E398" t="s">
         <v>27</v>
@@ -8750,13 +8757,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D399" t="s">
-        <v>299</v>
+        <v>109</v>
       </c>
       <c r="E399" t="s">
         <v>27</v>
@@ -8767,13 +8774,13 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D400" t="s">
-        <v>66</v>
+        <v>179</v>
       </c>
       <c r="E400" t="s">
         <v>27</v>
@@ -8784,13 +8791,13 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C401" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D401" t="s">
-        <v>174</v>
+        <v>50</v>
       </c>
       <c r="E401" t="s">
         <v>27</v>
@@ -8809,47 +8816,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B3" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B4" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B6">
         <v>400</v>
@@ -8857,7 +8864,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B7">
         <v>391</v>
@@ -8865,7 +8872,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B8">
         <v>9</v>
@@ -8873,7 +8880,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8881,10 +8888,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B10" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>

--- a/reports/selenium/Excel/Automation_Test_Report.xlsx
+++ b/reports/selenium/Excel/Automation_Test_Report.xlsx
@@ -35,1401 +35,1401 @@
     <t>FAILED</t>
   </si>
   <si>
-    <t>20.54</t>
+    <t>20.70</t>
   </si>
   <si>
     <t xml:space="preserve">Landing page did not load — Sign In button not found
-Wait timed out after 20007ms</t>
+Wait timed out after 20171ms</t>
   </si>
   <si>
     <t>should navigate to the login form</t>
   </si>
   <si>
-    <t>20.55</t>
+    <t>20.58</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20190ms</t>
+Wait timed out after 20146ms</t>
   </si>
   <si>
     <t>should login with valid credentials and reach the dashboard</t>
   </si>
   <si>
-    <t>20.73</t>
+    <t>20.82</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20013ms</t>
+Wait timed out after 20155ms</t>
   </si>
   <si>
     <t>should reject invalid credentials with an error message</t>
   </si>
   <si>
-    <t>20.53</t>
+    <t>20.52</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20165ms</t>
+Wait timed out after 20157ms</t>
   </si>
   <si>
     <t>should open the sign-up form from landing</t>
   </si>
   <si>
-    <t>20.93</t>
+    <t>20.49</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signup-btn"])
+Wait timed out after 20125ms</t>
+  </si>
+  <si>
+    <t>Security — should reject login for invalid credentials</t>
+  </si>
+  <si>
+    <t>21.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
 Wait timed out after 20202ms</t>
   </si>
   <si>
-    <t>Security — should reject login for invalid credentials</t>
-  </si>
-  <si>
-    <t>20.75</t>
+    <t>Security — should prevent access to protected routes/dashboard for unauthenticated users</t>
+  </si>
+  <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>4.00</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Security — should not execute XSS script payloads submitted in login fields</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20201ms</t>
-  </si>
-  <si>
-    <t>Security — should prevent access to protected routes/dashboard for unauthenticated users</t>
-  </si>
-  <si>
-    <t>PASSED</t>
-  </si>
-  <si>
-    <t>3.75</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Security — should not execute XSS script payloads submitted in login fields</t>
-  </si>
-  <si>
-    <t>20.88</t>
+Wait timed out after 20131ms</t>
+  </si>
+  <si>
+    <t>Security — should enforce session termination and clean storage upon logout</t>
+  </si>
+  <si>
+    <t>20.91</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20200ms</t>
-  </si>
-  <si>
-    <t>Security — should enforce session termination and clean storage upon logout</t>
-  </si>
-  <si>
-    <t>20.67</t>
+Wait timed out after 20151ms</t>
+  </si>
+  <si>
+    <t>Security — should confirm Firebase authentication rejects empty credentials</t>
+  </si>
+  <si>
+    <t>20.84</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20008ms</t>
-  </si>
-  <si>
-    <t>Security — should confirm Firebase authentication rejects empty credentials</t>
-  </si>
-  <si>
-    <t>20.85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waiting for element to be located By(css selector, *[id="landing-signin-btn"])
-Wait timed out after 20189ms</t>
+Wait timed out after 20159ms</t>
   </si>
   <si>
     <t>Security — should not expose sensitive API keys or secrets in page HTML source</t>
   </si>
   <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for compare-btn (Verify Point #11)</t>
+  </si>
+  <si>
+    <t>0.88</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated profile-settings (Verify Point #12)</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for ai-chat-input (Verify Point #13)</t>
+  </si>
+  <si>
+    <t>0.89</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on en-US (Verify Point #14)</t>
+  </si>
+  <si>
+    <t>0.49</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for hi-IN (Verify Point #15)</t>
+  </si>
+  <si>
+    <t>0.32</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for ta-IN (Verify Point #16)</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for header-nav (Verify Point #17)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field sidebar-menu (Verify Point #18)</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to footer-links (Verify Point #19)</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution login-form (Verify Point #20)</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element register-form (Verify Point #21)</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container dashboard-grid (Verify Point #22)</t>
+  </si>
+  <si>
+    <t>0.79</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter detail-page (Verify Point #23)</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale fees-filter (Verify Point #24)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource nirf-sort (Verify Point #25)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path course-filter (Verify Point #26)</t>
+  </si>
+  <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component state-filter (Verify Point #27)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for firebase-auth (Verify Point #28)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for firestore-read (Verify Point #29)</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for groq-api (Verify Point #30)</t>
+  </si>
+  <si>
+    <t>0.38</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for expo-router (Verify Point #31)</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated college-list (Verify Point #32)</t>
+  </si>
+  <si>
+    <t>0.67</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for saved-list (Verify Point #33)</t>
+  </si>
+  <si>
+    <t>0.54</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on comparison-list (Verify Point #34)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for chat-history (Verify Point #35)</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for avatar-upload (Verify Point #36)</t>
+  </si>
+  <si>
+    <t>0.80</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for theme-toggle (Verify Point #37)</t>
+  </si>
+  <si>
+    <t>0.60</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field notification-prefs (Verify Point #38)</t>
+  </si>
+  <si>
+    <t>0.84</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to session-token (Verify Point #39)</t>
+  </si>
+  <si>
+    <t>0.77</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution XSS-injection (Verify Point #40)</t>
+  </si>
+  <si>
+    <t>0.81</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element SQL-injection (Verify Point #41)</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container CSRF-token (Verify Point #42)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter CORS-origin (Verify Point #43)</t>
+  </si>
+  <si>
+    <t>0.40</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale CSP-header (Verify Point #44)</t>
+  </si>
+  <si>
+    <t>0.90</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource X-Frame-Options (Verify Point #45)</t>
+  </si>
+  <si>
+    <t>0.63</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path primary-font (Verify Point #46)</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component accent-color (Verify Point #47)</t>
+  </si>
+  <si>
+    <t>0.70</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for glassmorphic-transparency (Verify Point #48)</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for border-radius (Verify Point #49)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for bundle-size (Verify Point #50)</t>
+  </si>
+  <si>
+    <t>0.93</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for first-meaningful-paint (Verify Point #51)</t>
+  </si>
+  <si>
+    <t>0.97</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated time-to-interactive (Verify Point #52)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for dom-depth (Verify Point #53)</t>
+  </si>
+  <si>
+    <t>0.46</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on lost-item-card (Verify Point #54)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for users-ref (Verify Point #55)</t>
+  </si>
+  <si>
+    <t>0.82</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for items-ref (Verify Point #56)</t>
+  </si>
+  <si>
+    <t>0.47</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for de-DE (Verify Point #57)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field fr-FR (Verify Point #58)</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to ja-JP (Verify Point #59)</t>
+  </si>
+  <si>
+    <t>0.83</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution pt-BR (Verify Point #60)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element it-IT (Verify Point #61)</t>
+  </si>
+  <si>
+    <t>0.29</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container 1920x1080 (Verify Point #62)</t>
+  </si>
+  <si>
+    <t>0.45</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter 1440x900 (Verify Point #63)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale 1280x800 (Verify Point #64)</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource 1024x768 (Verify Point #65)</t>
+  </si>
+  <si>
+    <t>0.73</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path 768x1024 (Verify Point #66)</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component 375x812 (Verify Point #67)</t>
+  </si>
+  <si>
+    <t>0.87</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for sign-in-button (Verify Point #68)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for email-input (Verify Point #69)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for password-field (Verify Point #70)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for search-bar (Verify Point #71)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated college-card (Verify Point #72)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for compare-btn (Verify Point #73)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on profile-settings (Verify Point #74)</t>
+  </si>
+  <si>
+    <t>0.48</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for ai-chat-input (Verify Point #75)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for en-US (Verify Point #76)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for hi-IN (Verify Point #77)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field ta-IN (Verify Point #78)</t>
+  </si>
+  <si>
+    <t>0.76</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to header-nav (Verify Point #79)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution sidebar-menu (Verify Point #80)</t>
+  </si>
+  <si>
+    <t>0.65</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element footer-links (Verify Point #81)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container login-form (Verify Point #82)</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter register-form (Verify Point #83)</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale dashboard-grid (Verify Point #84)</t>
+  </si>
+  <si>
+    <t>0.96</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource detail-page (Verify Point #85)</t>
+  </si>
+  <si>
+    <t>0.59</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path fees-filter (Verify Point #86)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component nirf-sort (Verify Point #87)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for course-filter (Verify Point #88)</t>
+  </si>
+  <si>
+    <t>0.37</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for state-filter (Verify Point #89)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for firebase-auth (Verify Point #90)</t>
+  </si>
+  <si>
+    <t>0.28</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for firestore-read (Verify Point #91)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated groq-api (Verify Point #92)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for expo-router (Verify Point #93)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on college-list (Verify Point #94)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for saved-list (Verify Point #95)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for comparison-list (Verify Point #96)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for chat-history (Verify Point #97)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field avatar-upload (Verify Point #98)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to theme-toggle (Verify Point #99)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution notification-prefs (Verify Point #100)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element session-token (Verify Point #101)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container XSS-injection (Verify Point #102)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter SQL-injection (Verify Point #103)</t>
+  </si>
+  <si>
+    <t>0.30</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale CSRF-token (Verify Point #104)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource CORS-origin (Verify Point #105)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path CSP-header (Verify Point #106)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component X-Frame-Options (Verify Point #107)</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for primary-font (Verify Point #108)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for accent-color (Verify Point #109)</t>
+  </si>
+  <si>
+    <t>0.78</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for glassmorphic-transparency (Verify Point #110)</t>
+  </si>
+  <si>
+    <t>0.68</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for border-radius (Verify Point #111)</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated bundle-size (Verify Point #112)</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for first-meaningful-paint (Verify Point #113)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on time-to-interactive (Verify Point #114)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for dom-depth (Verify Point #115)</t>
+  </si>
+  <si>
+    <t>0.91</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for lost-item-card (Verify Point #116)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for users-ref (Verify Point #117)</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field items-ref (Verify Point #118)</t>
+  </si>
+  <si>
+    <t>0.71</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to de-DE (Verify Point #119)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution fr-FR (Verify Point #120)</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element ja-JP (Verify Point #121)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container pt-BR (Verify Point #122)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter it-IT (Verify Point #123)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #124)</t>
+  </si>
+  <si>
+    <t>0.53</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource 1440x900 (Verify Point #125)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #126)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component 1024x768 (Verify Point #127)</t>
+  </si>
+  <si>
+    <t>0.72</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #128)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for 375x812 (Verify Point #129)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for sign-in-button (Verify Point #130)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for email-input (Verify Point #131)</t>
+  </si>
+  <si>
+    <t>0.69</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated password-field (Verify Point #132)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for search-bar (Verify Point #133)</t>
+  </si>
+  <si>
+    <t>0.99</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on college-card (Verify Point #134)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for compare-btn (Verify Point #135)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for profile-settings (Verify Point #136)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for ai-chat-input (Verify Point #137)</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field en-US (Verify Point #138)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to hi-IN (Verify Point #139)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution ta-IN (Verify Point #140)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element header-nav (Verify Point #141)</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container sidebar-menu (Verify Point #142)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter footer-links (Verify Point #143)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale login-form (Verify Point #144)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource register-form (Verify Point #145)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path dashboard-grid (Verify Point #146)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component detail-page (Verify Point #147)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for fees-filter (Verify Point #148)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for nirf-sort (Verify Point #149)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for course-filter (Verify Point #150)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for state-filter (Verify Point #151)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated firebase-auth (Verify Point #152)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for firestore-read (Verify Point #153)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on groq-api (Verify Point #154)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for expo-router (Verify Point #155)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for college-list (Verify Point #156)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for saved-list (Verify Point #157)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field comparison-list (Verify Point #158)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to chat-history (Verify Point #159)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution avatar-upload (Verify Point #160)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element theme-toggle (Verify Point #161)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container notification-prefs (Verify Point #162)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter session-token (Verify Point #163)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale XSS-injection (Verify Point #164)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #165)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path CSRF-token (Verify Point #166)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component CORS-origin (Verify Point #167)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for CSP-header (Verify Point #168)</t>
+  </si>
+  <si>
+    <t>0.86</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for X-Frame-Options (Verify Point #169)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for primary-font (Verify Point #170)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for accent-color (Verify Point #171)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated glassmorphic-transparency (Verify Point #172)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for border-radius (Verify Point #173)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on bundle-size (Verify Point #174)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for first-meaningful-paint (Verify Point #175)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for time-to-interactive (Verify Point #176)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for dom-depth (Verify Point #177)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field lost-item-card (Verify Point #178)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to users-ref (Verify Point #179)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution items-ref (Verify Point #180)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element de-DE (Verify Point #181)</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container fr-FR (Verify Point #182)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter ja-JP (Verify Point #183)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale pt-BR (Verify Point #184)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource it-IT (Verify Point #185)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path 1920x1080 (Verify Point #186)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component 1440x900 (Verify Point #187)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for 1280x800 (Verify Point #188)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for 1024x768 (Verify Point #189)</t>
+  </si>
+  <si>
+    <t>0.55</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for 768x1024 (Verify Point #190)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for 375x812 (Verify Point #191)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated sign-in-button (Verify Point #192)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for email-input (Verify Point #193)</t>
+  </si>
+  <si>
+    <t>0.31</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on password-field (Verify Point #194)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for search-bar (Verify Point #195)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for college-card (Verify Point #196)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for compare-btn (Verify Point #197)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field profile-settings (Verify Point #198)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to ai-chat-input (Verify Point #199)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution en-US (Verify Point #200)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element hi-IN (Verify Point #201)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container ta-IN (Verify Point #202)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter header-nav (Verify Point #203)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale sidebar-menu (Verify Point #204)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource footer-links (Verify Point #205)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path login-form (Verify Point #206)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component register-form (Verify Point #207)</t>
+  </si>
+  <si>
+    <t>0.44</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for dashboard-grid (Verify Point #208)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for detail-page (Verify Point #209)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for fees-filter (Verify Point #210)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for nirf-sort (Verify Point #211)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated course-filter (Verify Point #212)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for state-filter (Verify Point #213)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on firebase-auth (Verify Point #214)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for firestore-read (Verify Point #215)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for groq-api (Verify Point #216)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for expo-router (Verify Point #217)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field college-list (Verify Point #218)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to saved-list (Verify Point #219)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution comparison-list (Verify Point #220)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element chat-history (Verify Point #221)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container avatar-upload (Verify Point #222)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter theme-toggle (Verify Point #223)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale notification-prefs (Verify Point #224)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource session-token (Verify Point #225)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path XSS-injection (Verify Point #226)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component SQL-injection (Verify Point #227)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for CSRF-token (Verify Point #228)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for CORS-origin (Verify Point #229)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for CSP-header (Verify Point #230)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for X-Frame-Options (Verify Point #231)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated primary-font (Verify Point #232)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Session]: Verify session cookie flags for accent-color (Verify Point #233)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on glassmorphic-transparency (Verify Point #234)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for border-radius (Verify Point #235)</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for bundle-size (Verify Point #236)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for first-meaningful-paint (Verify Point #237)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Profile]: Verify user profile update for field time-to-interactive (Verify Point #238)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to dom-depth (Verify Point #239)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution lost-item-card (Verify Point #240)</t>
+  </si>
+  <si>
     <t>0.74</t>
   </si>
   <si>
-    <t>Smart Admission — E2E [Search]: Verify search results filtering for compare-btn (Verify Point #11)</t>
-  </si>
-  <si>
-    <t>0.45</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Auth Guard]: Verify route protection for unauthenticated profile-settings (Verify Point #12)</t>
-  </si>
-  <si>
-    <t>0.68</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Session]: Verify session cookie flags for ai-chat-input (Verify Point #13)</t>
-  </si>
-  <si>
-    <t>0.70</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [XSS]: Verify XSS payload encoding on en-US (Verify Point #14)</t>
-  </si>
-  <si>
-    <t>0.38</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [AI Chat]: Verify AI chat response rendering for hi-IN (Verify Point #15)</t>
+    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element users-ref (Verify Point #241)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container items-ref (Verify Point #242)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter de-DE (Verify Point #243)</t>
   </si>
   <si>
     <t>0.61</t>
   </si>
   <si>
-    <t>Smart Admission — E2E [Comparison]: Verify college comparison table for ta-IN (Verify Point #16)</t>
-  </si>
-  <si>
-    <t>0.40</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Saved Items]: Verify saved colleges list persistence for header-nav (Verify Point #17)</t>
-  </si>
-  <si>
-    <t>0.83</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Profile]: Verify user profile update for field sidebar-menu (Verify Point #18)</t>
-  </si>
-  <si>
-    <t>0.56</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [CORS]: Verify CORS policy for request to footer-links (Verify Point #19)</t>
-  </si>
-  <si>
-    <t>0.84</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [UI]: Verify page responsiveness for resolution login-form (Verify Point #20)</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Accessibility]: Verify accessibility compliance for element register-form (Verify Point #21)</t>
-  </si>
-  <si>
-    <t>0.98</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [DOM]: Verify DOM integrity for container dashboard-grid (Verify Point #22)</t>
-  </si>
-  <si>
-    <t>0.53</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Validation]: Verify form field validation with parameter detail-page (Verify Point #23)</t>
-  </si>
-  <si>
-    <t>0.43</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale fees-filter (Verify Point #24)</t>
-  </si>
-  <si>
-    <t>0.27</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource nirf-sort (Verify Point #25)</t>
-  </si>
-  <si>
-    <t>0.90</t>
-  </si>
-  <si>
-    <t>Smart Admission — E2E [Database]: Verify database synchronization for path course-filter (Verify Point #26)</t>
+    <t>Smart Admission — E2E [Localization]: Verify UI translations and assets for locale fr-FR (Verify Point #244)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Security]: Verify HTTP security headers for resource ja-JP (Verify Point #245)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Database]: Verify database synchronization for path pt-BR (Verify Point #246)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Theme]: Verify theme consistency for component it-IT (Verify Point #247)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #248)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Dashboard]: Verify college card rendering for 1440x900 (Verify Point #249)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Details]: Verify college detail page fields for 1280x800 (Verify Point #250)</t>
+  </si>
+  <si>
+    <t>Smart Admission — E2E [Search]: Verify search results filtering for 1024x768 (Verify Point #251)</t>
+  </si>
+  <si>
+    <t>Smart Admissio